--- a/Översikt VETLANDA.xlsx
+++ b/Översikt VETLANDA.xlsx
@@ -601,7 +601,7 @@
         <v>45097</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>46178</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         <v>45371</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>44817</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>44890</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>45183</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>45558</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>45168</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>46107</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>45957</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>45520</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>45930</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>45754</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>45170</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>44612</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>44840</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>44908</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>46002</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>46100</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>45203</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>45819</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>46163</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>46188</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>44545</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>44564</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>45583</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>44819</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         <v>45763</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>45477</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3915,7 +3915,7 @@
         <v>45814</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>46045</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         <v>45048</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>45599</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>45646</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4450,7 +4450,7 @@
         <v>45131</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>44515</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>44470</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>44752</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>44643</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>45589</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         <v>44468</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         <v>45713</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>45673</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>45891</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         <v>44572</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>45965</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>45303</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5852,7 +5852,7 @@
         <v>45148</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>46166</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>45357</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6170,7 +6170,7 @@
         <v>45616</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>45035</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         <v>45400</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         <v>45211</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
         <v>45310</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>46279</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>45792</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
         <v>45835</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         <v>45840</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7138,7 +7138,7 @@
         <v>45713</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         <v>45860</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7354,7 +7354,7 @@
         <v>45106</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>45509</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7566,7 +7566,7 @@
         <v>45497</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7672,7 +7672,7 @@
         <v>45201</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>45539</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7884,7 +7884,7 @@
         <v>46051</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7994,7 +7994,7 @@
         <v>44834</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>44462</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
         <v>44721</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         <v>44747</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>44592</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8519,7 +8519,7 @@
         <v>44740</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         <v>45597</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8734,7 +8734,7 @@
         <v>44830</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>45596</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8944,7 +8944,7 @@
         <v>45555</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9049,7 +9049,7 @@
         <v>45021</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9154,7 +9154,7 @@
         <v>44781</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9259,7 +9259,7 @@
         <v>45586</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9364,7 +9364,7 @@
         <v>44748</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>44824</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>45240</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         <v>44728</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
         <v>45342</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9893,7 +9893,7 @@
         <v>45586</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9998,7 +9998,7 @@
         <v>45835</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10103,7 +10103,7 @@
         <v>45672</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         <v>45239</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10322,7 +10322,7 @@
         <v>45880</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>45904</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10532,7 +10532,7 @@
         <v>45645</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10637,7 +10637,7 @@
         <v>46141</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         <v>44998</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10851,7 +10851,7 @@
         <v>44880</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         <v>45419</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>45085</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11166,7 +11166,7 @@
         <v>45408</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11271,7 +11271,7 @@
         <v>44819</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>45119</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11481,7 +11481,7 @@
         <v>45009</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11586,7 +11586,7 @@
         <v>46069</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11691,7 +11691,7 @@
         <v>46071</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11796,7 +11796,7 @@
         <v>45261</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11901,7 +11901,7 @@
         <v>45378</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12006,7 +12006,7 @@
         <v>46188</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12111,7 +12111,7 @@
         <v>45104</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>44816</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12325,7 +12325,7 @@
         <v>45532</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12430,7 +12430,7 @@
         <v>45775</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12535,7 +12535,7 @@
         <v>44833</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12640,7 +12640,7 @@
         <v>45930</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12754,7 +12754,7 @@
         <v>46248</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12859,7 +12859,7 @@
         <v>45337</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12964,7 +12964,7 @@
         <v>45565</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13069,7 +13069,7 @@
         <v>44916</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13174,7 +13174,7 @@
         <v>45352</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13279,7 +13279,7 @@
         <v>45643</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         <v>45791</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13489,7 +13489,7 @@
         <v>45736</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13598,7 +13598,7 @@
         <v>45820</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13708,7 +13708,7 @@
         <v>45839</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13813,7 +13813,7 @@
         <v>45604</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13918,7 +13918,7 @@
         <v>45497</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14023,7 +14023,7 @@
         <v>45614</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14128,7 +14128,7 @@
         <v>45742</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>44490</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14310,7 +14310,7 @@
         <v>44858</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14383,7 +14383,7 @@
         <v>44781</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14456,7 +14456,7 @@
         <v>44838</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14529,7 +14529,7 @@
         <v>44732</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14602,7 +14602,7 @@
         <v>44781</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14675,7 +14675,7 @@
         <v>44515</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14748,7 +14748,7 @@
         <v>44508</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14821,7 +14821,7 @@
         <v>44504</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>44496</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14967,7 +14967,7 @@
         <v>44579</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15040,7 +15040,7 @@
         <v>44601</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15113,7 +15113,7 @@
         <v>44889</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15186,7 +15186,7 @@
         <v>44544</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15259,7 +15259,7 @@
         <v>44510</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15332,7 +15332,7 @@
         <v>44468</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15405,7 +15405,7 @@
         <v>44517</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15478,7 +15478,7 @@
         <v>44764</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>44510</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15624,7 +15624,7 @@
         <v>44503</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15697,7 +15697,7 @@
         <v>44819</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15770,7 +15770,7 @@
         <v>44459</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15843,7 +15843,7 @@
         <v>44592</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15916,7 +15916,7 @@
         <v>44750</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         <v>44825</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16062,7 +16062,7 @@
         <v>44460</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16135,7 +16135,7 @@
         <v>44488</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16208,7 +16208,7 @@
         <v>44602</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16281,7 +16281,7 @@
         <v>44638</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>44510</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16427,7 +16427,7 @@
         <v>44721</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16500,7 +16500,7 @@
         <v>44785</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16573,7 +16573,7 @@
         <v>44592</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16646,7 +16646,7 @@
         <v>44587</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16719,7 +16719,7 @@
         <v>44782</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16792,7 +16792,7 @@
         <v>44815</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16865,7 +16865,7 @@
         <v>44504</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16938,7 +16938,7 @@
         <v>44580</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17011,7 +17011,7 @@
         <v>44691</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17084,7 +17084,7 @@
         <v>44880</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17157,7 +17157,7 @@
         <v>44460</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17230,7 +17230,7 @@
         <v>44462</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17303,7 +17303,7 @@
         <v>44545</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17376,7 +17376,7 @@
         <v>44624</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17449,7 +17449,7 @@
         <v>44750</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17522,7 +17522,7 @@
         <v>44477</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17595,7 +17595,7 @@
         <v>44595</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17668,7 +17668,7 @@
         <v>44608</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17741,7 +17741,7 @@
         <v>44460</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17814,7 +17814,7 @@
         <v>44820</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17887,7 +17887,7 @@
         <v>44816</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17960,7 +17960,7 @@
         <v>44461</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18033,7 +18033,7 @@
         <v>44645</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18106,7 +18106,7 @@
         <v>44819</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18179,7 +18179,7 @@
         <v>44656</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18252,7 +18252,7 @@
         <v>44784</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18325,7 +18325,7 @@
         <v>44585</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18403,7 +18403,7 @@
         <v>44585</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18481,7 +18481,7 @@
         <v>44585</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18559,7 +18559,7 @@
         <v>44834</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18632,7 +18632,7 @@
         <v>44740</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18710,7 +18710,7 @@
         <v>44750</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18783,7 +18783,7 @@
         <v>44587</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18856,7 +18856,7 @@
         <v>44743</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18929,7 +18929,7 @@
         <v>44474</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19002,7 +19002,7 @@
         <v>44600</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19075,7 +19075,7 @@
         <v>44859</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19148,7 +19148,7 @@
         <v>44593</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19221,7 +19221,7 @@
         <v>44743</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19294,7 +19294,7 @@
         <v>44778</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19367,7 +19367,7 @@
         <v>44504</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19440,7 +19440,7 @@
         <v>44834</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19513,7 +19513,7 @@
         <v>44477</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19586,7 +19586,7 @@
         <v>44482</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19659,7 +19659,7 @@
         <v>44509</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>44517</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19805,7 +19805,7 @@
         <v>44572</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19878,7 +19878,7 @@
         <v>44721</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19951,7 +19951,7 @@
         <v>44592</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20024,7 +20024,7 @@
         <v>44841</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20097,7 +20097,7 @@
         <v>44888</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20170,7 +20170,7 @@
         <v>44587</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20243,7 +20243,7 @@
         <v>44655</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>44461</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20389,7 +20389,7 @@
         <v>44459</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>44502</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20535,7 +20535,7 @@
         <v>44515</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20613,7 +20613,7 @@
         <v>44592</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20686,7 +20686,7 @@
         <v>44462</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20759,7 +20759,7 @@
         <v>44564</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20832,7 +20832,7 @@
         <v>44781</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20905,7 +20905,7 @@
         <v>44531</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20978,7 +20978,7 @@
         <v>44636</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21051,7 +21051,7 @@
         <v>44834</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21124,7 +21124,7 @@
         <v>44733</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21197,7 +21197,7 @@
         <v>44683</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21270,7 +21270,7 @@
         <v>44602</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21343,7 +21343,7 @@
         <v>44463</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21416,7 +21416,7 @@
         <v>44792</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21489,7 +21489,7 @@
         <v>44657</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21562,7 +21562,7 @@
         <v>44827</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21635,7 +21635,7 @@
         <v>45561</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21708,7 +21708,7 @@
         <v>45251</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21781,7 +21781,7 @@
         <v>44967</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21854,7 +21854,7 @@
         <v>44967</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21927,7 +21927,7 @@
         <v>44792</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22000,7 +22000,7 @@
         <v>44592</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22073,7 +22073,7 @@
         <v>45265</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22146,7 +22146,7 @@
         <v>45267</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22219,7 +22219,7 @@
         <v>44880</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22292,7 +22292,7 @@
         <v>45569</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22370,7 +22370,7 @@
         <v>45580</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22443,7 +22443,7 @@
         <v>45674</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22516,7 +22516,7 @@
         <v>44903</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22589,7 +22589,7 @@
         <v>44998</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22662,7 +22662,7 @@
         <v>45663</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22735,7 +22735,7 @@
         <v>44902</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22808,7 +22808,7 @@
         <v>45175</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22881,7 +22881,7 @@
         <v>45205</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22954,7 +22954,7 @@
         <v>45771</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23032,7 +23032,7 @@
         <v>45771</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23110,7 +23110,7 @@
         <v>45057</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23183,7 +23183,7 @@
         <v>45278</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23256,7 +23256,7 @@
         <v>45259</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23329,7 +23329,7 @@
         <v>44936</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23402,7 +23402,7 @@
         <v>44488</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23475,7 +23475,7 @@
         <v>44582</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23548,7 +23548,7 @@
         <v>45264</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23621,7 +23621,7 @@
         <v>44831</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23694,7 +23694,7 @@
         <v>45091</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23767,7 +23767,7 @@
         <v>45188</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23840,7 +23840,7 @@
         <v>45307</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23913,7 +23913,7 @@
         <v>44530</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23986,7 +23986,7 @@
         <v>45350</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24059,7 +24059,7 @@
         <v>45071</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24132,7 +24132,7 @@
         <v>44851</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24205,7 +24205,7 @@
         <v>45135</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24278,7 +24278,7 @@
         <v>45229</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24351,7 +24351,7 @@
         <v>45055</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24424,7 +24424,7 @@
         <v>44600</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24497,7 +24497,7 @@
         <v>44477</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24570,7 +24570,7 @@
         <v>45351</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24643,7 +24643,7 @@
         <v>45602</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24716,7 +24716,7 @@
         <v>45575</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24789,7 +24789,7 @@
         <v>44747</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24862,7 +24862,7 @@
         <v>45031</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>44710</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25008,7 +25008,7 @@
         <v>44986</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25081,7 +25081,7 @@
         <v>45384</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25154,7 +25154,7 @@
         <v>45434</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25227,7 +25227,7 @@
         <v>45439</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25300,7 +25300,7 @@
         <v>45104</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25373,7 +25373,7 @@
         <v>45097</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25446,7 +25446,7 @@
         <v>45097</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25519,7 +25519,7 @@
         <v>45335</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25592,7 +25592,7 @@
         <v>45645</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25665,7 +25665,7 @@
         <v>45300</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>45709</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25811,7 +25811,7 @@
         <v>45099</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25884,7 +25884,7 @@
         <v>45309</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25957,7 +25957,7 @@
         <v>45309</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26030,7 +26030,7 @@
         <v>45406</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26103,7 +26103,7 @@
         <v>45645</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26176,7 +26176,7 @@
         <v>45470</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26249,7 +26249,7 @@
         <v>45097</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26322,7 +26322,7 @@
         <v>44762</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26395,7 +26395,7 @@
         <v>45272</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26468,7 +26468,7 @@
         <v>45363</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26546,7 +26546,7 @@
         <v>44949</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26619,7 +26619,7 @@
         <v>45309</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26692,7 +26692,7 @@
         <v>44487</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26765,7 +26765,7 @@
         <v>45118</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26838,7 +26838,7 @@
         <v>45113</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26911,7 +26911,7 @@
         <v>45336</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26984,7 +26984,7 @@
         <v>45161</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27057,7 +27057,7 @@
         <v>45162</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27130,7 +27130,7 @@
         <v>44916</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27203,7 +27203,7 @@
         <v>44916</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27276,7 +27276,7 @@
         <v>45701</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27354,7 +27354,7 @@
         <v>45414</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27432,7 +27432,7 @@
         <v>45082</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27505,7 +27505,7 @@
         <v>45580</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27578,7 +27578,7 @@
         <v>45461</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27651,7 +27651,7 @@
         <v>45226</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27724,7 +27724,7 @@
         <v>45163</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27797,7 +27797,7 @@
         <v>45188</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27870,7 +27870,7 @@
         <v>45188</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27943,7 +27943,7 @@
         <v>44655</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28016,7 +28016,7 @@
         <v>45191</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28089,7 +28089,7 @@
         <v>45754</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28167,7 +28167,7 @@
         <v>45754</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28245,7 +28245,7 @@
         <v>45351</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28318,7 +28318,7 @@
         <v>45628</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28391,7 +28391,7 @@
         <v>44972</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28464,7 +28464,7 @@
         <v>44952</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28537,7 +28537,7 @@
         <v>45097</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         <v>45209</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28683,7 +28683,7 @@
         <v>44888</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28756,7 +28756,7 @@
         <v>44916</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28829,7 +28829,7 @@
         <v>44770</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28902,7 +28902,7 @@
         <v>45572</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28975,7 +28975,7 @@
         <v>45580</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29048,7 +29048,7 @@
         <v>45190</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29121,7 +29121,7 @@
         <v>45362</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29194,7 +29194,7 @@
         <v>45625</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29267,7 +29267,7 @@
         <v>44977</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29340,7 +29340,7 @@
         <v>45104</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29413,7 +29413,7 @@
         <v>45645</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29486,7 +29486,7 @@
         <v>45645</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29564,7 +29564,7 @@
         <v>45754</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>45545</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29715,7 +29715,7 @@
         <v>45135</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29788,7 +29788,7 @@
         <v>45135</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29861,7 +29861,7 @@
         <v>45135</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29934,7 +29934,7 @@
         <v>44641</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30007,7 +30007,7 @@
         <v>45117</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30080,7 +30080,7 @@
         <v>44482</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30153,7 +30153,7 @@
         <v>44888</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30226,7 +30226,7 @@
         <v>45099</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30299,7 +30299,7 @@
         <v>45610</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30372,7 +30372,7 @@
         <v>45042</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30445,7 +30445,7 @@
         <v>45742</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30518,7 +30518,7 @@
         <v>45329</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30591,7 +30591,7 @@
         <v>45329</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30664,7 +30664,7 @@
         <v>44984</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30737,7 +30737,7 @@
         <v>44592</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30810,7 +30810,7 @@
         <v>45448</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30883,7 +30883,7 @@
         <v>45441</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30956,7 +30956,7 @@
         <v>45228</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31029,7 +31029,7 @@
         <v>44693</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31102,7 +31102,7 @@
         <v>45274</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31175,7 +31175,7 @@
         <v>45330</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31248,7 +31248,7 @@
         <v>45363</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31326,7 +31326,7 @@
         <v>44916</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31399,7 +31399,7 @@
         <v>45202</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31472,7 +31472,7 @@
         <v>45702</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31545,7 +31545,7 @@
         <v>45595</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31618,7 +31618,7 @@
         <v>45376</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31691,7 +31691,7 @@
         <v>44531</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31764,7 +31764,7 @@
         <v>45166</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31837,7 +31837,7 @@
         <v>45365</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31910,7 +31910,7 @@
         <v>45414</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31988,7 +31988,7 @@
         <v>45251</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32061,7 +32061,7 @@
         <v>44515</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32139,7 +32139,7 @@
         <v>44984</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32212,7 +32212,7 @@
         <v>45107</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32285,7 +32285,7 @@
         <v>45232</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32358,7 +32358,7 @@
         <v>45048</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32431,7 +32431,7 @@
         <v>45319</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32504,7 +32504,7 @@
         <v>45462</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32577,7 +32577,7 @@
         <v>45006</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32650,7 +32650,7 @@
         <v>44984</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32723,7 +32723,7 @@
         <v>44984</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32796,7 +32796,7 @@
         <v>45357</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32869,7 +32869,7 @@
         <v>45581</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32947,7 +32947,7 @@
         <v>45069</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33020,7 +33020,7 @@
         <v>44945</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33093,7 +33093,7 @@
         <v>45015</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33166,7 +33166,7 @@
         <v>45310</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33239,7 +33239,7 @@
         <v>45484</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33312,7 +33312,7 @@
         <v>45351</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33385,7 +33385,7 @@
         <v>45170</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33458,7 +33458,7 @@
         <v>45107</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33531,7 +33531,7 @@
         <v>45684</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33609,7 +33609,7 @@
         <v>45330</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33682,7 +33682,7 @@
         <v>44946</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33755,7 +33755,7 @@
         <v>45099</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33828,7 +33828,7 @@
         <v>45352</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33901,7 +33901,7 @@
         <v>44460</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33974,7 +33974,7 @@
         <v>44837</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34047,7 +34047,7 @@
         <v>45351</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34120,7 +34120,7 @@
         <v>44484</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34193,7 +34193,7 @@
         <v>45201</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34266,7 +34266,7 @@
         <v>45097</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34339,7 +34339,7 @@
         <v>45748</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34417,7 +34417,7 @@
         <v>45748</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34495,7 +34495,7 @@
         <v>45883</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34568,7 +34568,7 @@
         <v>45884</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34641,7 +34641,7 @@
         <v>44965</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34714,7 +34714,7 @@
         <v>45902</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34787,7 +34787,7 @@
         <v>45884</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34860,7 +34860,7 @@
         <v>46112</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34938,7 +34938,7 @@
         <v>45965</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35011,7 +35011,7 @@
         <v>44970</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35084,7 +35084,7 @@
         <v>45133</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35157,7 +35157,7 @@
         <v>45525</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35230,7 +35230,7 @@
         <v>45357</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35303,7 +35303,7 @@
         <v>45785</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35376,7 +35376,7 @@
         <v>45912</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35449,7 +35449,7 @@
         <v>45231</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35522,7 +35522,7 @@
         <v>45840</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35595,7 +35595,7 @@
         <v>45866</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35668,7 +35668,7 @@
         <v>44462</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35741,7 +35741,7 @@
         <v>44545</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35814,7 +35814,7 @@
         <v>45925</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35887,7 +35887,7 @@
         <v>45681</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35960,7 +35960,7 @@
         <v>45152</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36033,7 +36033,7 @@
         <v>45971</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36106,7 +36106,7 @@
         <v>44503</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36179,7 +36179,7 @@
         <v>45230</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36257,7 +36257,7 @@
         <v>45888</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36330,7 +36330,7 @@
         <v>45888</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36403,7 +36403,7 @@
         <v>44480</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36476,7 +36476,7 @@
         <v>45541</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36549,7 +36549,7 @@
         <v>45677</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36622,7 +36622,7 @@
         <v>44741</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36695,7 +36695,7 @@
         <v>45272</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36768,7 +36768,7 @@
         <v>45084</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36841,7 +36841,7 @@
         <v>45889</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36914,7 +36914,7 @@
         <v>45786</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36987,7 +36987,7 @@
         <v>46006</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37060,7 +37060,7 @@
         <v>45763</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37133,7 +37133,7 @@
         <v>45888</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37206,7 +37206,7 @@
         <v>45742</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37279,7 +37279,7 @@
         <v>45889</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37352,7 +37352,7 @@
         <v>45888</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37425,7 +37425,7 @@
         <v>45888</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37498,7 +37498,7 @@
         <v>45888</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37571,7 +37571,7 @@
         <v>45826</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37644,7 +37644,7 @@
         <v>44600</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37717,7 +37717,7 @@
         <v>45889</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37790,7 +37790,7 @@
         <v>45742</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37863,7 +37863,7 @@
         <v>45331</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37936,7 +37936,7 @@
         <v>45331</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38009,7 +38009,7 @@
         <v>45222</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38082,7 +38082,7 @@
         <v>45770</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38155,7 +38155,7 @@
         <v>44970</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38228,7 +38228,7 @@
         <v>45671</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38301,7 +38301,7 @@
         <v>45435</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38374,7 +38374,7 @@
         <v>45693</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38447,7 +38447,7 @@
         <v>45230</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38525,7 +38525,7 @@
         <v>45889</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38598,7 +38598,7 @@
         <v>45204</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38671,7 +38671,7 @@
         <v>45455</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38744,7 +38744,7 @@
         <v>45561</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38817,7 +38817,7 @@
         <v>45839</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38890,7 +38890,7 @@
         <v>45785</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38963,7 +38963,7 @@
         <v>45282</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39036,7 +39036,7 @@
         <v>45245</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39109,7 +39109,7 @@
         <v>45623</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39182,7 +39182,7 @@
         <v>45631</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39255,7 +39255,7 @@
         <v>45247</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39328,7 +39328,7 @@
         <v>45259</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39401,7 +39401,7 @@
         <v>45841</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39474,7 +39474,7 @@
         <v>46136</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39547,7 +39547,7 @@
         <v>45608</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39620,7 +39620,7 @@
         <v>45370</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39693,7 +39693,7 @@
         <v>45873</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39766,7 +39766,7 @@
         <v>45322</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39839,7 +39839,7 @@
         <v>45341</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39912,7 +39912,7 @@
         <v>45898</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39985,7 +39985,7 @@
         <v>45035</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40058,7 +40058,7 @@
         <v>45971</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40131,7 +40131,7 @@
         <v>45819</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40204,7 +40204,7 @@
         <v>45610</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40277,7 +40277,7 @@
         <v>45645</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40355,7 +40355,7 @@
         <v>45645</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40433,7 +40433,7 @@
         <v>45737</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40506,7 +40506,7 @@
         <v>46122</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40579,7 +40579,7 @@
         <v>45587</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40652,7 +40652,7 @@
         <v>45839</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40725,7 +40725,7 @@
         <v>45076</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40798,7 +40798,7 @@
         <v>45902</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40871,7 +40871,7 @@
         <v>45006</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40944,7 +40944,7 @@
         <v>45153</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41017,7 +41017,7 @@
         <v>45755</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41090,7 +41090,7 @@
         <v>45670</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41163,7 +41163,7 @@
         <v>44580</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41236,7 +41236,7 @@
         <v>45825</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41309,7 +41309,7 @@
         <v>45348</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41382,7 +41382,7 @@
         <v>45839</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41455,7 +41455,7 @@
         <v>44538</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41528,7 +41528,7 @@
         <v>45089</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41601,7 +41601,7 @@
         <v>44785</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41674,7 +41674,7 @@
         <v>46052</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41747,7 +41747,7 @@
         <v>45883</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41820,7 +41820,7 @@
         <v>45691</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41898,7 +41898,7 @@
         <v>44459</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41971,7 +41971,7 @@
         <v>45615</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42044,7 +42044,7 @@
         <v>45538</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42117,7 +42117,7 @@
         <v>45298</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42190,7 +42190,7 @@
         <v>45911</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42263,7 +42263,7 @@
         <v>45911</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42336,7 +42336,7 @@
         <v>45372</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42409,7 +42409,7 @@
         <v>45076</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42482,7 +42482,7 @@
         <v>45827</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42555,7 +42555,7 @@
         <v>44473</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42628,7 +42628,7 @@
         <v>45170</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42701,7 +42701,7 @@
         <v>45401</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42774,7 +42774,7 @@
         <v>44607</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42847,7 +42847,7 @@
         <v>44837</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42920,7 +42920,7 @@
         <v>44511</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42993,7 +42993,7 @@
         <v>45089</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43066,7 +43066,7 @@
         <v>45443</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43139,7 +43139,7 @@
         <v>45240</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43212,7 +43212,7 @@
         <v>45922</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43285,7 +43285,7 @@
         <v>45168</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43358,7 +43358,7 @@
         <v>45321</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43431,7 +43431,7 @@
         <v>44470</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43504,7 +43504,7 @@
         <v>45163</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43577,7 +43577,7 @@
         <v>45925</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43650,7 +43650,7 @@
         <v>44510</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43723,7 +43723,7 @@
         <v>45925</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43796,7 +43796,7 @@
         <v>45589</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43869,7 +43869,7 @@
         <v>45211</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43942,7 +43942,7 @@
         <v>45414</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44015,7 +44015,7 @@
         <v>44894</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44088,7 +44088,7 @@
         <v>45519</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44161,7 +44161,7 @@
         <v>45931</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44234,7 +44234,7 @@
         <v>45314</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44307,7 +44307,7 @@
         <v>45433</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44380,7 +44380,7 @@
         <v>45097</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44453,7 +44453,7 @@
         <v>45448</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44526,7 +44526,7 @@
         <v>45645</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44604,7 +44604,7 @@
         <v>45645</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44682,7 +44682,7 @@
         <v>45644</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44755,7 +44755,7 @@
         <v>45936</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44828,7 +44828,7 @@
         <v>45936</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44901,7 +44901,7 @@
         <v>45649</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44979,7 +44979,7 @@
         <v>45114</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45052,7 +45052,7 @@
         <v>44858</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45125,7 +45125,7 @@
         <v>45545</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45198,7 +45198,7 @@
         <v>45250</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45271,7 +45271,7 @@
         <v>45224</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45349,7 +45349,7 @@
         <v>45645</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45427,7 +45427,7 @@
         <v>45944</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45500,7 +45500,7 @@
         <v>45763</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45573,7 +45573,7 @@
         <v>45672</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45646,7 +45646,7 @@
         <v>45946</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45719,7 +45719,7 @@
         <v>45264</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45792,7 +45792,7 @@
         <v>45525</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45865,7 +45865,7 @@
         <v>44965</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45938,7 +45938,7 @@
         <v>44926</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46011,7 +46011,7 @@
         <v>44926</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46084,7 +46084,7 @@
         <v>45401</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46157,7 +46157,7 @@
         <v>46153</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46230,7 +46230,7 @@
         <v>45950</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46303,7 +46303,7 @@
         <v>45392</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46376,7 +46376,7 @@
         <v>45953</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46449,7 +46449,7 @@
         <v>45394</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46522,7 +46522,7 @@
         <v>45953</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46595,7 +46595,7 @@
         <v>44602</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46668,7 +46668,7 @@
         <v>45007</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46741,7 +46741,7 @@
         <v>46153</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46814,7 +46814,7 @@
         <v>45568</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46892,7 +46892,7 @@
         <v>45297</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46965,7 +46965,7 @@
         <v>45236</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47038,7 +47038,7 @@
         <v>45625</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47111,7 +47111,7 @@
         <v>45105</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47184,7 +47184,7 @@
         <v>46153</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47257,7 +47257,7 @@
         <v>44859</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47330,7 +47330,7 @@
         <v>46153</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47403,7 +47403,7 @@
         <v>45674</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47476,7 +47476,7 @@
         <v>46153</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47549,7 +47549,7 @@
         <v>46154</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47627,7 +47627,7 @@
         <v>44481</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47700,7 +47700,7 @@
         <v>45866</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47773,7 +47773,7 @@
         <v>45639</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47846,7 +47846,7 @@
         <v>44655</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47919,7 +47919,7 @@
         <v>44970</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47992,7 +47992,7 @@
         <v>45329</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48065,7 +48065,7 @@
         <v>44847</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48138,7 +48138,7 @@
         <v>45180</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48211,7 +48211,7 @@
         <v>45173</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48284,7 +48284,7 @@
         <v>45173</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48357,7 +48357,7 @@
         <v>45345</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48430,7 +48430,7 @@
         <v>45526</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48503,7 +48503,7 @@
         <v>45170</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48576,7 +48576,7 @@
         <v>45170</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48649,7 +48649,7 @@
         <v>45974</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48722,7 +48722,7 @@
         <v>45975</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48795,7 +48795,7 @@
         <v>45303</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48868,7 +48868,7 @@
         <v>45104</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48941,7 +48941,7 @@
         <v>45981</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49019,7 +49019,7 @@
         <v>45981</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49092,7 +49092,7 @@
         <v>46126</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49165,7 +49165,7 @@
         <v>45981</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49238,7 +49238,7 @@
         <v>45982</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49311,7 +49311,7 @@
         <v>45981</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49384,7 +49384,7 @@
         <v>45113</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49457,7 +49457,7 @@
         <v>45446</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49530,7 +49530,7 @@
         <v>45438</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49603,7 +49603,7 @@
         <v>45400</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49681,7 +49681,7 @@
         <v>46160</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49754,7 +49754,7 @@
         <v>45182</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49832,7 +49832,7 @@
         <v>45182</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49905,7 +49905,7 @@
         <v>46161</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49978,7 +49978,7 @@
         <v>46160</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50051,7 +50051,7 @@
         <v>44607</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50124,7 +50124,7 @@
         <v>45761</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50197,7 +50197,7 @@
         <v>45992</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50270,7 +50270,7 @@
         <v>45992</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50343,7 +50343,7 @@
         <v>45669</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50416,7 +50416,7 @@
         <v>45992</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50489,7 +50489,7 @@
         <v>46160</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50562,7 +50562,7 @@
         <v>45992</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50635,7 +50635,7 @@
         <v>46064</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50708,7 +50708,7 @@
         <v>45930</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50781,7 +50781,7 @@
         <v>45315</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50854,7 +50854,7 @@
         <v>45462</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50927,7 +50927,7 @@
         <v>45449</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51000,7 +51000,7 @@
         <v>44463</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51073,7 +51073,7 @@
         <v>45327</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51146,7 +51146,7 @@
         <v>45164</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51219,7 +51219,7 @@
         <v>46160</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51292,7 +51292,7 @@
         <v>45330</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51365,7 +51365,7 @@
         <v>44995</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51438,7 +51438,7 @@
         <v>46163</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51511,7 +51511,7 @@
         <v>45692</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51584,7 +51584,7 @@
         <v>45106</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51657,7 +51657,7 @@
         <v>45574</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51735,7 +51735,7 @@
         <v>45616</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51808,7 +51808,7 @@
         <v>46161</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51881,7 +51881,7 @@
         <v>45510</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51954,7 +51954,7 @@
         <v>45219</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52032,7 +52032,7 @@
         <v>45274</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52105,7 +52105,7 @@
         <v>45999</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52178,7 +52178,7 @@
         <v>45999</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52251,7 +52251,7 @@
         <v>45250</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52324,7 +52324,7 @@
         <v>44587</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52397,7 +52397,7 @@
         <v>44783</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52470,7 +52470,7 @@
         <v>44830</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52543,7 +52543,7 @@
         <v>45544</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52616,7 +52616,7 @@
         <v>45133</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52689,7 +52689,7 @@
         <v>45408</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52762,7 +52762,7 @@
         <v>44834</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52835,7 +52835,7 @@
         <v>46001</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52908,7 +52908,7 @@
         <v>45366</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52981,7 +52981,7 @@
         <v>44815</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53054,7 +53054,7 @@
         <v>45069</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53127,7 +53127,7 @@
         <v>45440</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53200,7 +53200,7 @@
         <v>45701</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53278,7 +53278,7 @@
         <v>45302</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53351,7 +53351,7 @@
         <v>46003</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53424,7 +53424,7 @@
         <v>45930</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53502,7 +53502,7 @@
         <v>45615</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53575,7 +53575,7 @@
         <v>45113</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53648,7 +53648,7 @@
         <v>44683</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53721,7 +53721,7 @@
         <v>46009</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53794,7 +53794,7 @@
         <v>46007</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53867,7 +53867,7 @@
         <v>46007</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53940,7 +53940,7 @@
         <v>46009</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54013,7 +54013,7 @@
         <v>45546</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54086,7 +54086,7 @@
         <v>45999</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54159,7 +54159,7 @@
         <v>44839</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54232,7 +54232,7 @@
         <v>46009</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54305,7 +54305,7 @@
         <v>46009</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54378,7 +54378,7 @@
         <v>44970</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54451,7 +54451,7 @@
         <v>45222</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54524,7 +54524,7 @@
         <v>46010</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54597,7 +54597,7 @@
         <v>45183</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54670,7 +54670,7 @@
         <v>44965</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54743,7 +54743,7 @@
         <v>46010</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54816,7 +54816,7 @@
         <v>45000</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54889,7 +54889,7 @@
         <v>45183</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54962,7 +54962,7 @@
         <v>45706</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55035,7 +55035,7 @@
         <v>45827</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55108,7 +55108,7 @@
         <v>44839</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55181,7 +55181,7 @@
         <v>44753</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55254,7 +55254,7 @@
         <v>45135</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55327,7 +55327,7 @@
         <v>44802</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55405,7 +55405,7 @@
         <v>46003</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55478,7 +55478,7 @@
         <v>45446</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55551,7 +55551,7 @@
         <v>46029</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55624,7 +55624,7 @@
         <v>44929</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55697,7 +55697,7 @@
         <v>44743</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55770,7 +55770,7 @@
         <v>46031</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55843,7 +55843,7 @@
         <v>46031</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55916,7 +55916,7 @@
         <v>44481</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55989,7 +55989,7 @@
         <v>46030</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56062,7 +56062,7 @@
         <v>46030</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56135,7 +56135,7 @@
         <v>46031</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56208,7 +56208,7 @@
         <v>45170</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56281,7 +56281,7 @@
         <v>45497</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56354,7 +56354,7 @@
         <v>45497</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56427,7 +56427,7 @@
         <v>44462</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56500,7 +56500,7 @@
         <v>45119</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56573,7 +56573,7 @@
         <v>45401</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56646,7 +56646,7 @@
         <v>44952</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56719,7 +56719,7 @@
         <v>45112</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56792,7 +56792,7 @@
         <v>45107</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56865,7 +56865,7 @@
         <v>44747</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56938,7 +56938,7 @@
         <v>45526</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57011,7 +57011,7 @@
         <v>44600</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57084,7 +57084,7 @@
         <v>45569</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57157,7 +57157,7 @@
         <v>44930</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57230,7 +57230,7 @@
         <v>45033</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57303,7 +57303,7 @@
         <v>45572</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57376,7 +57376,7 @@
         <v>46044</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57449,7 +57449,7 @@
         <v>46045</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57522,7 +57522,7 @@
         <v>46048</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57595,7 +57595,7 @@
         <v>45341</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57668,7 +57668,7 @@
         <v>46048</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57741,7 +57741,7 @@
         <v>46048</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57814,7 +57814,7 @@
         <v>45348</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57887,7 +57887,7 @@
         <v>46175</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57960,7 +57960,7 @@
         <v>46049</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58033,7 +58033,7 @@
         <v>46048</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58106,7 +58106,7 @@
         <v>44740</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58184,7 +58184,7 @@
         <v>45406</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58257,7 +58257,7 @@
         <v>44998</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58330,7 +58330,7 @@
         <v>45302</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58403,7 +58403,7 @@
         <v>44869</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58476,7 +58476,7 @@
         <v>46055</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58549,7 +58549,7 @@
         <v>45174</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58622,7 +58622,7 @@
         <v>45133</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58695,7 +58695,7 @@
         <v>46178</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58768,7 +58768,7 @@
         <v>45363</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58846,7 +58846,7 @@
         <v>45363</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58924,7 +58924,7 @@
         <v>45363</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59002,7 +59002,7 @@
         <v>45364</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59075,7 +59075,7 @@
         <v>46178</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59148,7 +59148,7 @@
         <v>45104</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59221,7 +59221,7 @@
         <v>45281</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59294,7 +59294,7 @@
         <v>45525</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59367,7 +59367,7 @@
         <v>46178</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59440,7 +59440,7 @@
         <v>46178</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59513,7 +59513,7 @@
         <v>46178</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59586,7 +59586,7 @@
         <v>46178</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59659,7 +59659,7 @@
         <v>46062</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59732,7 +59732,7 @@
         <v>46063</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59805,7 +59805,7 @@
         <v>45006</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59878,7 +59878,7 @@
         <v>46062</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59951,7 +59951,7 @@
         <v>46178</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60024,7 +60024,7 @@
         <v>46178</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60097,7 +60097,7 @@
         <v>46063</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60170,7 +60170,7 @@
         <v>46063</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60243,7 +60243,7 @@
         <v>46063</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60316,7 +60316,7 @@
         <v>45202</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60389,7 +60389,7 @@
         <v>45563</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60467,7 +60467,7 @@
         <v>45357</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60540,7 +60540,7 @@
         <v>46182</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60613,7 +60613,7 @@
         <v>46182</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60686,7 +60686,7 @@
         <v>45173</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60759,7 +60759,7 @@
         <v>45629</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60832,7 +60832,7 @@
         <v>46182</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60905,7 +60905,7 @@
         <v>45314</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60978,7 +60978,7 @@
         <v>46077</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61051,7 +61051,7 @@
         <v>45420</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61124,7 +61124,7 @@
         <v>46077</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61197,7 +61197,7 @@
         <v>46184</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61270,7 +61270,7 @@
         <v>45195</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61343,7 +61343,7 @@
         <v>45238</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61421,7 +61421,7 @@
         <v>44880</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61494,7 +61494,7 @@
         <v>44880</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61567,7 +61567,7 @@
         <v>45079</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61640,7 +61640,7 @@
         <v>45091</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61713,7 +61713,7 @@
         <v>46184</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61786,7 +61786,7 @@
         <v>44602</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61859,7 +61859,7 @@
         <v>45163</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61932,7 +61932,7 @@
         <v>46184</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62005,7 +62005,7 @@
         <v>46084</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62078,7 +62078,7 @@
         <v>46084</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62151,7 +62151,7 @@
         <v>44523</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62224,7 +62224,7 @@
         <v>46185</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62297,7 +62297,7 @@
         <v>46084</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62370,7 +62370,7 @@
         <v>44677</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62443,7 +62443,7 @@
         <v>46188</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62516,7 +62516,7 @@
         <v>45303</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62589,7 +62589,7 @@
         <v>44592</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62662,7 +62662,7 @@
         <v>46185</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62735,7 +62735,7 @@
         <v>45475</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62808,7 +62808,7 @@
         <v>45211</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62881,7 +62881,7 @@
         <v>46087</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62954,7 +62954,7 @@
         <v>45352</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63027,7 +63027,7 @@
         <v>45538</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63100,7 +63100,7 @@
         <v>45329</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63178,7 +63178,7 @@
         <v>45314</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63251,7 +63251,7 @@
         <v>45645</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63329,7 +63329,7 @@
         <v>46091</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63402,7 +63402,7 @@
         <v>46092</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63475,7 +63475,7 @@
         <v>46092</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63548,7 +63548,7 @@
         <v>46190</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63621,7 +63621,7 @@
         <v>44815</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63694,7 +63694,7 @@
         <v>44497</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63767,7 +63767,7 @@
         <v>46002</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63840,7 +63840,7 @@
         <v>46097</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63913,7 +63913,7 @@
         <v>45091</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63986,7 +63986,7 @@
         <v>46098</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64059,7 +64059,7 @@
         <v>45022</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64132,7 +64132,7 @@
         <v>45526</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64205,7 +64205,7 @@
         <v>45114</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64278,7 +64278,7 @@
         <v>45925</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64351,7 +64351,7 @@
         <v>46099</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64424,7 +64424,7 @@
         <v>45440</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64497,7 +64497,7 @@
         <v>46195</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64570,7 +64570,7 @@
         <v>46100</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64643,7 +64643,7 @@
         <v>44587</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64716,7 +64716,7 @@
         <v>46104</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64789,7 +64789,7 @@
         <v>44715</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64862,7 +64862,7 @@
         <v>46196</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64935,7 +64935,7 @@
         <v>46196</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65008,7 +65008,7 @@
         <v>44813</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65081,7 +65081,7 @@
         <v>46104</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65154,7 +65154,7 @@
         <v>46104</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65227,7 +65227,7 @@
         <v>45365</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65300,7 +65300,7 @@
         <v>45385</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65373,7 +65373,7 @@
         <v>46107</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65446,7 +65446,7 @@
         <v>46197</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65519,7 +65519,7 @@
         <v>44946</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65592,7 +65592,7 @@
         <v>46107</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65665,7 +65665,7 @@
         <v>46107</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65738,7 +65738,7 @@
         <v>46197</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65811,7 +65811,7 @@
         <v>46111</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65884,7 +65884,7 @@
         <v>46244</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65957,7 +65957,7 @@
         <v>46111</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66030,7 +66030,7 @@
         <v>44805</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66103,7 +66103,7 @@
         <v>46202</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66176,7 +66176,7 @@
         <v>44813</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66249,7 +66249,7 @@
         <v>45398</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66322,7 +66322,7 @@
         <v>45307</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66395,7 +66395,7 @@
         <v>44825</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66468,7 +66468,7 @@
         <v>44917</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66541,7 +66541,7 @@
         <v>45177</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66619,7 +66619,7 @@
         <v>45174</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66697,7 +66697,7 @@
         <v>45329</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66770,7 +66770,7 @@
         <v>46121</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66843,7 +66843,7 @@
         <v>46122</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66916,7 +66916,7 @@
         <v>46121</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66989,7 +66989,7 @@
         <v>45245</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67062,7 +67062,7 @@
         <v>44462</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67135,7 +67135,7 @@
         <v>45737</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67208,7 +67208,7 @@
         <v>46244</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67281,7 +67281,7 @@
         <v>45719</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67354,7 +67354,7 @@
         <v>46126</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67427,7 +67427,7 @@
         <v>46128</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67500,7 +67500,7 @@
         <v>46128</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67573,7 +67573,7 @@
         <v>46128</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67646,7 +67646,7 @@
         <v>46128</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67719,7 +67719,7 @@
         <v>45364</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -67792,7 +67792,7 @@
         <v>46127</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -67865,7 +67865,7 @@
         <v>45089</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67938,7 +67938,7 @@
         <v>44459</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -68011,7 +68011,7 @@
         <v>46128</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -68084,7 +68084,7 @@
         <v>45660</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -68157,7 +68157,7 @@
         <v>45107</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -68230,7 +68230,7 @@
         <v>45184</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -68303,7 +68303,7 @@
         <v>46133</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -68376,7 +68376,7 @@
         <v>46133</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68449,7 +68449,7 @@
         <v>46204</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68522,7 +68522,7 @@
         <v>45589</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68595,7 +68595,7 @@
         <v>45589</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -68668,7 +68668,7 @@
         <v>45532</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -68741,7 +68741,7 @@
         <v>45370</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -68814,7 +68814,7 @@
         <v>46246</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68887,7 +68887,7 @@
         <v>45406</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -68960,7 +68960,7 @@
         <v>44595</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -69033,7 +69033,7 @@
         <v>45903</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -69106,7 +69106,7 @@
         <v>45104</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -69179,7 +69179,7 @@
         <v>45071</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -69252,7 +69252,7 @@
         <v>45839</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -69325,7 +69325,7 @@
         <v>45699</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -69398,7 +69398,7 @@
         <v>45827</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -69471,7 +69471,7 @@
         <v>45216</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69544,7 +69544,7 @@
         <v>46037</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -69617,7 +69617,7 @@
         <v>45944</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -69690,7 +69690,7 @@
         <v>45112</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -69763,7 +69763,7 @@
         <v>45303</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -69836,7 +69836,7 @@
         <v>45891</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -69909,7 +69909,7 @@
         <v>45313</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -69982,7 +69982,7 @@
         <v>45799</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -70055,7 +70055,7 @@
         <v>45306</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -70128,7 +70128,7 @@
         <v>45678</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -70201,7 +70201,7 @@
         <v>45182</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -70274,7 +70274,7 @@
         <v>44495</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -70347,7 +70347,7 @@
         <v>45219</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -70420,7 +70420,7 @@
         <v>45931</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -70493,7 +70493,7 @@
         <v>45030</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70566,7 +70566,7 @@
         <v>44510</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -70639,7 +70639,7 @@
         <v>45544</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -70712,7 +70712,7 @@
         <v>45895</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -70785,7 +70785,7 @@
         <v>45691</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -70858,7 +70858,7 @@
         <v>44488</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -70931,7 +70931,7 @@
         <v>45631</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -71004,7 +71004,7 @@
         <v>45216</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -71082,7 +71082,7 @@
         <v>45359</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -71155,7 +71155,7 @@
         <v>46245</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -71228,7 +71228,7 @@
         <v>45376</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -71301,7 +71301,7 @@
         <v>44810</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -71374,7 +71374,7 @@
         <v>45209</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -71447,7 +71447,7 @@
         <v>45183</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -71520,7 +71520,7 @@
         <v>45595</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -71593,7 +71593,7 @@
         <v>45575</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -71666,7 +71666,7 @@
         <v>46252</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -71739,7 +71739,7 @@
         <v>45062</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -71812,7 +71812,7 @@
         <v>45231</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -71885,7 +71885,7 @@
         <v>45699</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -71958,7 +71958,7 @@
         <v>45737</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -72031,7 +72031,7 @@
         <v>44930</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -72104,7 +72104,7 @@
         <v>44971</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -72177,7 +72177,7 @@
         <v>45602</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -72250,7 +72250,7 @@
         <v>45092</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -72323,7 +72323,7 @@
         <v>45674</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -72396,7 +72396,7 @@
         <v>45478</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -72469,7 +72469,7 @@
         <v>45769</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -72547,7 +72547,7 @@
         <v>45164</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -72620,7 +72620,7 @@
         <v>46255</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -72693,7 +72693,7 @@
         <v>45309</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -72766,7 +72766,7 @@
         <v>45309</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -72839,7 +72839,7 @@
         <v>45182</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -72917,7 +72917,7 @@
         <v>46069</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -72990,7 +72990,7 @@
         <v>46259</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -73063,7 +73063,7 @@
         <v>45329</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -73136,7 +73136,7 @@
         <v>45222</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -73209,7 +73209,7 @@
         <v>45492</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -73282,7 +73282,7 @@
         <v>45323</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -73355,7 +73355,7 @@
         <v>46213</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -73428,7 +73428,7 @@
         <v>45763</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -73501,7 +73501,7 @@
         <v>45384</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -73574,7 +73574,7 @@
         <v>45296</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -73647,7 +73647,7 @@
         <v>46168</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -73720,7 +73720,7 @@
         <v>45763</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -73793,7 +73793,7 @@
         <v>45763</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -73866,7 +73866,7 @@
         <v>45763</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -73939,7 +73939,7 @@
         <v>46258</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -74012,7 +74012,7 @@
         <v>44946</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -74085,7 +74085,7 @@
         <v>45462</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -74158,7 +74158,7 @@
         <v>46259</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -74231,7 +74231,7 @@
         <v>44879</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -74304,7 +74304,7 @@
         <v>45719</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -74377,7 +74377,7 @@
         <v>45540</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -74450,7 +74450,7 @@
         <v>46177</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -74523,7 +74523,7 @@
         <v>45134</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -74596,7 +74596,7 @@
         <v>45316</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -74669,7 +74669,7 @@
         <v>45414</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -74742,7 +74742,7 @@
         <v>45607</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -74815,7 +74815,7 @@
         <v>44818</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -74888,7 +74888,7 @@
         <v>45673</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -74961,7 +74961,7 @@
         <v>44831</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -75034,7 +75034,7 @@
         <v>45001</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -75112,7 +75112,7 @@
         <v>45992</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -75185,7 +75185,7 @@
         <v>45254</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -75263,7 +75263,7 @@
         <v>45090</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -75336,7 +75336,7 @@
         <v>45132</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -75409,7 +75409,7 @@
         <v>45335</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -75482,7 +75482,7 @@
         <v>46265</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -75555,7 +75555,7 @@
         <v>45602</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -75628,7 +75628,7 @@
         <v>44963</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -75701,7 +75701,7 @@
         <v>45168</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -75774,7 +75774,7 @@
         <v>45400</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -75847,7 +75847,7 @@
         <v>45188</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -75920,7 +75920,7 @@
         <v>46178</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -75993,7 +75993,7 @@
         <v>45670</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -76066,7 +76066,7 @@
         <v>44902</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -76139,7 +76139,7 @@
         <v>44564</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -76217,7 +76217,7 @@
         <v>45189</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -76295,7 +76295,7 @@
         <v>45691</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -76368,7 +76368,7 @@
         <v>44916</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -76441,7 +76441,7 @@
         <v>44957</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -76514,7 +76514,7 @@
         <v>46269</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -76587,7 +76587,7 @@
         <v>44502</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -76660,7 +76660,7 @@
         <v>45702</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -76738,7 +76738,7 @@
         <v>46268</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -76811,7 +76811,7 @@
         <v>45134</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -76884,7 +76884,7 @@
         <v>45348</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -76957,7 +76957,7 @@
         <v>45439</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -77030,7 +77030,7 @@
         <v>44781</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -77103,7 +77103,7 @@
         <v>45783</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -77176,7 +77176,7 @@
         <v>45783</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -77249,7 +77249,7 @@
         <v>46273</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -77322,7 +77322,7 @@
         <v>46258</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -77395,7 +77395,7 @@
         <v>46274</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -77468,7 +77468,7 @@
         <v>46273</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -77541,7 +77541,7 @@
         <v>46234</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -77614,7 +77614,7 @@
         <v>46276</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -77687,7 +77687,7 @@
         <v>46276</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -77760,7 +77760,7 @@
         <v>46234</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -77833,7 +77833,7 @@
         <v>45439</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -77906,7 +77906,7 @@
         <v>46279</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -77979,7 +77979,7 @@
         <v>46276</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -78052,7 +78052,7 @@
         <v>46276</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -78125,7 +78125,7 @@
         <v>46276</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -78198,7 +78198,7 @@
         <v>46233</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -78271,7 +78271,7 @@
         <v>46234</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -78344,7 +78344,7 @@
         <v>44592</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -78417,7 +78417,7 @@
         <v>45786</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -78490,7 +78490,7 @@
         <v>46237</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -78563,7 +78563,7 @@
         <v>45601</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -78636,7 +78636,7 @@
         <v>45456</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -78709,7 +78709,7 @@
         <v>45716</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -78782,7 +78782,7 @@
         <v>46280</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -78855,7 +78855,7 @@
         <v>45792</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -78928,7 +78928,7 @@
         <v>46240</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -79001,7 +79001,7 @@
         <v>46247</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -79079,7 +79079,7 @@
         <v>45741</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -79157,7 +79157,7 @@
         <v>45741</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -79235,7 +79235,7 @@
         <v>45728</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -79308,7 +79308,7 @@
         <v>45259</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -79381,7 +79381,7 @@
         <v>46283</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -79454,7 +79454,7 @@
         <v>45610</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -79527,7 +79527,7 @@
         <v>45743</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -79600,7 +79600,7 @@
         <v>46248</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -79678,7 +79678,7 @@
         <v>45737</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -79751,7 +79751,7 @@
         <v>45737</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -79824,7 +79824,7 @@
         <v>45742</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -79897,7 +79897,7 @@
         <v>45733</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -79970,7 +79970,7 @@
         <v>45733</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -80043,7 +80043,7 @@
         <v>45803</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -80116,7 +80116,7 @@
         <v>45743</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -80189,7 +80189,7 @@
         <v>45442</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -80262,7 +80262,7 @@
         <v>45708</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -80335,7 +80335,7 @@
         <v>45616</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -80408,7 +80408,7 @@
         <v>45359</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -80481,7 +80481,7 @@
         <v>46247</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
@@ -80559,7 +80559,7 @@
         <v>45805</v>
       </c>
       <c r="E1032" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
@@ -80632,7 +80632,7 @@
         <v>45434</v>
       </c>
       <c r="E1033" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
@@ -80705,7 +80705,7 @@
         <v>45811</v>
       </c>
       <c r="E1034" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
@@ -80778,7 +80778,7 @@
         <v>45615</v>
       </c>
       <c r="E1035" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
@@ -80851,7 +80851,7 @@
         <v>45505</v>
       </c>
       <c r="E1036" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
@@ -80924,7 +80924,7 @@
         <v>45812</v>
       </c>
       <c r="E1037" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
@@ -80997,7 +80997,7 @@
         <v>45816</v>
       </c>
       <c r="E1038" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1038" t="inlineStr">
         <is>
@@ -81070,7 +81070,7 @@
         <v>45819</v>
       </c>
       <c r="E1039" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1039" t="inlineStr">
         <is>
@@ -81143,7 +81143,7 @@
         <v>45819</v>
       </c>
       <c r="E1040" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1040" t="inlineStr">
         <is>
@@ -81216,7 +81216,7 @@
         <v>45819</v>
       </c>
       <c r="E1041" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1041" t="inlineStr">
         <is>
@@ -81289,7 +81289,7 @@
         <v>45819</v>
       </c>
       <c r="E1042" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1042" t="inlineStr">
         <is>
@@ -81362,7 +81362,7 @@
         <v>45737</v>
       </c>
       <c r="E1043" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1043" t="inlineStr">
         <is>
@@ -81435,7 +81435,7 @@
         <v>45838</v>
       </c>
       <c r="E1044" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1044" t="inlineStr">
         <is>
@@ -81508,7 +81508,7 @@
         <v>45839</v>
       </c>
       <c r="E1045" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1045" t="inlineStr">
         <is>
@@ -81581,7 +81581,7 @@
         <v>45840</v>
       </c>
       <c r="E1046" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1046" t="inlineStr">
         <is>
@@ -81654,7 +81654,7 @@
         <v>45840</v>
       </c>
       <c r="E1047" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1047" t="inlineStr">
         <is>
@@ -81727,7 +81727,7 @@
         <v>45845</v>
       </c>
       <c r="E1048" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1048" t="inlineStr">
         <is>
@@ -81800,7 +81800,7 @@
         <v>45729</v>
       </c>
       <c r="E1049" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1049" t="inlineStr">
         <is>
@@ -81873,7 +81873,7 @@
         <v>45748</v>
       </c>
       <c r="E1050" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1050" t="inlineStr">
         <is>
@@ -81946,7 +81946,7 @@
         <v>45747</v>
       </c>
       <c r="E1051" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1051" t="inlineStr">
         <is>
@@ -82019,7 +82019,7 @@
         <v>45625</v>
       </c>
       <c r="E1052" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1052" t="inlineStr">
         <is>
@@ -82092,7 +82092,7 @@
         <v>45715</v>
       </c>
       <c r="E1053" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1053" t="inlineStr">
         <is>
@@ -82165,7 +82165,7 @@
         <v>45715</v>
       </c>
       <c r="E1054" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1054" t="inlineStr">
         <is>
@@ -82238,7 +82238,7 @@
         <v>44834</v>
       </c>
       <c r="E1055" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1055" t="inlineStr">
         <is>
@@ -82311,7 +82311,7 @@
         <v>45847</v>
       </c>
       <c r="E1056" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1056" t="inlineStr">
         <is>
@@ -82384,7 +82384,7 @@
         <v>45763</v>
       </c>
       <c r="E1057" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1057" t="inlineStr">
         <is>
@@ -82457,7 +82457,7 @@
         <v>45852</v>
       </c>
       <c r="E1058" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1058" t="inlineStr">
         <is>
@@ -82530,7 +82530,7 @@
         <v>45672</v>
       </c>
       <c r="E1059" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1059" t="inlineStr">
         <is>
@@ -82603,7 +82603,7 @@
         <v>45163</v>
       </c>
       <c r="E1060" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1060" t="inlineStr">
         <is>
@@ -82676,7 +82676,7 @@
         <v>44549</v>
       </c>
       <c r="E1061" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1061" t="inlineStr">
         <is>
@@ -82749,7 +82749,7 @@
         <v>45322</v>
       </c>
       <c r="E1062" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1062" t="inlineStr">
         <is>
@@ -82822,7 +82822,7 @@
         <v>45005</v>
       </c>
       <c r="E1063" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1063" t="inlineStr">
         <is>
@@ -82895,7 +82895,7 @@
         <v>44564</v>
       </c>
       <c r="E1064" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1064" t="inlineStr">
         <is>
@@ -82968,7 +82968,7 @@
         <v>45866</v>
       </c>
       <c r="E1065" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1065" t="inlineStr">
         <is>
@@ -83041,7 +83041,7 @@
         <v>45288</v>
       </c>
       <c r="E1066" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1066" t="inlineStr">
         <is>
@@ -83114,7 +83114,7 @@
         <v>45733</v>
       </c>
       <c r="E1067" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1067" t="inlineStr">
         <is>
@@ -83187,7 +83187,7 @@
         <v>45113</v>
       </c>
       <c r="E1068" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1068" t="inlineStr">
         <is>
@@ -83260,7 +83260,7 @@
         <v>45875</v>
       </c>
       <c r="E1069" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1069" t="inlineStr">
         <is>
@@ -83333,7 +83333,7 @@
         <v>45875</v>
       </c>
       <c r="E1070" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1070" t="inlineStr">
         <is>
@@ -83406,7 +83406,7 @@
         <v>45875</v>
       </c>
       <c r="E1071" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1071" t="inlineStr">
         <is>
@@ -83479,7 +83479,7 @@
         <v>45882</v>
       </c>
       <c r="E1072" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1072" t="inlineStr">
         <is>
@@ -83552,7 +83552,7 @@
         <v>45882</v>
       </c>
       <c r="E1073" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1073" t="inlineStr">
         <is>
@@ -83625,7 +83625,7 @@
         <v>45636</v>
       </c>
       <c r="E1074" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1074" t="inlineStr">
         <is>
@@ -83698,7 +83698,7 @@
         <v>45580</v>
       </c>
       <c r="E1075" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1075" t="inlineStr">
         <is>
@@ -83771,7 +83771,7 @@
         <v>45447</v>
       </c>
       <c r="E1076" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1076" t="inlineStr">
         <is>
@@ -83844,7 +83844,7 @@
         <v>45170</v>
       </c>
       <c r="E1077" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1077" t="inlineStr">
         <is>
@@ -83917,7 +83917,7 @@
         <v>45106</v>
       </c>
       <c r="E1078" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1078" t="inlineStr">
         <is>
@@ -83990,7 +83990,7 @@
         <v>45467</v>
       </c>
       <c r="E1079" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1079" t="inlineStr">
         <is>
@@ -84063,7 +84063,7 @@
         <v>44509</v>
       </c>
       <c r="E1080" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1080" t="inlineStr">
         <is>
@@ -84141,7 +84141,7 @@
         <v>45664</v>
       </c>
       <c r="E1081" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1081" t="inlineStr">
         <is>
@@ -84214,7 +84214,7 @@
         <v>45208</v>
       </c>
       <c r="E1082" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1082" t="inlineStr">
         <is>
@@ -84287,7 +84287,7 @@
         <v>45406</v>
       </c>
       <c r="E1083" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1083" t="inlineStr">
         <is>
@@ -84360,7 +84360,7 @@
         <v>45497</v>
       </c>
       <c r="E1084" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1084" t="inlineStr">
         <is>
@@ -84433,7 +84433,7 @@
         <v>45497</v>
       </c>
       <c r="E1085" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1085" t="inlineStr">
         <is>
@@ -84506,7 +84506,7 @@
         <v>45106</v>
       </c>
       <c r="E1086" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1086" t="inlineStr">
         <is>
@@ -84579,7 +84579,7 @@
         <v>45646</v>
       </c>
       <c r="E1087" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1087" t="inlineStr">
         <is>
@@ -84652,7 +84652,7 @@
         <v>44459</v>
       </c>
       <c r="E1088" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1088" t="inlineStr">
         <is>
@@ -84725,7 +84725,7 @@
         <v>45646</v>
       </c>
       <c r="E1089" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1089" t="inlineStr">
         <is>
@@ -84798,7 +84798,7 @@
         <v>45580</v>
       </c>
       <c r="E1090" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1090" t="inlineStr">
         <is>
@@ -84871,7 +84871,7 @@
         <v>45646</v>
       </c>
       <c r="E1091" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1091" t="inlineStr">
         <is>
@@ -84944,7 +84944,7 @@
         <v>45646</v>
       </c>
       <c r="E1092" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1092" t="inlineStr">
         <is>
@@ -85017,7 +85017,7 @@
         <v>45408</v>
       </c>
       <c r="E1093" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1093" t="inlineStr">
         <is>
@@ -85090,7 +85090,7 @@
         <v>45414</v>
       </c>
       <c r="E1094" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1094" t="inlineStr">
         <is>
@@ -85163,7 +85163,7 @@
         <v>45173</v>
       </c>
       <c r="E1095" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1095" t="inlineStr">
         <is>
@@ -85236,7 +85236,7 @@
         <v>45646</v>
       </c>
       <c r="E1096" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1096" t="inlineStr">
         <is>
@@ -85309,7 +85309,7 @@
         <v>45715</v>
       </c>
       <c r="E1097" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1097" t="inlineStr">
         <is>
@@ -85382,7 +85382,7 @@
         <v>45720</v>
       </c>
       <c r="E1098" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1098" t="inlineStr">
         <is>
@@ -85455,7 +85455,7 @@
         <v>45800</v>
       </c>
       <c r="E1099" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1099" t="inlineStr">
         <is>
@@ -85533,7 +85533,7 @@
         <v>45831</v>
       </c>
       <c r="E1100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1100" t="inlineStr">
         <is>
@@ -85606,7 +85606,7 @@
         <v>45785</v>
       </c>
       <c r="E1101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1101" t="inlineStr">
         <is>
@@ -85679,7 +85679,7 @@
         <v>46073</v>
       </c>
       <c r="E1102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1102" t="inlineStr">
         <is>
@@ -85752,7 +85752,7 @@
         <v>46163</v>
       </c>
       <c r="E1103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1103" t="inlineStr">
         <is>
@@ -85825,7 +85825,7 @@
         <v>46274</v>
       </c>
       <c r="E1104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1104" t="inlineStr">
         <is>

--- a/Översikt VETLANDA.xlsx
+++ b/Översikt VETLANDA.xlsx
@@ -601,7 +601,7 @@
         <v>45097</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>46178</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         <v>45371</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>44890</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>44817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>45183</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>45558</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>45168</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>46107</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>45930</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>45957</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>45520</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>45754</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>45170</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>44612</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>46002</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>46100</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>44908</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>44840</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>45203</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>45819</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>46163</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>46188</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>44545</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>44564</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>45763</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>45477</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>46045</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>45599</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         <v>45048</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>44819</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         <v>45814</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>45583</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>45646</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4450,7 +4450,7 @@
         <v>45131</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>44515</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>44470</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>44752</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>44643</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>45400</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         <v>45310</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5221,7 +5221,7 @@
         <v>45035</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>45357</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5433,7 +5433,7 @@
         <v>44572</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
         <v>45589</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         <v>44468</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5751,7 +5751,7 @@
         <v>45965</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>45891</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         <v>45792</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>45835</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6179,7 +6179,7 @@
         <v>45840</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         <v>45148</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>45713</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         <v>46166</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6607,7 +6607,7 @@
         <v>45860</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6713,7 +6713,7 @@
         <v>45303</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         <v>46279</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         <v>45713</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>45211</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         <v>45673</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         <v>45616</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7354,7 +7354,7 @@
         <v>45106</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>45509</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7566,7 +7566,7 @@
         <v>45497</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7672,7 +7672,7 @@
         <v>45201</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>45539</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7884,7 +7884,7 @@
         <v>46051</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7994,7 +7994,7 @@
         <v>44834</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>44721</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
         <v>44747</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         <v>44592</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>44740</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8524,7 +8524,7 @@
         <v>44824</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         <v>45378</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8734,7 +8734,7 @@
         <v>45342</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>45119</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8944,7 +8944,7 @@
         <v>44833</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9049,7 +9049,7 @@
         <v>45835</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9154,7 +9154,7 @@
         <v>45672</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         <v>45736</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
         <v>45904</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9477,7 +9477,7 @@
         <v>45645</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>45021</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9687,7 +9687,7 @@
         <v>46069</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9792,7 +9792,7 @@
         <v>46071</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         <v>45586</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
         <v>45085</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10107,7 +10107,7 @@
         <v>44781</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         <v>44816</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10317,7 +10317,7 @@
         <v>45880</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10422,7 +10422,7 @@
         <v>45775</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         <v>45820</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10637,7 +10637,7 @@
         <v>46141</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         <v>45009</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10851,7 +10851,7 @@
         <v>45839</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         <v>45240</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>45419</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11166,7 +11166,7 @@
         <v>44880</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11271,7 +11271,7 @@
         <v>46188</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>45565</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11481,7 +11481,7 @@
         <v>45586</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11586,7 +11586,7 @@
         <v>45596</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11691,7 +11691,7 @@
         <v>45597</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11796,7 +11796,7 @@
         <v>45555</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11901,7 +11901,7 @@
         <v>45408</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12006,7 +12006,7 @@
         <v>45930</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>45261</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12225,7 +12225,7 @@
         <v>44748</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12330,7 +12330,7 @@
         <v>44830</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>44916</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12540,7 +12540,7 @@
         <v>46248</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12645,7 +12645,7 @@
         <v>45239</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12755,7 +12755,7 @@
         <v>45104</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12864,7 +12864,7 @@
         <v>44728</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12973,7 +12973,7 @@
         <v>44819</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13078,7 +13078,7 @@
         <v>45337</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13183,7 +13183,7 @@
         <v>45532</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13288,7 +13288,7 @@
         <v>44998</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13393,7 +13393,7 @@
         <v>45643</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13498,7 +13498,7 @@
         <v>45352</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13603,7 +13603,7 @@
         <v>45791</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13708,7 +13708,7 @@
         <v>45604</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13813,7 +13813,7 @@
         <v>45497</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13918,7 +13918,7 @@
         <v>45614</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14023,7 +14023,7 @@
         <v>45742</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14132,7 +14132,7 @@
         <v>44490</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14205,7 +14205,7 @@
         <v>44858</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
         <v>44781</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14351,7 +14351,7 @@
         <v>44838</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14424,7 +14424,7 @@
         <v>44781</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14497,7 +14497,7 @@
         <v>44732</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14570,7 +14570,7 @@
         <v>44515</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14643,7 +14643,7 @@
         <v>44508</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14716,7 +14716,7 @@
         <v>44504</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14789,7 +14789,7 @@
         <v>44496</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14862,7 +14862,7 @@
         <v>44579</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14935,7 +14935,7 @@
         <v>44601</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>44889</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
         <v>44544</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15154,7 +15154,7 @@
         <v>44510</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15227,7 +15227,7 @@
         <v>44468</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15300,7 +15300,7 @@
         <v>44517</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15373,7 +15373,7 @@
         <v>44764</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15446,7 +15446,7 @@
         <v>44510</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15519,7 +15519,7 @@
         <v>44503</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15592,7 +15592,7 @@
         <v>44819</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
         <v>44592</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15738,7 +15738,7 @@
         <v>44750</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15811,7 +15811,7 @@
         <v>44825</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15884,7 +15884,7 @@
         <v>44488</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15957,7 +15957,7 @@
         <v>44602</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16030,7 +16030,7 @@
         <v>44638</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16103,7 +16103,7 @@
         <v>44721</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16176,7 +16176,7 @@
         <v>44510</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16249,7 +16249,7 @@
         <v>44785</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16322,7 +16322,7 @@
         <v>44592</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16395,7 +16395,7 @@
         <v>44587</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>44782</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16541,7 +16541,7 @@
         <v>44815</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16614,7 +16614,7 @@
         <v>44504</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16687,7 +16687,7 @@
         <v>44580</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16760,7 +16760,7 @@
         <v>44691</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16833,7 +16833,7 @@
         <v>44880</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16906,7 +16906,7 @@
         <v>44545</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16979,7 +16979,7 @@
         <v>44750</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17052,7 +17052,7 @@
         <v>44624</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17125,7 +17125,7 @@
         <v>44595</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17198,7 +17198,7 @@
         <v>44477</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17271,7 +17271,7 @@
         <v>44608</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>44820</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>44816</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17490,7 +17490,7 @@
         <v>44819</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17563,7 +17563,7 @@
         <v>44645</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17636,7 +17636,7 @@
         <v>44656</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17709,7 +17709,7 @@
         <v>44784</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17782,7 +17782,7 @@
         <v>44585</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17860,7 +17860,7 @@
         <v>44585</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17938,7 +17938,7 @@
         <v>44585</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18016,7 +18016,7 @@
         <v>44834</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18089,7 +18089,7 @@
         <v>44740</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18167,7 +18167,7 @@
         <v>44750</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>44587</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18313,7 +18313,7 @@
         <v>44743</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18386,7 +18386,7 @@
         <v>44474</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18459,7 +18459,7 @@
         <v>44600</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
         <v>44859</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18605,7 +18605,7 @@
         <v>44593</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18678,7 +18678,7 @@
         <v>44743</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18751,7 +18751,7 @@
         <v>44778</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18824,7 +18824,7 @@
         <v>44504</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18897,7 +18897,7 @@
         <v>44834</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18970,7 +18970,7 @@
         <v>44477</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19043,7 +19043,7 @@
         <v>44482</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19116,7 +19116,7 @@
         <v>44509</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19189,7 +19189,7 @@
         <v>44592</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19262,7 +19262,7 @@
         <v>44517</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19335,7 +19335,7 @@
         <v>44721</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>44572</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19481,7 +19481,7 @@
         <v>44841</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19554,7 +19554,7 @@
         <v>44888</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19627,7 +19627,7 @@
         <v>44587</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>44655</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19773,7 +19773,7 @@
         <v>44502</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>44515</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19924,7 +19924,7 @@
         <v>44592</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19997,7 +19997,7 @@
         <v>44564</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20070,7 +20070,7 @@
         <v>44781</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>44531</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20216,7 +20216,7 @@
         <v>44636</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20289,7 +20289,7 @@
         <v>44834</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20362,7 +20362,7 @@
         <v>44733</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20435,7 +20435,7 @@
         <v>44683</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20508,7 +20508,7 @@
         <v>44602</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20581,7 +20581,7 @@
         <v>44792</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20654,7 +20654,7 @@
         <v>44657</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20727,7 +20727,7 @@
         <v>44827</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20800,7 +20800,7 @@
         <v>45329</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20873,7 +20873,7 @@
         <v>45323</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20946,7 +20946,7 @@
         <v>45267</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21019,7 +21019,7 @@
         <v>45335</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21092,7 +21092,7 @@
         <v>44834</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
         <v>44825</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21238,7 +21238,7 @@
         <v>45272</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>45329</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21384,7 +21384,7 @@
         <v>45202</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21457,7 +21457,7 @@
         <v>45401</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21530,7 +21530,7 @@
         <v>45300</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>45345</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21676,7 +21676,7 @@
         <v>45364</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21749,7 +21749,7 @@
         <v>45091</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21822,7 +21822,7 @@
         <v>45414</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21900,7 +21900,7 @@
         <v>44815</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21973,7 +21973,7 @@
         <v>45211</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22046,7 +22046,7 @@
         <v>45097</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22119,7 +22119,7 @@
         <v>45384</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22192,7 +22192,7 @@
         <v>44929</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22265,7 +22265,7 @@
         <v>45107</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22338,7 +22338,7 @@
         <v>45296</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22411,7 +22411,7 @@
         <v>45240</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22484,7 +22484,7 @@
         <v>44902</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22557,7 +22557,7 @@
         <v>44530</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22630,7 +22630,7 @@
         <v>45370</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22703,7 +22703,7 @@
         <v>44813</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22776,7 +22776,7 @@
         <v>45532</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22849,7 +22849,7 @@
         <v>45119</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22922,7 +22922,7 @@
         <v>45394</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22995,7 +22995,7 @@
         <v>45461</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23068,7 +23068,7 @@
         <v>45440</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23141,7 +23141,7 @@
         <v>45439</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23214,7 +23214,7 @@
         <v>44880</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23287,7 +23287,7 @@
         <v>44880</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23360,7 +23360,7 @@
         <v>45309</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23433,7 +23433,7 @@
         <v>44837</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23506,7 +23506,7 @@
         <v>45363</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23584,7 +23584,7 @@
         <v>44482</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23657,7 +23657,7 @@
         <v>45763</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23730,7 +23730,7 @@
         <v>45763</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23803,7 +23803,7 @@
         <v>45763</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23876,7 +23876,7 @@
         <v>45884</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23949,7 +23949,7 @@
         <v>45201</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24022,7 +24022,7 @@
         <v>45827</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24095,7 +24095,7 @@
         <v>45443</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24168,7 +24168,7 @@
         <v>45435</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24241,7 +24241,7 @@
         <v>44837</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24314,7 +24314,7 @@
         <v>45449</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24387,7 +24387,7 @@
         <v>46003</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24460,7 +24460,7 @@
         <v>45446</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24533,7 +24533,7 @@
         <v>45330</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24606,7 +24606,7 @@
         <v>46030</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24679,7 +24679,7 @@
         <v>46030</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24752,7 +24752,7 @@
         <v>45884</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24825,7 +24825,7 @@
         <v>45497</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24898,7 +24898,7 @@
         <v>45497</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24971,7 +24971,7 @@
         <v>45743</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25044,7 +25044,7 @@
         <v>45733</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25117,7 +25117,7 @@
         <v>45733</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25190,7 +25190,7 @@
         <v>45737</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25263,7 +25263,7 @@
         <v>45737</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25336,7 +25336,7 @@
         <v>45544</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25409,7 +25409,7 @@
         <v>45546</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25482,7 +25482,7 @@
         <v>45742</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25555,7 +25555,7 @@
         <v>45728</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25628,7 +25628,7 @@
         <v>45741</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25706,7 +25706,7 @@
         <v>45741</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25784,7 +25784,7 @@
         <v>46029</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25857,7 +25857,7 @@
         <v>46031</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25930,7 +25930,7 @@
         <v>46031</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26003,7 +26003,7 @@
         <v>44481</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26076,7 +26076,7 @@
         <v>44858</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26149,7 +26149,7 @@
         <v>45826</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26222,7 +26222,7 @@
         <v>44515</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26300,7 +26300,7 @@
         <v>45888</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26373,7 +26373,7 @@
         <v>45742</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26446,7 +26446,7 @@
         <v>45888</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26519,7 +26519,7 @@
         <v>46031</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26592,7 +26592,7 @@
         <v>45786</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26665,7 +26665,7 @@
         <v>45742</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26738,7 +26738,7 @@
         <v>45888</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26811,7 +26811,7 @@
         <v>45839</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26884,7 +26884,7 @@
         <v>44564</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26962,7 +26962,7 @@
         <v>45541</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27035,7 +27035,7 @@
         <v>45888</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27108,7 +27108,7 @@
         <v>45888</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27181,7 +27181,7 @@
         <v>45888</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27254,7 +27254,7 @@
         <v>45341</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27327,7 +27327,7 @@
         <v>45889</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27400,7 +27400,7 @@
         <v>45677</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27473,7 +27473,7 @@
         <v>45889</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27546,7 +27546,7 @@
         <v>45889</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27619,7 +27619,7 @@
         <v>45259</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27692,7 +27692,7 @@
         <v>44531</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27765,7 +27765,7 @@
         <v>45610</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27838,7 +27838,7 @@
         <v>45770</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27911,7 +27911,7 @@
         <v>45839</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27984,7 +27984,7 @@
         <v>45623</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28057,7 +28057,7 @@
         <v>45898</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28130,7 +28130,7 @@
         <v>44602</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28203,7 +28203,7 @@
         <v>45538</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28276,7 +28276,7 @@
         <v>46044</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28349,7 +28349,7 @@
         <v>44592</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28422,7 +28422,7 @@
         <v>45106</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28495,7 +28495,7 @@
         <v>46048</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28568,7 +28568,7 @@
         <v>46048</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28641,7 +28641,7 @@
         <v>45902</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28714,7 +28714,7 @@
         <v>45581</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28792,7 +28792,7 @@
         <v>45819</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28865,7 +28865,7 @@
         <v>45737</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28938,7 +28938,7 @@
         <v>46045</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29011,7 +29011,7 @@
         <v>45587</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29084,7 +29084,7 @@
         <v>46048</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29157,7 +29157,7 @@
         <v>46048</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29230,7 +29230,7 @@
         <v>44600</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29303,7 +29303,7 @@
         <v>46049</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29376,7 +29376,7 @@
         <v>45708</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29449,7 +29449,7 @@
         <v>45357</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29522,7 +29522,7 @@
         <v>45170</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29595,7 +29595,7 @@
         <v>45170</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29668,7 +29668,7 @@
         <v>45442</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29741,7 +29741,7 @@
         <v>44587</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29814,7 +29814,7 @@
         <v>44902</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29887,7 +29887,7 @@
         <v>44926</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29960,7 +29960,7 @@
         <v>44926</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30033,7 +30033,7 @@
         <v>45420</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30106,7 +30106,7 @@
         <v>46055</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30179,7 +30179,7 @@
         <v>45743</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30252,7 +30252,7 @@
         <v>45133</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30325,7 +30325,7 @@
         <v>45803</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30398,7 +30398,7 @@
         <v>45911</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30471,7 +30471,7 @@
         <v>45911</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30544,7 +30544,7 @@
         <v>45216</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30617,7 +30617,7 @@
         <v>46062</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30690,7 +30690,7 @@
         <v>45742</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30763,7 +30763,7 @@
         <v>45561</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30836,7 +30836,7 @@
         <v>46062</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30909,7 +30909,7 @@
         <v>45492</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30982,7 +30982,7 @@
         <v>46063</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31055,7 +31055,7 @@
         <v>46063</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31128,7 +31128,7 @@
         <v>46063</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31201,7 +31201,7 @@
         <v>46063</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31274,7 +31274,7 @@
         <v>45462</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31347,7 +31347,7 @@
         <v>45922</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31420,7 +31420,7 @@
         <v>45519</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31493,7 +31493,7 @@
         <v>45616</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31566,7 +31566,7 @@
         <v>45359</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31639,7 +31639,7 @@
         <v>45691</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31712,7 +31712,7 @@
         <v>44946</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31785,7 +31785,7 @@
         <v>45033</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31858,7 +31858,7 @@
         <v>45925</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31931,7 +31931,7 @@
         <v>45022</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32004,7 +32004,7 @@
         <v>45563</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32082,7 +32082,7 @@
         <v>46077</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32155,7 +32155,7 @@
         <v>46077</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32228,7 +32228,7 @@
         <v>45706</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32301,7 +32301,7 @@
         <v>45545</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32374,7 +32374,7 @@
         <v>45925</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32447,7 +32447,7 @@
         <v>44600</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32520,7 +32520,7 @@
         <v>45663</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32593,7 +32593,7 @@
         <v>45107</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32666,7 +32666,7 @@
         <v>45678</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32739,7 +32739,7 @@
         <v>45805</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32812,7 +32812,7 @@
         <v>46084</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32885,7 +32885,7 @@
         <v>45505</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32958,7 +32958,7 @@
         <v>45931</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33031,7 +33031,7 @@
         <v>46084</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33104,7 +33104,7 @@
         <v>45434</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33177,7 +33177,7 @@
         <v>46084</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33250,7 +33250,7 @@
         <v>44715</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33323,7 +33323,7 @@
         <v>45162</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33396,7 +33396,7 @@
         <v>45222</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>44641</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33542,7 +33542,7 @@
         <v>45936</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33615,7 +33615,7 @@
         <v>46087</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33688,7 +33688,7 @@
         <v>44965</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33761,7 +33761,7 @@
         <v>45615</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33834,7 +33834,7 @@
         <v>45936</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33907,7 +33907,7 @@
         <v>46091</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33980,7 +33980,7 @@
         <v>44945</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34053,7 +34053,7 @@
         <v>46002</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34126,7 +34126,7 @@
         <v>46092</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34199,7 +34199,7 @@
         <v>44916</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34272,7 +34272,7 @@
         <v>45209</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34345,7 +34345,7 @@
         <v>45448</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34418,7 +34418,7 @@
         <v>44916</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34491,7 +34491,7 @@
         <v>44916</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34564,7 +34564,7 @@
         <v>44977</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34637,7 +34637,7 @@
         <v>45448</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34710,7 +34710,7 @@
         <v>46097</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34783,7 +34783,7 @@
         <v>44930</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34856,7 +34856,7 @@
         <v>45944</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34929,7 +34929,7 @@
         <v>46098</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35002,7 +35002,7 @@
         <v>46099</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35075,7 +35075,7 @@
         <v>45006</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35148,7 +35148,7 @@
         <v>46100</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35221,7 +35221,7 @@
         <v>45006</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35294,7 +35294,7 @@
         <v>45946</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35367,7 +35367,7 @@
         <v>45089</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35440,7 +35440,7 @@
         <v>45812</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35513,7 +35513,7 @@
         <v>45589</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35586,7 +35586,7 @@
         <v>45589</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35659,7 +35659,7 @@
         <v>45062</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35732,7 +35732,7 @@
         <v>45950</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35805,7 +35805,7 @@
         <v>45183</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35878,7 +35878,7 @@
         <v>46104</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35951,7 +35951,7 @@
         <v>46104</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36024,7 +36024,7 @@
         <v>45184</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36097,7 +36097,7 @@
         <v>45251</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36170,7 +36170,7 @@
         <v>46104</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36243,7 +36243,7 @@
         <v>46107</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36316,7 +36316,7 @@
         <v>46107</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36389,7 +36389,7 @@
         <v>44693</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36462,7 +36462,7 @@
         <v>46107</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36535,7 +36535,7 @@
         <v>45953</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36608,7 +36608,7 @@
         <v>46111</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36681,7 +36681,7 @@
         <v>46111</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36754,7 +36754,7 @@
         <v>45281</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36827,7 +36827,7 @@
         <v>45351</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36900,7 +36900,7 @@
         <v>45357</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36973,7 +36973,7 @@
         <v>46121</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37046,7 +37046,7 @@
         <v>45580</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37119,7 +37119,7 @@
         <v>44984</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37192,7 +37192,7 @@
         <v>45307</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37265,7 +37265,7 @@
         <v>46121</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37338,7 +37338,7 @@
         <v>46122</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37411,7 +37411,7 @@
         <v>45107</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37484,7 +37484,7 @@
         <v>46126</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37557,7 +37557,7 @@
         <v>45628</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37630,7 +37630,7 @@
         <v>45811</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37703,7 +37703,7 @@
         <v>45097</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37776,7 +37776,7 @@
         <v>45097</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37849,7 +37849,7 @@
         <v>45525</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37922,7 +37922,7 @@
         <v>45672</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37995,7 +37995,7 @@
         <v>45974</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38068,7 +38068,7 @@
         <v>45229</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38141,7 +38141,7 @@
         <v>46127</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38214,7 +38214,7 @@
         <v>46128</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38287,7 +38287,7 @@
         <v>46128</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38360,7 +38360,7 @@
         <v>45816</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38433,7 +38433,7 @@
         <v>46128</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38506,7 +38506,7 @@
         <v>45631</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38579,7 +38579,7 @@
         <v>46128</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38652,7 +38652,7 @@
         <v>46128</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38725,7 +38725,7 @@
         <v>45975</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38798,7 +38798,7 @@
         <v>44936</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38871,7 +38871,7 @@
         <v>46133</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38944,7 +38944,7 @@
         <v>45981</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39017,7 +39017,7 @@
         <v>45981</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39095,7 +39095,7 @@
         <v>45981</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39168,7 +39168,7 @@
         <v>46133</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39241,7 +39241,7 @@
         <v>44802</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39319,7 +39319,7 @@
         <v>45981</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39392,7 +39392,7 @@
         <v>46006</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39465,7 +39465,7 @@
         <v>45982</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39538,7 +39538,7 @@
         <v>45153</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39611,7 +39611,7 @@
         <v>45891</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39684,7 +39684,7 @@
         <v>46037</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39757,7 +39757,7 @@
         <v>45015</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39830,7 +39830,7 @@
         <v>46112</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39908,7 +39908,7 @@
         <v>45306</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39981,7 +39981,7 @@
         <v>45883</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40054,7 +40054,7 @@
         <v>45895</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40127,7 +40127,7 @@
         <v>45163</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40200,7 +40200,7 @@
         <v>45912</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40273,7 +40273,7 @@
         <v>45944</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40346,7 +40346,7 @@
         <v>45755</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40419,7 +40419,7 @@
         <v>45699</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40492,7 +40492,7 @@
         <v>45889</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40565,7 +40565,7 @@
         <v>45902</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40638,7 +40638,7 @@
         <v>45971</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40711,7 +40711,7 @@
         <v>45629</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40784,7 +40784,7 @@
         <v>45348</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40857,7 +40857,7 @@
         <v>45608</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40930,7 +40930,7 @@
         <v>45164</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41003,7 +41003,7 @@
         <v>45825</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41076,7 +41076,7 @@
         <v>45971</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41149,7 +41149,7 @@
         <v>45610</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41222,7 +41222,7 @@
         <v>44538</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41295,7 +41295,7 @@
         <v>45112</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41368,7 +41368,7 @@
         <v>45000</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41441,7 +41441,7 @@
         <v>45903</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41514,7 +41514,7 @@
         <v>45992</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41587,7 +41587,7 @@
         <v>45839</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41660,7 +41660,7 @@
         <v>46052</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41733,7 +41733,7 @@
         <v>45799</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41806,7 +41806,7 @@
         <v>45827</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41879,7 +41879,7 @@
         <v>44770</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41952,7 +41952,7 @@
         <v>45670</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42025,7 +42025,7 @@
         <v>45992</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42098,7 +42098,7 @@
         <v>45931</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42171,7 +42171,7 @@
         <v>45965</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42244,7 +42244,7 @@
         <v>45992</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42317,7 +42317,7 @@
         <v>45839</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42390,7 +42390,7 @@
         <v>45866</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42463,7 +42463,7 @@
         <v>45873</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42536,7 +42536,7 @@
         <v>45883</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42609,7 +42609,7 @@
         <v>45693</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42682,7 +42682,7 @@
         <v>45763</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42755,7 +42755,7 @@
         <v>45925</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42828,7 +42828,7 @@
         <v>45645</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42906,7 +42906,7 @@
         <v>45645</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42984,7 +42984,7 @@
         <v>44595</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43057,7 +43057,7 @@
         <v>45076</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43130,7 +43130,7 @@
         <v>45170</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43203,7 +43203,7 @@
         <v>44783</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43276,7 +43276,7 @@
         <v>44785</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43349,7 +43349,7 @@
         <v>44986</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43422,7 +43422,7 @@
         <v>45113</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43495,7 +43495,7 @@
         <v>45114</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43568,7 +43568,7 @@
         <v>45631</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43641,7 +43641,7 @@
         <v>45999</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43714,7 +43714,7 @@
         <v>45999</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43787,7 +43787,7 @@
         <v>45785</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43860,7 +43860,7 @@
         <v>46001</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43933,7 +43933,7 @@
         <v>45692</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44006,7 +44006,7 @@
         <v>45827</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44079,7 +44079,7 @@
         <v>45691</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44152,7 +44152,7 @@
         <v>44582</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44225,7 +44225,7 @@
         <v>45709</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44298,7 +44298,7 @@
         <v>44839</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44371,7 +44371,7 @@
         <v>44510</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44444,7 +44444,7 @@
         <v>45819</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44517,7 +44517,7 @@
         <v>45840</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44590,7 +44590,7 @@
         <v>46003</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44663,7 +44663,7 @@
         <v>45644</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44736,7 +44736,7 @@
         <v>44473</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44809,7 +44809,7 @@
         <v>45525</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44882,7 +44882,7 @@
         <v>45819</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44955,7 +44955,7 @@
         <v>45133</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45028,7 +45028,7 @@
         <v>46007</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45101,7 +45101,7 @@
         <v>46007</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45174,7 +45174,7 @@
         <v>45819</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45247,7 +45247,7 @@
         <v>45999</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45320,7 +45320,7 @@
         <v>45763</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45393,7 +45393,7 @@
         <v>45222</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45466,7 +45466,7 @@
         <v>45719</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45539,7 +45539,7 @@
         <v>45819</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45612,7 +45612,7 @@
         <v>46010</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45685,7 +45685,7 @@
         <v>46010</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45758,7 +45758,7 @@
         <v>46009</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45831,7 +45831,7 @@
         <v>46009</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45904,7 +45904,7 @@
         <v>45691</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45982,7 +45982,7 @@
         <v>46009</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46055,7 +46055,7 @@
         <v>44815</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46128,7 +46128,7 @@
         <v>44894</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46201,7 +46201,7 @@
         <v>45434</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46274,7 +46274,7 @@
         <v>45313</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46347,7 +46347,7 @@
         <v>45841</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46420,7 +46420,7 @@
         <v>44810</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46493,7 +46493,7 @@
         <v>45205</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46566,7 +46566,7 @@
         <v>45071</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46639,7 +46639,7 @@
         <v>45785</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46712,7 +46712,7 @@
         <v>45274</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46785,7 +46785,7 @@
         <v>45173</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46858,7 +46858,7 @@
         <v>45589</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46931,7 +46931,7 @@
         <v>46122</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47004,7 +47004,7 @@
         <v>45079</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47077,7 +47077,7 @@
         <v>44740</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47155,7 +47155,7 @@
         <v>45001</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47233,7 +47233,7 @@
         <v>45702</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47306,7 +47306,7 @@
         <v>45572</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47379,7 +47379,7 @@
         <v>45069</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47452,7 +47452,7 @@
         <v>44916</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47525,7 +47525,7 @@
         <v>45105</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47598,7 +47598,7 @@
         <v>45232</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47671,7 +47671,7 @@
         <v>44818</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47744,7 +47744,7 @@
         <v>45082</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47817,7 +47817,7 @@
         <v>45568</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47895,7 +47895,7 @@
         <v>44511</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47968,7 +47968,7 @@
         <v>45538</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48041,7 +48041,7 @@
         <v>44753</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48114,7 +48114,7 @@
         <v>46153</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48187,7 +48187,7 @@
         <v>45748</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48265,7 +48265,7 @@
         <v>45748</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48343,7 +48343,7 @@
         <v>44869</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48416,7 +48416,7 @@
         <v>46153</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48489,7 +48489,7 @@
         <v>45754</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48567,7 +48567,7 @@
         <v>46153</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48640,7 +48640,7 @@
         <v>46153</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48713,7 +48713,7 @@
         <v>46154</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48791,7 +48791,7 @@
         <v>44477</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48864,7 +48864,7 @@
         <v>45400</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48942,7 +48942,7 @@
         <v>45438</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49015,7 +49015,7 @@
         <v>45526</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49088,7 +49088,7 @@
         <v>45737</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49161,7 +49161,7 @@
         <v>45406</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49234,7 +49234,7 @@
         <v>45104</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49307,7 +49307,7 @@
         <v>44487</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49380,7 +49380,7 @@
         <v>45639</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49453,7 +49453,7 @@
         <v>46126</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49526,7 +49526,7 @@
         <v>45297</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49599,7 +49599,7 @@
         <v>45866</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49672,7 +49672,7 @@
         <v>45838</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49745,7 +49745,7 @@
         <v>45278</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49818,7 +49818,7 @@
         <v>45771</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49896,7 +49896,7 @@
         <v>45771</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49974,7 +49974,7 @@
         <v>45351</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50047,7 +50047,7 @@
         <v>46064</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50120,7 +50120,7 @@
         <v>45250</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50193,7 +50193,7 @@
         <v>45761</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50266,7 +50266,7 @@
         <v>45930</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50339,7 +50339,7 @@
         <v>46160</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50412,7 +50412,7 @@
         <v>45376</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50485,7 +50485,7 @@
         <v>45099</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50558,7 +50558,7 @@
         <v>46160</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50631,7 +50631,7 @@
         <v>46160</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50704,7 +50704,7 @@
         <v>45097</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50777,7 +50777,7 @@
         <v>46161</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50850,7 +50850,7 @@
         <v>45769</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50928,7 +50928,7 @@
         <v>45104</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51001,7 +51001,7 @@
         <v>45840</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51074,7 +51074,7 @@
         <v>45840</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51147,7 +51147,7 @@
         <v>45839</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51220,7 +51220,7 @@
         <v>45314</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51293,7 +51293,7 @@
         <v>45384</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51366,7 +51366,7 @@
         <v>46160</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51439,7 +51439,7 @@
         <v>46161</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51512,7 +51512,7 @@
         <v>44946</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51585,7 +51585,7 @@
         <v>45625</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51658,7 +51658,7 @@
         <v>45715</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51731,7 +51731,7 @@
         <v>45747</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51804,7 +51804,7 @@
         <v>45089</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51877,7 +51877,7 @@
         <v>45729</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51950,7 +51950,7 @@
         <v>45845</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52023,7 +52023,7 @@
         <v>45715</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52096,7 +52096,7 @@
         <v>45336</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52169,7 +52169,7 @@
         <v>45748</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52242,7 +52242,7 @@
         <v>45930</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52320,7 +52320,7 @@
         <v>46163</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52393,7 +52393,7 @@
         <v>45701</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52471,7 +52471,7 @@
         <v>45104</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52544,7 +52544,7 @@
         <v>45104</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52617,7 +52617,7 @@
         <v>45847</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52690,7 +52690,7 @@
         <v>45372</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52763,7 +52763,7 @@
         <v>44834</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52836,7 +52836,7 @@
         <v>45231</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52909,7 +52909,7 @@
         <v>45852</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52982,7 +52982,7 @@
         <v>45763</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53055,7 +53055,7 @@
         <v>45099</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53128,7 +53128,7 @@
         <v>45580</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53201,7 +53201,7 @@
         <v>45330</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53274,7 +53274,7 @@
         <v>45254</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53352,7 +53352,7 @@
         <v>45247</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53425,7 +53425,7 @@
         <v>45265</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53498,7 +53498,7 @@
         <v>44831</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53571,7 +53571,7 @@
         <v>44510</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53644,7 +53644,7 @@
         <v>45322</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53717,7 +53717,7 @@
         <v>45005</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53790,7 +53790,7 @@
         <v>45331</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53863,7 +53863,7 @@
         <v>45575</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53936,7 +53936,7 @@
         <v>45163</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54009,7 +54009,7 @@
         <v>44549</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54082,7 +54082,7 @@
         <v>45672</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54155,7 +54155,7 @@
         <v>44564</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54228,7 +54228,7 @@
         <v>45163</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54301,7 +54301,7 @@
         <v>45092</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54374,7 +54374,7 @@
         <v>45414</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54447,7 +54447,7 @@
         <v>45006</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54520,7 +54520,7 @@
         <v>44503</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54593,7 +54593,7 @@
         <v>45733</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54666,7 +54666,7 @@
         <v>46175</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54739,7 +54739,7 @@
         <v>45569</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54817,7 +54817,7 @@
         <v>45113</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54890,7 +54890,7 @@
         <v>45866</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54963,7 +54963,7 @@
         <v>44984</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55036,7 +55036,7 @@
         <v>44984</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55109,7 +55109,7 @@
         <v>45433</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55182,7 +55182,7 @@
         <v>44879</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55255,7 +55255,7 @@
         <v>45462</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55328,7 +55328,7 @@
         <v>44859</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55401,7 +55401,7 @@
         <v>45455</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55474,7 +55474,7 @@
         <v>45030</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55547,7 +55547,7 @@
         <v>45602</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55620,7 +55620,7 @@
         <v>45303</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55693,7 +55693,7 @@
         <v>45288</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55766,7 +55766,7 @@
         <v>44995</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55839,7 +55839,7 @@
         <v>45615</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55912,7 +55912,7 @@
         <v>45348</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55985,7 +55985,7 @@
         <v>45117</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56058,7 +56058,7 @@
         <v>45112</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56131,7 +56131,7 @@
         <v>45174</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56209,7 +56209,7 @@
         <v>46178</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56282,7 +56282,7 @@
         <v>46178</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56355,7 +56355,7 @@
         <v>46178</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56428,7 +56428,7 @@
         <v>46178</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56501,7 +56501,7 @@
         <v>45084</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56574,7 +56574,7 @@
         <v>44587</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56647,7 +56647,7 @@
         <v>46178</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56720,7 +56720,7 @@
         <v>46178</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56793,7 +56793,7 @@
         <v>45166</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56866,7 +56866,7 @@
         <v>46182</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56939,7 +56939,7 @@
         <v>45401</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57012,7 +57012,7 @@
         <v>45616</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57085,7 +57085,7 @@
         <v>46182</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57158,7 +57158,7 @@
         <v>44523</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57231,7 +57231,7 @@
         <v>45048</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57304,7 +57304,7 @@
         <v>46184</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57377,7 +57377,7 @@
         <v>46182</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57450,7 +57450,7 @@
         <v>45175</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57523,7 +57523,7 @@
         <v>46184</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57596,7 +57596,7 @@
         <v>46184</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57669,7 +57669,7 @@
         <v>46185</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57742,7 +57742,7 @@
         <v>45401</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57815,7 +57815,7 @@
         <v>45168</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57888,7 +57888,7 @@
         <v>44545</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57961,7 +57961,7 @@
         <v>45161</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58034,7 +58034,7 @@
         <v>46185</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58107,7 +58107,7 @@
         <v>45113</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58180,7 +58180,7 @@
         <v>45470</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58253,7 +58253,7 @@
         <v>45182</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58326,7 +58326,7 @@
         <v>45478</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58399,7 +58399,7 @@
         <v>45406</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58472,7 +58472,7 @@
         <v>46188</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58545,7 +58545,7 @@
         <v>45545</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58618,7 +58618,7 @@
         <v>45569</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58691,7 +58691,7 @@
         <v>45875</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58764,7 +58764,7 @@
         <v>45925</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58837,7 +58837,7 @@
         <v>46190</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58910,7 +58910,7 @@
         <v>45540</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58983,7 +58983,7 @@
         <v>45350</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59056,7 +59056,7 @@
         <v>45525</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59129,7 +59129,7 @@
         <v>45031</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59202,7 +59202,7 @@
         <v>45875</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59275,7 +59275,7 @@
         <v>46195</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59348,7 +59348,7 @@
         <v>45875</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59421,7 +59421,7 @@
         <v>45341</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59494,7 +59494,7 @@
         <v>46197</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59567,7 +59567,7 @@
         <v>45168</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59640,7 +59640,7 @@
         <v>46196</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59713,7 +59713,7 @@
         <v>46196</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59786,7 +59786,7 @@
         <v>46197</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59859,7 +59859,7 @@
         <v>45091</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59932,7 +59932,7 @@
         <v>45104</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60005,7 +60005,7 @@
         <v>45170</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60078,7 +60078,7 @@
         <v>45170</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60151,7 +60151,7 @@
         <v>44592</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60224,7 +60224,7 @@
         <v>45882</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60297,7 +60297,7 @@
         <v>45882</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60370,7 +60370,7 @@
         <v>45602</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60443,7 +60443,7 @@
         <v>45699</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60516,7 +60516,7 @@
         <v>46202</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60589,7 +60589,7 @@
         <v>44602</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60662,7 +60662,7 @@
         <v>44580</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60735,7 +60735,7 @@
         <v>44607</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60808,7 +60808,7 @@
         <v>45163</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60881,7 +60881,7 @@
         <v>45189</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60959,7 +60959,7 @@
         <v>45177</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61037,7 +61037,7 @@
         <v>45645</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61115,7 +61115,7 @@
         <v>45174</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61188,7 +61188,7 @@
         <v>45610</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61261,7 +61261,7 @@
         <v>45352</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61334,7 +61334,7 @@
         <v>46204</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61407,7 +61407,7 @@
         <v>45366</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61480,7 +61480,7 @@
         <v>45645</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61553,7 +61553,7 @@
         <v>44600</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61626,7 +61626,7 @@
         <v>45681</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61699,7 +61699,7 @@
         <v>46252</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61772,7 +61772,7 @@
         <v>45625</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61845,7 +61845,7 @@
         <v>45231</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61918,7 +61918,7 @@
         <v>45607</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61991,7 +61991,7 @@
         <v>45118</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62064,7 +62064,7 @@
         <v>45510</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62137,7 +62137,7 @@
         <v>45134</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62210,7 +62210,7 @@
         <v>46069</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62283,7 +62283,7 @@
         <v>45195</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62356,7 +62356,7 @@
         <v>45133</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62429,7 +62429,7 @@
         <v>45090</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62502,7 +62502,7 @@
         <v>46255</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62575,7 +62575,7 @@
         <v>45097</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62648,7 +62648,7 @@
         <v>45216</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62726,7 +62726,7 @@
         <v>46213</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62799,7 +62799,7 @@
         <v>45209</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62872,7 +62872,7 @@
         <v>45211</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62945,7 +62945,7 @@
         <v>46168</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63018,7 +63018,7 @@
         <v>45230</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63096,7 +63096,7 @@
         <v>45561</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63169,7 +63169,7 @@
         <v>45113</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63242,7 +63242,7 @@
         <v>44655</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63315,7 +63315,7 @@
         <v>45572</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63388,7 +63388,7 @@
         <v>45398</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63461,7 +63461,7 @@
         <v>45446</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63534,7 +63534,7 @@
         <v>46258</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63607,7 +63607,7 @@
         <v>45392</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63680,7 +63680,7 @@
         <v>44888</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63753,7 +63753,7 @@
         <v>45202</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63826,7 +63826,7 @@
         <v>45236</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63899,7 +63899,7 @@
         <v>46259</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63972,7 +63972,7 @@
         <v>45173</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64045,7 +64045,7 @@
         <v>45173</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64118,7 +64118,7 @@
         <v>46259</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64191,7 +64191,7 @@
         <v>45180</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64264,7 +64264,7 @@
         <v>45188</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64337,7 +64337,7 @@
         <v>46177</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64410,7 +64410,7 @@
         <v>44762</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64483,7 +64483,7 @@
         <v>45400</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64556,7 +64556,7 @@
         <v>45191</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64629,7 +64629,7 @@
         <v>45188</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64702,7 +64702,7 @@
         <v>45204</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64775,7 +64775,7 @@
         <v>45238</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64853,7 +64853,7 @@
         <v>45135</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64926,7 +64926,7 @@
         <v>45135</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -64999,7 +64999,7 @@
         <v>45135</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65072,7 +65072,7 @@
         <v>45259</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65145,7 +65145,7 @@
         <v>45322</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65218,7 +65218,7 @@
         <v>45135</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65291,7 +65291,7 @@
         <v>45319</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65364,7 +65364,7 @@
         <v>45245</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65437,7 +65437,7 @@
         <v>46265</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65510,7 +65510,7 @@
         <v>45754</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65588,7 +65588,7 @@
         <v>45754</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65666,7 +65666,7 @@
         <v>45307</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65739,7 +65739,7 @@
         <v>44741</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65812,7 +65812,7 @@
         <v>44813</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65885,7 +65885,7 @@
         <v>45719</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65958,7 +65958,7 @@
         <v>45671</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66031,7 +66031,7 @@
         <v>45331</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66104,7 +66104,7 @@
         <v>44970</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66177,7 +66177,7 @@
         <v>45357</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66250,7 +66250,7 @@
         <v>45309</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66323,7 +66323,7 @@
         <v>45352</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66396,7 +66396,7 @@
         <v>44830</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66469,7 +66469,7 @@
         <v>45309</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66542,7 +66542,7 @@
         <v>45309</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66615,7 +66615,7 @@
         <v>44839</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66688,7 +66688,7 @@
         <v>46268</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66761,7 +66761,7 @@
         <v>45250</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66834,7 +66834,7 @@
         <v>45314</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66907,7 +66907,7 @@
         <v>45309</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -66980,7 +66980,7 @@
         <v>44805</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67053,7 +67053,7 @@
         <v>45076</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67126,7 +67126,7 @@
         <v>46269</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67199,7 +67199,7 @@
         <v>45007</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67272,7 +67272,7 @@
         <v>44792</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67345,7 +67345,7 @@
         <v>45303</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67418,7 +67418,7 @@
         <v>45365</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67491,7 +67491,7 @@
         <v>44481</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67564,7 +67564,7 @@
         <v>45302</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67637,7 +67637,7 @@
         <v>45264</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -67710,7 +67710,7 @@
         <v>45264</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -67783,7 +67783,7 @@
         <v>46258</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67856,7 +67856,7 @@
         <v>45330</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -67929,7 +67929,7 @@
         <v>46274</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -68002,7 +68002,7 @@
         <v>45351</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -68075,7 +68075,7 @@
         <v>46273</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -68148,7 +68148,7 @@
         <v>46273</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -68221,7 +68221,7 @@
         <v>45272</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -68294,7 +68294,7 @@
         <v>46276</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68367,7 +68367,7 @@
         <v>46233</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68440,7 +68440,7 @@
         <v>46276</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68513,7 +68513,7 @@
         <v>46276</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -68586,7 +68586,7 @@
         <v>46276</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -68659,7 +68659,7 @@
         <v>46276</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -68732,7 +68732,7 @@
         <v>46279</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68805,7 +68805,7 @@
         <v>46234</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -68878,7 +68878,7 @@
         <v>45071</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -68951,7 +68951,7 @@
         <v>46237</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -69024,7 +69024,7 @@
         <v>45645</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -69097,7 +69097,7 @@
         <v>45370</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -69170,7 +69170,7 @@
         <v>45645</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -69248,7 +69248,7 @@
         <v>45259</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -69321,7 +69321,7 @@
         <v>44888</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -69394,7 +69394,7 @@
         <v>46234</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69467,7 +69467,7 @@
         <v>46234</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -69540,7 +69540,7 @@
         <v>45595</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -69613,7 +69613,7 @@
         <v>45674</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -69686,7 +69686,7 @@
         <v>45316</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -69759,7 +69759,7 @@
         <v>44971</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -69832,7 +69832,7 @@
         <v>44851</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -69905,7 +69905,7 @@
         <v>45475</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -69978,7 +69978,7 @@
         <v>46283</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -70051,7 +70051,7 @@
         <v>45953</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -70124,7 +70124,7 @@
         <v>45329</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -70197,7 +70197,7 @@
         <v>45329</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -70270,7 +70270,7 @@
         <v>44965</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -70343,7 +70343,7 @@
         <v>46240</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -70416,7 +70416,7 @@
         <v>44497</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70489,7 +70489,7 @@
         <v>44484</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -70562,7 +70562,7 @@
         <v>44916</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -70635,7 +70635,7 @@
         <v>44488</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -70708,7 +70708,7 @@
         <v>44502</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -70781,7 +70781,7 @@
         <v>44957</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -70854,7 +70854,7 @@
         <v>44967</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -70927,7 +70927,7 @@
         <v>44967</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -71000,7 +71000,7 @@
         <v>44903</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -71073,7 +71073,7 @@
         <v>45414</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -71151,7 +71151,7 @@
         <v>45414</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -71224,7 +71224,7 @@
         <v>44952</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -71297,7 +71297,7 @@
         <v>46245</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -71370,7 +71370,7 @@
         <v>44607</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -71443,7 +71443,7 @@
         <v>46244</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -71516,7 +71516,7 @@
         <v>44831</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -71589,7 +71589,7 @@
         <v>45408</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -71662,7 +71662,7 @@
         <v>46280</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -71735,7 +71735,7 @@
         <v>44880</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -71808,7 +71808,7 @@
         <v>46244</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -71881,7 +71881,7 @@
         <v>44998</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -71954,7 +71954,7 @@
         <v>44592</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -72027,7 +72027,7 @@
         <v>45302</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -72100,7 +72100,7 @@
         <v>44946</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -72173,7 +72173,7 @@
         <v>44683</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -72246,7 +72246,7 @@
         <v>46009</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -72319,7 +72319,7 @@
         <v>45440</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -72392,7 +72392,7 @@
         <v>46247</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -72470,7 +72470,7 @@
         <v>46289</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -72543,7 +72543,7 @@
         <v>46290</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -72616,7 +72616,7 @@
         <v>46178</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -72689,7 +72689,7 @@
         <v>46289</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -72762,7 +72762,7 @@
         <v>44677</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -72835,7 +72835,7 @@
         <v>45674</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -72908,7 +72908,7 @@
         <v>46247</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -72986,7 +72986,7 @@
         <v>45351</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -73059,7 +73059,7 @@
         <v>45363</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -73137,7 +73137,7 @@
         <v>45363</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -73215,7 +73215,7 @@
         <v>44917</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -73288,7 +73288,7 @@
         <v>44747</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -73361,7 +73361,7 @@
         <v>46246</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -73434,7 +73434,7 @@
         <v>45363</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -73512,7 +73512,7 @@
         <v>45363</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -73590,7 +73590,7 @@
         <v>45190</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -73663,7 +73663,7 @@
         <v>45441</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -73736,7 +73736,7 @@
         <v>46248</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -73814,7 +73814,7 @@
         <v>46178</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -73887,7 +73887,7 @@
         <v>44972</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -73960,7 +73960,7 @@
         <v>44488</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -74033,7 +74033,7 @@
         <v>44952</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -74106,7 +74106,7 @@
         <v>44984</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -74179,7 +74179,7 @@
         <v>45152</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -74252,7 +74252,7 @@
         <v>44480</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -74325,7 +74325,7 @@
         <v>44655</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -74398,7 +74398,7 @@
         <v>45055</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -74471,7 +74471,7 @@
         <v>44495</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -74544,7 +74544,7 @@
         <v>45224</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -74622,7 +74622,7 @@
         <v>45097</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -74695,7 +74695,7 @@
         <v>45069</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -74768,7 +74768,7 @@
         <v>45669</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -74841,7 +74841,7 @@
         <v>45107</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -74914,7 +74914,7 @@
         <v>44470</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -74987,7 +74987,7 @@
         <v>45219</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -75060,7 +75060,7 @@
         <v>45615</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -75133,7 +75133,7 @@
         <v>45183</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -75206,7 +75206,7 @@
         <v>45364</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -75279,7 +75279,7 @@
         <v>44963</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -75352,7 +75352,7 @@
         <v>45135</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -75425,7 +75425,7 @@
         <v>45219</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -75503,7 +75503,7 @@
         <v>44930</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -75576,7 +75576,7 @@
         <v>45282</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -75649,7 +75649,7 @@
         <v>45245</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -75722,7 +75722,7 @@
         <v>44847</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -75795,7 +75795,7 @@
         <v>45310</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -75868,7 +75868,7 @@
         <v>45763</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -75941,7 +75941,7 @@
         <v>45574</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -76019,7 +76019,7 @@
         <v>45575</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -76092,7 +76092,7 @@
         <v>45362</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -76165,7 +76165,7 @@
         <v>45251</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -76238,7 +76238,7 @@
         <v>45057</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -76311,7 +76311,7 @@
         <v>44998</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -76384,7 +76384,7 @@
         <v>44970</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -76457,7 +76457,7 @@
         <v>45164</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -76530,7 +76530,7 @@
         <v>44747</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -76603,7 +76603,7 @@
         <v>45091</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -76676,7 +76676,7 @@
         <v>45329</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -76754,7 +76754,7 @@
         <v>45406</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -76827,7 +76827,7 @@
         <v>45134</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -76900,7 +76900,7 @@
         <v>45365</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -76973,7 +76973,7 @@
         <v>45099</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -77046,7 +77046,7 @@
         <v>45462</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -77119,7 +77119,7 @@
         <v>44965</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -77192,7 +77192,7 @@
         <v>45484</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -77265,7 +77265,7 @@
         <v>45526</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -77338,7 +77338,7 @@
         <v>45303</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -77411,7 +77411,7 @@
         <v>45226</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -77484,7 +77484,7 @@
         <v>45042</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -77557,7 +77557,7 @@
         <v>45114</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -77630,7 +77630,7 @@
         <v>45327</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -77703,7 +77703,7 @@
         <v>45035</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -77776,7 +77776,7 @@
         <v>45298</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -77849,7 +77849,7 @@
         <v>45684</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -77927,7 +77927,7 @@
         <v>45660</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -78000,7 +78000,7 @@
         <v>45182</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -78078,7 +78078,7 @@
         <v>45182</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -78156,7 +78156,7 @@
         <v>45182</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -78229,7 +78229,7 @@
         <v>45188</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -78302,7 +78302,7 @@
         <v>45089</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -78375,7 +78375,7 @@
         <v>45222</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -78448,7 +78448,7 @@
         <v>45602</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -78521,7 +78521,7 @@
         <v>45335</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -78594,7 +78594,7 @@
         <v>45645</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -78667,7 +78667,7 @@
         <v>45645</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -78745,7 +78745,7 @@
         <v>45580</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -78818,7 +78818,7 @@
         <v>44710</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -78891,7 +78891,7 @@
         <v>45321</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -78964,7 +78964,7 @@
         <v>45183</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -79037,7 +79037,7 @@
         <v>44743</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -79110,7 +79110,7 @@
         <v>45132</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -79183,7 +79183,7 @@
         <v>45649</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -79261,7 +79261,7 @@
         <v>45526</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -79334,7 +79334,7 @@
         <v>45673</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -79407,7 +79407,7 @@
         <v>45701</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -79485,7 +79485,7 @@
         <v>44970</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -79558,7 +79558,7 @@
         <v>45359</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -79631,7 +79631,7 @@
         <v>45625</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -79704,7 +79704,7 @@
         <v>45544</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -79777,7 +79777,7 @@
         <v>44970</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -79850,7 +79850,7 @@
         <v>45674</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -79923,7 +79923,7 @@
         <v>45385</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -79996,7 +79996,7 @@
         <v>45188</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -80069,7 +80069,7 @@
         <v>45314</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -80142,7 +80142,7 @@
         <v>45645</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -80220,7 +80220,7 @@
         <v>45645</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -80298,7 +80298,7 @@
         <v>45228</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -80371,7 +80371,7 @@
         <v>45329</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -80444,7 +80444,7 @@
         <v>45737</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
@@ -80517,7 +80517,7 @@
         <v>45737</v>
       </c>
       <c r="E1032" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
@@ -80590,7 +80590,7 @@
         <v>45376</v>
       </c>
       <c r="E1033" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
@@ -80663,7 +80663,7 @@
         <v>45702</v>
       </c>
       <c r="E1034" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
@@ -80741,7 +80741,7 @@
         <v>45315</v>
       </c>
       <c r="E1035" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
@@ -80814,7 +80814,7 @@
         <v>44949</v>
       </c>
       <c r="E1036" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
@@ -80887,7 +80887,7 @@
         <v>45230</v>
       </c>
       <c r="E1037" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
@@ -80965,7 +80965,7 @@
         <v>45595</v>
       </c>
       <c r="E1038" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1038" t="inlineStr">
         <is>
@@ -81038,7 +81038,7 @@
         <v>45670</v>
       </c>
       <c r="E1039" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1039" t="inlineStr">
         <is>
@@ -81111,7 +81111,7 @@
         <v>45274</v>
       </c>
       <c r="E1040" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1040" t="inlineStr">
         <is>
@@ -81184,7 +81184,7 @@
         <v>44781</v>
       </c>
       <c r="E1041" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1041" t="inlineStr">
         <is>
@@ -81257,7 +81257,7 @@
         <v>45439</v>
       </c>
       <c r="E1042" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1042" t="inlineStr">
         <is>
@@ -81330,7 +81330,7 @@
         <v>45348</v>
       </c>
       <c r="E1043" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1043" t="inlineStr">
         <is>
@@ -81403,7 +81403,7 @@
         <v>45783</v>
       </c>
       <c r="E1044" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1044" t="inlineStr">
         <is>
@@ -81476,7 +81476,7 @@
         <v>45783</v>
       </c>
       <c r="E1045" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1045" t="inlineStr">
         <is>
@@ -81549,7 +81549,7 @@
         <v>45716</v>
       </c>
       <c r="E1046" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1046" t="inlineStr">
         <is>
@@ -81622,7 +81622,7 @@
         <v>45456</v>
       </c>
       <c r="E1047" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1047" t="inlineStr">
         <is>
@@ -81695,7 +81695,7 @@
         <v>44592</v>
       </c>
       <c r="E1048" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1048" t="inlineStr">
         <is>
@@ -81768,7 +81768,7 @@
         <v>45439</v>
       </c>
       <c r="E1049" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1049" t="inlineStr">
         <is>
@@ -81841,7 +81841,7 @@
         <v>45786</v>
       </c>
       <c r="E1050" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1050" t="inlineStr">
         <is>
@@ -81914,7 +81914,7 @@
         <v>45601</v>
       </c>
       <c r="E1051" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1051" t="inlineStr">
         <is>
@@ -81987,7 +81987,7 @@
         <v>45792</v>
       </c>
       <c r="E1052" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1052" t="inlineStr">
         <is>
@@ -82060,7 +82060,7 @@
         <v>45636</v>
       </c>
       <c r="E1053" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1053" t="inlineStr">
         <is>
@@ -82133,7 +82133,7 @@
         <v>45580</v>
       </c>
       <c r="E1054" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1054" t="inlineStr">
         <is>
@@ -82206,7 +82206,7 @@
         <v>45447</v>
       </c>
       <c r="E1055" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1055" t="inlineStr">
         <is>
@@ -82279,7 +82279,7 @@
         <v>45170</v>
       </c>
       <c r="E1056" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1056" t="inlineStr">
         <is>
@@ -82352,7 +82352,7 @@
         <v>45106</v>
       </c>
       <c r="E1057" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1057" t="inlineStr">
         <is>
@@ -82425,7 +82425,7 @@
         <v>45467</v>
       </c>
       <c r="E1058" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1058" t="inlineStr">
         <is>
@@ -82498,7 +82498,7 @@
         <v>44509</v>
       </c>
       <c r="E1059" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1059" t="inlineStr">
         <is>
@@ -82576,7 +82576,7 @@
         <v>45664</v>
       </c>
       <c r="E1060" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1060" t="inlineStr">
         <is>
@@ -82649,7 +82649,7 @@
         <v>45208</v>
       </c>
       <c r="E1061" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1061" t="inlineStr">
         <is>
@@ -82722,7 +82722,7 @@
         <v>45406</v>
       </c>
       <c r="E1062" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1062" t="inlineStr">
         <is>
@@ -82795,7 +82795,7 @@
         <v>45497</v>
       </c>
       <c r="E1063" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1063" t="inlineStr">
         <is>
@@ -82868,7 +82868,7 @@
         <v>45497</v>
       </c>
       <c r="E1064" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1064" t="inlineStr">
         <is>
@@ -82941,7 +82941,7 @@
         <v>45106</v>
       </c>
       <c r="E1065" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1065" t="inlineStr">
         <is>
@@ -83014,7 +83014,7 @@
         <v>45646</v>
       </c>
       <c r="E1066" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1066" t="inlineStr">
         <is>
@@ -83087,7 +83087,7 @@
         <v>45646</v>
       </c>
       <c r="E1067" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1067" t="inlineStr">
         <is>
@@ -83160,7 +83160,7 @@
         <v>45580</v>
       </c>
       <c r="E1068" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1068" t="inlineStr">
         <is>
@@ -83233,7 +83233,7 @@
         <v>45646</v>
       </c>
       <c r="E1069" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1069" t="inlineStr">
         <is>
@@ -83306,7 +83306,7 @@
         <v>45646</v>
       </c>
       <c r="E1070" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1070" t="inlineStr">
         <is>
@@ -83379,7 +83379,7 @@
         <v>45408</v>
       </c>
       <c r="E1071" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1071" t="inlineStr">
         <is>
@@ -83452,7 +83452,7 @@
         <v>45414</v>
       </c>
       <c r="E1072" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1072" t="inlineStr">
         <is>
@@ -83525,7 +83525,7 @@
         <v>45173</v>
       </c>
       <c r="E1073" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1073" t="inlineStr">
         <is>
@@ -83598,7 +83598,7 @@
         <v>45646</v>
       </c>
       <c r="E1074" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1074" t="inlineStr">
         <is>
@@ -83671,7 +83671,7 @@
         <v>45715</v>
       </c>
       <c r="E1075" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1075" t="inlineStr">
         <is>
@@ -83744,7 +83744,7 @@
         <v>45720</v>
       </c>
       <c r="E1076" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1076" t="inlineStr">
         <is>
@@ -83817,7 +83817,7 @@
         <v>45800</v>
       </c>
       <c r="E1077" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1077" t="inlineStr">
         <is>
@@ -83895,7 +83895,7 @@
         <v>45831</v>
       </c>
       <c r="E1078" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1078" t="inlineStr">
         <is>
@@ -83968,7 +83968,7 @@
         <v>45785</v>
       </c>
       <c r="E1079" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1079" t="inlineStr">
         <is>
@@ -84041,7 +84041,7 @@
         <v>46073</v>
       </c>
       <c r="E1080" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1080" t="inlineStr">
         <is>
@@ -84114,7 +84114,7 @@
         <v>46163</v>
       </c>
       <c r="E1081" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1081" t="inlineStr">
         <is>
@@ -84187,7 +84187,7 @@
         <v>46274</v>
       </c>
       <c r="E1082" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1082" t="inlineStr">
         <is>

--- a/Översikt VETLANDA.xlsx
+++ b/Översikt VETLANDA.xlsx
@@ -601,7 +601,7 @@
         <v>45097</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>46178</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         <v>45371</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>44890</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>44817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>45183</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>45558</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>45168</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>46107</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>45930</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>45957</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>45520</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>45754</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>45170</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>44612</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>46002</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>46100</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>44908</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>44840</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>45203</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>45819</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>46163</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>46188</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>44545</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>44564</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>45763</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>45477</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>46045</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>45599</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         <v>45048</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>44819</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         <v>45814</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>45583</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>45646</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4450,7 +4450,7 @@
         <v>45131</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>44515</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>44470</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>44752</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>44643</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>45400</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         <v>45310</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5221,7 +5221,7 @@
         <v>45035</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>45357</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5433,7 +5433,7 @@
         <v>44572</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
         <v>45589</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         <v>44468</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5751,7 +5751,7 @@
         <v>45965</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>45891</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         <v>45792</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>45835</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6179,7 +6179,7 @@
         <v>45840</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         <v>45148</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>45713</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         <v>46166</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6607,7 +6607,7 @@
         <v>45860</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6713,7 +6713,7 @@
         <v>45303</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         <v>46279</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         <v>45713</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>45211</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         <v>45673</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         <v>45616</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7354,7 +7354,7 @@
         <v>45106</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>45509</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7566,7 +7566,7 @@
         <v>45497</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7672,7 +7672,7 @@
         <v>45201</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>45539</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7884,7 +7884,7 @@
         <v>46051</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7994,7 +7994,7 @@
         <v>44834</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>44721</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
         <v>44747</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         <v>44592</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>44740</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8524,7 +8524,7 @@
         <v>44824</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         <v>45378</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8734,7 +8734,7 @@
         <v>45342</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>45119</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8944,7 +8944,7 @@
         <v>44833</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9049,7 +9049,7 @@
         <v>45835</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9154,7 +9154,7 @@
         <v>45672</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         <v>45736</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
         <v>45904</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9477,7 +9477,7 @@
         <v>45645</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>45021</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9687,7 +9687,7 @@
         <v>46069</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9792,7 +9792,7 @@
         <v>46071</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         <v>45586</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
         <v>45085</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10107,7 +10107,7 @@
         <v>44781</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         <v>44816</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10317,7 +10317,7 @@
         <v>45880</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10422,7 +10422,7 @@
         <v>45775</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         <v>45820</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10637,7 +10637,7 @@
         <v>46141</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         <v>45009</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10851,7 +10851,7 @@
         <v>45839</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         <v>45240</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>45419</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11166,7 +11166,7 @@
         <v>44880</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11271,7 +11271,7 @@
         <v>46188</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>45565</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11481,7 +11481,7 @@
         <v>45586</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11586,7 +11586,7 @@
         <v>45596</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11691,7 +11691,7 @@
         <v>45597</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11796,7 +11796,7 @@
         <v>45555</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11901,7 +11901,7 @@
         <v>45408</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12006,7 +12006,7 @@
         <v>45930</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>45261</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12225,7 +12225,7 @@
         <v>44748</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12330,7 +12330,7 @@
         <v>44830</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>44916</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12540,7 +12540,7 @@
         <v>46248</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12645,7 +12645,7 @@
         <v>45239</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12755,7 +12755,7 @@
         <v>45104</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12864,7 +12864,7 @@
         <v>44728</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12973,7 +12973,7 @@
         <v>44819</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13078,7 +13078,7 @@
         <v>45337</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13183,7 +13183,7 @@
         <v>45532</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13288,7 +13288,7 @@
         <v>44998</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13393,7 +13393,7 @@
         <v>45643</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13498,7 +13498,7 @@
         <v>45352</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13603,7 +13603,7 @@
         <v>45791</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13708,7 +13708,7 @@
         <v>45604</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13813,7 +13813,7 @@
         <v>45497</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13918,7 +13918,7 @@
         <v>45614</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14023,7 +14023,7 @@
         <v>45742</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14132,7 +14132,7 @@
         <v>44490</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14205,7 +14205,7 @@
         <v>44858</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
         <v>44781</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14351,7 +14351,7 @@
         <v>44838</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14424,7 +14424,7 @@
         <v>44781</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14497,7 +14497,7 @@
         <v>44732</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14570,7 +14570,7 @@
         <v>44515</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14643,7 +14643,7 @@
         <v>44508</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14716,7 +14716,7 @@
         <v>44504</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14789,7 +14789,7 @@
         <v>44496</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14862,7 +14862,7 @@
         <v>44579</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14935,7 +14935,7 @@
         <v>44601</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>44889</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
         <v>44544</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15154,7 +15154,7 @@
         <v>44510</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15227,7 +15227,7 @@
         <v>44468</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15300,7 +15300,7 @@
         <v>44517</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15373,7 +15373,7 @@
         <v>44764</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15446,7 +15446,7 @@
         <v>44510</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15519,7 +15519,7 @@
         <v>44503</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15592,7 +15592,7 @@
         <v>44819</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
         <v>44592</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15738,7 +15738,7 @@
         <v>44750</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15811,7 +15811,7 @@
         <v>44825</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15884,7 +15884,7 @@
         <v>44488</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15957,7 +15957,7 @@
         <v>44602</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16030,7 +16030,7 @@
         <v>44638</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16103,7 +16103,7 @@
         <v>44721</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16176,7 +16176,7 @@
         <v>44510</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16249,7 +16249,7 @@
         <v>44785</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16322,7 +16322,7 @@
         <v>44592</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16395,7 +16395,7 @@
         <v>44587</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>44782</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16541,7 +16541,7 @@
         <v>44815</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16614,7 +16614,7 @@
         <v>44504</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16687,7 +16687,7 @@
         <v>44580</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16760,7 +16760,7 @@
         <v>44691</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16833,7 +16833,7 @@
         <v>44880</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16906,7 +16906,7 @@
         <v>44545</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16979,7 +16979,7 @@
         <v>44750</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17052,7 +17052,7 @@
         <v>44624</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17125,7 +17125,7 @@
         <v>44595</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17198,7 +17198,7 @@
         <v>44477</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17271,7 +17271,7 @@
         <v>44608</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>44820</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>44816</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17490,7 +17490,7 @@
         <v>44819</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17563,7 +17563,7 @@
         <v>44645</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17636,7 +17636,7 @@
         <v>44656</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17709,7 +17709,7 @@
         <v>44784</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17782,7 +17782,7 @@
         <v>44585</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17860,7 +17860,7 @@
         <v>44585</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17938,7 +17938,7 @@
         <v>44585</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18016,7 +18016,7 @@
         <v>44834</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18089,7 +18089,7 @@
         <v>44740</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18167,7 +18167,7 @@
         <v>44750</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>44587</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18313,7 +18313,7 @@
         <v>44743</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18386,7 +18386,7 @@
         <v>44474</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18459,7 +18459,7 @@
         <v>44600</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
         <v>44859</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18605,7 +18605,7 @@
         <v>44593</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18678,7 +18678,7 @@
         <v>44743</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18751,7 +18751,7 @@
         <v>44778</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18824,7 +18824,7 @@
         <v>44504</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18897,7 +18897,7 @@
         <v>44834</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18970,7 +18970,7 @@
         <v>44477</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19043,7 +19043,7 @@
         <v>44482</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19116,7 +19116,7 @@
         <v>44509</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19189,7 +19189,7 @@
         <v>44592</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19262,7 +19262,7 @@
         <v>44517</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19335,7 +19335,7 @@
         <v>44721</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>44572</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19481,7 +19481,7 @@
         <v>44841</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19554,7 +19554,7 @@
         <v>44888</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19627,7 +19627,7 @@
         <v>44587</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>44655</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19773,7 +19773,7 @@
         <v>44502</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>44515</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19924,7 +19924,7 @@
         <v>44592</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19997,7 +19997,7 @@
         <v>44564</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20070,7 +20070,7 @@
         <v>44781</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>44531</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20216,7 +20216,7 @@
         <v>44636</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20289,7 +20289,7 @@
         <v>44834</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20362,7 +20362,7 @@
         <v>44733</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20435,7 +20435,7 @@
         <v>44683</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20508,7 +20508,7 @@
         <v>44602</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20581,7 +20581,7 @@
         <v>44792</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20654,7 +20654,7 @@
         <v>44657</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20727,7 +20727,7 @@
         <v>44827</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20800,7 +20800,7 @@
         <v>45329</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20873,7 +20873,7 @@
         <v>45323</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20946,7 +20946,7 @@
         <v>45267</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21019,7 +21019,7 @@
         <v>45335</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21092,7 +21092,7 @@
         <v>44834</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
         <v>44825</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21238,7 +21238,7 @@
         <v>45272</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>45329</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21384,7 +21384,7 @@
         <v>45202</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21457,7 +21457,7 @@
         <v>45401</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21530,7 +21530,7 @@
         <v>45300</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>45345</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21676,7 +21676,7 @@
         <v>45364</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21749,7 +21749,7 @@
         <v>45091</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21822,7 +21822,7 @@
         <v>45414</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21900,7 +21900,7 @@
         <v>44815</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21973,7 +21973,7 @@
         <v>45211</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22046,7 +22046,7 @@
         <v>45097</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22119,7 +22119,7 @@
         <v>45384</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22192,7 +22192,7 @@
         <v>44929</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22265,7 +22265,7 @@
         <v>45107</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22338,7 +22338,7 @@
         <v>45296</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22411,7 +22411,7 @@
         <v>45240</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22484,7 +22484,7 @@
         <v>44902</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22557,7 +22557,7 @@
         <v>44530</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22630,7 +22630,7 @@
         <v>45370</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22703,7 +22703,7 @@
         <v>44813</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22776,7 +22776,7 @@
         <v>45532</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22849,7 +22849,7 @@
         <v>45119</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22922,7 +22922,7 @@
         <v>45394</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22995,7 +22995,7 @@
         <v>45461</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23068,7 +23068,7 @@
         <v>45440</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23141,7 +23141,7 @@
         <v>45439</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23214,7 +23214,7 @@
         <v>44880</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23287,7 +23287,7 @@
         <v>44880</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23360,7 +23360,7 @@
         <v>45309</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23433,7 +23433,7 @@
         <v>44837</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23506,7 +23506,7 @@
         <v>45363</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23584,7 +23584,7 @@
         <v>44482</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23657,7 +23657,7 @@
         <v>45763</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23730,7 +23730,7 @@
         <v>45763</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23803,7 +23803,7 @@
         <v>45763</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23876,7 +23876,7 @@
         <v>45884</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23949,7 +23949,7 @@
         <v>45201</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24022,7 +24022,7 @@
         <v>45827</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24095,7 +24095,7 @@
         <v>45443</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24168,7 +24168,7 @@
         <v>45435</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24241,7 +24241,7 @@
         <v>44837</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24314,7 +24314,7 @@
         <v>45449</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24387,7 +24387,7 @@
         <v>46003</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24460,7 +24460,7 @@
         <v>45446</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24533,7 +24533,7 @@
         <v>45330</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24606,7 +24606,7 @@
         <v>46030</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24679,7 +24679,7 @@
         <v>46030</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24752,7 +24752,7 @@
         <v>45884</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24825,7 +24825,7 @@
         <v>45497</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24898,7 +24898,7 @@
         <v>45497</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24971,7 +24971,7 @@
         <v>45743</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25044,7 +25044,7 @@
         <v>45733</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25117,7 +25117,7 @@
         <v>45733</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25190,7 +25190,7 @@
         <v>45737</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25263,7 +25263,7 @@
         <v>45737</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25336,7 +25336,7 @@
         <v>45544</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25409,7 +25409,7 @@
         <v>45546</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25482,7 +25482,7 @@
         <v>45742</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25555,7 +25555,7 @@
         <v>45728</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25628,7 +25628,7 @@
         <v>45741</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25706,7 +25706,7 @@
         <v>45741</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25784,7 +25784,7 @@
         <v>46029</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25857,7 +25857,7 @@
         <v>46031</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25930,7 +25930,7 @@
         <v>46031</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26003,7 +26003,7 @@
         <v>44481</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26076,7 +26076,7 @@
         <v>44858</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26149,7 +26149,7 @@
         <v>45826</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26222,7 +26222,7 @@
         <v>44515</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26300,7 +26300,7 @@
         <v>45888</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26373,7 +26373,7 @@
         <v>45742</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26446,7 +26446,7 @@
         <v>45888</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26519,7 +26519,7 @@
         <v>46031</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26592,7 +26592,7 @@
         <v>45786</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26665,7 +26665,7 @@
         <v>45742</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26738,7 +26738,7 @@
         <v>45888</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26811,7 +26811,7 @@
         <v>45839</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26884,7 +26884,7 @@
         <v>44564</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26962,7 +26962,7 @@
         <v>45541</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27035,7 +27035,7 @@
         <v>45888</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27108,7 +27108,7 @@
         <v>45888</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27181,7 +27181,7 @@
         <v>45888</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27254,7 +27254,7 @@
         <v>45341</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27327,7 +27327,7 @@
         <v>45889</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27400,7 +27400,7 @@
         <v>45677</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27473,7 +27473,7 @@
         <v>45889</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27546,7 +27546,7 @@
         <v>45889</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27619,7 +27619,7 @@
         <v>45259</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27692,7 +27692,7 @@
         <v>44531</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27765,7 +27765,7 @@
         <v>45610</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27838,7 +27838,7 @@
         <v>45770</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27911,7 +27911,7 @@
         <v>45839</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27984,7 +27984,7 @@
         <v>45623</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28057,7 +28057,7 @@
         <v>45898</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28130,7 +28130,7 @@
         <v>44602</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28203,7 +28203,7 @@
         <v>45538</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28276,7 +28276,7 @@
         <v>46044</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28349,7 +28349,7 @@
         <v>44592</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28422,7 +28422,7 @@
         <v>45106</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28495,7 +28495,7 @@
         <v>46048</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28568,7 +28568,7 @@
         <v>46048</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28641,7 +28641,7 @@
         <v>45902</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28714,7 +28714,7 @@
         <v>45581</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28792,7 +28792,7 @@
         <v>45819</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28865,7 +28865,7 @@
         <v>45737</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28938,7 +28938,7 @@
         <v>46045</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29011,7 +29011,7 @@
         <v>45587</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29084,7 +29084,7 @@
         <v>46048</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29157,7 +29157,7 @@
         <v>46048</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29230,7 +29230,7 @@
         <v>44600</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29303,7 +29303,7 @@
         <v>46049</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29376,7 +29376,7 @@
         <v>45708</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29449,7 +29449,7 @@
         <v>45357</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29522,7 +29522,7 @@
         <v>45170</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29595,7 +29595,7 @@
         <v>45170</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29668,7 +29668,7 @@
         <v>45442</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29741,7 +29741,7 @@
         <v>44587</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29814,7 +29814,7 @@
         <v>44902</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29887,7 +29887,7 @@
         <v>44926</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29960,7 +29960,7 @@
         <v>44926</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30033,7 +30033,7 @@
         <v>45420</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30106,7 +30106,7 @@
         <v>46055</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30179,7 +30179,7 @@
         <v>45743</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30252,7 +30252,7 @@
         <v>45133</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30325,7 +30325,7 @@
         <v>45803</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30398,7 +30398,7 @@
         <v>45911</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30471,7 +30471,7 @@
         <v>45911</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30544,7 +30544,7 @@
         <v>45216</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30617,7 +30617,7 @@
         <v>46062</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30690,7 +30690,7 @@
         <v>45742</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30763,7 +30763,7 @@
         <v>45561</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30836,7 +30836,7 @@
         <v>46062</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30909,7 +30909,7 @@
         <v>45492</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30982,7 +30982,7 @@
         <v>46063</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31055,7 +31055,7 @@
         <v>46063</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31128,7 +31128,7 @@
         <v>46063</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31201,7 +31201,7 @@
         <v>46063</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31274,7 +31274,7 @@
         <v>45462</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31347,7 +31347,7 @@
         <v>45922</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31420,7 +31420,7 @@
         <v>45519</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31493,7 +31493,7 @@
         <v>45616</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31566,7 +31566,7 @@
         <v>45359</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31639,7 +31639,7 @@
         <v>45691</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31712,7 +31712,7 @@
         <v>44946</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31785,7 +31785,7 @@
         <v>45033</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31858,7 +31858,7 @@
         <v>45925</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31931,7 +31931,7 @@
         <v>45022</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32004,7 +32004,7 @@
         <v>45563</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32082,7 +32082,7 @@
         <v>46077</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32155,7 +32155,7 @@
         <v>46077</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32228,7 +32228,7 @@
         <v>45706</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32301,7 +32301,7 @@
         <v>45545</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32374,7 +32374,7 @@
         <v>45925</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32447,7 +32447,7 @@
         <v>44600</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32520,7 +32520,7 @@
         <v>45663</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32593,7 +32593,7 @@
         <v>45107</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32666,7 +32666,7 @@
         <v>45678</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32739,7 +32739,7 @@
         <v>45805</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32812,7 +32812,7 @@
         <v>46084</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32885,7 +32885,7 @@
         <v>45505</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32958,7 +32958,7 @@
         <v>45931</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33031,7 +33031,7 @@
         <v>46084</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33104,7 +33104,7 @@
         <v>45434</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33177,7 +33177,7 @@
         <v>46084</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33250,7 +33250,7 @@
         <v>44715</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33323,7 +33323,7 @@
         <v>45162</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33396,7 +33396,7 @@
         <v>45222</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>44641</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33542,7 +33542,7 @@
         <v>45936</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33615,7 +33615,7 @@
         <v>46087</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33688,7 +33688,7 @@
         <v>44965</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33761,7 +33761,7 @@
         <v>45615</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33834,7 +33834,7 @@
         <v>45936</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33907,7 +33907,7 @@
         <v>46091</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33980,7 +33980,7 @@
         <v>44945</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34053,7 +34053,7 @@
         <v>46002</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34126,7 +34126,7 @@
         <v>46092</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34199,7 +34199,7 @@
         <v>44916</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34272,7 +34272,7 @@
         <v>45209</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34345,7 +34345,7 @@
         <v>45448</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34418,7 +34418,7 @@
         <v>44916</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34491,7 +34491,7 @@
         <v>44916</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34564,7 +34564,7 @@
         <v>44977</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34637,7 +34637,7 @@
         <v>45448</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34710,7 +34710,7 @@
         <v>46097</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34783,7 +34783,7 @@
         <v>44930</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34856,7 +34856,7 @@
         <v>45944</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34929,7 +34929,7 @@
         <v>46098</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35002,7 +35002,7 @@
         <v>46099</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35075,7 +35075,7 @@
         <v>45006</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35148,7 +35148,7 @@
         <v>46100</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35221,7 +35221,7 @@
         <v>45006</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35294,7 +35294,7 @@
         <v>45946</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35367,7 +35367,7 @@
         <v>45089</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35440,7 +35440,7 @@
         <v>45812</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35513,7 +35513,7 @@
         <v>45589</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35586,7 +35586,7 @@
         <v>45589</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35659,7 +35659,7 @@
         <v>45062</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35732,7 +35732,7 @@
         <v>45950</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35805,7 +35805,7 @@
         <v>45183</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35878,7 +35878,7 @@
         <v>46104</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35951,7 +35951,7 @@
         <v>46104</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36024,7 +36024,7 @@
         <v>45184</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36097,7 +36097,7 @@
         <v>45251</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36170,7 +36170,7 @@
         <v>46104</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36243,7 +36243,7 @@
         <v>46107</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36316,7 +36316,7 @@
         <v>46107</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36389,7 +36389,7 @@
         <v>44693</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36462,7 +36462,7 @@
         <v>46107</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36535,7 +36535,7 @@
         <v>45953</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36608,7 +36608,7 @@
         <v>46111</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36681,7 +36681,7 @@
         <v>46111</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36754,7 +36754,7 @@
         <v>45281</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36827,7 +36827,7 @@
         <v>45351</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36900,7 +36900,7 @@
         <v>45357</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36973,7 +36973,7 @@
         <v>46121</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37046,7 +37046,7 @@
         <v>45580</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37119,7 +37119,7 @@
         <v>44984</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37192,7 +37192,7 @@
         <v>45307</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37265,7 +37265,7 @@
         <v>46121</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37338,7 +37338,7 @@
         <v>46122</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37411,7 +37411,7 @@
         <v>45107</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37484,7 +37484,7 @@
         <v>46126</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37557,7 +37557,7 @@
         <v>45628</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37630,7 +37630,7 @@
         <v>45811</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37703,7 +37703,7 @@
         <v>45097</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37776,7 +37776,7 @@
         <v>45097</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37849,7 +37849,7 @@
         <v>45525</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37922,7 +37922,7 @@
         <v>45672</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37995,7 +37995,7 @@
         <v>45974</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38068,7 +38068,7 @@
         <v>45229</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38141,7 +38141,7 @@
         <v>46127</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38214,7 +38214,7 @@
         <v>46128</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38287,7 +38287,7 @@
         <v>46128</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38360,7 +38360,7 @@
         <v>45816</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38433,7 +38433,7 @@
         <v>46128</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38506,7 +38506,7 @@
         <v>45631</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38579,7 +38579,7 @@
         <v>46128</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38652,7 +38652,7 @@
         <v>46128</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38725,7 +38725,7 @@
         <v>45975</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38798,7 +38798,7 @@
         <v>44936</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38871,7 +38871,7 @@
         <v>46133</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38944,7 +38944,7 @@
         <v>45981</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39017,7 +39017,7 @@
         <v>45981</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39095,7 +39095,7 @@
         <v>45981</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39168,7 +39168,7 @@
         <v>46133</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39241,7 +39241,7 @@
         <v>44802</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39319,7 +39319,7 @@
         <v>45981</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39392,7 +39392,7 @@
         <v>46006</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39465,7 +39465,7 @@
         <v>45982</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39538,7 +39538,7 @@
         <v>45153</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39611,7 +39611,7 @@
         <v>45891</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39684,7 +39684,7 @@
         <v>46037</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39757,7 +39757,7 @@
         <v>45015</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39830,7 +39830,7 @@
         <v>46112</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39908,7 +39908,7 @@
         <v>45306</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39981,7 +39981,7 @@
         <v>45883</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40054,7 +40054,7 @@
         <v>45895</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40127,7 +40127,7 @@
         <v>45163</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40200,7 +40200,7 @@
         <v>45912</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40273,7 +40273,7 @@
         <v>45944</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40346,7 +40346,7 @@
         <v>45755</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40419,7 +40419,7 @@
         <v>45699</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40492,7 +40492,7 @@
         <v>45889</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40565,7 +40565,7 @@
         <v>45902</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40638,7 +40638,7 @@
         <v>45971</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40711,7 +40711,7 @@
         <v>45629</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40784,7 +40784,7 @@
         <v>45348</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40857,7 +40857,7 @@
         <v>45608</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40930,7 +40930,7 @@
         <v>45164</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41003,7 +41003,7 @@
         <v>45825</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41076,7 +41076,7 @@
         <v>45971</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41149,7 +41149,7 @@
         <v>45610</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41222,7 +41222,7 @@
         <v>44538</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41295,7 +41295,7 @@
         <v>45112</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41368,7 +41368,7 @@
         <v>45000</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41441,7 +41441,7 @@
         <v>45903</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41514,7 +41514,7 @@
         <v>45992</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41587,7 +41587,7 @@
         <v>45839</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41660,7 +41660,7 @@
         <v>46052</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41733,7 +41733,7 @@
         <v>45799</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41806,7 +41806,7 @@
         <v>45827</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41879,7 +41879,7 @@
         <v>44770</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41952,7 +41952,7 @@
         <v>45670</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42025,7 +42025,7 @@
         <v>45992</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42098,7 +42098,7 @@
         <v>45931</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42171,7 +42171,7 @@
         <v>45965</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42244,7 +42244,7 @@
         <v>45992</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42317,7 +42317,7 @@
         <v>45839</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42390,7 +42390,7 @@
         <v>45866</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42463,7 +42463,7 @@
         <v>45873</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42536,7 +42536,7 @@
         <v>45883</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42609,7 +42609,7 @@
         <v>45693</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42682,7 +42682,7 @@
         <v>45763</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42755,7 +42755,7 @@
         <v>45925</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42828,7 +42828,7 @@
         <v>45645</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42906,7 +42906,7 @@
         <v>45645</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42984,7 +42984,7 @@
         <v>44595</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43057,7 +43057,7 @@
         <v>45076</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43130,7 +43130,7 @@
         <v>45170</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43203,7 +43203,7 @@
         <v>44783</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43276,7 +43276,7 @@
         <v>44785</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43349,7 +43349,7 @@
         <v>44986</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43422,7 +43422,7 @@
         <v>45113</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43495,7 +43495,7 @@
         <v>45114</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43568,7 +43568,7 @@
         <v>45631</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43641,7 +43641,7 @@
         <v>45999</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43714,7 +43714,7 @@
         <v>45999</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43787,7 +43787,7 @@
         <v>45785</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43860,7 +43860,7 @@
         <v>46001</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43933,7 +43933,7 @@
         <v>45692</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44006,7 +44006,7 @@
         <v>45827</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44079,7 +44079,7 @@
         <v>45691</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44152,7 +44152,7 @@
         <v>44582</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44225,7 +44225,7 @@
         <v>45709</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44298,7 +44298,7 @@
         <v>44839</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44371,7 +44371,7 @@
         <v>44510</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44444,7 +44444,7 @@
         <v>45819</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44517,7 +44517,7 @@
         <v>45840</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44590,7 +44590,7 @@
         <v>46003</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44663,7 +44663,7 @@
         <v>45644</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44736,7 +44736,7 @@
         <v>44473</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44809,7 +44809,7 @@
         <v>45525</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44882,7 +44882,7 @@
         <v>45819</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44955,7 +44955,7 @@
         <v>45133</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45028,7 +45028,7 @@
         <v>46007</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45101,7 +45101,7 @@
         <v>46007</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45174,7 +45174,7 @@
         <v>45819</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45247,7 +45247,7 @@
         <v>45999</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45320,7 +45320,7 @@
         <v>45763</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45393,7 +45393,7 @@
         <v>45222</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45466,7 +45466,7 @@
         <v>45719</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45539,7 +45539,7 @@
         <v>45819</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45612,7 +45612,7 @@
         <v>46010</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45685,7 +45685,7 @@
         <v>46010</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45758,7 +45758,7 @@
         <v>46009</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45831,7 +45831,7 @@
         <v>46009</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45904,7 +45904,7 @@
         <v>45691</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45982,7 +45982,7 @@
         <v>46009</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46055,7 +46055,7 @@
         <v>44815</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46128,7 +46128,7 @@
         <v>44894</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46201,7 +46201,7 @@
         <v>45434</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46274,7 +46274,7 @@
         <v>45313</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46347,7 +46347,7 @@
         <v>45841</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46420,7 +46420,7 @@
         <v>44810</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46493,7 +46493,7 @@
         <v>45205</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46566,7 +46566,7 @@
         <v>45071</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46639,7 +46639,7 @@
         <v>45785</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46712,7 +46712,7 @@
         <v>45274</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46785,7 +46785,7 @@
         <v>45173</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46858,7 +46858,7 @@
         <v>45589</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46931,7 +46931,7 @@
         <v>46122</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47004,7 +47004,7 @@
         <v>45079</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47077,7 +47077,7 @@
         <v>44740</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47155,7 +47155,7 @@
         <v>45001</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47233,7 +47233,7 @@
         <v>45702</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47306,7 +47306,7 @@
         <v>45572</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47379,7 +47379,7 @@
         <v>45069</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47452,7 +47452,7 @@
         <v>44916</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47525,7 +47525,7 @@
         <v>45105</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47598,7 +47598,7 @@
         <v>45232</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47671,7 +47671,7 @@
         <v>44818</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47744,7 +47744,7 @@
         <v>45082</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47817,7 +47817,7 @@
         <v>45568</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47895,7 +47895,7 @@
         <v>44511</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47968,7 +47968,7 @@
         <v>45538</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48041,7 +48041,7 @@
         <v>44753</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48114,7 +48114,7 @@
         <v>46153</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48187,7 +48187,7 @@
         <v>45748</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48265,7 +48265,7 @@
         <v>45748</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48343,7 +48343,7 @@
         <v>44869</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48416,7 +48416,7 @@
         <v>46153</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48489,7 +48489,7 @@
         <v>45754</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48567,7 +48567,7 @@
         <v>46153</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48640,7 +48640,7 @@
         <v>46153</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48713,7 +48713,7 @@
         <v>46154</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48791,7 +48791,7 @@
         <v>44477</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48864,7 +48864,7 @@
         <v>45400</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48942,7 +48942,7 @@
         <v>45438</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49015,7 +49015,7 @@
         <v>45526</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49088,7 +49088,7 @@
         <v>45737</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49161,7 +49161,7 @@
         <v>45406</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49234,7 +49234,7 @@
         <v>45104</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49307,7 +49307,7 @@
         <v>44487</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49380,7 +49380,7 @@
         <v>45639</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49453,7 +49453,7 @@
         <v>46126</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49526,7 +49526,7 @@
         <v>45297</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49599,7 +49599,7 @@
         <v>45866</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49672,7 +49672,7 @@
         <v>45838</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49745,7 +49745,7 @@
         <v>45278</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49818,7 +49818,7 @@
         <v>45771</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49896,7 +49896,7 @@
         <v>45771</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49974,7 +49974,7 @@
         <v>45351</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50047,7 +50047,7 @@
         <v>46064</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50120,7 +50120,7 @@
         <v>45250</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50193,7 +50193,7 @@
         <v>45761</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50266,7 +50266,7 @@
         <v>45930</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50339,7 +50339,7 @@
         <v>46160</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50412,7 +50412,7 @@
         <v>45376</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50485,7 +50485,7 @@
         <v>45099</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50558,7 +50558,7 @@
         <v>46160</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50631,7 +50631,7 @@
         <v>46160</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50704,7 +50704,7 @@
         <v>45097</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50777,7 +50777,7 @@
         <v>46161</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50850,7 +50850,7 @@
         <v>45769</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50928,7 +50928,7 @@
         <v>45104</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51001,7 +51001,7 @@
         <v>45840</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51074,7 +51074,7 @@
         <v>45840</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51147,7 +51147,7 @@
         <v>45839</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51220,7 +51220,7 @@
         <v>45314</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51293,7 +51293,7 @@
         <v>45384</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51366,7 +51366,7 @@
         <v>46160</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51439,7 +51439,7 @@
         <v>46161</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51512,7 +51512,7 @@
         <v>44946</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51585,7 +51585,7 @@
         <v>45625</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51658,7 +51658,7 @@
         <v>45715</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51731,7 +51731,7 @@
         <v>45747</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51804,7 +51804,7 @@
         <v>45089</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51877,7 +51877,7 @@
         <v>45729</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51950,7 +51950,7 @@
         <v>45845</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52023,7 +52023,7 @@
         <v>45715</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52096,7 +52096,7 @@
         <v>45336</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52169,7 +52169,7 @@
         <v>45748</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52242,7 +52242,7 @@
         <v>45930</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52320,7 +52320,7 @@
         <v>46163</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52393,7 +52393,7 @@
         <v>45701</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52471,7 +52471,7 @@
         <v>45104</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52544,7 +52544,7 @@
         <v>45104</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52617,7 +52617,7 @@
         <v>45847</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52690,7 +52690,7 @@
         <v>45372</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52763,7 +52763,7 @@
         <v>44834</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52836,7 +52836,7 @@
         <v>45231</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52909,7 +52909,7 @@
         <v>45852</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52982,7 +52982,7 @@
         <v>45763</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53055,7 +53055,7 @@
         <v>45099</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53128,7 +53128,7 @@
         <v>45580</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53201,7 +53201,7 @@
         <v>45330</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53274,7 +53274,7 @@
         <v>45254</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53352,7 +53352,7 @@
         <v>45247</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53425,7 +53425,7 @@
         <v>45265</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53498,7 +53498,7 @@
         <v>44831</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53571,7 +53571,7 @@
         <v>44510</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53644,7 +53644,7 @@
         <v>45322</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53717,7 +53717,7 @@
         <v>45005</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53790,7 +53790,7 @@
         <v>45331</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53863,7 +53863,7 @@
         <v>45575</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53936,7 +53936,7 @@
         <v>45163</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54009,7 +54009,7 @@
         <v>44549</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54082,7 +54082,7 @@
         <v>45672</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54155,7 +54155,7 @@
         <v>44564</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54228,7 +54228,7 @@
         <v>45163</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54301,7 +54301,7 @@
         <v>45092</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54374,7 +54374,7 @@
         <v>45414</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54447,7 +54447,7 @@
         <v>45006</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54520,7 +54520,7 @@
         <v>44503</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54593,7 +54593,7 @@
         <v>45733</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54666,7 +54666,7 @@
         <v>46175</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54739,7 +54739,7 @@
         <v>45569</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54817,7 +54817,7 @@
         <v>45113</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54890,7 +54890,7 @@
         <v>45866</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54963,7 +54963,7 @@
         <v>44984</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55036,7 +55036,7 @@
         <v>44984</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55109,7 +55109,7 @@
         <v>45433</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55182,7 +55182,7 @@
         <v>44879</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55255,7 +55255,7 @@
         <v>45462</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55328,7 +55328,7 @@
         <v>44859</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55401,7 +55401,7 @@
         <v>45455</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55474,7 +55474,7 @@
         <v>45030</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55547,7 +55547,7 @@
         <v>45602</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55620,7 +55620,7 @@
         <v>45303</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55693,7 +55693,7 @@
         <v>45288</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55766,7 +55766,7 @@
         <v>44995</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55839,7 +55839,7 @@
         <v>45615</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55912,7 +55912,7 @@
         <v>45348</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55985,7 +55985,7 @@
         <v>45117</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56058,7 +56058,7 @@
         <v>45112</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56131,7 +56131,7 @@
         <v>45174</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56209,7 +56209,7 @@
         <v>46178</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56282,7 +56282,7 @@
         <v>46178</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56355,7 +56355,7 @@
         <v>46178</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56428,7 +56428,7 @@
         <v>46178</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56501,7 +56501,7 @@
         <v>45084</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56574,7 +56574,7 @@
         <v>44587</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56647,7 +56647,7 @@
         <v>46178</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56720,7 +56720,7 @@
         <v>46178</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56793,7 +56793,7 @@
         <v>45166</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56866,7 +56866,7 @@
         <v>46182</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56939,7 +56939,7 @@
         <v>45401</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57012,7 +57012,7 @@
         <v>45616</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57085,7 +57085,7 @@
         <v>46182</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57158,7 +57158,7 @@
         <v>44523</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57231,7 +57231,7 @@
         <v>45048</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57304,7 +57304,7 @@
         <v>46184</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57377,7 +57377,7 @@
         <v>46182</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57450,7 +57450,7 @@
         <v>45175</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57523,7 +57523,7 @@
         <v>46184</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57596,7 +57596,7 @@
         <v>46184</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57669,7 +57669,7 @@
         <v>46185</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57742,7 +57742,7 @@
         <v>45401</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57815,7 +57815,7 @@
         <v>45168</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57888,7 +57888,7 @@
         <v>44545</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57961,7 +57961,7 @@
         <v>45161</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58034,7 +58034,7 @@
         <v>46185</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58107,7 +58107,7 @@
         <v>45113</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58180,7 +58180,7 @@
         <v>45470</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58253,7 +58253,7 @@
         <v>45182</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58326,7 +58326,7 @@
         <v>45478</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58399,7 +58399,7 @@
         <v>45406</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58472,7 +58472,7 @@
         <v>46188</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58545,7 +58545,7 @@
         <v>45545</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58618,7 +58618,7 @@
         <v>45569</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58691,7 +58691,7 @@
         <v>45875</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58764,7 +58764,7 @@
         <v>45925</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58837,7 +58837,7 @@
         <v>46190</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58910,7 +58910,7 @@
         <v>45540</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58983,7 +58983,7 @@
         <v>45350</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59056,7 +59056,7 @@
         <v>45525</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59129,7 +59129,7 @@
         <v>45031</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59202,7 +59202,7 @@
         <v>45875</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59275,7 +59275,7 @@
         <v>46195</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59348,7 +59348,7 @@
         <v>45875</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59421,7 +59421,7 @@
         <v>45341</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59494,7 +59494,7 @@
         <v>46197</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59567,7 +59567,7 @@
         <v>45168</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59640,7 +59640,7 @@
         <v>46196</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59713,7 +59713,7 @@
         <v>46196</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59786,7 +59786,7 @@
         <v>46197</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59859,7 +59859,7 @@
         <v>45091</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59932,7 +59932,7 @@
         <v>45104</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60005,7 +60005,7 @@
         <v>45170</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60078,7 +60078,7 @@
         <v>45170</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60151,7 +60151,7 @@
         <v>44592</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60224,7 +60224,7 @@
         <v>45882</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60297,7 +60297,7 @@
         <v>45882</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60370,7 +60370,7 @@
         <v>45602</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60443,7 +60443,7 @@
         <v>45699</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60516,7 +60516,7 @@
         <v>46202</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60589,7 +60589,7 @@
         <v>44602</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60662,7 +60662,7 @@
         <v>44580</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60735,7 +60735,7 @@
         <v>44607</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60808,7 +60808,7 @@
         <v>45163</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60881,7 +60881,7 @@
         <v>45189</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60959,7 +60959,7 @@
         <v>45177</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61037,7 +61037,7 @@
         <v>45645</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61115,7 +61115,7 @@
         <v>45174</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61188,7 +61188,7 @@
         <v>45610</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61261,7 +61261,7 @@
         <v>45352</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61334,7 +61334,7 @@
         <v>46204</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61407,7 +61407,7 @@
         <v>45366</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61480,7 +61480,7 @@
         <v>45645</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61553,7 +61553,7 @@
         <v>44600</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61626,7 +61626,7 @@
         <v>45681</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61699,7 +61699,7 @@
         <v>46252</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61772,7 +61772,7 @@
         <v>45625</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61845,7 +61845,7 @@
         <v>45231</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61918,7 +61918,7 @@
         <v>45607</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61991,7 +61991,7 @@
         <v>45118</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62064,7 +62064,7 @@
         <v>45510</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62137,7 +62137,7 @@
         <v>45134</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62210,7 +62210,7 @@
         <v>46069</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62283,7 +62283,7 @@
         <v>45195</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62356,7 +62356,7 @@
         <v>45133</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62429,7 +62429,7 @@
         <v>45090</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62502,7 +62502,7 @@
         <v>46255</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62575,7 +62575,7 @@
         <v>45097</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62648,7 +62648,7 @@
         <v>45216</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62726,7 +62726,7 @@
         <v>46213</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62799,7 +62799,7 @@
         <v>45209</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62872,7 +62872,7 @@
         <v>45211</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62945,7 +62945,7 @@
         <v>46168</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63018,7 +63018,7 @@
         <v>45230</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63096,7 +63096,7 @@
         <v>45561</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63169,7 +63169,7 @@
         <v>45113</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63242,7 +63242,7 @@
         <v>44655</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63315,7 +63315,7 @@
         <v>45572</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63388,7 +63388,7 @@
         <v>45398</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63461,7 +63461,7 @@
         <v>45446</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63534,7 +63534,7 @@
         <v>46258</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63607,7 +63607,7 @@
         <v>45392</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63680,7 +63680,7 @@
         <v>44888</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63753,7 +63753,7 @@
         <v>45202</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63826,7 +63826,7 @@
         <v>45236</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63899,7 +63899,7 @@
         <v>46259</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63972,7 +63972,7 @@
         <v>45173</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64045,7 +64045,7 @@
         <v>45173</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64118,7 +64118,7 @@
         <v>46259</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64191,7 +64191,7 @@
         <v>45180</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64264,7 +64264,7 @@
         <v>45188</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64337,7 +64337,7 @@
         <v>46177</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64410,7 +64410,7 @@
         <v>44762</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64483,7 +64483,7 @@
         <v>45400</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64556,7 +64556,7 @@
         <v>45191</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64629,7 +64629,7 @@
         <v>45188</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64702,7 +64702,7 @@
         <v>45204</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64775,7 +64775,7 @@
         <v>45238</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64853,7 +64853,7 @@
         <v>45135</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64926,7 +64926,7 @@
         <v>45135</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -64999,7 +64999,7 @@
         <v>45135</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65072,7 +65072,7 @@
         <v>45259</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65145,7 +65145,7 @@
         <v>45322</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65218,7 +65218,7 @@
         <v>45135</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65291,7 +65291,7 @@
         <v>45319</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65364,7 +65364,7 @@
         <v>45245</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65437,7 +65437,7 @@
         <v>46265</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65510,7 +65510,7 @@
         <v>45754</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65588,7 +65588,7 @@
         <v>45754</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65666,7 +65666,7 @@
         <v>45307</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65739,7 +65739,7 @@
         <v>44741</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65812,7 +65812,7 @@
         <v>44813</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65885,7 +65885,7 @@
         <v>45719</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65958,7 +65958,7 @@
         <v>45671</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66031,7 +66031,7 @@
         <v>45331</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66104,7 +66104,7 @@
         <v>44970</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66177,7 +66177,7 @@
         <v>45357</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66250,7 +66250,7 @@
         <v>45309</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66323,7 +66323,7 @@
         <v>45352</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66396,7 +66396,7 @@
         <v>44830</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66469,7 +66469,7 @@
         <v>45309</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66542,7 +66542,7 @@
         <v>45309</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66615,7 +66615,7 @@
         <v>44839</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66688,7 +66688,7 @@
         <v>46268</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66761,7 +66761,7 @@
         <v>45250</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66834,7 +66834,7 @@
         <v>45314</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66907,7 +66907,7 @@
         <v>45309</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -66980,7 +66980,7 @@
         <v>44805</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67053,7 +67053,7 @@
         <v>45076</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67126,7 +67126,7 @@
         <v>46269</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67199,7 +67199,7 @@
         <v>45007</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67272,7 +67272,7 @@
         <v>44792</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67345,7 +67345,7 @@
         <v>45303</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67418,7 +67418,7 @@
         <v>45365</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67491,7 +67491,7 @@
         <v>44481</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67564,7 +67564,7 @@
         <v>45302</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67637,7 +67637,7 @@
         <v>45264</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -67710,7 +67710,7 @@
         <v>45264</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -67783,7 +67783,7 @@
         <v>46258</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67856,7 +67856,7 @@
         <v>45330</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -67929,7 +67929,7 @@
         <v>46274</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -68002,7 +68002,7 @@
         <v>45351</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -68075,7 +68075,7 @@
         <v>46273</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -68148,7 +68148,7 @@
         <v>46273</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -68221,7 +68221,7 @@
         <v>45272</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -68294,7 +68294,7 @@
         <v>46276</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68367,7 +68367,7 @@
         <v>46233</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68440,7 +68440,7 @@
         <v>46276</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68513,7 +68513,7 @@
         <v>46276</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -68586,7 +68586,7 @@
         <v>46276</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -68659,7 +68659,7 @@
         <v>46276</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -68732,7 +68732,7 @@
         <v>46279</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68805,7 +68805,7 @@
         <v>46234</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -68878,7 +68878,7 @@
         <v>45071</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -68951,7 +68951,7 @@
         <v>46237</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -69024,7 +69024,7 @@
         <v>45645</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -69097,7 +69097,7 @@
         <v>45370</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -69170,7 +69170,7 @@
         <v>45645</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -69248,7 +69248,7 @@
         <v>45259</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -69321,7 +69321,7 @@
         <v>44888</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -69394,7 +69394,7 @@
         <v>46234</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69467,7 +69467,7 @@
         <v>46234</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -69540,7 +69540,7 @@
         <v>45595</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -69613,7 +69613,7 @@
         <v>45674</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -69686,7 +69686,7 @@
         <v>45316</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -69759,7 +69759,7 @@
         <v>44971</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -69832,7 +69832,7 @@
         <v>44851</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -69905,7 +69905,7 @@
         <v>45475</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -69978,7 +69978,7 @@
         <v>46283</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -70051,7 +70051,7 @@
         <v>45953</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -70124,7 +70124,7 @@
         <v>45329</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -70197,7 +70197,7 @@
         <v>45329</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -70270,7 +70270,7 @@
         <v>44965</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -70343,7 +70343,7 @@
         <v>46240</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -70416,7 +70416,7 @@
         <v>44497</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70489,7 +70489,7 @@
         <v>44484</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -70562,7 +70562,7 @@
         <v>44916</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -70635,7 +70635,7 @@
         <v>44488</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -70708,7 +70708,7 @@
         <v>44502</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -70781,7 +70781,7 @@
         <v>44957</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -70854,7 +70854,7 @@
         <v>44967</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -70927,7 +70927,7 @@
         <v>44967</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -71000,7 +71000,7 @@
         <v>44903</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -71073,7 +71073,7 @@
         <v>45414</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -71151,7 +71151,7 @@
         <v>45414</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -71224,7 +71224,7 @@
         <v>44952</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -71297,7 +71297,7 @@
         <v>46245</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -71370,7 +71370,7 @@
         <v>44607</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -71443,7 +71443,7 @@
         <v>46244</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -71516,7 +71516,7 @@
         <v>44831</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -71589,7 +71589,7 @@
         <v>45408</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -71662,7 +71662,7 @@
         <v>46280</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -71735,7 +71735,7 @@
         <v>44880</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -71808,7 +71808,7 @@
         <v>46244</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -71881,7 +71881,7 @@
         <v>44998</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -71954,7 +71954,7 @@
         <v>44592</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -72027,7 +72027,7 @@
         <v>45302</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -72100,7 +72100,7 @@
         <v>44946</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -72173,7 +72173,7 @@
         <v>44683</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -72246,7 +72246,7 @@
         <v>46009</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -72319,7 +72319,7 @@
         <v>45440</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -72392,7 +72392,7 @@
         <v>46247</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -72470,7 +72470,7 @@
         <v>46289</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -72543,7 +72543,7 @@
         <v>46290</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -72616,7 +72616,7 @@
         <v>46178</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -72689,7 +72689,7 @@
         <v>46289</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -72762,7 +72762,7 @@
         <v>44677</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -72835,7 +72835,7 @@
         <v>45674</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -72908,7 +72908,7 @@
         <v>46247</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -72986,7 +72986,7 @@
         <v>45351</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -73059,7 +73059,7 @@
         <v>45363</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -73137,7 +73137,7 @@
         <v>45363</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -73215,7 +73215,7 @@
         <v>44917</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -73288,7 +73288,7 @@
         <v>44747</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -73361,7 +73361,7 @@
         <v>46246</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -73434,7 +73434,7 @@
         <v>45363</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -73512,7 +73512,7 @@
         <v>45363</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -73590,7 +73590,7 @@
         <v>45190</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -73663,7 +73663,7 @@
         <v>45441</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -73736,7 +73736,7 @@
         <v>46248</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -73814,7 +73814,7 @@
         <v>46178</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -73887,7 +73887,7 @@
         <v>44972</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -73960,7 +73960,7 @@
         <v>44488</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -74033,7 +74033,7 @@
         <v>44952</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -74106,7 +74106,7 @@
         <v>44984</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -74179,7 +74179,7 @@
         <v>45152</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -74252,7 +74252,7 @@
         <v>44480</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -74325,7 +74325,7 @@
         <v>44655</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -74398,7 +74398,7 @@
         <v>45055</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -74471,7 +74471,7 @@
         <v>44495</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -74544,7 +74544,7 @@
         <v>45224</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -74622,7 +74622,7 @@
         <v>45097</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -74695,7 +74695,7 @@
         <v>45069</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -74768,7 +74768,7 @@
         <v>45669</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -74841,7 +74841,7 @@
         <v>45107</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -74914,7 +74914,7 @@
         <v>44470</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -74987,7 +74987,7 @@
         <v>45219</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -75060,7 +75060,7 @@
         <v>45615</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -75133,7 +75133,7 @@
         <v>45183</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -75206,7 +75206,7 @@
         <v>45364</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -75279,7 +75279,7 @@
         <v>44963</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -75352,7 +75352,7 @@
         <v>45135</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -75425,7 +75425,7 @@
         <v>45219</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -75503,7 +75503,7 @@
         <v>44930</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -75576,7 +75576,7 @@
         <v>45282</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -75649,7 +75649,7 @@
         <v>45245</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -75722,7 +75722,7 @@
         <v>44847</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -75795,7 +75795,7 @@
         <v>45310</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -75868,7 +75868,7 @@
         <v>45763</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -75941,7 +75941,7 @@
         <v>45574</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -76019,7 +76019,7 @@
         <v>45575</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -76092,7 +76092,7 @@
         <v>45362</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -76165,7 +76165,7 @@
         <v>45251</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -76238,7 +76238,7 @@
         <v>45057</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -76311,7 +76311,7 @@
         <v>44998</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -76384,7 +76384,7 @@
         <v>44970</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -76457,7 +76457,7 @@
         <v>45164</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -76530,7 +76530,7 @@
         <v>44747</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -76603,7 +76603,7 @@
         <v>45091</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -76676,7 +76676,7 @@
         <v>45329</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -76754,7 +76754,7 @@
         <v>45406</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -76827,7 +76827,7 @@
         <v>45134</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -76900,7 +76900,7 @@
         <v>45365</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -76973,7 +76973,7 @@
         <v>45099</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -77046,7 +77046,7 @@
         <v>45462</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -77119,7 +77119,7 @@
         <v>44965</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -77192,7 +77192,7 @@
         <v>45484</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -77265,7 +77265,7 @@
         <v>45526</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -77338,7 +77338,7 @@
         <v>45303</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -77411,7 +77411,7 @@
         <v>45226</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -77484,7 +77484,7 @@
         <v>45042</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -77557,7 +77557,7 @@
         <v>45114</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -77630,7 +77630,7 @@
         <v>45327</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -77703,7 +77703,7 @@
         <v>45035</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -77776,7 +77776,7 @@
         <v>45298</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -77849,7 +77849,7 @@
         <v>45684</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -77927,7 +77927,7 @@
         <v>45660</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -78000,7 +78000,7 @@
         <v>45182</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -78078,7 +78078,7 @@
         <v>45182</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -78156,7 +78156,7 @@
         <v>45182</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -78229,7 +78229,7 @@
         <v>45188</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -78302,7 +78302,7 @@
         <v>45089</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -78375,7 +78375,7 @@
         <v>45222</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -78448,7 +78448,7 @@
         <v>45602</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -78521,7 +78521,7 @@
         <v>45335</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -78594,7 +78594,7 @@
         <v>45645</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -78667,7 +78667,7 @@
         <v>45645</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -78745,7 +78745,7 @@
         <v>45580</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -78818,7 +78818,7 @@
         <v>44710</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -78891,7 +78891,7 @@
         <v>45321</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -78964,7 +78964,7 @@
         <v>45183</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -79037,7 +79037,7 @@
         <v>44743</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -79110,7 +79110,7 @@
         <v>45132</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -79183,7 +79183,7 @@
         <v>45649</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -79261,7 +79261,7 @@
         <v>45526</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -79334,7 +79334,7 @@
         <v>45673</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -79407,7 +79407,7 @@
         <v>45701</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -79485,7 +79485,7 @@
         <v>44970</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -79558,7 +79558,7 @@
         <v>45359</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -79631,7 +79631,7 @@
         <v>45625</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -79704,7 +79704,7 @@
         <v>45544</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -79777,7 +79777,7 @@
         <v>44970</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -79850,7 +79850,7 @@
         <v>45674</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -79923,7 +79923,7 @@
         <v>45385</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -79996,7 +79996,7 @@
         <v>45188</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -80069,7 +80069,7 @@
         <v>45314</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -80142,7 +80142,7 @@
         <v>45645</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -80220,7 +80220,7 @@
         <v>45645</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -80298,7 +80298,7 @@
         <v>45228</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -80371,7 +80371,7 @@
         <v>45329</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -80444,7 +80444,7 @@
         <v>45737</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
@@ -80517,7 +80517,7 @@
         <v>45737</v>
       </c>
       <c r="E1032" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
@@ -80590,7 +80590,7 @@
         <v>45376</v>
       </c>
       <c r="E1033" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
@@ -80663,7 +80663,7 @@
         <v>45702</v>
       </c>
       <c r="E1034" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
@@ -80741,7 +80741,7 @@
         <v>45315</v>
       </c>
       <c r="E1035" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
@@ -80814,7 +80814,7 @@
         <v>44949</v>
       </c>
       <c r="E1036" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
@@ -80887,7 +80887,7 @@
         <v>45230</v>
       </c>
       <c r="E1037" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
@@ -80965,7 +80965,7 @@
         <v>45595</v>
       </c>
       <c r="E1038" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1038" t="inlineStr">
         <is>
@@ -81038,7 +81038,7 @@
         <v>45670</v>
       </c>
       <c r="E1039" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1039" t="inlineStr">
         <is>
@@ -81111,7 +81111,7 @@
         <v>45274</v>
       </c>
       <c r="E1040" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1040" t="inlineStr">
         <is>
@@ -81184,7 +81184,7 @@
         <v>44781</v>
       </c>
       <c r="E1041" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1041" t="inlineStr">
         <is>
@@ -81257,7 +81257,7 @@
         <v>45439</v>
       </c>
       <c r="E1042" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1042" t="inlineStr">
         <is>
@@ -81330,7 +81330,7 @@
         <v>45348</v>
       </c>
       <c r="E1043" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1043" t="inlineStr">
         <is>
@@ -81403,7 +81403,7 @@
         <v>45783</v>
       </c>
       <c r="E1044" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1044" t="inlineStr">
         <is>
@@ -81476,7 +81476,7 @@
         <v>45783</v>
       </c>
       <c r="E1045" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1045" t="inlineStr">
         <is>
@@ -81549,7 +81549,7 @@
         <v>45716</v>
       </c>
       <c r="E1046" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1046" t="inlineStr">
         <is>
@@ -81622,7 +81622,7 @@
         <v>45456</v>
       </c>
       <c r="E1047" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1047" t="inlineStr">
         <is>
@@ -81695,7 +81695,7 @@
         <v>44592</v>
       </c>
       <c r="E1048" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1048" t="inlineStr">
         <is>
@@ -81768,7 +81768,7 @@
         <v>45439</v>
       </c>
       <c r="E1049" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1049" t="inlineStr">
         <is>
@@ -81841,7 +81841,7 @@
         <v>45786</v>
       </c>
       <c r="E1050" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1050" t="inlineStr">
         <is>
@@ -81914,7 +81914,7 @@
         <v>45601</v>
       </c>
       <c r="E1051" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1051" t="inlineStr">
         <is>
@@ -81987,7 +81987,7 @@
         <v>45792</v>
       </c>
       <c r="E1052" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1052" t="inlineStr">
         <is>
@@ -82060,7 +82060,7 @@
         <v>45636</v>
       </c>
       <c r="E1053" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1053" t="inlineStr">
         <is>
@@ -82133,7 +82133,7 @@
         <v>45580</v>
       </c>
       <c r="E1054" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1054" t="inlineStr">
         <is>
@@ -82206,7 +82206,7 @@
         <v>45447</v>
       </c>
       <c r="E1055" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1055" t="inlineStr">
         <is>
@@ -82279,7 +82279,7 @@
         <v>45170</v>
       </c>
       <c r="E1056" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1056" t="inlineStr">
         <is>
@@ -82352,7 +82352,7 @@
         <v>45106</v>
       </c>
       <c r="E1057" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1057" t="inlineStr">
         <is>
@@ -82425,7 +82425,7 @@
         <v>45467</v>
       </c>
       <c r="E1058" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1058" t="inlineStr">
         <is>
@@ -82498,7 +82498,7 @@
         <v>44509</v>
       </c>
       <c r="E1059" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1059" t="inlineStr">
         <is>
@@ -82576,7 +82576,7 @@
         <v>45664</v>
       </c>
       <c r="E1060" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1060" t="inlineStr">
         <is>
@@ -82649,7 +82649,7 @@
         <v>45208</v>
       </c>
       <c r="E1061" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1061" t="inlineStr">
         <is>
@@ -82722,7 +82722,7 @@
         <v>45406</v>
       </c>
       <c r="E1062" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1062" t="inlineStr">
         <is>
@@ -82795,7 +82795,7 @@
         <v>45497</v>
       </c>
       <c r="E1063" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1063" t="inlineStr">
         <is>
@@ -82868,7 +82868,7 @@
         <v>45497</v>
       </c>
       <c r="E1064" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1064" t="inlineStr">
         <is>
@@ -82941,7 +82941,7 @@
         <v>45106</v>
       </c>
       <c r="E1065" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1065" t="inlineStr">
         <is>
@@ -83014,7 +83014,7 @@
         <v>45646</v>
       </c>
       <c r="E1066" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1066" t="inlineStr">
         <is>
@@ -83087,7 +83087,7 @@
         <v>45646</v>
       </c>
       <c r="E1067" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1067" t="inlineStr">
         <is>
@@ -83160,7 +83160,7 @@
         <v>45580</v>
       </c>
       <c r="E1068" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1068" t="inlineStr">
         <is>
@@ -83233,7 +83233,7 @@
         <v>45646</v>
       </c>
       <c r="E1069" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1069" t="inlineStr">
         <is>
@@ -83306,7 +83306,7 @@
         <v>45646</v>
       </c>
       <c r="E1070" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1070" t="inlineStr">
         <is>
@@ -83379,7 +83379,7 @@
         <v>45408</v>
       </c>
       <c r="E1071" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1071" t="inlineStr">
         <is>
@@ -83452,7 +83452,7 @@
         <v>45414</v>
       </c>
       <c r="E1072" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1072" t="inlineStr">
         <is>
@@ -83525,7 +83525,7 @@
         <v>45173</v>
       </c>
       <c r="E1073" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1073" t="inlineStr">
         <is>
@@ -83598,7 +83598,7 @@
         <v>45646</v>
       </c>
       <c r="E1074" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1074" t="inlineStr">
         <is>
@@ -83671,7 +83671,7 @@
         <v>45715</v>
       </c>
       <c r="E1075" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1075" t="inlineStr">
         <is>
@@ -83744,7 +83744,7 @@
         <v>45720</v>
       </c>
       <c r="E1076" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1076" t="inlineStr">
         <is>
@@ -83817,7 +83817,7 @@
         <v>45800</v>
       </c>
       <c r="E1077" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1077" t="inlineStr">
         <is>
@@ -83895,7 +83895,7 @@
         <v>45831</v>
       </c>
       <c r="E1078" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1078" t="inlineStr">
         <is>
@@ -83968,7 +83968,7 @@
         <v>45785</v>
       </c>
       <c r="E1079" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1079" t="inlineStr">
         <is>
@@ -84041,7 +84041,7 @@
         <v>46073</v>
       </c>
       <c r="E1080" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1080" t="inlineStr">
         <is>
@@ -84114,7 +84114,7 @@
         <v>46163</v>
       </c>
       <c r="E1081" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1081" t="inlineStr">
         <is>
@@ -84187,7 +84187,7 @@
         <v>46274</v>
       </c>
       <c r="E1082" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1082" t="inlineStr">
         <is>

--- a/Översikt VETLANDA.xlsx
+++ b/Översikt VETLANDA.xlsx
@@ -601,7 +601,7 @@
         <v>45097</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>46178</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         <v>45371</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>44817</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>44890</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>45183</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>45558</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>45168</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>46107</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>45930</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>45520</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>45957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>45754</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>45170</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>44612</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>46002</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>46100</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>44840</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>44908</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>45203</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>45819</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>46163</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>46188</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>44545</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>44564</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>46045</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>45599</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>45583</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>44819</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         <v>45763</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>45477</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         <v>45814</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>45048</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>46255</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4450,7 +4450,7 @@
         <v>45646</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>45131</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
         <v>44515</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>44752</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>44643</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         <v>45589</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5107,7 +5107,7 @@
         <v>45713</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>45965</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
         <v>45792</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>45673</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>45835</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>45840</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         <v>45713</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>44572</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>45891</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         <v>45860</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>45303</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>46166</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6387,7 +6387,7 @@
         <v>45148</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         <v>45357</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
         <v>45616</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6705,7 +6705,7 @@
         <v>46279</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6816,7 +6816,7 @@
         <v>45035</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>46293</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>45400</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>45211</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>45310</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>45106</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7461,7 +7461,7 @@
         <v>45509</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         <v>45497</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>45201</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         <v>45539</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         <v>46051</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         <v>44490</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
         <v>44834</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         <v>44721</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         <v>44747</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>44592</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8520,7 +8520,7 @@
         <v>44740</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
         <v>45596</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         <v>45597</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8840,7 +8840,7 @@
         <v>44830</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         <v>45643</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9050,7 +9050,7 @@
         <v>45835</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9155,7 +9155,7 @@
         <v>45791</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>45904</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9365,7 +9365,7 @@
         <v>45645</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9470,7 +9470,7 @@
         <v>45555</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9575,7 +9575,7 @@
         <v>45736</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
         <v>44781</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9789,7 +9789,7 @@
         <v>45021</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9894,7 +9894,7 @@
         <v>45586</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         <v>46069</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10104,7 +10104,7 @@
         <v>44748</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10209,7 +10209,7 @@
         <v>46071</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10314,7 +10314,7 @@
         <v>44824</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
         <v>45240</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10524,7 +10524,7 @@
         <v>44728</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10633,7 +10633,7 @@
         <v>45342</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10738,7 +10738,7 @@
         <v>45820</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10848,7 +10848,7 @@
         <v>45586</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10953,7 +10953,7 @@
         <v>45839</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
         <v>45775</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11163,7 +11163,7 @@
         <v>45239</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11273,7 +11273,7 @@
         <v>44998</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11378,7 +11378,7 @@
         <v>45880</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11483,7 +11483,7 @@
         <v>44880</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>46141</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>45419</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>45672</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
         <v>46188</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12016,7 +12016,7 @@
         <v>45085</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12121,7 +12121,7 @@
         <v>45408</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12226,7 +12226,7 @@
         <v>44819</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12331,7 +12331,7 @@
         <v>45119</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
         <v>45009</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12541,7 +12541,7 @@
         <v>45930</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12655,7 +12655,7 @@
         <v>45261</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
         <v>45378</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12865,7 +12865,7 @@
         <v>46248</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12970,7 +12970,7 @@
         <v>45104</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>44816</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13184,7 +13184,7 @@
         <v>45532</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         <v>44833</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13394,7 +13394,7 @@
         <v>46297</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13499,7 +13499,7 @@
         <v>45337</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13604,7 +13604,7 @@
         <v>45565</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>44916</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>45352</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13919,7 +13919,7 @@
         <v>45604</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14024,7 +14024,7 @@
         <v>45497</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14129,7 +14129,7 @@
         <v>45614</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14234,7 +14234,7 @@
         <v>45742</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14343,7 +14343,7 @@
         <v>44838</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>44858</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14489,7 +14489,7 @@
         <v>44781</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14562,7 +14562,7 @@
         <v>44732</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14635,7 +14635,7 @@
         <v>44781</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14708,7 +14708,7 @@
         <v>44515</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14781,7 +14781,7 @@
         <v>44504</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>44508</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14927,7 +14927,7 @@
         <v>44496</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15000,7 +15000,7 @@
         <v>44579</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15073,7 +15073,7 @@
         <v>44601</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15146,7 +15146,7 @@
         <v>44889</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15219,7 +15219,7 @@
         <v>44544</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15292,7 +15292,7 @@
         <v>44510</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15365,7 +15365,7 @@
         <v>44517</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15438,7 +15438,7 @@
         <v>44764</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15511,7 +15511,7 @@
         <v>44503</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15584,7 +15584,7 @@
         <v>44819</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>44592</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15730,7 +15730,7 @@
         <v>44750</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15803,7 +15803,7 @@
         <v>44825</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15876,7 +15876,7 @@
         <v>44488</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15949,7 +15949,7 @@
         <v>44602</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16022,7 +16022,7 @@
         <v>44638</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16095,7 +16095,7 @@
         <v>44510</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16168,7 +16168,7 @@
         <v>44721</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16241,7 +16241,7 @@
         <v>44510</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16314,7 +16314,7 @@
         <v>44785</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16387,7 +16387,7 @@
         <v>44592</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16460,7 +16460,7 @@
         <v>44587</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16533,7 +16533,7 @@
         <v>44782</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16606,7 +16606,7 @@
         <v>44815</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16679,7 +16679,7 @@
         <v>44504</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16752,7 +16752,7 @@
         <v>44580</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16825,7 +16825,7 @@
         <v>44691</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16898,7 +16898,7 @@
         <v>44880</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
         <v>44545</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17044,7 +17044,7 @@
         <v>44750</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17117,7 +17117,7 @@
         <v>44624</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17190,7 +17190,7 @@
         <v>44477</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>44595</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17336,7 +17336,7 @@
         <v>44820</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17409,7 +17409,7 @@
         <v>44816</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>44645</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17555,7 +17555,7 @@
         <v>44608</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17628,7 +17628,7 @@
         <v>44819</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
         <v>44656</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>44784</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17847,7 +17847,7 @@
         <v>44585</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17925,7 +17925,7 @@
         <v>44585</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18003,7 +18003,7 @@
         <v>44585</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18081,7 +18081,7 @@
         <v>44834</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>44740</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18232,7 +18232,7 @@
         <v>44750</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18305,7 +18305,7 @@
         <v>44587</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18378,7 +18378,7 @@
         <v>44743</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18451,7 +18451,7 @@
         <v>44474</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18524,7 +18524,7 @@
         <v>44600</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18597,7 +18597,7 @@
         <v>44859</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18670,7 +18670,7 @@
         <v>44593</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18743,7 +18743,7 @@
         <v>44743</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18816,7 +18816,7 @@
         <v>44778</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18889,7 +18889,7 @@
         <v>44504</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18962,7 +18962,7 @@
         <v>44834</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19035,7 +19035,7 @@
         <v>44477</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19108,7 +19108,7 @@
         <v>44482</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19181,7 +19181,7 @@
         <v>44509</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19254,7 +19254,7 @@
         <v>44517</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19327,7 +19327,7 @@
         <v>44592</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19400,7 +19400,7 @@
         <v>44572</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19473,7 +19473,7 @@
         <v>44721</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19546,7 +19546,7 @@
         <v>44841</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19619,7 +19619,7 @@
         <v>44888</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19692,7 +19692,7 @@
         <v>44587</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19765,7 +19765,7 @@
         <v>44655</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19838,7 +19838,7 @@
         <v>44502</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19911,7 +19911,7 @@
         <v>44515</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19989,7 +19989,7 @@
         <v>44592</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20062,7 +20062,7 @@
         <v>44564</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20135,7 +20135,7 @@
         <v>44781</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20208,7 +20208,7 @@
         <v>44531</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20281,7 +20281,7 @@
         <v>44636</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>44834</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20427,7 +20427,7 @@
         <v>44733</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20500,7 +20500,7 @@
         <v>44683</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20573,7 +20573,7 @@
         <v>44602</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20646,7 +20646,7 @@
         <v>44792</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20719,7 +20719,7 @@
         <v>44657</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20792,7 +20792,7 @@
         <v>44827</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20865,7 +20865,7 @@
         <v>44902</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20938,7 +20938,7 @@
         <v>44488</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21011,7 +21011,7 @@
         <v>45561</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21084,7 +21084,7 @@
         <v>45251</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>45674</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21230,7 +21230,7 @@
         <v>44477</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21303,7 +21303,7 @@
         <v>44998</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21376,7 +21376,7 @@
         <v>45351</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21449,7 +21449,7 @@
         <v>45602</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21522,7 +21522,7 @@
         <v>45265</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21595,7 +21595,7 @@
         <v>45267</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21668,7 +21668,7 @@
         <v>45575</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21741,7 +21741,7 @@
         <v>44880</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21814,7 +21814,7 @@
         <v>45569</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21892,7 +21892,7 @@
         <v>44903</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21965,7 +21965,7 @@
         <v>44967</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22038,7 +22038,7 @@
         <v>44967</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22111,7 +22111,7 @@
         <v>45175</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22184,7 +22184,7 @@
         <v>45580</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22257,7 +22257,7 @@
         <v>45278</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22330,7 +22330,7 @@
         <v>44936</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22403,7 +22403,7 @@
         <v>44792</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22476,7 +22476,7 @@
         <v>45264</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22549,7 +22549,7 @@
         <v>44592</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22622,7 +22622,7 @@
         <v>45259</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22695,7 +22695,7 @@
         <v>45663</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22768,7 +22768,7 @@
         <v>44582</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22841,7 +22841,7 @@
         <v>44831</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22914,7 +22914,7 @@
         <v>45205</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22987,7 +22987,7 @@
         <v>45771</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23065,7 +23065,7 @@
         <v>45771</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>45057</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23216,7 +23216,7 @@
         <v>45307</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23289,7 +23289,7 @@
         <v>45091</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
         <v>45071</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23435,7 +23435,7 @@
         <v>45188</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23508,7 +23508,7 @@
         <v>44530</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23581,7 +23581,7 @@
         <v>45350</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23654,7 +23654,7 @@
         <v>45229</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>45055</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23800,7 +23800,7 @@
         <v>44600</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23873,7 +23873,7 @@
         <v>45135</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>44710</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24019,7 +24019,7 @@
         <v>44851</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>44592</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24165,7 +24165,7 @@
         <v>45406</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24238,7 +24238,7 @@
         <v>45786</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24311,7 +24311,7 @@
         <v>44762</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24384,7 +24384,7 @@
         <v>46001</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24457,7 +24457,7 @@
         <v>45601</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24530,7 +24530,7 @@
         <v>45456</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24603,7 +24603,7 @@
         <v>45716</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24676,7 +24676,7 @@
         <v>44747</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>45031</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24822,7 +24822,7 @@
         <v>44986</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24895,7 +24895,7 @@
         <v>45097</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24968,7 +24968,7 @@
         <v>45097</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25041,7 +25041,7 @@
         <v>45335</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25114,7 +25114,7 @@
         <v>45341</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25187,7 +25187,7 @@
         <v>45384</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25260,7 +25260,7 @@
         <v>45434</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25333,7 +25333,7 @@
         <v>45839</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25406,7 +25406,7 @@
         <v>46003</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25479,7 +25479,7 @@
         <v>45439</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25552,7 +25552,7 @@
         <v>45645</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25625,7 +25625,7 @@
         <v>45201</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25698,7 +25698,7 @@
         <v>45104</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25771,7 +25771,7 @@
         <v>45709</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25844,7 +25844,7 @@
         <v>45645</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25917,7 +25917,7 @@
         <v>46009</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25990,7 +25990,7 @@
         <v>45300</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26063,7 +26063,7 @@
         <v>46007</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26136,7 +26136,7 @@
         <v>46007</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26209,7 +26209,7 @@
         <v>46009</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>45099</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26355,7 +26355,7 @@
         <v>45884</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26428,7 +26428,7 @@
         <v>45999</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26501,7 +26501,7 @@
         <v>46009</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26574,7 +26574,7 @@
         <v>45470</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26647,7 +26647,7 @@
         <v>45309</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26720,7 +26720,7 @@
         <v>45309</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26793,7 +26793,7 @@
         <v>46010</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26866,7 +26866,7 @@
         <v>45097</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26939,7 +26939,7 @@
         <v>45272</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27012,7 +27012,7 @@
         <v>46010</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27085,7 +27085,7 @@
         <v>45363</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         <v>45827</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27236,7 +27236,7 @@
         <v>45888</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27309,7 +27309,7 @@
         <v>45888</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>45541</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27455,7 +27455,7 @@
         <v>45677</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27528,7 +27528,7 @@
         <v>45889</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27601,7 +27601,7 @@
         <v>45786</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27674,7 +27674,7 @@
         <v>45113</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27747,7 +27747,7 @@
         <v>45888</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27820,7 +27820,7 @@
         <v>45742</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27893,7 +27893,7 @@
         <v>45889</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27966,7 +27966,7 @@
         <v>45888</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28039,7 +28039,7 @@
         <v>45888</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28112,7 +28112,7 @@
         <v>45888</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28185,7 +28185,7 @@
         <v>44949</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28258,7 +28258,7 @@
         <v>45826</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28331,7 +28331,7 @@
         <v>45889</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28404,7 +28404,7 @@
         <v>45742</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28477,7 +28477,7 @@
         <v>45770</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28550,7 +28550,7 @@
         <v>45309</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28623,7 +28623,7 @@
         <v>44487</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28696,7 +28696,7 @@
         <v>45161</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28769,7 +28769,7 @@
         <v>45118</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28842,7 +28842,7 @@
         <v>45839</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28915,7 +28915,7 @@
         <v>46003</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28988,7 +28988,7 @@
         <v>45623</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29061,7 +29061,7 @@
         <v>46029</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29134,7 +29134,7 @@
         <v>45336</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29207,7 +29207,7 @@
         <v>46031</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29280,7 +29280,7 @@
         <v>45162</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29353,7 +29353,7 @@
         <v>45414</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29431,7 +29431,7 @@
         <v>46030</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29504,7 +29504,7 @@
         <v>46030</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29577,7 +29577,7 @@
         <v>45226</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29650,7 +29650,7 @@
         <v>45188</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29723,7 +29723,7 @@
         <v>46031</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29796,7 +29796,7 @@
         <v>45898</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29869,7 +29869,7 @@
         <v>44916</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29942,7 +29942,7 @@
         <v>44916</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30015,7 +30015,7 @@
         <v>45701</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30093,7 +30093,7 @@
         <v>45082</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30166,7 +30166,7 @@
         <v>45461</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30239,7 +30239,7 @@
         <v>45163</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30312,7 +30312,7 @@
         <v>45819</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30385,7 +30385,7 @@
         <v>45188</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30458,7 +30458,7 @@
         <v>44655</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30531,7 +30531,7 @@
         <v>45737</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30604,7 +30604,7 @@
         <v>45587</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30677,7 +30677,7 @@
         <v>45580</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30750,7 +30750,7 @@
         <v>45902</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30823,7 +30823,7 @@
         <v>45191</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>44952</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30969,7 +30969,7 @@
         <v>45209</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31042,7 +31042,7 @@
         <v>44888</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31115,7 +31115,7 @@
         <v>45754</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31193,7 +31193,7 @@
         <v>45754</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31271,7 +31271,7 @@
         <v>45351</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31344,7 +31344,7 @@
         <v>45628</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31417,7 +31417,7 @@
         <v>44972</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31490,7 +31490,7 @@
         <v>45097</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31563,7 +31563,7 @@
         <v>45792</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31636,7 +31636,7 @@
         <v>45911</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31709,7 +31709,7 @@
         <v>45911</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31782,7 +31782,7 @@
         <v>44770</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31855,7 +31855,7 @@
         <v>45572</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31928,7 +31928,7 @@
         <v>46044</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32001,7 +32001,7 @@
         <v>46045</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32074,7 +32074,7 @@
         <v>44916</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32147,7 +32147,7 @@
         <v>46048</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32220,7 +32220,7 @@
         <v>46048</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32293,7 +32293,7 @@
         <v>46048</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32366,7 +32366,7 @@
         <v>45741</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32444,7 +32444,7 @@
         <v>45741</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32522,7 +32522,7 @@
         <v>45728</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32595,7 +32595,7 @@
         <v>45259</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32668,7 +32668,7 @@
         <v>45190</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32741,7 +32741,7 @@
         <v>45610</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32814,7 +32814,7 @@
         <v>45743</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32887,7 +32887,7 @@
         <v>45737</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32960,7 +32960,7 @@
         <v>45737</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33033,7 +33033,7 @@
         <v>46049</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33106,7 +33106,7 @@
         <v>46048</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33179,7 +33179,7 @@
         <v>45742</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33252,7 +33252,7 @@
         <v>45733</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33325,7 +33325,7 @@
         <v>45733</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33398,7 +33398,7 @@
         <v>45803</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33471,7 +33471,7 @@
         <v>45743</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33544,7 +33544,7 @@
         <v>45442</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33617,7 +33617,7 @@
         <v>45708</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33690,7 +33690,7 @@
         <v>44592</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33763,7 +33763,7 @@
         <v>45448</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33836,7 +33836,7 @@
         <v>45616</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33909,7 +33909,7 @@
         <v>45359</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33982,7 +33982,7 @@
         <v>45166</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34055,7 +34055,7 @@
         <v>45805</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34128,7 +34128,7 @@
         <v>45580</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34201,7 +34201,7 @@
         <v>45922</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34274,7 +34274,7 @@
         <v>45625</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34347,7 +34347,7 @@
         <v>45362</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34420,7 +34420,7 @@
         <v>45925</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34493,7 +34493,7 @@
         <v>46055</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         <v>45133</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34639,7 +34639,7 @@
         <v>44977</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34712,7 +34712,7 @@
         <v>45434</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34785,7 +34785,7 @@
         <v>45545</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34858,7 +34858,7 @@
         <v>45104</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34931,7 +34931,7 @@
         <v>45645</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35004,7 +35004,7 @@
         <v>45645</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35082,7 +35082,7 @@
         <v>45754</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35160,7 +35160,7 @@
         <v>45135</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35233,7 +35233,7 @@
         <v>45135</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35306,7 +35306,7 @@
         <v>45135</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35379,7 +35379,7 @@
         <v>45931</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35452,7 +35452,7 @@
         <v>44641</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35525,7 +35525,7 @@
         <v>44482</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35598,7 +35598,7 @@
         <v>46062</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35671,7 +35671,7 @@
         <v>46063</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35744,7 +35744,7 @@
         <v>45042</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35817,7 +35817,7 @@
         <v>46063</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35890,7 +35890,7 @@
         <v>46063</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35963,7 +35963,7 @@
         <v>46063</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36036,7 +36036,7 @@
         <v>45329</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36109,7 +36109,7 @@
         <v>45329</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36182,7 +36182,7 @@
         <v>45117</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36255,7 +36255,7 @@
         <v>45811</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36328,7 +36328,7 @@
         <v>45936</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36401,7 +36401,7 @@
         <v>44888</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36474,7 +36474,7 @@
         <v>45099</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36547,7 +36547,7 @@
         <v>45610</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36620,7 +36620,7 @@
         <v>45742</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36693,7 +36693,7 @@
         <v>44984</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36766,7 +36766,7 @@
         <v>45228</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>45441</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36912,7 +36912,7 @@
         <v>45274</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36985,7 +36985,7 @@
         <v>44693</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37058,7 +37058,7 @@
         <v>45615</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37131,7 +37131,7 @@
         <v>46077</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37204,7 +37204,7 @@
         <v>45944</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37277,7 +37277,7 @@
         <v>45595</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37350,7 +37350,7 @@
         <v>45330</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37423,7 +37423,7 @@
         <v>45505</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37496,7 +37496,7 @@
         <v>46077</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37569,7 +37569,7 @@
         <v>45202</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37642,7 +37642,7 @@
         <v>45702</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37715,7 +37715,7 @@
         <v>45376</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37788,7 +37788,7 @@
         <v>45946</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37861,7 +37861,7 @@
         <v>45363</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37939,7 +37939,7 @@
         <v>44916</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38012,7 +38012,7 @@
         <v>44531</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38085,7 +38085,7 @@
         <v>45950</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38158,7 +38158,7 @@
         <v>45365</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38231,7 +38231,7 @@
         <v>45414</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38309,7 +38309,7 @@
         <v>45953</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38382,7 +38382,7 @@
         <v>46084</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38455,7 +38455,7 @@
         <v>46084</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38528,7 +38528,7 @@
         <v>45107</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38601,7 +38601,7 @@
         <v>45251</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38674,7 +38674,7 @@
         <v>46084</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38747,7 +38747,7 @@
         <v>45319</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38820,7 +38820,7 @@
         <v>44515</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38898,7 +38898,7 @@
         <v>44984</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38971,7 +38971,7 @@
         <v>45232</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39044,7 +39044,7 @@
         <v>45462</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39117,7 +39117,7 @@
         <v>44984</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39190,7 +39190,7 @@
         <v>44984</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39263,7 +39263,7 @@
         <v>45357</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39336,7 +39336,7 @@
         <v>45812</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39409,7 +39409,7 @@
         <v>45048</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39482,7 +39482,7 @@
         <v>46087</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39555,7 +39555,7 @@
         <v>45816</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39628,7 +39628,7 @@
         <v>46091</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39701,7 +39701,7 @@
         <v>45581</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39779,7 +39779,7 @@
         <v>44945</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39852,7 +39852,7 @@
         <v>45006</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39925,7 +39925,7 @@
         <v>46092</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39998,7 +39998,7 @@
         <v>45069</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40071,7 +40071,7 @@
         <v>45484</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40144,7 +40144,7 @@
         <v>46002</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40217,7 +40217,7 @@
         <v>46097</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40290,7 +40290,7 @@
         <v>45015</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40363,7 +40363,7 @@
         <v>45310</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40436,7 +40436,7 @@
         <v>45351</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40509,7 +40509,7 @@
         <v>46098</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40582,7 +40582,7 @@
         <v>45170</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40655,7 +40655,7 @@
         <v>46099</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40728,7 +40728,7 @@
         <v>45097</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40801,7 +40801,7 @@
         <v>46100</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40874,7 +40874,7 @@
         <v>46104</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40947,7 +40947,7 @@
         <v>45684</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41025,7 +41025,7 @@
         <v>45330</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41098,7 +41098,7 @@
         <v>46104</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41171,7 +41171,7 @@
         <v>45974</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41244,7 +41244,7 @@
         <v>44946</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41317,7 +41317,7 @@
         <v>45975</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41390,7 +41390,7 @@
         <v>45107</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41463,7 +41463,7 @@
         <v>45819</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41536,7 +41536,7 @@
         <v>45099</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41609,7 +41609,7 @@
         <v>46107</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41682,7 +41682,7 @@
         <v>45981</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41760,7 +41760,7 @@
         <v>45819</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41833,7 +41833,7 @@
         <v>45819</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41906,7 +41906,7 @@
         <v>45981</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41979,7 +41979,7 @@
         <v>45352</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42052,7 +42052,7 @@
         <v>46107</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42125,7 +42125,7 @@
         <v>45819</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42198,7 +42198,7 @@
         <v>45981</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42271,7 +42271,7 @@
         <v>46107</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42344,7 +42344,7 @@
         <v>45982</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42417,7 +42417,7 @@
         <v>46111</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42490,7 +42490,7 @@
         <v>45981</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42563,7 +42563,7 @@
         <v>46111</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42636,7 +42636,7 @@
         <v>44837</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42709,7 +42709,7 @@
         <v>45351</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42782,7 +42782,7 @@
         <v>44484</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>45748</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42933,7 +42933,7 @@
         <v>45748</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43011,7 +43011,7 @@
         <v>45992</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43084,7 +43084,7 @@
         <v>46121</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43157,7 +43157,7 @@
         <v>46122</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43230,7 +43230,7 @@
         <v>45992</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43303,7 +43303,7 @@
         <v>46121</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43376,7 +43376,7 @@
         <v>44965</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43449,7 +43449,7 @@
         <v>46126</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43522,7 +43522,7 @@
         <v>46128</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43595,7 +43595,7 @@
         <v>46128</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43668,7 +43668,7 @@
         <v>46128</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43741,7 +43741,7 @@
         <v>44970</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43814,7 +43814,7 @@
         <v>46128</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43887,7 +43887,7 @@
         <v>45999</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43960,7 +43960,7 @@
         <v>45133</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44033,7 +44033,7 @@
         <v>45999</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44106,7 +44106,7 @@
         <v>45357</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44179,7 +44179,7 @@
         <v>46127</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44252,7 +44252,7 @@
         <v>46128</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44325,7 +44325,7 @@
         <v>45231</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44398,7 +44398,7 @@
         <v>46133</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44471,7 +44471,7 @@
         <v>46133</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44544,7 +44544,7 @@
         <v>44545</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44617,7 +44617,7 @@
         <v>45681</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44690,7 +44690,7 @@
         <v>45152</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44763,7 +44763,7 @@
         <v>44503</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44836,7 +44836,7 @@
         <v>45230</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44914,7 +44914,7 @@
         <v>44480</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44987,7 +44987,7 @@
         <v>44741</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45060,7 +45060,7 @@
         <v>45272</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45133,7 +45133,7 @@
         <v>45084</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45206,7 +45206,7 @@
         <v>44600</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45279,7 +45279,7 @@
         <v>45903</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45352,7 +45352,7 @@
         <v>45331</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45425,7 +45425,7 @@
         <v>45331</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45498,7 +45498,7 @@
         <v>45222</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45571,7 +45571,7 @@
         <v>44970</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45644,7 +45644,7 @@
         <v>45671</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45717,7 +45717,7 @@
         <v>45435</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45790,7 +45790,7 @@
         <v>45230</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45868,7 +45868,7 @@
         <v>45204</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45941,7 +45941,7 @@
         <v>45839</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46014,7 +46014,7 @@
         <v>45699</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46087,7 +46087,7 @@
         <v>45827</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46160,7 +46160,7 @@
         <v>45455</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46233,7 +46233,7 @@
         <v>46037</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46306,7 +46306,7 @@
         <v>45561</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46379,7 +46379,7 @@
         <v>45737</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46452,7 +46452,7 @@
         <v>45944</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46525,7 +46525,7 @@
         <v>45112</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46598,7 +46598,7 @@
         <v>45282</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46671,7 +46671,7 @@
         <v>45245</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46744,7 +46744,7 @@
         <v>45891</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46817,7 +46817,7 @@
         <v>45631</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46890,7 +46890,7 @@
         <v>45247</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46963,7 +46963,7 @@
         <v>45838</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47036,7 +47036,7 @@
         <v>45313</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47109,7 +47109,7 @@
         <v>45799</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47182,7 +47182,7 @@
         <v>45306</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47255,7 +47255,7 @@
         <v>45259</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47328,7 +47328,7 @@
         <v>45839</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47401,7 +47401,7 @@
         <v>45370</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47474,7 +47474,7 @@
         <v>45931</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47547,7 +47547,7 @@
         <v>45322</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47620,7 +47620,7 @@
         <v>44510</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47693,7 +47693,7 @@
         <v>45895</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47766,7 +47766,7 @@
         <v>45035</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47839,7 +47839,7 @@
         <v>45840</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47912,7 +47912,7 @@
         <v>45840</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47985,7 +47985,7 @@
         <v>45883</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48058,7 +48058,7 @@
         <v>45645</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48136,7 +48136,7 @@
         <v>45645</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48214,7 +48214,7 @@
         <v>45845</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48287,7 +48287,7 @@
         <v>45076</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48360,7 +48360,7 @@
         <v>45006</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48433,7 +48433,7 @@
         <v>44580</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48506,7 +48506,7 @@
         <v>45089</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48579,7 +48579,7 @@
         <v>45729</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48652,7 +48652,7 @@
         <v>45748</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48725,7 +48725,7 @@
         <v>45747</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48798,7 +48798,7 @@
         <v>45625</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48871,7 +48871,7 @@
         <v>45615</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48944,7 +48944,7 @@
         <v>45715</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49017,7 +49017,7 @@
         <v>45715</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49090,7 +49090,7 @@
         <v>45902</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49163,7 +49163,7 @@
         <v>44834</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49236,7 +49236,7 @@
         <v>46112</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49314,7 +49314,7 @@
         <v>45965</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49387,7 +49387,7 @@
         <v>45847</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49460,7 +49460,7 @@
         <v>45525</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49533,7 +49533,7 @@
         <v>45785</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49606,7 +49606,7 @@
         <v>45538</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49679,7 +49679,7 @@
         <v>45912</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49752,7 +49752,7 @@
         <v>45298</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49825,7 +49825,7 @@
         <v>45763</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49898,7 +49898,7 @@
         <v>45840</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49971,7 +49971,7 @@
         <v>45372</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50044,7 +50044,7 @@
         <v>45866</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50117,7 +50117,7 @@
         <v>45925</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50190,7 +50190,7 @@
         <v>45076</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50263,7 +50263,7 @@
         <v>45971</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50336,7 +50336,7 @@
         <v>44473</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50409,7 +50409,7 @@
         <v>45170</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50482,7 +50482,7 @@
         <v>45401</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50555,7 +50555,7 @@
         <v>45852</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50628,7 +50628,7 @@
         <v>44607</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50701,7 +50701,7 @@
         <v>46006</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50774,7 +50774,7 @@
         <v>45763</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50847,7 +50847,7 @@
         <v>44837</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50920,7 +50920,7 @@
         <v>45693</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50993,7 +50993,7 @@
         <v>44511</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51066,7 +51066,7 @@
         <v>45889</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51139,7 +51139,7 @@
         <v>45089</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51212,7 +51212,7 @@
         <v>45443</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51285,7 +51285,7 @@
         <v>45240</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51358,7 +51358,7 @@
         <v>45168</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51431,7 +51431,7 @@
         <v>45785</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51504,7 +51504,7 @@
         <v>45321</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51577,7 +51577,7 @@
         <v>45163</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51650,7 +51650,7 @@
         <v>45841</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51723,7 +51723,7 @@
         <v>45608</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51796,7 +51796,7 @@
         <v>45873</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51869,7 +51869,7 @@
         <v>44510</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51942,7 +51942,7 @@
         <v>45971</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52015,7 +52015,7 @@
         <v>45610</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52088,7 +52088,7 @@
         <v>46122</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52161,7 +52161,7 @@
         <v>45153</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52234,7 +52234,7 @@
         <v>45755</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52307,7 +52307,7 @@
         <v>45670</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52380,7 +52380,7 @@
         <v>45825</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52453,7 +52453,7 @@
         <v>45348</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52526,7 +52526,7 @@
         <v>45839</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52599,7 +52599,7 @@
         <v>45672</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52672,7 +52672,7 @@
         <v>45163</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52745,7 +52745,7 @@
         <v>45211</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52818,7 +52818,7 @@
         <v>44538</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52891,7 +52891,7 @@
         <v>44549</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52964,7 +52964,7 @@
         <v>45322</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53037,7 +53037,7 @@
         <v>44785</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53110,7 +53110,7 @@
         <v>46052</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53183,7 +53183,7 @@
         <v>45883</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53256,7 +53256,7 @@
         <v>45414</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53329,7 +53329,7 @@
         <v>44894</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53402,7 +53402,7 @@
         <v>45519</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53475,7 +53475,7 @@
         <v>45691</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53553,7 +53553,7 @@
         <v>45005</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53626,7 +53626,7 @@
         <v>45314</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53699,7 +53699,7 @@
         <v>45433</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53772,7 +53772,7 @@
         <v>45097</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53845,7 +53845,7 @@
         <v>45448</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53918,7 +53918,7 @@
         <v>44564</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53991,7 +53991,7 @@
         <v>45645</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54069,7 +54069,7 @@
         <v>45645</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54147,7 +54147,7 @@
         <v>45644</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54220,7 +54220,7 @@
         <v>45649</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54298,7 +54298,7 @@
         <v>45866</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54371,7 +54371,7 @@
         <v>45288</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54444,7 +54444,7 @@
         <v>45733</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54517,7 +54517,7 @@
         <v>45114</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54590,7 +54590,7 @@
         <v>44858</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54663,7 +54663,7 @@
         <v>45545</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54736,7 +54736,7 @@
         <v>45250</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54809,7 +54809,7 @@
         <v>45224</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54887,7 +54887,7 @@
         <v>45113</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54960,7 +54960,7 @@
         <v>45827</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55033,7 +55033,7 @@
         <v>45645</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55111,7 +55111,7 @@
         <v>45763</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55184,7 +55184,7 @@
         <v>45672</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55257,7 +55257,7 @@
         <v>45589</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55330,7 +55330,7 @@
         <v>45264</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55403,7 +55403,7 @@
         <v>45525</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55476,7 +55476,7 @@
         <v>44965</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55549,7 +55549,7 @@
         <v>44926</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55622,7 +55622,7 @@
         <v>44926</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55695,7 +55695,7 @@
         <v>45401</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55768,7 +55768,7 @@
         <v>45392</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55841,7 +55841,7 @@
         <v>45394</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55914,7 +55914,7 @@
         <v>44602</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55987,7 +55987,7 @@
         <v>45007</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56060,7 +56060,7 @@
         <v>45568</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56138,7 +56138,7 @@
         <v>45297</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56211,7 +56211,7 @@
         <v>45236</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56284,7 +56284,7 @@
         <v>45625</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56357,7 +56357,7 @@
         <v>46153</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56430,7 +56430,7 @@
         <v>45105</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56503,7 +56503,7 @@
         <v>44859</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56576,7 +56576,7 @@
         <v>46153</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56649,7 +56649,7 @@
         <v>46153</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56722,7 +56722,7 @@
         <v>45674</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56795,7 +56795,7 @@
         <v>46153</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56868,7 +56868,7 @@
         <v>46154</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56946,7 +56946,7 @@
         <v>45866</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57019,7 +57019,7 @@
         <v>45639</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57092,7 +57092,7 @@
         <v>44481</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57165,7 +57165,7 @@
         <v>46126</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57238,7 +57238,7 @@
         <v>45875</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57311,7 +57311,7 @@
         <v>45400</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57389,7 +57389,7 @@
         <v>44655</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57462,7 +57462,7 @@
         <v>46160</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57535,7 +57535,7 @@
         <v>44970</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57608,7 +57608,7 @@
         <v>45329</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57681,7 +57681,7 @@
         <v>46161</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57754,7 +57754,7 @@
         <v>44847</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57827,7 +57827,7 @@
         <v>46160</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57900,7 +57900,7 @@
         <v>45761</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57973,7 +57973,7 @@
         <v>46160</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58046,7 +58046,7 @@
         <v>45180</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58119,7 +58119,7 @@
         <v>45173</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58192,7 +58192,7 @@
         <v>45173</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58265,7 +58265,7 @@
         <v>46064</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58338,7 +58338,7 @@
         <v>45875</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58411,7 +58411,7 @@
         <v>45930</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58484,7 +58484,7 @@
         <v>45345</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58557,7 +58557,7 @@
         <v>46160</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58630,7 +58630,7 @@
         <v>45526</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58703,7 +58703,7 @@
         <v>45875</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58776,7 +58776,7 @@
         <v>45170</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58849,7 +58849,7 @@
         <v>45170</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58922,7 +58922,7 @@
         <v>46163</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58995,7 +58995,7 @@
         <v>46161</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59068,7 +59068,7 @@
         <v>45303</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59141,7 +59141,7 @@
         <v>45104</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59214,7 +59214,7 @@
         <v>45930</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59292,7 +59292,7 @@
         <v>45113</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59365,7 +59365,7 @@
         <v>45446</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59438,7 +59438,7 @@
         <v>45438</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59511,7 +59511,7 @@
         <v>45182</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59589,7 +59589,7 @@
         <v>45182</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59662,7 +59662,7 @@
         <v>44607</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59735,7 +59735,7 @@
         <v>45669</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59808,7 +59808,7 @@
         <v>45882</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59881,7 +59881,7 @@
         <v>45315</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59954,7 +59954,7 @@
         <v>45462</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60027,7 +60027,7 @@
         <v>45882</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60100,7 +60100,7 @@
         <v>46175</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60173,7 +60173,7 @@
         <v>45884</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60246,7 +60246,7 @@
         <v>45449</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60319,7 +60319,7 @@
         <v>45327</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60392,7 +60392,7 @@
         <v>45164</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60465,7 +60465,7 @@
         <v>46178</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60538,7 +60538,7 @@
         <v>45330</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60611,7 +60611,7 @@
         <v>46178</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60684,7 +60684,7 @@
         <v>46178</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60757,7 +60757,7 @@
         <v>46178</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60830,7 +60830,7 @@
         <v>46178</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60903,7 +60903,7 @@
         <v>46178</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60976,7 +60976,7 @@
         <v>44995</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61049,7 +61049,7 @@
         <v>45692</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61122,7 +61122,7 @@
         <v>46182</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61195,7 +61195,7 @@
         <v>46182</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61268,7 +61268,7 @@
         <v>45106</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61341,7 +61341,7 @@
         <v>45574</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61419,7 +61419,7 @@
         <v>46182</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61492,7 +61492,7 @@
         <v>45616</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61565,7 +61565,7 @@
         <v>45510</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61638,7 +61638,7 @@
         <v>46184</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61711,7 +61711,7 @@
         <v>45219</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61789,7 +61789,7 @@
         <v>45274</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61862,7 +61862,7 @@
         <v>46184</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61935,7 +61935,7 @@
         <v>45250</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62008,7 +62008,7 @@
         <v>46184</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62081,7 +62081,7 @@
         <v>46185</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62154,7 +62154,7 @@
         <v>44587</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62227,7 +62227,7 @@
         <v>46188</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62300,7 +62300,7 @@
         <v>44783</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62373,7 +62373,7 @@
         <v>46185</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62446,7 +62446,7 @@
         <v>44830</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62519,7 +62519,7 @@
         <v>45544</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62592,7 +62592,7 @@
         <v>45133</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62665,7 +62665,7 @@
         <v>45408</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62738,7 +62738,7 @@
         <v>44834</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62811,7 +62811,7 @@
         <v>45366</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62884,7 +62884,7 @@
         <v>44815</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62957,7 +62957,7 @@
         <v>45069</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63030,7 +63030,7 @@
         <v>45440</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63103,7 +63103,7 @@
         <v>46190</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63176,7 +63176,7 @@
         <v>45701</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63254,7 +63254,7 @@
         <v>45302</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63327,7 +63327,7 @@
         <v>45615</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63400,7 +63400,7 @@
         <v>45113</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63473,7 +63473,7 @@
         <v>44683</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63546,7 +63546,7 @@
         <v>45925</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63619,7 +63619,7 @@
         <v>45546</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63692,7 +63692,7 @@
         <v>44839</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63765,7 +63765,7 @@
         <v>44970</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63838,7 +63838,7 @@
         <v>46195</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63911,7 +63911,7 @@
         <v>45222</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63984,7 +63984,7 @@
         <v>45183</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64057,7 +64057,7 @@
         <v>46196</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64130,7 +64130,7 @@
         <v>46196</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64203,7 +64203,7 @@
         <v>44965</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64276,7 +64276,7 @@
         <v>45000</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64349,7 +64349,7 @@
         <v>45183</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64422,7 +64422,7 @@
         <v>45706</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64495,7 +64495,7 @@
         <v>46197</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64568,7 +64568,7 @@
         <v>44839</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64641,7 +64641,7 @@
         <v>44753</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64714,7 +64714,7 @@
         <v>45135</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64787,7 +64787,7 @@
         <v>46197</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64860,7 +64860,7 @@
         <v>46202</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64933,7 +64933,7 @@
         <v>44802</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65011,7 +65011,7 @@
         <v>45446</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65084,7 +65084,7 @@
         <v>46204</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65157,7 +65157,7 @@
         <v>44929</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65230,7 +65230,7 @@
         <v>44743</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65303,7 +65303,7 @@
         <v>44481</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65376,7 +65376,7 @@
         <v>45170</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65449,7 +65449,7 @@
         <v>45497</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65522,7 +65522,7 @@
         <v>45497</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65595,7 +65595,7 @@
         <v>45119</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65668,7 +65668,7 @@
         <v>45401</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65741,7 +65741,7 @@
         <v>44952</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65814,7 +65814,7 @@
         <v>45112</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65887,7 +65887,7 @@
         <v>45107</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65960,7 +65960,7 @@
         <v>44747</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66033,7 +66033,7 @@
         <v>45526</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66106,7 +66106,7 @@
         <v>44600</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66179,7 +66179,7 @@
         <v>45569</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66252,7 +66252,7 @@
         <v>44930</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66325,7 +66325,7 @@
         <v>46069</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66398,7 +66398,7 @@
         <v>46259</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66471,7 +66471,7 @@
         <v>45033</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66544,7 +66544,7 @@
         <v>45572</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66617,7 +66617,7 @@
         <v>45341</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66690,7 +66690,7 @@
         <v>45348</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66763,7 +66763,7 @@
         <v>46213</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66836,7 +66836,7 @@
         <v>46168</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66909,7 +66909,7 @@
         <v>46258</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66982,7 +66982,7 @@
         <v>46259</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67055,7 +67055,7 @@
         <v>46177</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67128,7 +67128,7 @@
         <v>44740</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67206,7 +67206,7 @@
         <v>45406</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67279,7 +67279,7 @@
         <v>44998</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67352,7 +67352,7 @@
         <v>45302</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67425,7 +67425,7 @@
         <v>44869</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67498,7 +67498,7 @@
         <v>45174</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67571,7 +67571,7 @@
         <v>46265</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67644,7 +67644,7 @@
         <v>45363</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67722,7 +67722,7 @@
         <v>45363</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -67800,7 +67800,7 @@
         <v>45363</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -67878,7 +67878,7 @@
         <v>45364</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67951,7 +67951,7 @@
         <v>45104</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -68024,7 +68024,7 @@
         <v>45281</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -68097,7 +68097,7 @@
         <v>45525</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -68170,7 +68170,7 @@
         <v>45006</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -68243,7 +68243,7 @@
         <v>45202</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -68316,7 +68316,7 @@
         <v>45563</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -68394,7 +68394,7 @@
         <v>45357</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68467,7 +68467,7 @@
         <v>45173</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68540,7 +68540,7 @@
         <v>46269</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68613,7 +68613,7 @@
         <v>45629</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -68686,7 +68686,7 @@
         <v>46268</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -68759,7 +68759,7 @@
         <v>45314</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -68832,7 +68832,7 @@
         <v>45420</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68905,7 +68905,7 @@
         <v>45195</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -68978,7 +68978,7 @@
         <v>45238</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -69056,7 +69056,7 @@
         <v>44880</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -69129,7 +69129,7 @@
         <v>44880</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -69202,7 +69202,7 @@
         <v>45079</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -69275,7 +69275,7 @@
         <v>45091</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -69348,7 +69348,7 @@
         <v>46273</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -69421,7 +69421,7 @@
         <v>44602</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -69494,7 +69494,7 @@
         <v>45163</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69567,7 +69567,7 @@
         <v>46258</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -69640,7 +69640,7 @@
         <v>46274</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -69713,7 +69713,7 @@
         <v>46273</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -69786,7 +69786,7 @@
         <v>44523</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -69859,7 +69859,7 @@
         <v>46234</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -69932,7 +69932,7 @@
         <v>46276</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -70005,7 +70005,7 @@
         <v>46276</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -70078,7 +70078,7 @@
         <v>46234</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -70151,7 +70151,7 @@
         <v>46279</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -70224,7 +70224,7 @@
         <v>46276</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -70297,7 +70297,7 @@
         <v>46276</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -70370,7 +70370,7 @@
         <v>46276</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -70443,7 +70443,7 @@
         <v>46233</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -70516,7 +70516,7 @@
         <v>46234</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70589,7 +70589,7 @@
         <v>44677</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -70662,7 +70662,7 @@
         <v>46237</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -70735,7 +70735,7 @@
         <v>45303</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -70808,7 +70808,7 @@
         <v>44592</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -70881,7 +70881,7 @@
         <v>45475</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -70954,7 +70954,7 @@
         <v>45211</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -71027,7 +71027,7 @@
         <v>45352</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -71100,7 +71100,7 @@
         <v>45538</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -71173,7 +71173,7 @@
         <v>46240</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -71246,7 +71246,7 @@
         <v>45329</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -71324,7 +71324,7 @@
         <v>45314</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -71397,7 +71397,7 @@
         <v>45645</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -71475,7 +71475,7 @@
         <v>44815</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -71548,7 +71548,7 @@
         <v>44497</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -71621,7 +71621,7 @@
         <v>45091</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -71694,7 +71694,7 @@
         <v>45022</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -71767,7 +71767,7 @@
         <v>46283</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -71840,7 +71840,7 @@
         <v>45526</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -71913,7 +71913,7 @@
         <v>45114</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -71986,7 +71986,7 @@
         <v>45440</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -72059,7 +72059,7 @@
         <v>44587</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -72132,7 +72132,7 @@
         <v>44715</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -72205,7 +72205,7 @@
         <v>44813</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -72278,7 +72278,7 @@
         <v>45365</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -72351,7 +72351,7 @@
         <v>45385</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -72424,7 +72424,7 @@
         <v>46244</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -72497,7 +72497,7 @@
         <v>45953</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -72570,7 +72570,7 @@
         <v>44946</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -72643,7 +72643,7 @@
         <v>46245</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -72716,7 +72716,7 @@
         <v>46244</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -72789,7 +72789,7 @@
         <v>44805</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -72862,7 +72862,7 @@
         <v>44813</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -72935,7 +72935,7 @@
         <v>46289</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -73008,7 +73008,7 @@
         <v>45398</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -73081,7 +73081,7 @@
         <v>46289</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -73154,7 +73154,7 @@
         <v>45307</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -73227,7 +73227,7 @@
         <v>44825</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -73300,7 +73300,7 @@
         <v>44917</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -73373,7 +73373,7 @@
         <v>45177</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -73451,7 +73451,7 @@
         <v>45174</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -73529,7 +73529,7 @@
         <v>46246</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -73602,7 +73602,7 @@
         <v>45329</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -73675,7 +73675,7 @@
         <v>46280</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -73748,7 +73748,7 @@
         <v>46293</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -73821,7 +73821,7 @@
         <v>45245</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -73894,7 +73894,7 @@
         <v>46178</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -73967,7 +73967,7 @@
         <v>45737</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -74040,7 +74040,7 @@
         <v>45719</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -74113,7 +74113,7 @@
         <v>46178</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -74186,7 +74186,7 @@
         <v>45364</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -74259,7 +74259,7 @@
         <v>45089</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -74332,7 +74332,7 @@
         <v>45660</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -74405,7 +74405,7 @@
         <v>45107</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -74478,7 +74478,7 @@
         <v>45184</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -74551,7 +74551,7 @@
         <v>46293</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -74624,7 +74624,7 @@
         <v>46293</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -74697,7 +74697,7 @@
         <v>45589</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -74770,7 +74770,7 @@
         <v>45589</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -74843,7 +74843,7 @@
         <v>45532</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -74916,7 +74916,7 @@
         <v>45370</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -74989,7 +74989,7 @@
         <v>46290</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -75062,7 +75062,7 @@
         <v>45925</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -75135,7 +75135,7 @@
         <v>45406</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -75208,7 +75208,7 @@
         <v>46009</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -75281,7 +75281,7 @@
         <v>44595</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -75354,7 +75354,7 @@
         <v>45104</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -75427,7 +75427,7 @@
         <v>46252</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -75500,7 +75500,7 @@
         <v>45071</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -75573,7 +75573,7 @@
         <v>46294</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -75646,7 +75646,7 @@
         <v>45216</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -75719,7 +75719,7 @@
         <v>45303</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -75792,7 +75792,7 @@
         <v>46294</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -75865,7 +75865,7 @@
         <v>45678</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -75938,7 +75938,7 @@
         <v>45182</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -76011,7 +76011,7 @@
         <v>44495</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -76084,7 +76084,7 @@
         <v>45219</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -76157,7 +76157,7 @@
         <v>45030</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -76230,7 +76230,7 @@
         <v>45544</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -76303,7 +76303,7 @@
         <v>45691</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -76376,7 +76376,7 @@
         <v>46248</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -76454,7 +76454,7 @@
         <v>44488</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -76527,7 +76527,7 @@
         <v>46296</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -76600,7 +76600,7 @@
         <v>45631</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -76673,7 +76673,7 @@
         <v>46247</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -76751,7 +76751,7 @@
         <v>46247</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -76829,7 +76829,7 @@
         <v>45216</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -76907,7 +76907,7 @@
         <v>46297</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -76980,7 +76980,7 @@
         <v>46296</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -77053,7 +77053,7 @@
         <v>45359</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -77126,7 +77126,7 @@
         <v>46297</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -77199,7 +77199,7 @@
         <v>45936</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -77272,7 +77272,7 @@
         <v>46062</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -77345,7 +77345,7 @@
         <v>46295</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -77418,7 +77418,7 @@
         <v>46031</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -77491,7 +77491,7 @@
         <v>45376</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -77564,7 +77564,7 @@
         <v>44810</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -77637,7 +77637,7 @@
         <v>45209</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -77710,7 +77710,7 @@
         <v>45183</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -77783,7 +77783,7 @@
         <v>45595</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -77856,7 +77856,7 @@
         <v>45575</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -77929,7 +77929,7 @@
         <v>45062</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -78002,7 +78002,7 @@
         <v>45231</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -78075,7 +78075,7 @@
         <v>45699</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -78148,7 +78148,7 @@
         <v>45737</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -78221,7 +78221,7 @@
         <v>44930</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -78294,7 +78294,7 @@
         <v>44971</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -78367,7 +78367,7 @@
         <v>45602</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -78440,7 +78440,7 @@
         <v>45092</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -78513,7 +78513,7 @@
         <v>45674</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -78586,7 +78586,7 @@
         <v>45478</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -78659,7 +78659,7 @@
         <v>45769</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -78737,7 +78737,7 @@
         <v>45164</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -78810,7 +78810,7 @@
         <v>45309</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -78883,7 +78883,7 @@
         <v>45309</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -78956,7 +78956,7 @@
         <v>45182</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -79034,7 +79034,7 @@
         <v>45329</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -79107,7 +79107,7 @@
         <v>45222</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -79180,7 +79180,7 @@
         <v>45492</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -79253,7 +79253,7 @@
         <v>45323</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -79326,7 +79326,7 @@
         <v>45763</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -79399,7 +79399,7 @@
         <v>45384</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -79472,7 +79472,7 @@
         <v>45296</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -79545,7 +79545,7 @@
         <v>45763</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -79618,7 +79618,7 @@
         <v>45763</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -79691,7 +79691,7 @@
         <v>45763</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -79764,7 +79764,7 @@
         <v>44946</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -79837,7 +79837,7 @@
         <v>45462</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -79910,7 +79910,7 @@
         <v>44879</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -79983,7 +79983,7 @@
         <v>45719</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -80056,7 +80056,7 @@
         <v>45540</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -80129,7 +80129,7 @@
         <v>45134</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -80202,7 +80202,7 @@
         <v>45316</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -80275,7 +80275,7 @@
         <v>45414</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -80348,7 +80348,7 @@
         <v>45607</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -80421,7 +80421,7 @@
         <v>44818</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -80494,7 +80494,7 @@
         <v>45673</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
@@ -80567,7 +80567,7 @@
         <v>44831</v>
       </c>
       <c r="E1032" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
@@ -80640,7 +80640,7 @@
         <v>45001</v>
       </c>
       <c r="E1033" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
@@ -80718,7 +80718,7 @@
         <v>45254</v>
       </c>
       <c r="E1034" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
@@ -80796,7 +80796,7 @@
         <v>45090</v>
       </c>
       <c r="E1035" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
@@ -80869,7 +80869,7 @@
         <v>45132</v>
       </c>
       <c r="E1036" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
@@ -80942,7 +80942,7 @@
         <v>45335</v>
       </c>
       <c r="E1037" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
@@ -81015,7 +81015,7 @@
         <v>45602</v>
       </c>
       <c r="E1038" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1038" t="inlineStr">
         <is>
@@ -81088,7 +81088,7 @@
         <v>44963</v>
       </c>
       <c r="E1039" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1039" t="inlineStr">
         <is>
@@ -81161,7 +81161,7 @@
         <v>45168</v>
       </c>
       <c r="E1040" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1040" t="inlineStr">
         <is>
@@ -81234,7 +81234,7 @@
         <v>45400</v>
       </c>
       <c r="E1041" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1041" t="inlineStr">
         <is>
@@ -81307,7 +81307,7 @@
         <v>45188</v>
       </c>
       <c r="E1042" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1042" t="inlineStr">
         <is>
@@ -81380,7 +81380,7 @@
         <v>45670</v>
       </c>
       <c r="E1043" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1043" t="inlineStr">
         <is>
@@ -81453,7 +81453,7 @@
         <v>44902</v>
       </c>
       <c r="E1044" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1044" t="inlineStr">
         <is>
@@ -81526,7 +81526,7 @@
         <v>44564</v>
       </c>
       <c r="E1045" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1045" t="inlineStr">
         <is>
@@ -81604,7 +81604,7 @@
         <v>45189</v>
       </c>
       <c r="E1046" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1046" t="inlineStr">
         <is>
@@ -81682,7 +81682,7 @@
         <v>45691</v>
       </c>
       <c r="E1047" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1047" t="inlineStr">
         <is>
@@ -81755,7 +81755,7 @@
         <v>44916</v>
       </c>
       <c r="E1048" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1048" t="inlineStr">
         <is>
@@ -81828,7 +81828,7 @@
         <v>44957</v>
       </c>
       <c r="E1049" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1049" t="inlineStr">
         <is>
@@ -81901,7 +81901,7 @@
         <v>44502</v>
       </c>
       <c r="E1050" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1050" t="inlineStr">
         <is>
@@ -81974,7 +81974,7 @@
         <v>45702</v>
       </c>
       <c r="E1051" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1051" t="inlineStr">
         <is>
@@ -82052,7 +82052,7 @@
         <v>45134</v>
       </c>
       <c r="E1052" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1052" t="inlineStr">
         <is>
@@ -82125,7 +82125,7 @@
         <v>45348</v>
       </c>
       <c r="E1053" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1053" t="inlineStr">
         <is>
@@ -82198,7 +82198,7 @@
         <v>45439</v>
       </c>
       <c r="E1054" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1054" t="inlineStr">
         <is>
@@ -82271,7 +82271,7 @@
         <v>44781</v>
       </c>
       <c r="E1055" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1055" t="inlineStr">
         <is>
@@ -82344,7 +82344,7 @@
         <v>45783</v>
       </c>
       <c r="E1056" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1056" t="inlineStr">
         <is>
@@ -82417,7 +82417,7 @@
         <v>45783</v>
       </c>
       <c r="E1057" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1057" t="inlineStr">
         <is>
@@ -82490,7 +82490,7 @@
         <v>45439</v>
       </c>
       <c r="E1058" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1058" t="inlineStr">
         <is>
@@ -82563,7 +82563,7 @@
         <v>45636</v>
       </c>
       <c r="E1059" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1059" t="inlineStr">
         <is>
@@ -82636,7 +82636,7 @@
         <v>45580</v>
       </c>
       <c r="E1060" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1060" t="inlineStr">
         <is>
@@ -82709,7 +82709,7 @@
         <v>45447</v>
       </c>
       <c r="E1061" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1061" t="inlineStr">
         <is>
@@ -82782,7 +82782,7 @@
         <v>45170</v>
       </c>
       <c r="E1062" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1062" t="inlineStr">
         <is>
@@ -82855,7 +82855,7 @@
         <v>45106</v>
       </c>
       <c r="E1063" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1063" t="inlineStr">
         <is>
@@ -82928,7 +82928,7 @@
         <v>45467</v>
       </c>
       <c r="E1064" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1064" t="inlineStr">
         <is>
@@ -83001,7 +83001,7 @@
         <v>44509</v>
       </c>
       <c r="E1065" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1065" t="inlineStr">
         <is>
@@ -83079,7 +83079,7 @@
         <v>45664</v>
       </c>
       <c r="E1066" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1066" t="inlineStr">
         <is>
@@ -83152,7 +83152,7 @@
         <v>45208</v>
       </c>
       <c r="E1067" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1067" t="inlineStr">
         <is>
@@ -83225,7 +83225,7 @@
         <v>45406</v>
       </c>
       <c r="E1068" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1068" t="inlineStr">
         <is>
@@ -83298,7 +83298,7 @@
         <v>45497</v>
       </c>
       <c r="E1069" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1069" t="inlineStr">
         <is>
@@ -83371,7 +83371,7 @@
         <v>45497</v>
       </c>
       <c r="E1070" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1070" t="inlineStr">
         <is>
@@ -83444,7 +83444,7 @@
         <v>45106</v>
       </c>
       <c r="E1071" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1071" t="inlineStr">
         <is>
@@ -83517,7 +83517,7 @@
         <v>45646</v>
       </c>
       <c r="E1072" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1072" t="inlineStr">
         <is>
@@ -83590,7 +83590,7 @@
         <v>45646</v>
       </c>
       <c r="E1073" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1073" t="inlineStr">
         <is>
@@ -83663,7 +83663,7 @@
         <v>45580</v>
       </c>
       <c r="E1074" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1074" t="inlineStr">
         <is>
@@ -83736,7 +83736,7 @@
         <v>45646</v>
       </c>
       <c r="E1075" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1075" t="inlineStr">
         <is>
@@ -83809,7 +83809,7 @@
         <v>45646</v>
       </c>
       <c r="E1076" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1076" t="inlineStr">
         <is>
@@ -83882,7 +83882,7 @@
         <v>45408</v>
       </c>
       <c r="E1077" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1077" t="inlineStr">
         <is>
@@ -83955,7 +83955,7 @@
         <v>45414</v>
       </c>
       <c r="E1078" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1078" t="inlineStr">
         <is>
@@ -84028,7 +84028,7 @@
         <v>45173</v>
       </c>
       <c r="E1079" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1079" t="inlineStr">
         <is>
@@ -84101,7 +84101,7 @@
         <v>45646</v>
       </c>
       <c r="E1080" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1080" t="inlineStr">
         <is>
@@ -84174,7 +84174,7 @@
         <v>45715</v>
       </c>
       <c r="E1081" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1081" t="inlineStr">
         <is>
@@ -84247,7 +84247,7 @@
         <v>45720</v>
       </c>
       <c r="E1082" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1082" t="inlineStr">
         <is>
@@ -84320,7 +84320,7 @@
         <v>45800</v>
       </c>
       <c r="E1083" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1083" t="inlineStr">
         <is>
@@ -84398,7 +84398,7 @@
         <v>45831</v>
       </c>
       <c r="E1084" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1084" t="inlineStr">
         <is>
@@ -84471,7 +84471,7 @@
         <v>45785</v>
       </c>
       <c r="E1085" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1085" t="inlineStr">
         <is>
@@ -84544,7 +84544,7 @@
         <v>46073</v>
       </c>
       <c r="E1086" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1086" t="inlineStr">
         <is>
@@ -84617,7 +84617,7 @@
         <v>46163</v>
       </c>
       <c r="E1087" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1087" t="inlineStr">
         <is>
@@ -84690,7 +84690,7 @@
         <v>46274</v>
       </c>
       <c r="E1088" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1088" t="inlineStr">
         <is>
@@ -84763,7 +84763,7 @@
         <v>46296</v>
       </c>
       <c r="E1089" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1089" t="inlineStr">
         <is>

--- a/Översikt VETLANDA.xlsx
+++ b/Översikt VETLANDA.xlsx
@@ -601,7 +601,7 @@
         <v>45097</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>46178</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         <v>45371</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>44817</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>44890</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>45183</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>45558</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>45168</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>46107</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>45930</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>45520</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>45957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>45754</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>45170</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>44612</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>46002</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>46100</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>44840</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>44908</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>45203</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>45819</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>46163</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>46188</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>44545</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>44564</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>46045</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>45599</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>45583</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>44819</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         <v>45763</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>45477</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         <v>45814</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>45048</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>46255</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4450,7 +4450,7 @@
         <v>45646</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>45131</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
         <v>44515</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>44752</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>44643</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         <v>45589</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5107,7 +5107,7 @@
         <v>45713</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>45965</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
         <v>45792</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>45673</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>45835</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>45840</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         <v>45713</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>44572</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>45891</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         <v>45860</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>45303</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>46166</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6387,7 +6387,7 @@
         <v>45148</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         <v>45357</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
         <v>45616</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6705,7 +6705,7 @@
         <v>46279</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6816,7 +6816,7 @@
         <v>45035</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>46293</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>45400</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>45211</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>45310</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>45106</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7461,7 +7461,7 @@
         <v>45509</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         <v>45497</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>45201</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         <v>45539</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         <v>46051</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         <v>44490</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
         <v>44834</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         <v>44721</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         <v>44747</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>44592</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8520,7 +8520,7 @@
         <v>44740</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
         <v>45596</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         <v>45597</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8840,7 +8840,7 @@
         <v>44830</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         <v>45643</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9050,7 +9050,7 @@
         <v>45835</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9155,7 +9155,7 @@
         <v>45791</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>45904</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9365,7 +9365,7 @@
         <v>45645</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9470,7 +9470,7 @@
         <v>45555</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9575,7 +9575,7 @@
         <v>45736</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
         <v>44781</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9789,7 +9789,7 @@
         <v>45021</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9894,7 +9894,7 @@
         <v>45586</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         <v>46069</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10104,7 +10104,7 @@
         <v>44748</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10209,7 +10209,7 @@
         <v>46071</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10314,7 +10314,7 @@
         <v>44824</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
         <v>45240</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10524,7 +10524,7 @@
         <v>44728</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10633,7 +10633,7 @@
         <v>45342</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10738,7 +10738,7 @@
         <v>45820</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10848,7 +10848,7 @@
         <v>45586</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10953,7 +10953,7 @@
         <v>45839</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
         <v>45775</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11163,7 +11163,7 @@
         <v>45239</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11273,7 +11273,7 @@
         <v>44998</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11378,7 +11378,7 @@
         <v>45880</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11483,7 +11483,7 @@
         <v>44880</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>46141</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>45419</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>45672</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
         <v>46188</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12016,7 +12016,7 @@
         <v>45085</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12121,7 +12121,7 @@
         <v>45408</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12226,7 +12226,7 @@
         <v>44819</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12331,7 +12331,7 @@
         <v>45119</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
         <v>45009</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12541,7 +12541,7 @@
         <v>45930</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12655,7 +12655,7 @@
         <v>45261</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
         <v>45378</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12865,7 +12865,7 @@
         <v>46248</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12970,7 +12970,7 @@
         <v>45104</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>44816</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13184,7 +13184,7 @@
         <v>45532</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         <v>44833</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13394,7 +13394,7 @@
         <v>46297</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13499,7 +13499,7 @@
         <v>45337</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13604,7 +13604,7 @@
         <v>45565</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>44916</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>45352</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13919,7 +13919,7 @@
         <v>45604</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14024,7 +14024,7 @@
         <v>45497</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14129,7 +14129,7 @@
         <v>45614</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14234,7 +14234,7 @@
         <v>45742</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14343,7 +14343,7 @@
         <v>44838</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>44858</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14489,7 +14489,7 @@
         <v>44781</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14562,7 +14562,7 @@
         <v>44732</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14635,7 +14635,7 @@
         <v>44781</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14708,7 +14708,7 @@
         <v>44515</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14781,7 +14781,7 @@
         <v>44504</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>44508</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14927,7 +14927,7 @@
         <v>44496</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15000,7 +15000,7 @@
         <v>44579</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15073,7 +15073,7 @@
         <v>44601</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15146,7 +15146,7 @@
         <v>44889</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15219,7 +15219,7 @@
         <v>44544</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15292,7 +15292,7 @@
         <v>44510</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15365,7 +15365,7 @@
         <v>44517</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15438,7 +15438,7 @@
         <v>44764</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15511,7 +15511,7 @@
         <v>44503</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15584,7 +15584,7 @@
         <v>44819</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>44592</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15730,7 +15730,7 @@
         <v>44750</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15803,7 +15803,7 @@
         <v>44825</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15876,7 +15876,7 @@
         <v>44488</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15949,7 +15949,7 @@
         <v>44602</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16022,7 +16022,7 @@
         <v>44638</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16095,7 +16095,7 @@
         <v>44510</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16168,7 +16168,7 @@
         <v>44721</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16241,7 +16241,7 @@
         <v>44510</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16314,7 +16314,7 @@
         <v>44785</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16387,7 +16387,7 @@
         <v>44592</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16460,7 +16460,7 @@
         <v>44587</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16533,7 +16533,7 @@
         <v>44782</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16606,7 +16606,7 @@
         <v>44815</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16679,7 +16679,7 @@
         <v>44504</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16752,7 +16752,7 @@
         <v>44580</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16825,7 +16825,7 @@
         <v>44691</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16898,7 +16898,7 @@
         <v>44880</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
         <v>44545</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17044,7 +17044,7 @@
         <v>44750</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17117,7 +17117,7 @@
         <v>44624</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17190,7 +17190,7 @@
         <v>44477</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>44595</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17336,7 +17336,7 @@
         <v>44820</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17409,7 +17409,7 @@
         <v>44816</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>44645</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17555,7 +17555,7 @@
         <v>44608</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17628,7 +17628,7 @@
         <v>44819</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
         <v>44656</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>44784</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17847,7 +17847,7 @@
         <v>44585</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17925,7 +17925,7 @@
         <v>44585</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18003,7 +18003,7 @@
         <v>44585</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18081,7 +18081,7 @@
         <v>44834</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>44740</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18232,7 +18232,7 @@
         <v>44750</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18305,7 +18305,7 @@
         <v>44587</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18378,7 +18378,7 @@
         <v>44743</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18451,7 +18451,7 @@
         <v>44474</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18524,7 +18524,7 @@
         <v>44600</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18597,7 +18597,7 @@
         <v>44859</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18670,7 +18670,7 @@
         <v>44593</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18743,7 +18743,7 @@
         <v>44743</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18816,7 +18816,7 @@
         <v>44778</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18889,7 +18889,7 @@
         <v>44504</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18962,7 +18962,7 @@
         <v>44834</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19035,7 +19035,7 @@
         <v>44477</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19108,7 +19108,7 @@
         <v>44482</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19181,7 +19181,7 @@
         <v>44509</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19254,7 +19254,7 @@
         <v>44517</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19327,7 +19327,7 @@
         <v>44592</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19400,7 +19400,7 @@
         <v>44572</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19473,7 +19473,7 @@
         <v>44721</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19546,7 +19546,7 @@
         <v>44841</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19619,7 +19619,7 @@
         <v>44888</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19692,7 +19692,7 @@
         <v>44587</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19765,7 +19765,7 @@
         <v>44655</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19838,7 +19838,7 @@
         <v>44502</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19911,7 +19911,7 @@
         <v>44515</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19989,7 +19989,7 @@
         <v>44592</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20062,7 +20062,7 @@
         <v>44564</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20135,7 +20135,7 @@
         <v>44781</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20208,7 +20208,7 @@
         <v>44531</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20281,7 +20281,7 @@
         <v>44636</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>44834</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20427,7 +20427,7 @@
         <v>44733</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20500,7 +20500,7 @@
         <v>44683</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20573,7 +20573,7 @@
         <v>44602</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20646,7 +20646,7 @@
         <v>44792</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20719,7 +20719,7 @@
         <v>44657</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20792,7 +20792,7 @@
         <v>44827</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20865,7 +20865,7 @@
         <v>44902</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20938,7 +20938,7 @@
         <v>44488</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21011,7 +21011,7 @@
         <v>45561</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21084,7 +21084,7 @@
         <v>45251</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>45674</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21230,7 +21230,7 @@
         <v>44477</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21303,7 +21303,7 @@
         <v>44998</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21376,7 +21376,7 @@
         <v>45351</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21449,7 +21449,7 @@
         <v>45602</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21522,7 +21522,7 @@
         <v>45265</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21595,7 +21595,7 @@
         <v>45267</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21668,7 +21668,7 @@
         <v>45575</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21741,7 +21741,7 @@
         <v>44880</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21814,7 +21814,7 @@
         <v>45569</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21892,7 +21892,7 @@
         <v>44903</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21965,7 +21965,7 @@
         <v>44967</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22038,7 +22038,7 @@
         <v>44967</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22111,7 +22111,7 @@
         <v>45175</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22184,7 +22184,7 @@
         <v>45580</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22257,7 +22257,7 @@
         <v>45278</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22330,7 +22330,7 @@
         <v>44936</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22403,7 +22403,7 @@
         <v>44792</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22476,7 +22476,7 @@
         <v>45264</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22549,7 +22549,7 @@
         <v>44592</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22622,7 +22622,7 @@
         <v>45259</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22695,7 +22695,7 @@
         <v>45663</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22768,7 +22768,7 @@
         <v>44582</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22841,7 +22841,7 @@
         <v>44831</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22914,7 +22914,7 @@
         <v>45205</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22987,7 +22987,7 @@
         <v>45771</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23065,7 +23065,7 @@
         <v>45771</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>45057</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23216,7 +23216,7 @@
         <v>45307</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23289,7 +23289,7 @@
         <v>45091</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
         <v>45071</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23435,7 +23435,7 @@
         <v>45188</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23508,7 +23508,7 @@
         <v>44530</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23581,7 +23581,7 @@
         <v>45350</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23654,7 +23654,7 @@
         <v>45229</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>45055</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23800,7 +23800,7 @@
         <v>44600</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23873,7 +23873,7 @@
         <v>45135</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>44710</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24019,7 +24019,7 @@
         <v>44851</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>44592</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24165,7 +24165,7 @@
         <v>45406</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24238,7 +24238,7 @@
         <v>45786</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24311,7 +24311,7 @@
         <v>44762</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24384,7 +24384,7 @@
         <v>46001</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24457,7 +24457,7 @@
         <v>45601</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24530,7 +24530,7 @@
         <v>45456</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24603,7 +24603,7 @@
         <v>45716</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24676,7 +24676,7 @@
         <v>44747</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>45031</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24822,7 +24822,7 @@
         <v>44986</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24895,7 +24895,7 @@
         <v>45097</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24968,7 +24968,7 @@
         <v>45097</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25041,7 +25041,7 @@
         <v>45335</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25114,7 +25114,7 @@
         <v>45341</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25187,7 +25187,7 @@
         <v>45384</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25260,7 +25260,7 @@
         <v>45434</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25333,7 +25333,7 @@
         <v>45839</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25406,7 +25406,7 @@
         <v>46003</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25479,7 +25479,7 @@
         <v>45439</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25552,7 +25552,7 @@
         <v>45645</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25625,7 +25625,7 @@
         <v>45201</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25698,7 +25698,7 @@
         <v>45104</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25771,7 +25771,7 @@
         <v>45709</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25844,7 +25844,7 @@
         <v>45645</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25917,7 +25917,7 @@
         <v>46009</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25990,7 +25990,7 @@
         <v>45300</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26063,7 +26063,7 @@
         <v>46007</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26136,7 +26136,7 @@
         <v>46007</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26209,7 +26209,7 @@
         <v>46009</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>45099</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26355,7 +26355,7 @@
         <v>45884</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26428,7 +26428,7 @@
         <v>45999</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26501,7 +26501,7 @@
         <v>46009</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26574,7 +26574,7 @@
         <v>45470</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26647,7 +26647,7 @@
         <v>45309</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26720,7 +26720,7 @@
         <v>45309</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26793,7 +26793,7 @@
         <v>46010</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26866,7 +26866,7 @@
         <v>45097</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26939,7 +26939,7 @@
         <v>45272</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27012,7 +27012,7 @@
         <v>46010</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27085,7 +27085,7 @@
         <v>45363</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         <v>45827</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27236,7 +27236,7 @@
         <v>45888</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27309,7 +27309,7 @@
         <v>45888</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>45541</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27455,7 +27455,7 @@
         <v>45677</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27528,7 +27528,7 @@
         <v>45889</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27601,7 +27601,7 @@
         <v>45786</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27674,7 +27674,7 @@
         <v>45113</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27747,7 +27747,7 @@
         <v>45888</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27820,7 +27820,7 @@
         <v>45742</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27893,7 +27893,7 @@
         <v>45889</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27966,7 +27966,7 @@
         <v>45888</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28039,7 +28039,7 @@
         <v>45888</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28112,7 +28112,7 @@
         <v>45888</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28185,7 +28185,7 @@
         <v>44949</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28258,7 +28258,7 @@
         <v>45826</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28331,7 +28331,7 @@
         <v>45889</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28404,7 +28404,7 @@
         <v>45742</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28477,7 +28477,7 @@
         <v>45770</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28550,7 +28550,7 @@
         <v>45309</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28623,7 +28623,7 @@
         <v>44487</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28696,7 +28696,7 @@
         <v>45161</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28769,7 +28769,7 @@
         <v>45118</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28842,7 +28842,7 @@
         <v>45839</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28915,7 +28915,7 @@
         <v>46003</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28988,7 +28988,7 @@
         <v>45623</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29061,7 +29061,7 @@
         <v>46029</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29134,7 +29134,7 @@
         <v>45336</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29207,7 +29207,7 @@
         <v>46031</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29280,7 +29280,7 @@
         <v>45162</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29353,7 +29353,7 @@
         <v>45414</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29431,7 +29431,7 @@
         <v>46030</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29504,7 +29504,7 @@
         <v>46030</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29577,7 +29577,7 @@
         <v>45226</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29650,7 +29650,7 @@
         <v>45188</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29723,7 +29723,7 @@
         <v>46031</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29796,7 +29796,7 @@
         <v>45898</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29869,7 +29869,7 @@
         <v>44916</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29942,7 +29942,7 @@
         <v>44916</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30015,7 +30015,7 @@
         <v>45701</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30093,7 +30093,7 @@
         <v>45082</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30166,7 +30166,7 @@
         <v>45461</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30239,7 +30239,7 @@
         <v>45163</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30312,7 +30312,7 @@
         <v>45819</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30385,7 +30385,7 @@
         <v>45188</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30458,7 +30458,7 @@
         <v>44655</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30531,7 +30531,7 @@
         <v>45737</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30604,7 +30604,7 @@
         <v>45587</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30677,7 +30677,7 @@
         <v>45580</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30750,7 +30750,7 @@
         <v>45902</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30823,7 +30823,7 @@
         <v>45191</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>44952</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30969,7 +30969,7 @@
         <v>45209</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31042,7 +31042,7 @@
         <v>44888</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31115,7 +31115,7 @@
         <v>45754</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31193,7 +31193,7 @@
         <v>45754</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31271,7 +31271,7 @@
         <v>45351</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31344,7 +31344,7 @@
         <v>45628</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31417,7 +31417,7 @@
         <v>44972</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31490,7 +31490,7 @@
         <v>45097</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31563,7 +31563,7 @@
         <v>45792</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31636,7 +31636,7 @@
         <v>45911</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31709,7 +31709,7 @@
         <v>45911</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31782,7 +31782,7 @@
         <v>44770</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31855,7 +31855,7 @@
         <v>45572</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31928,7 +31928,7 @@
         <v>46044</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32001,7 +32001,7 @@
         <v>46045</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32074,7 +32074,7 @@
         <v>44916</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32147,7 +32147,7 @@
         <v>46048</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32220,7 +32220,7 @@
         <v>46048</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32293,7 +32293,7 @@
         <v>46048</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32366,7 +32366,7 @@
         <v>45741</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32444,7 +32444,7 @@
         <v>45741</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32522,7 +32522,7 @@
         <v>45728</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32595,7 +32595,7 @@
         <v>45259</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32668,7 +32668,7 @@
         <v>45190</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32741,7 +32741,7 @@
         <v>45610</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32814,7 +32814,7 @@
         <v>45743</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32887,7 +32887,7 @@
         <v>45737</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32960,7 +32960,7 @@
         <v>45737</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33033,7 +33033,7 @@
         <v>46049</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33106,7 +33106,7 @@
         <v>46048</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33179,7 +33179,7 @@
         <v>45742</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33252,7 +33252,7 @@
         <v>45733</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33325,7 +33325,7 @@
         <v>45733</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33398,7 +33398,7 @@
         <v>45803</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33471,7 +33471,7 @@
         <v>45743</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33544,7 +33544,7 @@
         <v>45442</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33617,7 +33617,7 @@
         <v>45708</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33690,7 +33690,7 @@
         <v>44592</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33763,7 +33763,7 @@
         <v>45448</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33836,7 +33836,7 @@
         <v>45616</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33909,7 +33909,7 @@
         <v>45359</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33982,7 +33982,7 @@
         <v>45166</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34055,7 +34055,7 @@
         <v>45805</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34128,7 +34128,7 @@
         <v>45580</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34201,7 +34201,7 @@
         <v>45922</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34274,7 +34274,7 @@
         <v>45625</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34347,7 +34347,7 @@
         <v>45362</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34420,7 +34420,7 @@
         <v>45925</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34493,7 +34493,7 @@
         <v>46055</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         <v>45133</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34639,7 +34639,7 @@
         <v>44977</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34712,7 +34712,7 @@
         <v>45434</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34785,7 +34785,7 @@
         <v>45545</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34858,7 +34858,7 @@
         <v>45104</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34931,7 +34931,7 @@
         <v>45645</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35004,7 +35004,7 @@
         <v>45645</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35082,7 +35082,7 @@
         <v>45754</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35160,7 +35160,7 @@
         <v>45135</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35233,7 +35233,7 @@
         <v>45135</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35306,7 +35306,7 @@
         <v>45135</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35379,7 +35379,7 @@
         <v>45931</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35452,7 +35452,7 @@
         <v>44641</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35525,7 +35525,7 @@
         <v>44482</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35598,7 +35598,7 @@
         <v>46062</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35671,7 +35671,7 @@
         <v>46063</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35744,7 +35744,7 @@
         <v>45042</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35817,7 +35817,7 @@
         <v>46063</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35890,7 +35890,7 @@
         <v>46063</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35963,7 +35963,7 @@
         <v>46063</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36036,7 +36036,7 @@
         <v>45329</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36109,7 +36109,7 @@
         <v>45329</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36182,7 +36182,7 @@
         <v>45117</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36255,7 +36255,7 @@
         <v>45811</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36328,7 +36328,7 @@
         <v>45936</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36401,7 +36401,7 @@
         <v>44888</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36474,7 +36474,7 @@
         <v>45099</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36547,7 +36547,7 @@
         <v>45610</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36620,7 +36620,7 @@
         <v>45742</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36693,7 +36693,7 @@
         <v>44984</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36766,7 +36766,7 @@
         <v>45228</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>45441</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36912,7 +36912,7 @@
         <v>45274</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36985,7 +36985,7 @@
         <v>44693</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37058,7 +37058,7 @@
         <v>45615</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37131,7 +37131,7 @@
         <v>46077</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37204,7 +37204,7 @@
         <v>45944</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37277,7 +37277,7 @@
         <v>45595</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37350,7 +37350,7 @@
         <v>45330</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37423,7 +37423,7 @@
         <v>45505</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37496,7 +37496,7 @@
         <v>46077</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37569,7 +37569,7 @@
         <v>45202</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37642,7 +37642,7 @@
         <v>45702</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37715,7 +37715,7 @@
         <v>45376</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37788,7 +37788,7 @@
         <v>45946</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37861,7 +37861,7 @@
         <v>45363</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37939,7 +37939,7 @@
         <v>44916</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38012,7 +38012,7 @@
         <v>44531</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38085,7 +38085,7 @@
         <v>45950</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38158,7 +38158,7 @@
         <v>45365</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38231,7 +38231,7 @@
         <v>45414</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38309,7 +38309,7 @@
         <v>45953</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38382,7 +38382,7 @@
         <v>46084</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38455,7 +38455,7 @@
         <v>46084</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38528,7 +38528,7 @@
         <v>45107</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38601,7 +38601,7 @@
         <v>45251</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38674,7 +38674,7 @@
         <v>46084</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38747,7 +38747,7 @@
         <v>45319</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38820,7 +38820,7 @@
         <v>44515</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38898,7 +38898,7 @@
         <v>44984</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38971,7 +38971,7 @@
         <v>45232</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39044,7 +39044,7 @@
         <v>45462</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39117,7 +39117,7 @@
         <v>44984</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39190,7 +39190,7 @@
         <v>44984</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39263,7 +39263,7 @@
         <v>45357</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39336,7 +39336,7 @@
         <v>45812</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39409,7 +39409,7 @@
         <v>45048</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39482,7 +39482,7 @@
         <v>46087</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39555,7 +39555,7 @@
         <v>45816</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39628,7 +39628,7 @@
         <v>46091</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39701,7 +39701,7 @@
         <v>45581</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39779,7 +39779,7 @@
         <v>44945</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39852,7 +39852,7 @@
         <v>45006</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39925,7 +39925,7 @@
         <v>46092</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39998,7 +39998,7 @@
         <v>45069</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40071,7 +40071,7 @@
         <v>45484</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40144,7 +40144,7 @@
         <v>46002</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40217,7 +40217,7 @@
         <v>46097</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40290,7 +40290,7 @@
         <v>45015</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40363,7 +40363,7 @@
         <v>45310</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40436,7 +40436,7 @@
         <v>45351</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40509,7 +40509,7 @@
         <v>46098</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40582,7 +40582,7 @@
         <v>45170</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40655,7 +40655,7 @@
         <v>46099</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40728,7 +40728,7 @@
         <v>45097</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40801,7 +40801,7 @@
         <v>46100</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40874,7 +40874,7 @@
         <v>46104</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40947,7 +40947,7 @@
         <v>45684</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41025,7 +41025,7 @@
         <v>45330</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41098,7 +41098,7 @@
         <v>46104</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41171,7 +41171,7 @@
         <v>45974</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41244,7 +41244,7 @@
         <v>44946</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41317,7 +41317,7 @@
         <v>45975</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41390,7 +41390,7 @@
         <v>45107</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41463,7 +41463,7 @@
         <v>45819</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41536,7 +41536,7 @@
         <v>45099</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41609,7 +41609,7 @@
         <v>46107</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41682,7 +41682,7 @@
         <v>45981</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41760,7 +41760,7 @@
         <v>45819</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41833,7 +41833,7 @@
         <v>45819</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41906,7 +41906,7 @@
         <v>45981</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41979,7 +41979,7 @@
         <v>45352</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42052,7 +42052,7 @@
         <v>46107</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42125,7 +42125,7 @@
         <v>45819</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42198,7 +42198,7 @@
         <v>45981</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42271,7 +42271,7 @@
         <v>46107</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42344,7 +42344,7 @@
         <v>45982</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42417,7 +42417,7 @@
         <v>46111</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42490,7 +42490,7 @@
         <v>45981</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42563,7 +42563,7 @@
         <v>46111</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42636,7 +42636,7 @@
         <v>44837</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42709,7 +42709,7 @@
         <v>45351</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42782,7 +42782,7 @@
         <v>44484</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>45748</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42933,7 +42933,7 @@
         <v>45748</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43011,7 +43011,7 @@
         <v>45992</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43084,7 +43084,7 @@
         <v>46121</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43157,7 +43157,7 @@
         <v>46122</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43230,7 +43230,7 @@
         <v>45992</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43303,7 +43303,7 @@
         <v>46121</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43376,7 +43376,7 @@
         <v>44965</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43449,7 +43449,7 @@
         <v>46126</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43522,7 +43522,7 @@
         <v>46128</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43595,7 +43595,7 @@
         <v>46128</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43668,7 +43668,7 @@
         <v>46128</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43741,7 +43741,7 @@
         <v>44970</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43814,7 +43814,7 @@
         <v>46128</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43887,7 +43887,7 @@
         <v>45999</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43960,7 +43960,7 @@
         <v>45133</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44033,7 +44033,7 @@
         <v>45999</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44106,7 +44106,7 @@
         <v>45357</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44179,7 +44179,7 @@
         <v>46127</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44252,7 +44252,7 @@
         <v>46128</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44325,7 +44325,7 @@
         <v>45231</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44398,7 +44398,7 @@
         <v>46133</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44471,7 +44471,7 @@
         <v>46133</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44544,7 +44544,7 @@
         <v>44545</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44617,7 +44617,7 @@
         <v>45681</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44690,7 +44690,7 @@
         <v>45152</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44763,7 +44763,7 @@
         <v>44503</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44836,7 +44836,7 @@
         <v>45230</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44914,7 +44914,7 @@
         <v>44480</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44987,7 +44987,7 @@
         <v>44741</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45060,7 +45060,7 @@
         <v>45272</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45133,7 +45133,7 @@
         <v>45084</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45206,7 +45206,7 @@
         <v>44600</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45279,7 +45279,7 @@
         <v>45903</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45352,7 +45352,7 @@
         <v>45331</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45425,7 +45425,7 @@
         <v>45331</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45498,7 +45498,7 @@
         <v>45222</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45571,7 +45571,7 @@
         <v>44970</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45644,7 +45644,7 @@
         <v>45671</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45717,7 +45717,7 @@
         <v>45435</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45790,7 +45790,7 @@
         <v>45230</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45868,7 +45868,7 @@
         <v>45204</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45941,7 +45941,7 @@
         <v>45839</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46014,7 +46014,7 @@
         <v>45699</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46087,7 +46087,7 @@
         <v>45827</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46160,7 +46160,7 @@
         <v>45455</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46233,7 +46233,7 @@
         <v>46037</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46306,7 +46306,7 @@
         <v>45561</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46379,7 +46379,7 @@
         <v>45737</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46452,7 +46452,7 @@
         <v>45944</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46525,7 +46525,7 @@
         <v>45112</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46598,7 +46598,7 @@
         <v>45282</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46671,7 +46671,7 @@
         <v>45245</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46744,7 +46744,7 @@
         <v>45891</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46817,7 +46817,7 @@
         <v>45631</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46890,7 +46890,7 @@
         <v>45247</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46963,7 +46963,7 @@
         <v>45838</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47036,7 +47036,7 @@
         <v>45313</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47109,7 +47109,7 @@
         <v>45799</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47182,7 +47182,7 @@
         <v>45306</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47255,7 +47255,7 @@
         <v>45259</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47328,7 +47328,7 @@
         <v>45839</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47401,7 +47401,7 @@
         <v>45370</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47474,7 +47474,7 @@
         <v>45931</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47547,7 +47547,7 @@
         <v>45322</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47620,7 +47620,7 @@
         <v>44510</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47693,7 +47693,7 @@
         <v>45895</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47766,7 +47766,7 @@
         <v>45035</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47839,7 +47839,7 @@
         <v>45840</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47912,7 +47912,7 @@
         <v>45840</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47985,7 +47985,7 @@
         <v>45883</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48058,7 +48058,7 @@
         <v>45645</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48136,7 +48136,7 @@
         <v>45645</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48214,7 +48214,7 @@
         <v>45845</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48287,7 +48287,7 @@
         <v>45076</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48360,7 +48360,7 @@
         <v>45006</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48433,7 +48433,7 @@
         <v>44580</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48506,7 +48506,7 @@
         <v>45089</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48579,7 +48579,7 @@
         <v>45729</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48652,7 +48652,7 @@
         <v>45748</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48725,7 +48725,7 @@
         <v>45747</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48798,7 +48798,7 @@
         <v>45625</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48871,7 +48871,7 @@
         <v>45615</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48944,7 +48944,7 @@
         <v>45715</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49017,7 +49017,7 @@
         <v>45715</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49090,7 +49090,7 @@
         <v>45902</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49163,7 +49163,7 @@
         <v>44834</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49236,7 +49236,7 @@
         <v>46112</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49314,7 +49314,7 @@
         <v>45965</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49387,7 +49387,7 @@
         <v>45847</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49460,7 +49460,7 @@
         <v>45525</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49533,7 +49533,7 @@
         <v>45785</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49606,7 +49606,7 @@
         <v>45538</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49679,7 +49679,7 @@
         <v>45912</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49752,7 +49752,7 @@
         <v>45298</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49825,7 +49825,7 @@
         <v>45763</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49898,7 +49898,7 @@
         <v>45840</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49971,7 +49971,7 @@
         <v>45372</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50044,7 +50044,7 @@
         <v>45866</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50117,7 +50117,7 @@
         <v>45925</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50190,7 +50190,7 @@
         <v>45076</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50263,7 +50263,7 @@
         <v>45971</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50336,7 +50336,7 @@
         <v>44473</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50409,7 +50409,7 @@
         <v>45170</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50482,7 +50482,7 @@
         <v>45401</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50555,7 +50555,7 @@
         <v>45852</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50628,7 +50628,7 @@
         <v>44607</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50701,7 +50701,7 @@
         <v>46006</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50774,7 +50774,7 @@
         <v>45763</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50847,7 +50847,7 @@
         <v>44837</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50920,7 +50920,7 @@
         <v>45693</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50993,7 +50993,7 @@
         <v>44511</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51066,7 +51066,7 @@
         <v>45889</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51139,7 +51139,7 @@
         <v>45089</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51212,7 +51212,7 @@
         <v>45443</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51285,7 +51285,7 @@
         <v>45240</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51358,7 +51358,7 @@
         <v>45168</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51431,7 +51431,7 @@
         <v>45785</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51504,7 +51504,7 @@
         <v>45321</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51577,7 +51577,7 @@
         <v>45163</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51650,7 +51650,7 @@
         <v>45841</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51723,7 +51723,7 @@
         <v>45608</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51796,7 +51796,7 @@
         <v>45873</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51869,7 +51869,7 @@
         <v>44510</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51942,7 +51942,7 @@
         <v>45971</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52015,7 +52015,7 @@
         <v>45610</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52088,7 +52088,7 @@
         <v>46122</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52161,7 +52161,7 @@
         <v>45153</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52234,7 +52234,7 @@
         <v>45755</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52307,7 +52307,7 @@
         <v>45670</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52380,7 +52380,7 @@
         <v>45825</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52453,7 +52453,7 @@
         <v>45348</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52526,7 +52526,7 @@
         <v>45839</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52599,7 +52599,7 @@
         <v>45672</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52672,7 +52672,7 @@
         <v>45163</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52745,7 +52745,7 @@
         <v>45211</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52818,7 +52818,7 @@
         <v>44538</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52891,7 +52891,7 @@
         <v>44549</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52964,7 +52964,7 @@
         <v>45322</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53037,7 +53037,7 @@
         <v>44785</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53110,7 +53110,7 @@
         <v>46052</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53183,7 +53183,7 @@
         <v>45883</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53256,7 +53256,7 @@
         <v>45414</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53329,7 +53329,7 @@
         <v>44894</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53402,7 +53402,7 @@
         <v>45519</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53475,7 +53475,7 @@
         <v>45691</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53553,7 +53553,7 @@
         <v>45005</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53626,7 +53626,7 @@
         <v>45314</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53699,7 +53699,7 @@
         <v>45433</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53772,7 +53772,7 @@
         <v>45097</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53845,7 +53845,7 @@
         <v>45448</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53918,7 +53918,7 @@
         <v>44564</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53991,7 +53991,7 @@
         <v>45645</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54069,7 +54069,7 @@
         <v>45645</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54147,7 +54147,7 @@
         <v>45644</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54220,7 +54220,7 @@
         <v>45649</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54298,7 +54298,7 @@
         <v>45866</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54371,7 +54371,7 @@
         <v>45288</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54444,7 +54444,7 @@
         <v>45733</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54517,7 +54517,7 @@
         <v>45114</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54590,7 +54590,7 @@
         <v>44858</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54663,7 +54663,7 @@
         <v>45545</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54736,7 +54736,7 @@
         <v>45250</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54809,7 +54809,7 @@
         <v>45224</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54887,7 +54887,7 @@
         <v>45113</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54960,7 +54960,7 @@
         <v>45827</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55033,7 +55033,7 @@
         <v>45645</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55111,7 +55111,7 @@
         <v>45763</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55184,7 +55184,7 @@
         <v>45672</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55257,7 +55257,7 @@
         <v>45589</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55330,7 +55330,7 @@
         <v>45264</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55403,7 +55403,7 @@
         <v>45525</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55476,7 +55476,7 @@
         <v>44965</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55549,7 +55549,7 @@
         <v>44926</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55622,7 +55622,7 @@
         <v>44926</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55695,7 +55695,7 @@
         <v>45401</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55768,7 +55768,7 @@
         <v>45392</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55841,7 +55841,7 @@
         <v>45394</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55914,7 +55914,7 @@
         <v>44602</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55987,7 +55987,7 @@
         <v>45007</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56060,7 +56060,7 @@
         <v>45568</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56138,7 +56138,7 @@
         <v>45297</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56211,7 +56211,7 @@
         <v>45236</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56284,7 +56284,7 @@
         <v>45625</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56357,7 +56357,7 @@
         <v>46153</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56430,7 +56430,7 @@
         <v>45105</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56503,7 +56503,7 @@
         <v>44859</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56576,7 +56576,7 @@
         <v>46153</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56649,7 +56649,7 @@
         <v>46153</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56722,7 +56722,7 @@
         <v>45674</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56795,7 +56795,7 @@
         <v>46153</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56868,7 +56868,7 @@
         <v>46154</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56946,7 +56946,7 @@
         <v>45866</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57019,7 +57019,7 @@
         <v>45639</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57092,7 +57092,7 @@
         <v>44481</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57165,7 +57165,7 @@
         <v>46126</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57238,7 +57238,7 @@
         <v>45875</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57311,7 +57311,7 @@
         <v>45400</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57389,7 +57389,7 @@
         <v>44655</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57462,7 +57462,7 @@
         <v>46160</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57535,7 +57535,7 @@
         <v>44970</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57608,7 +57608,7 @@
         <v>45329</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57681,7 +57681,7 @@
         <v>46161</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57754,7 +57754,7 @@
         <v>44847</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57827,7 +57827,7 @@
         <v>46160</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57900,7 +57900,7 @@
         <v>45761</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57973,7 +57973,7 @@
         <v>46160</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58046,7 +58046,7 @@
         <v>45180</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58119,7 +58119,7 @@
         <v>45173</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58192,7 +58192,7 @@
         <v>45173</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58265,7 +58265,7 @@
         <v>46064</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58338,7 +58338,7 @@
         <v>45875</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58411,7 +58411,7 @@
         <v>45930</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58484,7 +58484,7 @@
         <v>45345</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58557,7 +58557,7 @@
         <v>46160</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58630,7 +58630,7 @@
         <v>45526</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58703,7 +58703,7 @@
         <v>45875</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58776,7 +58776,7 @@
         <v>45170</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58849,7 +58849,7 @@
         <v>45170</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58922,7 +58922,7 @@
         <v>46163</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58995,7 +58995,7 @@
         <v>46161</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59068,7 +59068,7 @@
         <v>45303</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59141,7 +59141,7 @@
         <v>45104</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59214,7 +59214,7 @@
         <v>45930</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59292,7 +59292,7 @@
         <v>45113</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59365,7 +59365,7 @@
         <v>45446</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59438,7 +59438,7 @@
         <v>45438</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59511,7 +59511,7 @@
         <v>45182</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59589,7 +59589,7 @@
         <v>45182</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59662,7 +59662,7 @@
         <v>44607</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59735,7 +59735,7 @@
         <v>45669</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59808,7 +59808,7 @@
         <v>45882</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59881,7 +59881,7 @@
         <v>45315</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59954,7 +59954,7 @@
         <v>45462</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60027,7 +60027,7 @@
         <v>45882</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60100,7 +60100,7 @@
         <v>46175</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60173,7 +60173,7 @@
         <v>45884</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60246,7 +60246,7 @@
         <v>45449</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60319,7 +60319,7 @@
         <v>45327</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60392,7 +60392,7 @@
         <v>45164</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60465,7 +60465,7 @@
         <v>46178</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60538,7 +60538,7 @@
         <v>45330</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60611,7 +60611,7 @@
         <v>46178</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60684,7 +60684,7 @@
         <v>46178</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60757,7 +60757,7 @@
         <v>46178</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60830,7 +60830,7 @@
         <v>46178</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60903,7 +60903,7 @@
         <v>46178</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60976,7 +60976,7 @@
         <v>44995</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61049,7 +61049,7 @@
         <v>45692</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61122,7 +61122,7 @@
         <v>46182</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61195,7 +61195,7 @@
         <v>46182</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61268,7 +61268,7 @@
         <v>45106</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61341,7 +61341,7 @@
         <v>45574</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61419,7 +61419,7 @@
         <v>46182</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61492,7 +61492,7 @@
         <v>45616</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61565,7 +61565,7 @@
         <v>45510</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61638,7 +61638,7 @@
         <v>46184</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61711,7 +61711,7 @@
         <v>45219</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61789,7 +61789,7 @@
         <v>45274</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61862,7 +61862,7 @@
         <v>46184</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61935,7 +61935,7 @@
         <v>45250</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62008,7 +62008,7 @@
         <v>46184</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62081,7 +62081,7 @@
         <v>46185</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62154,7 +62154,7 @@
         <v>44587</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62227,7 +62227,7 @@
         <v>46188</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62300,7 +62300,7 @@
         <v>44783</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62373,7 +62373,7 @@
         <v>46185</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62446,7 +62446,7 @@
         <v>44830</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62519,7 +62519,7 @@
         <v>45544</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62592,7 +62592,7 @@
         <v>45133</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62665,7 +62665,7 @@
         <v>45408</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62738,7 +62738,7 @@
         <v>44834</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62811,7 +62811,7 @@
         <v>45366</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62884,7 +62884,7 @@
         <v>44815</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62957,7 +62957,7 @@
         <v>45069</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63030,7 +63030,7 @@
         <v>45440</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63103,7 +63103,7 @@
         <v>46190</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63176,7 +63176,7 @@
         <v>45701</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63254,7 +63254,7 @@
         <v>45302</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63327,7 +63327,7 @@
         <v>45615</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63400,7 +63400,7 @@
         <v>45113</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63473,7 +63473,7 @@
         <v>44683</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63546,7 +63546,7 @@
         <v>45925</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63619,7 +63619,7 @@
         <v>45546</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63692,7 +63692,7 @@
         <v>44839</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63765,7 +63765,7 @@
         <v>44970</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63838,7 +63838,7 @@
         <v>46195</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63911,7 +63911,7 @@
         <v>45222</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63984,7 +63984,7 @@
         <v>45183</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64057,7 +64057,7 @@
         <v>46196</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64130,7 +64130,7 @@
         <v>46196</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64203,7 +64203,7 @@
         <v>44965</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64276,7 +64276,7 @@
         <v>45000</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64349,7 +64349,7 @@
         <v>45183</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64422,7 +64422,7 @@
         <v>45706</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64495,7 +64495,7 @@
         <v>46197</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64568,7 +64568,7 @@
         <v>44839</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64641,7 +64641,7 @@
         <v>44753</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64714,7 +64714,7 @@
         <v>45135</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64787,7 +64787,7 @@
         <v>46197</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64860,7 +64860,7 @@
         <v>46202</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64933,7 +64933,7 @@
         <v>44802</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65011,7 +65011,7 @@
         <v>45446</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65084,7 +65084,7 @@
         <v>46204</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65157,7 +65157,7 @@
         <v>44929</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65230,7 +65230,7 @@
         <v>44743</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65303,7 +65303,7 @@
         <v>44481</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65376,7 +65376,7 @@
         <v>45170</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65449,7 +65449,7 @@
         <v>45497</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65522,7 +65522,7 @@
         <v>45497</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65595,7 +65595,7 @@
         <v>45119</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65668,7 +65668,7 @@
         <v>45401</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65741,7 +65741,7 @@
         <v>44952</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65814,7 +65814,7 @@
         <v>45112</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65887,7 +65887,7 @@
         <v>45107</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65960,7 +65960,7 @@
         <v>44747</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66033,7 +66033,7 @@
         <v>45526</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66106,7 +66106,7 @@
         <v>44600</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66179,7 +66179,7 @@
         <v>45569</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66252,7 +66252,7 @@
         <v>44930</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66325,7 +66325,7 @@
         <v>46069</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66398,7 +66398,7 @@
         <v>46259</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66471,7 +66471,7 @@
         <v>45033</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66544,7 +66544,7 @@
         <v>45572</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66617,7 +66617,7 @@
         <v>45341</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66690,7 +66690,7 @@
         <v>45348</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66763,7 +66763,7 @@
         <v>46213</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66836,7 +66836,7 @@
         <v>46168</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66909,7 +66909,7 @@
         <v>46258</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66982,7 +66982,7 @@
         <v>46259</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67055,7 +67055,7 @@
         <v>46177</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67128,7 +67128,7 @@
         <v>44740</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67206,7 +67206,7 @@
         <v>45406</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67279,7 +67279,7 @@
         <v>44998</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67352,7 +67352,7 @@
         <v>45302</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67425,7 +67425,7 @@
         <v>44869</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67498,7 +67498,7 @@
         <v>45174</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67571,7 +67571,7 @@
         <v>46265</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67644,7 +67644,7 @@
         <v>45363</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67722,7 +67722,7 @@
         <v>45363</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -67800,7 +67800,7 @@
         <v>45363</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -67878,7 +67878,7 @@
         <v>45364</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67951,7 +67951,7 @@
         <v>45104</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -68024,7 +68024,7 @@
         <v>45281</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -68097,7 +68097,7 @@
         <v>45525</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -68170,7 +68170,7 @@
         <v>45006</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -68243,7 +68243,7 @@
         <v>45202</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -68316,7 +68316,7 @@
         <v>45563</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -68394,7 +68394,7 @@
         <v>45357</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68467,7 +68467,7 @@
         <v>45173</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68540,7 +68540,7 @@
         <v>46269</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68613,7 +68613,7 @@
         <v>45629</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -68686,7 +68686,7 @@
         <v>46268</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -68759,7 +68759,7 @@
         <v>45314</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -68832,7 +68832,7 @@
         <v>45420</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68905,7 +68905,7 @@
         <v>45195</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -68978,7 +68978,7 @@
         <v>45238</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -69056,7 +69056,7 @@
         <v>44880</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -69129,7 +69129,7 @@
         <v>44880</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -69202,7 +69202,7 @@
         <v>45079</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -69275,7 +69275,7 @@
         <v>45091</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -69348,7 +69348,7 @@
         <v>46273</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -69421,7 +69421,7 @@
         <v>44602</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -69494,7 +69494,7 @@
         <v>45163</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69567,7 +69567,7 @@
         <v>46258</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -69640,7 +69640,7 @@
         <v>46274</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -69713,7 +69713,7 @@
         <v>46273</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -69786,7 +69786,7 @@
         <v>44523</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -69859,7 +69859,7 @@
         <v>46234</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -69932,7 +69932,7 @@
         <v>46276</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -70005,7 +70005,7 @@
         <v>46276</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -70078,7 +70078,7 @@
         <v>46234</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -70151,7 +70151,7 @@
         <v>46279</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -70224,7 +70224,7 @@
         <v>46276</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -70297,7 +70297,7 @@
         <v>46276</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -70370,7 +70370,7 @@
         <v>46276</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -70443,7 +70443,7 @@
         <v>46233</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -70516,7 +70516,7 @@
         <v>46234</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70589,7 +70589,7 @@
         <v>44677</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -70662,7 +70662,7 @@
         <v>46237</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -70735,7 +70735,7 @@
         <v>45303</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -70808,7 +70808,7 @@
         <v>44592</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -70881,7 +70881,7 @@
         <v>45475</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -70954,7 +70954,7 @@
         <v>45211</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -71027,7 +71027,7 @@
         <v>45352</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -71100,7 +71100,7 @@
         <v>45538</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -71173,7 +71173,7 @@
         <v>46240</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -71246,7 +71246,7 @@
         <v>45329</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -71324,7 +71324,7 @@
         <v>45314</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -71397,7 +71397,7 @@
         <v>45645</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -71475,7 +71475,7 @@
         <v>44815</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -71548,7 +71548,7 @@
         <v>44497</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -71621,7 +71621,7 @@
         <v>45091</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -71694,7 +71694,7 @@
         <v>45022</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -71767,7 +71767,7 @@
         <v>46283</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -71840,7 +71840,7 @@
         <v>45526</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -71913,7 +71913,7 @@
         <v>45114</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -71986,7 +71986,7 @@
         <v>45440</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -72059,7 +72059,7 @@
         <v>44587</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -72132,7 +72132,7 @@
         <v>44715</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -72205,7 +72205,7 @@
         <v>44813</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -72278,7 +72278,7 @@
         <v>45365</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -72351,7 +72351,7 @@
         <v>45385</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -72424,7 +72424,7 @@
         <v>46244</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -72497,7 +72497,7 @@
         <v>45953</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -72570,7 +72570,7 @@
         <v>44946</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -72643,7 +72643,7 @@
         <v>46245</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -72716,7 +72716,7 @@
         <v>46244</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -72789,7 +72789,7 @@
         <v>44805</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -72862,7 +72862,7 @@
         <v>44813</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -72935,7 +72935,7 @@
         <v>46289</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -73008,7 +73008,7 @@
         <v>45398</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -73081,7 +73081,7 @@
         <v>46289</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -73154,7 +73154,7 @@
         <v>45307</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -73227,7 +73227,7 @@
         <v>44825</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -73300,7 +73300,7 @@
         <v>44917</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -73373,7 +73373,7 @@
         <v>45177</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -73451,7 +73451,7 @@
         <v>45174</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -73529,7 +73529,7 @@
         <v>46246</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -73602,7 +73602,7 @@
         <v>45329</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -73675,7 +73675,7 @@
         <v>46280</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -73748,7 +73748,7 @@
         <v>46293</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -73821,7 +73821,7 @@
         <v>45245</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -73894,7 +73894,7 @@
         <v>46178</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -73967,7 +73967,7 @@
         <v>45737</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -74040,7 +74040,7 @@
         <v>45719</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -74113,7 +74113,7 @@
         <v>46178</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -74186,7 +74186,7 @@
         <v>45364</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -74259,7 +74259,7 @@
         <v>45089</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -74332,7 +74332,7 @@
         <v>45660</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -74405,7 +74405,7 @@
         <v>45107</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -74478,7 +74478,7 @@
         <v>45184</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -74551,7 +74551,7 @@
         <v>46293</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -74624,7 +74624,7 @@
         <v>46293</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -74697,7 +74697,7 @@
         <v>45589</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -74770,7 +74770,7 @@
         <v>45589</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -74843,7 +74843,7 @@
         <v>45532</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -74916,7 +74916,7 @@
         <v>45370</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -74989,7 +74989,7 @@
         <v>46290</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -75062,7 +75062,7 @@
         <v>45925</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -75135,7 +75135,7 @@
         <v>45406</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -75208,7 +75208,7 @@
         <v>46009</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -75281,7 +75281,7 @@
         <v>44595</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -75354,7 +75354,7 @@
         <v>45104</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -75427,7 +75427,7 @@
         <v>46252</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -75500,7 +75500,7 @@
         <v>45071</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -75573,7 +75573,7 @@
         <v>46294</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -75646,7 +75646,7 @@
         <v>45216</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -75719,7 +75719,7 @@
         <v>45303</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -75792,7 +75792,7 @@
         <v>46294</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -75865,7 +75865,7 @@
         <v>45678</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -75938,7 +75938,7 @@
         <v>45182</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -76011,7 +76011,7 @@
         <v>44495</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -76084,7 +76084,7 @@
         <v>45219</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -76157,7 +76157,7 @@
         <v>45030</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -76230,7 +76230,7 @@
         <v>45544</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -76303,7 +76303,7 @@
         <v>45691</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -76376,7 +76376,7 @@
         <v>46248</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -76454,7 +76454,7 @@
         <v>44488</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -76527,7 +76527,7 @@
         <v>46296</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -76600,7 +76600,7 @@
         <v>45631</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -76673,7 +76673,7 @@
         <v>46247</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -76751,7 +76751,7 @@
         <v>46247</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -76829,7 +76829,7 @@
         <v>45216</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -76907,7 +76907,7 @@
         <v>46297</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -76980,7 +76980,7 @@
         <v>46296</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -77053,7 +77053,7 @@
         <v>45359</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -77126,7 +77126,7 @@
         <v>46297</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -77199,7 +77199,7 @@
         <v>45936</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -77272,7 +77272,7 @@
         <v>46062</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -77345,7 +77345,7 @@
         <v>46295</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -77418,7 +77418,7 @@
         <v>46031</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -77491,7 +77491,7 @@
         <v>45376</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -77564,7 +77564,7 @@
         <v>44810</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -77637,7 +77637,7 @@
         <v>45209</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -77710,7 +77710,7 @@
         <v>45183</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -77783,7 +77783,7 @@
         <v>45595</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -77856,7 +77856,7 @@
         <v>45575</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -77929,7 +77929,7 @@
         <v>45062</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -78002,7 +78002,7 @@
         <v>45231</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -78075,7 +78075,7 @@
         <v>45699</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -78148,7 +78148,7 @@
         <v>45737</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -78221,7 +78221,7 @@
         <v>44930</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -78294,7 +78294,7 @@
         <v>44971</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -78367,7 +78367,7 @@
         <v>45602</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -78440,7 +78440,7 @@
         <v>45092</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -78513,7 +78513,7 @@
         <v>45674</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -78586,7 +78586,7 @@
         <v>45478</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -78659,7 +78659,7 @@
         <v>45769</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -78737,7 +78737,7 @@
         <v>45164</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -78810,7 +78810,7 @@
         <v>45309</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -78883,7 +78883,7 @@
         <v>45309</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -78956,7 +78956,7 @@
         <v>45182</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -79034,7 +79034,7 @@
         <v>45329</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -79107,7 +79107,7 @@
         <v>45222</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -79180,7 +79180,7 @@
         <v>45492</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -79253,7 +79253,7 @@
         <v>45323</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -79326,7 +79326,7 @@
         <v>45763</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -79399,7 +79399,7 @@
         <v>45384</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -79472,7 +79472,7 @@
         <v>45296</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -79545,7 +79545,7 @@
         <v>45763</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -79618,7 +79618,7 @@
         <v>45763</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -79691,7 +79691,7 @@
         <v>45763</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -79764,7 +79764,7 @@
         <v>44946</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -79837,7 +79837,7 @@
         <v>45462</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -79910,7 +79910,7 @@
         <v>44879</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -79983,7 +79983,7 @@
         <v>45719</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -80056,7 +80056,7 @@
         <v>45540</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -80129,7 +80129,7 @@
         <v>45134</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -80202,7 +80202,7 @@
         <v>45316</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -80275,7 +80275,7 @@
         <v>45414</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -80348,7 +80348,7 @@
         <v>45607</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -80421,7 +80421,7 @@
         <v>44818</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -80494,7 +80494,7 @@
         <v>45673</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
@@ -80567,7 +80567,7 @@
         <v>44831</v>
       </c>
       <c r="E1032" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
@@ -80640,7 +80640,7 @@
         <v>45001</v>
       </c>
       <c r="E1033" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
@@ -80718,7 +80718,7 @@
         <v>45254</v>
       </c>
       <c r="E1034" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
@@ -80796,7 +80796,7 @@
         <v>45090</v>
       </c>
       <c r="E1035" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
@@ -80869,7 +80869,7 @@
         <v>45132</v>
       </c>
       <c r="E1036" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
@@ -80942,7 +80942,7 @@
         <v>45335</v>
       </c>
       <c r="E1037" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
@@ -81015,7 +81015,7 @@
         <v>45602</v>
       </c>
       <c r="E1038" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1038" t="inlineStr">
         <is>
@@ -81088,7 +81088,7 @@
         <v>44963</v>
       </c>
       <c r="E1039" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1039" t="inlineStr">
         <is>
@@ -81161,7 +81161,7 @@
         <v>45168</v>
       </c>
       <c r="E1040" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1040" t="inlineStr">
         <is>
@@ -81234,7 +81234,7 @@
         <v>45400</v>
       </c>
       <c r="E1041" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1041" t="inlineStr">
         <is>
@@ -81307,7 +81307,7 @@
         <v>45188</v>
       </c>
       <c r="E1042" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1042" t="inlineStr">
         <is>
@@ -81380,7 +81380,7 @@
         <v>45670</v>
       </c>
       <c r="E1043" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1043" t="inlineStr">
         <is>
@@ -81453,7 +81453,7 @@
         <v>44902</v>
       </c>
       <c r="E1044" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1044" t="inlineStr">
         <is>
@@ -81526,7 +81526,7 @@
         <v>44564</v>
       </c>
       <c r="E1045" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1045" t="inlineStr">
         <is>
@@ -81604,7 +81604,7 @@
         <v>45189</v>
       </c>
       <c r="E1046" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1046" t="inlineStr">
         <is>
@@ -81682,7 +81682,7 @@
         <v>45691</v>
       </c>
       <c r="E1047" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1047" t="inlineStr">
         <is>
@@ -81755,7 +81755,7 @@
         <v>44916</v>
       </c>
       <c r="E1048" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1048" t="inlineStr">
         <is>
@@ -81828,7 +81828,7 @@
         <v>44957</v>
       </c>
       <c r="E1049" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1049" t="inlineStr">
         <is>
@@ -81901,7 +81901,7 @@
         <v>44502</v>
       </c>
       <c r="E1050" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1050" t="inlineStr">
         <is>
@@ -81974,7 +81974,7 @@
         <v>45702</v>
       </c>
       <c r="E1051" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1051" t="inlineStr">
         <is>
@@ -82052,7 +82052,7 @@
         <v>45134</v>
       </c>
       <c r="E1052" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1052" t="inlineStr">
         <is>
@@ -82125,7 +82125,7 @@
         <v>45348</v>
       </c>
       <c r="E1053" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1053" t="inlineStr">
         <is>
@@ -82198,7 +82198,7 @@
         <v>45439</v>
       </c>
       <c r="E1054" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1054" t="inlineStr">
         <is>
@@ -82271,7 +82271,7 @@
         <v>44781</v>
       </c>
       <c r="E1055" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1055" t="inlineStr">
         <is>
@@ -82344,7 +82344,7 @@
         <v>45783</v>
       </c>
       <c r="E1056" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1056" t="inlineStr">
         <is>
@@ -82417,7 +82417,7 @@
         <v>45783</v>
       </c>
       <c r="E1057" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1057" t="inlineStr">
         <is>
@@ -82490,7 +82490,7 @@
         <v>45439</v>
       </c>
       <c r="E1058" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1058" t="inlineStr">
         <is>
@@ -82563,7 +82563,7 @@
         <v>45636</v>
       </c>
       <c r="E1059" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1059" t="inlineStr">
         <is>
@@ -82636,7 +82636,7 @@
         <v>45580</v>
       </c>
       <c r="E1060" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1060" t="inlineStr">
         <is>
@@ -82709,7 +82709,7 @@
         <v>45447</v>
       </c>
       <c r="E1061" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1061" t="inlineStr">
         <is>
@@ -82782,7 +82782,7 @@
         <v>45170</v>
       </c>
       <c r="E1062" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1062" t="inlineStr">
         <is>
@@ -82855,7 +82855,7 @@
         <v>45106</v>
       </c>
       <c r="E1063" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1063" t="inlineStr">
         <is>
@@ -82928,7 +82928,7 @@
         <v>45467</v>
       </c>
       <c r="E1064" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1064" t="inlineStr">
         <is>
@@ -83001,7 +83001,7 @@
         <v>44509</v>
       </c>
       <c r="E1065" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1065" t="inlineStr">
         <is>
@@ -83079,7 +83079,7 @@
         <v>45664</v>
       </c>
       <c r="E1066" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1066" t="inlineStr">
         <is>
@@ -83152,7 +83152,7 @@
         <v>45208</v>
       </c>
       <c r="E1067" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1067" t="inlineStr">
         <is>
@@ -83225,7 +83225,7 @@
         <v>45406</v>
       </c>
       <c r="E1068" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1068" t="inlineStr">
         <is>
@@ -83298,7 +83298,7 @@
         <v>45497</v>
       </c>
       <c r="E1069" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1069" t="inlineStr">
         <is>
@@ -83371,7 +83371,7 @@
         <v>45497</v>
       </c>
       <c r="E1070" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1070" t="inlineStr">
         <is>
@@ -83444,7 +83444,7 @@
         <v>45106</v>
       </c>
       <c r="E1071" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1071" t="inlineStr">
         <is>
@@ -83517,7 +83517,7 @@
         <v>45646</v>
       </c>
       <c r="E1072" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1072" t="inlineStr">
         <is>
@@ -83590,7 +83590,7 @@
         <v>45646</v>
       </c>
       <c r="E1073" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1073" t="inlineStr">
         <is>
@@ -83663,7 +83663,7 @@
         <v>45580</v>
       </c>
       <c r="E1074" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1074" t="inlineStr">
         <is>
@@ -83736,7 +83736,7 @@
         <v>45646</v>
       </c>
       <c r="E1075" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1075" t="inlineStr">
         <is>
@@ -83809,7 +83809,7 @@
         <v>45646</v>
       </c>
       <c r="E1076" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1076" t="inlineStr">
         <is>
@@ -83882,7 +83882,7 @@
         <v>45408</v>
       </c>
       <c r="E1077" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1077" t="inlineStr">
         <is>
@@ -83955,7 +83955,7 @@
         <v>45414</v>
       </c>
       <c r="E1078" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1078" t="inlineStr">
         <is>
@@ -84028,7 +84028,7 @@
         <v>45173</v>
       </c>
       <c r="E1079" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1079" t="inlineStr">
         <is>
@@ -84101,7 +84101,7 @@
         <v>45646</v>
       </c>
       <c r="E1080" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1080" t="inlineStr">
         <is>
@@ -84174,7 +84174,7 @@
         <v>45715</v>
       </c>
       <c r="E1081" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1081" t="inlineStr">
         <is>
@@ -84247,7 +84247,7 @@
         <v>45720</v>
       </c>
       <c r="E1082" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1082" t="inlineStr">
         <is>
@@ -84320,7 +84320,7 @@
         <v>45800</v>
       </c>
       <c r="E1083" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1083" t="inlineStr">
         <is>
@@ -84398,7 +84398,7 @@
         <v>45831</v>
       </c>
       <c r="E1084" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1084" t="inlineStr">
         <is>
@@ -84471,7 +84471,7 @@
         <v>45785</v>
       </c>
       <c r="E1085" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1085" t="inlineStr">
         <is>
@@ -84544,7 +84544,7 @@
         <v>46073</v>
       </c>
       <c r="E1086" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1086" t="inlineStr">
         <is>
@@ -84617,7 +84617,7 @@
         <v>46163</v>
       </c>
       <c r="E1087" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1087" t="inlineStr">
         <is>
@@ -84690,7 +84690,7 @@
         <v>46274</v>
       </c>
       <c r="E1088" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1088" t="inlineStr">
         <is>
@@ -84763,7 +84763,7 @@
         <v>46296</v>
       </c>
       <c r="E1089" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1089" t="inlineStr">
         <is>

--- a/Översikt VETLANDA.xlsx
+++ b/Översikt VETLANDA.xlsx
@@ -601,7 +601,7 @@
         <v>45097</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>46178</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         <v>45371</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>44890</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>44817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>45183</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>45558</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>45168</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>46107</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>45520</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>45957</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>45930</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>45170</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>44612</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>44840</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>45203</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>46100</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>44908</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>46002</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>45819</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>46163</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>46188</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>44564</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>44545</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>44819</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>45763</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>45477</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>45599</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3796,7 +3796,7 @@
         <v>45048</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>45583</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>46045</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>45814</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4224,7 +4224,7 @@
         <v>46255</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>45646</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>45131</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>44515</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>44752</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4767,7 +4767,7 @@
         <v>44643</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>45673</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>45400</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>45148</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5209,7 +5209,7 @@
         <v>45310</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5315,7 +5315,7 @@
         <v>45616</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5421,7 +5421,7 @@
         <v>45035</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>45303</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>45357</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>44572</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         <v>45589</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>45792</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         <v>45835</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         <v>45840</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
         <v>45965</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6379,7 +6379,7 @@
         <v>45713</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6489,7 +6489,7 @@
         <v>45860</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>45713</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>45891</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         <v>45211</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6913,7 +6913,7 @@
         <v>46166</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>46279</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>46293</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         <v>45106</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         <v>45509</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7448,7 +7448,7 @@
         <v>45497</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>45201</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>45539</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         <v>46051</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7876,7 +7876,7 @@
         <v>44490</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         <v>44834</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         <v>44592</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8191,7 +8191,7 @@
         <v>44747</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
         <v>44721</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8401,7 +8401,7 @@
         <v>45378</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8506,7 +8506,7 @@
         <v>44740</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8616,7 +8616,7 @@
         <v>45342</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         <v>45104</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8830,7 +8830,7 @@
         <v>44824</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
         <v>45119</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9040,7 +9040,7 @@
         <v>44833</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9145,7 +9145,7 @@
         <v>44728</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>45240</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9359,7 +9359,7 @@
         <v>44819</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
         <v>45337</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9569,7 +9569,7 @@
         <v>45835</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         <v>45672</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9783,7 +9783,7 @@
         <v>45532</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9888,7 +9888,7 @@
         <v>44998</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9993,7 +9993,7 @@
         <v>45419</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>44880</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
         <v>45645</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10308,7 +10308,7 @@
         <v>45643</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         <v>45352</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10518,7 +10518,7 @@
         <v>45021</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10623,7 +10623,7 @@
         <v>45791</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
         <v>45565</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>45586</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10938,7 +10938,7 @@
         <v>45596</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11043,7 +11043,7 @@
         <v>45597</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11148,7 +11148,7 @@
         <v>45586</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11253,7 +11253,7 @@
         <v>45555</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11358,7 +11358,7 @@
         <v>45736</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11467,7 +11467,7 @@
         <v>45408</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11572,7 +11572,7 @@
         <v>45085</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>44781</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11782,7 +11782,7 @@
         <v>45820</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
         <v>45261</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11997,7 +11997,7 @@
         <v>45839</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12102,7 +12102,7 @@
         <v>44816</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12207,7 +12207,7 @@
         <v>44748</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12312,7 +12312,7 @@
         <v>44830</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12417,7 +12417,7 @@
         <v>45009</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12522,7 +12522,7 @@
         <v>44916</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12627,7 +12627,7 @@
         <v>45880</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12732,7 +12732,7 @@
         <v>45239</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12842,7 +12842,7 @@
         <v>45775</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12947,7 +12947,7 @@
         <v>46071</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13052,7 +13052,7 @@
         <v>46188</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13157,7 +13157,7 @@
         <v>45930</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13271,7 +13271,7 @@
         <v>46248</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>46297</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13481,7 +13481,7 @@
         <v>46069</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>45904</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>45604</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13796,7 +13796,7 @@
         <v>45497</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13901,7 +13901,7 @@
         <v>45614</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14006,7 +14006,7 @@
         <v>45742</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14115,7 +14115,7 @@
         <v>44858</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14188,7 +14188,7 @@
         <v>44781</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14261,7 +14261,7 @@
         <v>44838</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>44781</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         <v>44732</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14480,7 +14480,7 @@
         <v>44515</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14553,7 +14553,7 @@
         <v>44508</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>44504</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14699,7 +14699,7 @@
         <v>44496</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14772,7 +14772,7 @@
         <v>44579</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14845,7 +14845,7 @@
         <v>44889</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14918,7 +14918,7 @@
         <v>44601</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>44544</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15064,7 +15064,7 @@
         <v>44510</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15137,7 +15137,7 @@
         <v>44517</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15210,7 +15210,7 @@
         <v>44764</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15283,7 +15283,7 @@
         <v>44510</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15356,7 +15356,7 @@
         <v>44503</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15429,7 +15429,7 @@
         <v>44819</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15502,7 +15502,7 @@
         <v>44592</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15575,7 +15575,7 @@
         <v>44750</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15648,7 +15648,7 @@
         <v>44825</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15721,7 +15721,7 @@
         <v>44488</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15794,7 +15794,7 @@
         <v>44602</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15867,7 +15867,7 @@
         <v>44638</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15940,7 +15940,7 @@
         <v>44510</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16013,7 +16013,7 @@
         <v>44721</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16086,7 +16086,7 @@
         <v>44785</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16159,7 +16159,7 @@
         <v>44592</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>44587</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16305,7 +16305,7 @@
         <v>44782</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16378,7 +16378,7 @@
         <v>44815</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16451,7 +16451,7 @@
         <v>44504</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16524,7 +16524,7 @@
         <v>44580</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16597,7 +16597,7 @@
         <v>44691</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16670,7 +16670,7 @@
         <v>44880</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16743,7 +16743,7 @@
         <v>44545</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16816,7 +16816,7 @@
         <v>44750</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16889,7 +16889,7 @@
         <v>44624</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16962,7 +16962,7 @@
         <v>44834</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17035,7 +17035,7 @@
         <v>44655</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17108,7 +17108,7 @@
         <v>44595</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17181,7 +17181,7 @@
         <v>44750</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17254,7 +17254,7 @@
         <v>44740</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17332,7 +17332,7 @@
         <v>44587</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17405,7 +17405,7 @@
         <v>44502</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17478,7 +17478,7 @@
         <v>44515</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17556,7 +17556,7 @@
         <v>44834</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17629,7 +17629,7 @@
         <v>44592</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17702,7 +17702,7 @@
         <v>44482</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17775,7 +17775,7 @@
         <v>44509</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17848,7 +17848,7 @@
         <v>44743</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17921,7 +17921,7 @@
         <v>44564</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17994,7 +17994,7 @@
         <v>44781</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18067,7 +18067,7 @@
         <v>44592</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18140,7 +18140,7 @@
         <v>44608</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18213,7 +18213,7 @@
         <v>44517</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>44600</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18359,7 +18359,7 @@
         <v>44820</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18432,7 +18432,7 @@
         <v>44816</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18505,7 +18505,7 @@
         <v>44572</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18578,7 +18578,7 @@
         <v>44721</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18651,7 +18651,7 @@
         <v>44859</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18724,7 +18724,7 @@
         <v>44841</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18797,7 +18797,7 @@
         <v>44531</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18870,7 +18870,7 @@
         <v>44645</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>44888</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>44819</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19089,7 +19089,7 @@
         <v>44656</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19162,7 +19162,7 @@
         <v>44636</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19235,7 +19235,7 @@
         <v>44784</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19308,7 +19308,7 @@
         <v>44593</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19381,7 +19381,7 @@
         <v>44834</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19454,7 +19454,7 @@
         <v>44743</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19527,7 +19527,7 @@
         <v>44587</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19600,7 +19600,7 @@
         <v>44585</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19678,7 +19678,7 @@
         <v>44585</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19756,7 +19756,7 @@
         <v>44585</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19834,7 +19834,7 @@
         <v>44733</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19907,7 +19907,7 @@
         <v>44683</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19980,7 +19980,7 @@
         <v>45232</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20053,7 +20053,7 @@
         <v>44778</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20126,7 +20126,7 @@
         <v>44602</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20199,7 +20199,7 @@
         <v>44792</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20272,7 +20272,7 @@
         <v>44504</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20345,7 +20345,7 @@
         <v>44747</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20418,7 +20418,7 @@
         <v>44818</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20491,7 +20491,7 @@
         <v>45082</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20564,7 +20564,7 @@
         <v>44815</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20637,7 +20637,7 @@
         <v>45364</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>45091</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20783,7 +20783,7 @@
         <v>45568</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20861,7 +20861,7 @@
         <v>45329</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20939,7 +20939,7 @@
         <v>44511</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21012,7 +21012,7 @@
         <v>44657</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21085,7 +21085,7 @@
         <v>45538</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21158,7 +21158,7 @@
         <v>45406</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21231,7 +21231,7 @@
         <v>45414</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21309,7 +21309,7 @@
         <v>44827</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21382,7 +21382,7 @@
         <v>45134</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21455,7 +21455,7 @@
         <v>45211</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21528,7 +21528,7 @@
         <v>44753</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21601,7 +21601,7 @@
         <v>45097</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21674,7 +21674,7 @@
         <v>45365</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21747,7 +21747,7 @@
         <v>45748</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21825,7 +21825,7 @@
         <v>45748</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21903,7 +21903,7 @@
         <v>44869</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         <v>45099</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22049,7 +22049,7 @@
         <v>45462</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22122,7 +22122,7 @@
         <v>44965</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22195,7 +22195,7 @@
         <v>45484</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22268,7 +22268,7 @@
         <v>45526</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
         <v>45384</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22414,7 +22414,7 @@
         <v>45323</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22487,7 +22487,7 @@
         <v>45438</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22560,7 +22560,7 @@
         <v>45526</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22633,7 +22633,7 @@
         <v>45406</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22706,7 +22706,7 @@
         <v>45303</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22779,7 +22779,7 @@
         <v>45335</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22852,7 +22852,7 @@
         <v>44834</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22925,7 +22925,7 @@
         <v>45104</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22998,7 +22998,7 @@
         <v>44487</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23071,7 +23071,7 @@
         <v>45329</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23144,7 +23144,7 @@
         <v>45297</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23217,7 +23217,7 @@
         <v>45226</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23290,7 +23290,7 @@
         <v>45042</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23363,7 +23363,7 @@
         <v>45114</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23436,7 +23436,7 @@
         <v>45278</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23509,7 +23509,7 @@
         <v>45771</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23587,7 +23587,7 @@
         <v>45771</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23665,7 +23665,7 @@
         <v>45351</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23738,7 +23738,7 @@
         <v>45250</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23811,7 +23811,7 @@
         <v>45267</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23884,7 +23884,7 @@
         <v>45376</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23957,7 +23957,7 @@
         <v>45327</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24030,7 +24030,7 @@
         <v>45099</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24103,7 +24103,7 @@
         <v>45035</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24176,7 +24176,7 @@
         <v>45329</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24249,7 +24249,7 @@
         <v>45202</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24322,7 +24322,7 @@
         <v>45097</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24395,7 +24395,7 @@
         <v>45298</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
         <v>44929</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24541,7 +24541,7 @@
         <v>45769</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24619,7 +24619,7 @@
         <v>45104</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>45107</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24765,7 +24765,7 @@
         <v>45296</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24838,7 +24838,7 @@
         <v>45684</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24916,7 +24916,7 @@
         <v>45240</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24989,7 +24989,7 @@
         <v>45314</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25062,7 +25062,7 @@
         <v>44902</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25135,7 +25135,7 @@
         <v>45384</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25208,7 +25208,7 @@
         <v>45660</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25281,7 +25281,7 @@
         <v>44530</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25354,7 +25354,7 @@
         <v>45182</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25432,7 +25432,7 @@
         <v>45182</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25510,7 +25510,7 @@
         <v>45182</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25583,7 +25583,7 @@
         <v>45188</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25656,7 +25656,7 @@
         <v>45370</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25729,7 +25729,7 @@
         <v>44825</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25802,7 +25802,7 @@
         <v>45272</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25875,7 +25875,7 @@
         <v>44813</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25948,7 +25948,7 @@
         <v>44946</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26021,7 +26021,7 @@
         <v>45401</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26094,7 +26094,7 @@
         <v>45089</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26167,7 +26167,7 @@
         <v>45394</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26240,7 +26240,7 @@
         <v>45300</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26313,7 +26313,7 @@
         <v>45222</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26386,7 +26386,7 @@
         <v>45119</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26459,7 +26459,7 @@
         <v>45089</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26532,7 +26532,7 @@
         <v>44837</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26605,7 +26605,7 @@
         <v>45532</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26678,7 +26678,7 @@
         <v>45336</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26751,7 +26751,7 @@
         <v>45461</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26824,7 +26824,7 @@
         <v>45440</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26897,7 +26897,7 @@
         <v>45439</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26970,7 +26970,7 @@
         <v>45345</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27043,7 +27043,7 @@
         <v>44880</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27116,7 +27116,7 @@
         <v>44880</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27189,7 +27189,7 @@
         <v>45602</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27262,7 +27262,7 @@
         <v>45701</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27340,7 +27340,7 @@
         <v>45104</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27413,7 +27413,7 @@
         <v>45104</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27486,7 +27486,7 @@
         <v>45335</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27559,7 +27559,7 @@
         <v>45372</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27632,7 +27632,7 @@
         <v>45309</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27705,7 +27705,7 @@
         <v>45231</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27778,7 +27778,7 @@
         <v>45363</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27856,7 +27856,7 @@
         <v>45099</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27929,7 +27929,7 @@
         <v>45645</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28002,7 +28002,7 @@
         <v>45580</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28075,7 +28075,7 @@
         <v>45580</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28148,7 +28148,7 @@
         <v>44710</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28221,7 +28221,7 @@
         <v>44482</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28294,7 +28294,7 @@
         <v>45763</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28367,7 +28367,7 @@
         <v>45763</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28440,7 +28440,7 @@
         <v>45763</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28513,7 +28513,7 @@
         <v>45201</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28586,7 +28586,7 @@
         <v>45321</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28659,7 +28659,7 @@
         <v>45183</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28732,7 +28732,7 @@
         <v>45884</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28805,7 +28805,7 @@
         <v>45443</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28878,7 +28878,7 @@
         <v>44743</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28951,7 +28951,7 @@
         <v>45435</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29024,7 +29024,7 @@
         <v>45132</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29097,7 +29097,7 @@
         <v>45649</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29175,7 +29175,7 @@
         <v>44837</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29248,7 +29248,7 @@
         <v>45330</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29321,7 +29321,7 @@
         <v>45254</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29399,7 +29399,7 @@
         <v>45247</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29472,7 +29472,7 @@
         <v>45449</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29545,7 +29545,7 @@
         <v>45265</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29618,7 +29618,7 @@
         <v>45826</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29691,7 +29691,7 @@
         <v>44831</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29764,7 +29764,7 @@
         <v>44510</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29837,7 +29837,7 @@
         <v>45526</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29910,7 +29910,7 @@
         <v>45673</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29983,7 +29983,7 @@
         <v>45888</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30056,7 +30056,7 @@
         <v>45701</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30134,7 +30134,7 @@
         <v>45446</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30207,7 +30207,7 @@
         <v>44970</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30280,7 +30280,7 @@
         <v>45331</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30353,7 +30353,7 @@
         <v>45742</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30426,7 +30426,7 @@
         <v>45330</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30499,7 +30499,7 @@
         <v>45575</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30572,7 +30572,7 @@
         <v>45888</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30645,7 +30645,7 @@
         <v>45786</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30718,7 +30718,7 @@
         <v>45742</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30791,7 +30791,7 @@
         <v>45888</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30864,7 +30864,7 @@
         <v>45839</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30937,7 +30937,7 @@
         <v>45541</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31010,7 +31010,7 @@
         <v>45888</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31083,7 +31083,7 @@
         <v>45888</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31156,7 +31156,7 @@
         <v>45888</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31229,7 +31229,7 @@
         <v>45341</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31302,7 +31302,7 @@
         <v>45889</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31375,7 +31375,7 @@
         <v>45163</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31448,7 +31448,7 @@
         <v>45092</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31521,7 +31521,7 @@
         <v>45414</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31594,7 +31594,7 @@
         <v>45006</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31667,7 +31667,7 @@
         <v>44503</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31740,7 +31740,7 @@
         <v>45677</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31813,7 +31813,7 @@
         <v>45359</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31886,7 +31886,7 @@
         <v>45497</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31959,7 +31959,7 @@
         <v>45497</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32032,7 +32032,7 @@
         <v>45569</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32110,7 +32110,7 @@
         <v>45544</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32183,7 +32183,7 @@
         <v>45546</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32256,7 +32256,7 @@
         <v>45625</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32329,7 +32329,7 @@
         <v>45889</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32402,7 +32402,7 @@
         <v>44984</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32475,7 +32475,7 @@
         <v>44984</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32548,7 +32548,7 @@
         <v>45433</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32621,7 +32621,7 @@
         <v>44879</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32694,7 +32694,7 @@
         <v>45544</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32767,7 +32767,7 @@
         <v>45462</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32840,7 +32840,7 @@
         <v>44859</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32913,7 +32913,7 @@
         <v>45455</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32986,7 +32986,7 @@
         <v>45030</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33059,7 +33059,7 @@
         <v>45889</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33132,7 +33132,7 @@
         <v>44970</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33205,7 +33205,7 @@
         <v>45770</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33278,7 +33278,7 @@
         <v>45839</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33351,7 +33351,7 @@
         <v>45623</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33424,7 +33424,7 @@
         <v>45898</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33497,7 +33497,7 @@
         <v>45674</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33570,7 +33570,7 @@
         <v>45602</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33643,7 +33643,7 @@
         <v>45385</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33716,7 +33716,7 @@
         <v>44481</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33789,7 +33789,7 @@
         <v>44858</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33862,7 +33862,7 @@
         <v>44515</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33940,7 +33940,7 @@
         <v>45902</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34013,7 +34013,7 @@
         <v>45188</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34086,7 +34086,7 @@
         <v>45314</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34159,7 +34159,7 @@
         <v>44564</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34237,7 +34237,7 @@
         <v>45819</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34310,7 +34310,7 @@
         <v>45737</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34383,7 +34383,7 @@
         <v>45645</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34461,7 +34461,7 @@
         <v>45228</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34534,7 +34534,7 @@
         <v>45329</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34607,7 +34607,7 @@
         <v>45737</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34680,7 +34680,7 @@
         <v>45737</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34753,7 +34753,7 @@
         <v>45587</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34826,7 +34826,7 @@
         <v>45303</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34899,7 +34899,7 @@
         <v>45376</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34972,7 +34972,7 @@
         <v>44531</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35045,7 +35045,7 @@
         <v>44995</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35118,7 +35118,7 @@
         <v>45702</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35196,7 +35196,7 @@
         <v>45615</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35269,7 +35269,7 @@
         <v>45348</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35342,7 +35342,7 @@
         <v>44602</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35415,7 +35415,7 @@
         <v>45538</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35488,7 +35488,7 @@
         <v>45315</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35561,7 +35561,7 @@
         <v>45117</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35634,7 +35634,7 @@
         <v>45112</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35707,7 +35707,7 @@
         <v>44949</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35780,7 +35780,7 @@
         <v>45174</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35858,7 +35858,7 @@
         <v>45230</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35936,7 +35936,7 @@
         <v>44592</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36009,7 +36009,7 @@
         <v>45595</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36082,7 +36082,7 @@
         <v>45274</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36155,7 +36155,7 @@
         <v>45106</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36228,7 +36228,7 @@
         <v>44781</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36301,7 +36301,7 @@
         <v>45439</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36374,7 +36374,7 @@
         <v>45581</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36452,7 +36452,7 @@
         <v>45084</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36525,7 +36525,7 @@
         <v>44587</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36598,7 +36598,7 @@
         <v>45348</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36671,7 +36671,7 @@
         <v>44600</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36744,7 +36744,7 @@
         <v>45166</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36817,7 +36817,7 @@
         <v>45911</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36890,7 +36890,7 @@
         <v>45911</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36963,7 +36963,7 @@
         <v>45401</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37036,7 +37036,7 @@
         <v>45616</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37109,7 +37109,7 @@
         <v>44523</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37182,7 +37182,7 @@
         <v>45048</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37255,7 +37255,7 @@
         <v>45783</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37328,7 +37328,7 @@
         <v>45357</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37401,7 +37401,7 @@
         <v>45175</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37474,7 +37474,7 @@
         <v>45170</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37547,7 +37547,7 @@
         <v>45170</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37620,7 +37620,7 @@
         <v>45783</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37693,7 +37693,7 @@
         <v>44587</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37766,7 +37766,7 @@
         <v>44902</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37839,7 +37839,7 @@
         <v>44926</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37912,7 +37912,7 @@
         <v>44926</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37985,7 +37985,7 @@
         <v>45420</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38058,7 +38058,7 @@
         <v>45401</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38131,7 +38131,7 @@
         <v>45716</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38204,7 +38204,7 @@
         <v>45168</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38277,7 +38277,7 @@
         <v>45456</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38350,7 +38350,7 @@
         <v>44592</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38423,7 +38423,7 @@
         <v>44545</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38496,7 +38496,7 @@
         <v>45161</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38569,7 +38569,7 @@
         <v>45439</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38642,7 +38642,7 @@
         <v>45216</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38715,7 +38715,7 @@
         <v>45786</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38788,7 +38788,7 @@
         <v>45113</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38861,7 +38861,7 @@
         <v>45470</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38934,7 +38934,7 @@
         <v>45182</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39007,7 +39007,7 @@
         <v>45478</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39080,7 +39080,7 @@
         <v>45406</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39153,7 +39153,7 @@
         <v>45742</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39226,7 +39226,7 @@
         <v>45561</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39299,7 +39299,7 @@
         <v>45545</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39372,7 +39372,7 @@
         <v>45601</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39445,7 +39445,7 @@
         <v>45922</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39518,7 +39518,7 @@
         <v>45492</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39591,7 +39591,7 @@
         <v>45569</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39664,7 +39664,7 @@
         <v>45462</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39737,7 +39737,7 @@
         <v>45519</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39810,7 +39810,7 @@
         <v>45540</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39883,7 +39883,7 @@
         <v>45350</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39956,7 +39956,7 @@
         <v>45525</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40029,7 +40029,7 @@
         <v>45925</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40102,7 +40102,7 @@
         <v>45691</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40175,7 +40175,7 @@
         <v>45031</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40248,7 +40248,7 @@
         <v>44946</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40321,7 +40321,7 @@
         <v>45792</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40394,7 +40394,7 @@
         <v>45033</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40467,7 +40467,7 @@
         <v>45022</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40540,7 +40540,7 @@
         <v>45341</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40613,7 +40613,7 @@
         <v>45168</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40686,7 +40686,7 @@
         <v>45563</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40764,7 +40764,7 @@
         <v>45706</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>45545</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40910,7 +40910,7 @@
         <v>45091</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40983,7 +40983,7 @@
         <v>44600</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41056,7 +41056,7 @@
         <v>45104</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41129,7 +41129,7 @@
         <v>45663</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41202,7 +41202,7 @@
         <v>45107</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41275,7 +41275,7 @@
         <v>45170</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41348,7 +41348,7 @@
         <v>45170</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41421,7 +41421,7 @@
         <v>44592</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41494,7 +41494,7 @@
         <v>45678</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41567,7 +41567,7 @@
         <v>45602</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41640,7 +41640,7 @@
         <v>45699</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41713,7 +41713,7 @@
         <v>44715</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41786,7 +41786,7 @@
         <v>45162</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41859,7 +41859,7 @@
         <v>45222</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41932,7 +41932,7 @@
         <v>45743</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42005,7 +42005,7 @@
         <v>45733</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42078,7 +42078,7 @@
         <v>45733</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42151,7 +42151,7 @@
         <v>45737</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42224,7 +42224,7 @@
         <v>45737</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42297,7 +42297,7 @@
         <v>44641</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42370,7 +42370,7 @@
         <v>45742</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42443,7 +42443,7 @@
         <v>45728</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42516,7 +42516,7 @@
         <v>45741</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42594,7 +42594,7 @@
         <v>44965</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42667,7 +42667,7 @@
         <v>45741</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42745,7 +42745,7 @@
         <v>44602</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42818,7 +42818,7 @@
         <v>44580</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42891,7 +42891,7 @@
         <v>44607</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42964,7 +42964,7 @@
         <v>45163</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43037,7 +43037,7 @@
         <v>44945</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43110,7 +43110,7 @@
         <v>45259</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43183,7 +43183,7 @@
         <v>45610</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43256,7 +43256,7 @@
         <v>45189</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43334,7 +43334,7 @@
         <v>45177</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43412,7 +43412,7 @@
         <v>44916</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43485,7 +43485,7 @@
         <v>45708</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43558,7 +43558,7 @@
         <v>45209</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43631,7 +43631,7 @@
         <v>45174</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43704,7 +43704,7 @@
         <v>45442</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43777,7 +43777,7 @@
         <v>45448</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43850,7 +43850,7 @@
         <v>44916</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43923,7 +43923,7 @@
         <v>44916</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43996,7 +43996,7 @@
         <v>45610</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44069,7 +44069,7 @@
         <v>45743</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44142,7 +44142,7 @@
         <v>45803</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44215,7 +44215,7 @@
         <v>45936</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44288,7 +44288,7 @@
         <v>45352</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44361,7 +44361,7 @@
         <v>45366</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44434,7 +44434,7 @@
         <v>44977</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44507,7 +44507,7 @@
         <v>45645</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44580,7 +44580,7 @@
         <v>45448</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44653,7 +44653,7 @@
         <v>44930</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44726,7 +44726,7 @@
         <v>45616</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44799,7 +44799,7 @@
         <v>44600</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44872,7 +44872,7 @@
         <v>45681</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44945,7 +44945,7 @@
         <v>45359</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45018,7 +45018,7 @@
         <v>45006</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45091,7 +45091,7 @@
         <v>45805</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45164,7 +45164,7 @@
         <v>45006</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45237,7 +45237,7 @@
         <v>45505</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45310,7 +45310,7 @@
         <v>45089</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45383,7 +45383,7 @@
         <v>45589</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45456,7 +45456,7 @@
         <v>45589</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45529,7 +45529,7 @@
         <v>45062</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45602,7 +45602,7 @@
         <v>45434</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45675,7 +45675,7 @@
         <v>45183</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45748,7 +45748,7 @@
         <v>45184</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45821,7 +45821,7 @@
         <v>45251</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45894,7 +45894,7 @@
         <v>45615</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45967,7 +45967,7 @@
         <v>45625</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46040,7 +46040,7 @@
         <v>45812</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46113,7 +46113,7 @@
         <v>44693</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46186,7 +46186,7 @@
         <v>45231</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46259,7 +46259,7 @@
         <v>45944</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46332,7 +46332,7 @@
         <v>45607</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46405,7 +46405,7 @@
         <v>45811</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46478,7 +46478,7 @@
         <v>45946</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46551,7 +46551,7 @@
         <v>45281</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46624,7 +46624,7 @@
         <v>45351</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46697,7 +46697,7 @@
         <v>45118</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46770,7 +46770,7 @@
         <v>45357</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46843,7 +46843,7 @@
         <v>45816</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46916,7 +46916,7 @@
         <v>45510</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46989,7 +46989,7 @@
         <v>45134</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47062,7 +47062,7 @@
         <v>45950</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47135,7 +47135,7 @@
         <v>45195</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47208,7 +47208,7 @@
         <v>45133</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47281,7 +47281,7 @@
         <v>45819</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47354,7 +47354,7 @@
         <v>45090</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47427,7 +47427,7 @@
         <v>45819</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47500,7 +47500,7 @@
         <v>45819</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47573,7 +47573,7 @@
         <v>45819</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47646,7 +47646,7 @@
         <v>45580</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47719,7 +47719,7 @@
         <v>44984</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47792,7 +47792,7 @@
         <v>45307</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47865,7 +47865,7 @@
         <v>45097</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47938,7 +47938,7 @@
         <v>45216</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48016,7 +48016,7 @@
         <v>45209</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48089,7 +48089,7 @@
         <v>45211</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48162,7 +48162,7 @@
         <v>45230</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48240,7 +48240,7 @@
         <v>45107</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48313,7 +48313,7 @@
         <v>45561</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48386,7 +48386,7 @@
         <v>45113</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48459,7 +48459,7 @@
         <v>44655</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48532,7 +48532,7 @@
         <v>45572</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48605,7 +48605,7 @@
         <v>45398</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48678,7 +48678,7 @@
         <v>45628</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48751,7 +48751,7 @@
         <v>45446</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48824,7 +48824,7 @@
         <v>45392</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48897,7 +48897,7 @@
         <v>44888</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48970,7 +48970,7 @@
         <v>45097</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49043,7 +49043,7 @@
         <v>45097</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49116,7 +49116,7 @@
         <v>45202</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49189,7 +49189,7 @@
         <v>45525</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49262,7 +49262,7 @@
         <v>45236</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49335,7 +49335,7 @@
         <v>45672</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49408,7 +49408,7 @@
         <v>45953</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49481,7 +49481,7 @@
         <v>45229</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49554,7 +49554,7 @@
         <v>45173</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49627,7 +49627,7 @@
         <v>45173</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49700,7 +49700,7 @@
         <v>45180</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49773,7 +49773,7 @@
         <v>45188</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49846,7 +49846,7 @@
         <v>45737</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49919,7 +49919,7 @@
         <v>45631</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49992,7 +49992,7 @@
         <v>45838</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50065,7 +50065,7 @@
         <v>44762</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50138,7 +50138,7 @@
         <v>44936</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50211,7 +50211,7 @@
         <v>45400</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50284,7 +50284,7 @@
         <v>45191</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50357,7 +50357,7 @@
         <v>45188</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50430,7 +50430,7 @@
         <v>45840</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50503,7 +50503,7 @@
         <v>45840</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50576,7 +50576,7 @@
         <v>45839</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50649,7 +50649,7 @@
         <v>44802</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50727,7 +50727,7 @@
         <v>45204</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50800,7 +50800,7 @@
         <v>45015</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50873,7 +50873,7 @@
         <v>45238</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50951,7 +50951,7 @@
         <v>45163</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51024,7 +51024,7 @@
         <v>45135</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51097,7 +51097,7 @@
         <v>45135</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51170,7 +51170,7 @@
         <v>45135</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51243,7 +51243,7 @@
         <v>45259</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51316,7 +51316,7 @@
         <v>45322</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51389,7 +51389,7 @@
         <v>45625</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51462,7 +51462,7 @@
         <v>45715</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51535,7 +51535,7 @@
         <v>45747</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51608,7 +51608,7 @@
         <v>45629</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51681,7 +51681,7 @@
         <v>45164</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51754,7 +51754,7 @@
         <v>45729</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51827,7 +51827,7 @@
         <v>45845</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51900,7 +51900,7 @@
         <v>45715</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51973,7 +51973,7 @@
         <v>45748</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52046,7 +52046,7 @@
         <v>45974</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52119,7 +52119,7 @@
         <v>45319</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52192,7 +52192,7 @@
         <v>45000</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52265,7 +52265,7 @@
         <v>45245</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52338,7 +52338,7 @@
         <v>44770</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52411,7 +52411,7 @@
         <v>45754</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52489,7 +52489,7 @@
         <v>45754</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52567,7 +52567,7 @@
         <v>45847</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52640,7 +52640,7 @@
         <v>44834</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52713,7 +52713,7 @@
         <v>45307</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52786,7 +52786,7 @@
         <v>44741</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52859,7 +52859,7 @@
         <v>45852</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52932,7 +52932,7 @@
         <v>45763</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53005,7 +53005,7 @@
         <v>44595</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53078,7 +53078,7 @@
         <v>44813</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53151,7 +53151,7 @@
         <v>45076</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53224,7 +53224,7 @@
         <v>45719</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53297,7 +53297,7 @@
         <v>45671</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53370,7 +53370,7 @@
         <v>45331</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53443,7 +53443,7 @@
         <v>45170</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53516,7 +53516,7 @@
         <v>44970</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53589,7 +53589,7 @@
         <v>44783</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53662,7 +53662,7 @@
         <v>44986</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53735,7 +53735,7 @@
         <v>45357</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53808,7 +53808,7 @@
         <v>45113</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53881,7 +53881,7 @@
         <v>45114</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53954,7 +53954,7 @@
         <v>45631</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54027,7 +54027,7 @@
         <v>45309</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54100,7 +54100,7 @@
         <v>45322</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54173,7 +54173,7 @@
         <v>45352</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54246,7 +54246,7 @@
         <v>44830</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54319,7 +54319,7 @@
         <v>45005</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54392,7 +54392,7 @@
         <v>45309</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54465,7 +54465,7 @@
         <v>45309</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54538,7 +54538,7 @@
         <v>45163</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54611,7 +54611,7 @@
         <v>44549</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54684,7 +54684,7 @@
         <v>45672</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54757,7 +54757,7 @@
         <v>44564</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54830,7 +54830,7 @@
         <v>44839</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54903,7 +54903,7 @@
         <v>45733</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54976,7 +54976,7 @@
         <v>45692</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55049,7 +55049,7 @@
         <v>45113</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55122,7 +55122,7 @@
         <v>45866</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55195,7 +55195,7 @@
         <v>45250</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55268,7 +55268,7 @@
         <v>45314</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55341,7 +55341,7 @@
         <v>45309</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55414,7 +55414,7 @@
         <v>44805</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55487,7 +55487,7 @@
         <v>45288</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55560,7 +55560,7 @@
         <v>45691</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55633,7 +55633,7 @@
         <v>44582</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55706,7 +55706,7 @@
         <v>45975</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55779,7 +55779,7 @@
         <v>45076</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55852,7 +55852,7 @@
         <v>45709</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55925,7 +55925,7 @@
         <v>44839</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55998,7 +55998,7 @@
         <v>45007</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56071,7 +56071,7 @@
         <v>45644</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56144,7 +56144,7 @@
         <v>44792</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56217,7 +56217,7 @@
         <v>45303</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56290,7 +56290,7 @@
         <v>45365</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56363,7 +56363,7 @@
         <v>44481</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56436,7 +56436,7 @@
         <v>45133</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56509,7 +56509,7 @@
         <v>45302</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56582,7 +56582,7 @@
         <v>45264</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56655,7 +56655,7 @@
         <v>45264</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56728,7 +56728,7 @@
         <v>45330</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56801,7 +56801,7 @@
         <v>45763</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56874,7 +56874,7 @@
         <v>45222</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56947,7 +56947,7 @@
         <v>45719</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57020,7 +57020,7 @@
         <v>45875</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57093,7 +57093,7 @@
         <v>45875</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57166,7 +57166,7 @@
         <v>45875</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57239,7 +57239,7 @@
         <v>44815</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57312,7 +57312,7 @@
         <v>44894</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57385,7 +57385,7 @@
         <v>45981</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57458,7 +57458,7 @@
         <v>45434</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57531,7 +57531,7 @@
         <v>45981</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57609,7 +57609,7 @@
         <v>45351</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57682,7 +57682,7 @@
         <v>45272</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57755,7 +57755,7 @@
         <v>45981</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57828,7 +57828,7 @@
         <v>45882</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57901,7 +57901,7 @@
         <v>45882</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57974,7 +57974,7 @@
         <v>44810</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58047,7 +58047,7 @@
         <v>45205</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58120,7 +58120,7 @@
         <v>45071</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58193,7 +58193,7 @@
         <v>46097</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58266,7 +58266,7 @@
         <v>45981</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58339,7 +58339,7 @@
         <v>45982</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58412,7 +58412,7 @@
         <v>45274</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58485,7 +58485,7 @@
         <v>46098</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58558,7 +58558,7 @@
         <v>45071</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58631,7 +58631,7 @@
         <v>46099</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58704,7 +58704,7 @@
         <v>46100</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58777,7 +58777,7 @@
         <v>45173</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58850,7 +58850,7 @@
         <v>45645</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58923,7 +58923,7 @@
         <v>45370</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58996,7 +58996,7 @@
         <v>45259</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59069,7 +59069,7 @@
         <v>44888</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59142,7 +59142,7 @@
         <v>46104</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59215,7 +59215,7 @@
         <v>45079</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59288,7 +59288,7 @@
         <v>45595</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59361,7 +59361,7 @@
         <v>44740</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59439,7 +59439,7 @@
         <v>45674</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59512,7 +59512,7 @@
         <v>46104</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59585,7 +59585,7 @@
         <v>46107</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59658,7 +59658,7 @@
         <v>45316</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59731,7 +59731,7 @@
         <v>45001</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59809,7 +59809,7 @@
         <v>46107</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59882,7 +59882,7 @@
         <v>46107</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59955,7 +59955,7 @@
         <v>45702</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60028,7 +60028,7 @@
         <v>44971</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60101,7 +60101,7 @@
         <v>44851</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60174,7 +60174,7 @@
         <v>45475</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60247,7 +60247,7 @@
         <v>46111</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60320,7 +60320,7 @@
         <v>46111</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60393,7 +60393,7 @@
         <v>45992</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60466,7 +60466,7 @@
         <v>45572</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60539,7 +60539,7 @@
         <v>45329</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60612,7 +60612,7 @@
         <v>45329</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60685,7 +60685,7 @@
         <v>44965</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60758,7 +60758,7 @@
         <v>45069</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60831,7 +60831,7 @@
         <v>44916</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60904,7 +60904,7 @@
         <v>45105</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60977,7 +60977,7 @@
         <v>44497</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61050,7 +61050,7 @@
         <v>46121</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61123,7 +61123,7 @@
         <v>44484</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61196,7 +61196,7 @@
         <v>44916</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61269,7 +61269,7 @@
         <v>44488</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61342,7 +61342,7 @@
         <v>46121</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61415,7 +61415,7 @@
         <v>46122</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61488,7 +61488,7 @@
         <v>44502</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61561,7 +61561,7 @@
         <v>45999</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61634,7 +61634,7 @@
         <v>45999</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61707,7 +61707,7 @@
         <v>46126</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61780,7 +61780,7 @@
         <v>46001</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61853,7 +61853,7 @@
         <v>46127</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61926,7 +61926,7 @@
         <v>46128</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61999,7 +61999,7 @@
         <v>46128</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62072,7 +62072,7 @@
         <v>46128</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62145,7 +62145,7 @@
         <v>44957</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62218,7 +62218,7 @@
         <v>44967</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62291,7 +62291,7 @@
         <v>44967</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62364,7 +62364,7 @@
         <v>44903</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62437,7 +62437,7 @@
         <v>46128</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62510,7 +62510,7 @@
         <v>46128</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62583,7 +62583,7 @@
         <v>45414</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62661,7 +62661,7 @@
         <v>45414</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62734,7 +62734,7 @@
         <v>44952</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62807,7 +62807,7 @@
         <v>44607</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62880,7 +62880,7 @@
         <v>46133</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62953,7 +62953,7 @@
         <v>44831</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63026,7 +63026,7 @@
         <v>45408</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63099,7 +63099,7 @@
         <v>44880</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63172,7 +63172,7 @@
         <v>46003</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63245,7 +63245,7 @@
         <v>46133</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63318,7 +63318,7 @@
         <v>44998</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63391,7 +63391,7 @@
         <v>44592</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63464,7 +63464,7 @@
         <v>46006</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63537,7 +63537,7 @@
         <v>45153</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63610,7 +63610,7 @@
         <v>45891</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63683,7 +63683,7 @@
         <v>46037</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63756,7 +63756,7 @@
         <v>46007</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63829,7 +63829,7 @@
         <v>46007</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63902,7 +63902,7 @@
         <v>45302</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63975,7 +63975,7 @@
         <v>46112</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64053,7 +64053,7 @@
         <v>45306</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64126,7 +64126,7 @@
         <v>45883</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64199,7 +64199,7 @@
         <v>45895</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64272,7 +64272,7 @@
         <v>45912</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64345,7 +64345,7 @@
         <v>44946</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64418,7 +64418,7 @@
         <v>45944</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64491,7 +64491,7 @@
         <v>45755</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64564,7 +64564,7 @@
         <v>44683</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64637,7 +64637,7 @@
         <v>45440</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64710,7 +64710,7 @@
         <v>45699</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64783,7 +64783,7 @@
         <v>45889</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64856,7 +64856,7 @@
         <v>45902</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64929,7 +64929,7 @@
         <v>45971</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65002,7 +65002,7 @@
         <v>45999</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65075,7 +65075,7 @@
         <v>45348</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65148,7 +65148,7 @@
         <v>45608</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65221,7 +65221,7 @@
         <v>45825</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65294,7 +65294,7 @@
         <v>45971</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65367,7 +65367,7 @@
         <v>45610</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65440,7 +65440,7 @@
         <v>44538</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65513,7 +65513,7 @@
         <v>46010</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65586,7 +65586,7 @@
         <v>45112</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65659,7 +65659,7 @@
         <v>46010</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65732,7 +65732,7 @@
         <v>46009</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65805,7 +65805,7 @@
         <v>44677</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65878,7 +65878,7 @@
         <v>46009</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65951,7 +65951,7 @@
         <v>45674</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66024,7 +66024,7 @@
         <v>45903</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66097,7 +66097,7 @@
         <v>45351</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66170,7 +66170,7 @@
         <v>45363</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66248,7 +66248,7 @@
         <v>45363</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66326,7 +66326,7 @@
         <v>45839</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66399,7 +66399,7 @@
         <v>46052</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66472,7 +66472,7 @@
         <v>45799</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66545,7 +66545,7 @@
         <v>45827</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66618,7 +66618,7 @@
         <v>45670</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66691,7 +66691,7 @@
         <v>45931</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66764,7 +66764,7 @@
         <v>45965</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66837,7 +66837,7 @@
         <v>45839</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66910,7 +66910,7 @@
         <v>45866</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -66983,7 +66983,7 @@
         <v>45873</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67056,7 +67056,7 @@
         <v>45883</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67129,7 +67129,7 @@
         <v>45693</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67202,7 +67202,7 @@
         <v>45763</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67275,7 +67275,7 @@
         <v>45925</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67348,7 +67348,7 @@
         <v>44917</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67421,7 +67421,7 @@
         <v>44747</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67494,7 +67494,7 @@
         <v>45827</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67567,7 +67567,7 @@
         <v>45363</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67645,7 +67645,7 @@
         <v>45363</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -67723,7 +67723,7 @@
         <v>45190</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -67796,7 +67796,7 @@
         <v>45441</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67869,7 +67869,7 @@
         <v>44785</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -67942,7 +67942,7 @@
         <v>44972</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -68015,7 +68015,7 @@
         <v>44488</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -68088,7 +68088,7 @@
         <v>45785</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -68161,7 +68161,7 @@
         <v>46030</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -68234,7 +68234,7 @@
         <v>46030</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -68307,7 +68307,7 @@
         <v>44952</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68380,7 +68380,7 @@
         <v>45827</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68453,7 +68453,7 @@
         <v>44984</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68526,7 +68526,7 @@
         <v>46029</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -68599,7 +68599,7 @@
         <v>46031</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -68672,7 +68672,7 @@
         <v>44510</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -68745,7 +68745,7 @@
         <v>45152</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68818,7 +68818,7 @@
         <v>45840</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -68891,7 +68891,7 @@
         <v>44480</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -68964,7 +68964,7 @@
         <v>45525</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -69037,7 +69037,7 @@
         <v>44655</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -69110,7 +69110,7 @@
         <v>45055</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -69183,7 +69183,7 @@
         <v>44495</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -69256,7 +69256,7 @@
         <v>45224</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -69334,7 +69334,7 @@
         <v>45097</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -69407,7 +69407,7 @@
         <v>45069</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69480,7 +69480,7 @@
         <v>45691</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -69558,7 +69558,7 @@
         <v>45669</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -69631,7 +69631,7 @@
         <v>45107</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -69704,7 +69704,7 @@
         <v>46044</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -69777,7 +69777,7 @@
         <v>45313</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -69850,7 +69850,7 @@
         <v>45219</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -69923,7 +69923,7 @@
         <v>45841</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -69996,7 +69996,7 @@
         <v>45615</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -70069,7 +70069,7 @@
         <v>45183</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -70142,7 +70142,7 @@
         <v>45364</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -70215,7 +70215,7 @@
         <v>44963</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -70288,7 +70288,7 @@
         <v>46048</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -70361,7 +70361,7 @@
         <v>45785</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -70434,7 +70434,7 @@
         <v>45135</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70507,7 +70507,7 @@
         <v>46048</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -70580,7 +70580,7 @@
         <v>45219</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -70658,7 +70658,7 @@
         <v>44930</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -70731,7 +70731,7 @@
         <v>45282</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -70804,7 +70804,7 @@
         <v>45245</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -70877,7 +70877,7 @@
         <v>44847</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -70950,7 +70950,7 @@
         <v>45310</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -71023,7 +71023,7 @@
         <v>46045</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -71096,7 +71096,7 @@
         <v>45763</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -71169,7 +71169,7 @@
         <v>45589</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -71242,7 +71242,7 @@
         <v>45574</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -71320,7 +71320,7 @@
         <v>46122</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -71393,7 +71393,7 @@
         <v>45575</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -71466,7 +71466,7 @@
         <v>45362</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -71539,7 +71539,7 @@
         <v>45251</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -71612,7 +71612,7 @@
         <v>45057</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -71685,7 +71685,7 @@
         <v>46048</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -71758,7 +71758,7 @@
         <v>44998</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -71831,7 +71831,7 @@
         <v>44970</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -71904,7 +71904,7 @@
         <v>46049</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -71977,7 +71977,7 @@
         <v>45164</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -72050,7 +72050,7 @@
         <v>46055</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -72123,7 +72123,7 @@
         <v>45133</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -72196,7 +72196,7 @@
         <v>46062</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -72269,7 +72269,7 @@
         <v>46063</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -72342,7 +72342,7 @@
         <v>46063</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -72415,7 +72415,7 @@
         <v>46063</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -72488,7 +72488,7 @@
         <v>46063</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -72561,7 +72561,7 @@
         <v>46153</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -72634,7 +72634,7 @@
         <v>46153</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -72707,7 +72707,7 @@
         <v>46077</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -72780,7 +72780,7 @@
         <v>46077</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -72853,7 +72853,7 @@
         <v>46153</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -72926,7 +72926,7 @@
         <v>46154</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -73004,7 +73004,7 @@
         <v>45400</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -73082,7 +73082,7 @@
         <v>46084</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -73155,7 +73155,7 @@
         <v>46084</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -73228,7 +73228,7 @@
         <v>46084</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -73301,7 +73301,7 @@
         <v>45639</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -73374,7 +73374,7 @@
         <v>46126</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -73447,7 +73447,7 @@
         <v>45866</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -73520,7 +73520,7 @@
         <v>46087</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -73593,7 +73593,7 @@
         <v>46064</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -73666,7 +73666,7 @@
         <v>45761</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -73739,7 +73739,7 @@
         <v>46091</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -73812,7 +73812,7 @@
         <v>45930</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -73885,7 +73885,7 @@
         <v>46160</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -73958,7 +73958,7 @@
         <v>46160</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -74031,7 +74031,7 @@
         <v>46160</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -74104,7 +74104,7 @@
         <v>46161</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -74177,7 +74177,7 @@
         <v>46002</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -74250,7 +74250,7 @@
         <v>46092</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -74323,7 +74323,7 @@
         <v>46160</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -74396,7 +74396,7 @@
         <v>46161</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -74469,7 +74469,7 @@
         <v>45930</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -74547,7 +74547,7 @@
         <v>46163</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -74620,7 +74620,7 @@
         <v>46175</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -74693,7 +74693,7 @@
         <v>46178</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -74766,7 +74766,7 @@
         <v>46178</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -74839,7 +74839,7 @@
         <v>46182</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -74912,7 +74912,7 @@
         <v>46182</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -74985,7 +74985,7 @@
         <v>46184</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -75058,7 +75058,7 @@
         <v>46182</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -75131,7 +75131,7 @@
         <v>46184</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -75204,7 +75204,7 @@
         <v>46184</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -75277,7 +75277,7 @@
         <v>46185</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -75350,7 +75350,7 @@
         <v>46188</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -75423,7 +75423,7 @@
         <v>45925</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -75496,7 +75496,7 @@
         <v>46190</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -75569,7 +75569,7 @@
         <v>46195</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -75642,7 +75642,7 @@
         <v>46197</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -75715,7 +75715,7 @@
         <v>46196</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -75788,7 +75788,7 @@
         <v>46202</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -75861,7 +75861,7 @@
         <v>46204</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -75934,7 +75934,7 @@
         <v>46069</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -76007,7 +76007,7 @@
         <v>46213</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -76080,7 +76080,7 @@
         <v>46168</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -76153,7 +76153,7 @@
         <v>46177</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -76226,7 +76226,7 @@
         <v>46265</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -76299,7 +76299,7 @@
         <v>46268</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -76372,7 +76372,7 @@
         <v>46269</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -76445,7 +76445,7 @@
         <v>46274</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -76518,7 +76518,7 @@
         <v>46273</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -76591,7 +76591,7 @@
         <v>46273</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -76664,7 +76664,7 @@
         <v>46276</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -76737,7 +76737,7 @@
         <v>46233</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -76810,7 +76810,7 @@
         <v>46276</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -76883,7 +76883,7 @@
         <v>46276</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -76956,7 +76956,7 @@
         <v>46276</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -77029,7 +77029,7 @@
         <v>46276</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -77102,7 +77102,7 @@
         <v>46279</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -77175,7 +77175,7 @@
         <v>46234</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -77248,7 +77248,7 @@
         <v>46237</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -77321,7 +77321,7 @@
         <v>46234</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -77394,7 +77394,7 @@
         <v>46234</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -77467,7 +77467,7 @@
         <v>46283</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -77540,7 +77540,7 @@
         <v>45953</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -77613,7 +77613,7 @@
         <v>46240</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -77686,7 +77686,7 @@
         <v>46245</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -77759,7 +77759,7 @@
         <v>46244</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -77832,7 +77832,7 @@
         <v>46280</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -77905,7 +77905,7 @@
         <v>46244</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -77978,7 +77978,7 @@
         <v>46009</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -78051,7 +78051,7 @@
         <v>46289</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -78124,7 +78124,7 @@
         <v>46290</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -78197,7 +78197,7 @@
         <v>46178</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -78270,7 +78270,7 @@
         <v>46289</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -78343,7 +78343,7 @@
         <v>46246</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -78416,7 +78416,7 @@
         <v>46178</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -78489,7 +78489,7 @@
         <v>46293</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -78562,7 +78562,7 @@
         <v>46293</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -78635,7 +78635,7 @@
         <v>46293</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -78708,7 +78708,7 @@
         <v>45925</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -78781,7 +78781,7 @@
         <v>46295</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -78854,7 +78854,7 @@
         <v>46296</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -78927,7 +78927,7 @@
         <v>46296</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -79000,7 +79000,7 @@
         <v>46252</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -79073,7 +79073,7 @@
         <v>46062</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -79146,7 +79146,7 @@
         <v>46297</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -79219,7 +79219,7 @@
         <v>46031</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -79292,7 +79292,7 @@
         <v>45936</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -79365,7 +79365,7 @@
         <v>46247</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -79443,7 +79443,7 @@
         <v>46247</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -79521,7 +79521,7 @@
         <v>46297</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -79594,7 +79594,7 @@
         <v>46248</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -79672,7 +79672,7 @@
         <v>46258</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -79745,7 +79745,7 @@
         <v>46259</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -79818,7 +79818,7 @@
         <v>46259</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -79891,7 +79891,7 @@
         <v>46301</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -79964,7 +79964,7 @@
         <v>46294</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -80037,7 +80037,7 @@
         <v>46258</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -80110,7 +80110,7 @@
         <v>46294</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -80183,7 +80183,7 @@
         <v>46301</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -80256,7 +80256,7 @@
         <v>46302</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -80329,7 +80329,7 @@
         <v>46153</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -80402,7 +80402,7 @@
         <v>46302</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
@@ -80475,7 +80475,7 @@
         <v>46303</v>
       </c>
       <c r="E1032" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
@@ -80548,7 +80548,7 @@
         <v>46003</v>
       </c>
       <c r="E1033" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
@@ -80621,7 +80621,7 @@
         <v>46185</v>
       </c>
       <c r="E1034" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
@@ -80694,7 +80694,7 @@
         <v>46303</v>
       </c>
       <c r="E1035" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
@@ -80767,7 +80767,7 @@
         <v>46178</v>
       </c>
       <c r="E1036" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
@@ -80840,7 +80840,7 @@
         <v>46196</v>
       </c>
       <c r="E1037" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
@@ -80913,7 +80913,7 @@
         <v>46304</v>
       </c>
       <c r="E1038" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1038" t="inlineStr">
         <is>
@@ -80986,7 +80986,7 @@
         <v>46302</v>
       </c>
       <c r="E1039" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1039" t="inlineStr">
         <is>
@@ -81059,7 +81059,7 @@
         <v>46303</v>
       </c>
       <c r="E1040" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1040" t="inlineStr">
         <is>
@@ -81132,7 +81132,7 @@
         <v>45884</v>
       </c>
       <c r="E1041" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1041" t="inlineStr">
         <is>
@@ -81205,7 +81205,7 @@
         <v>45636</v>
       </c>
       <c r="E1042" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1042" t="inlineStr">
         <is>
@@ -81278,7 +81278,7 @@
         <v>45580</v>
       </c>
       <c r="E1043" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1043" t="inlineStr">
         <is>
@@ -81351,7 +81351,7 @@
         <v>45447</v>
       </c>
       <c r="E1044" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1044" t="inlineStr">
         <is>
@@ -81424,7 +81424,7 @@
         <v>45170</v>
       </c>
       <c r="E1045" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1045" t="inlineStr">
         <is>
@@ -81497,7 +81497,7 @@
         <v>45106</v>
       </c>
       <c r="E1046" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1046" t="inlineStr">
         <is>
@@ -81570,7 +81570,7 @@
         <v>45467</v>
       </c>
       <c r="E1047" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1047" t="inlineStr">
         <is>
@@ -81643,7 +81643,7 @@
         <v>44509</v>
       </c>
       <c r="E1048" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1048" t="inlineStr">
         <is>
@@ -81721,7 +81721,7 @@
         <v>45664</v>
       </c>
       <c r="E1049" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1049" t="inlineStr">
         <is>
@@ -81794,7 +81794,7 @@
         <v>45208</v>
       </c>
       <c r="E1050" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1050" t="inlineStr">
         <is>
@@ -81867,7 +81867,7 @@
         <v>45406</v>
       </c>
       <c r="E1051" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1051" t="inlineStr">
         <is>
@@ -81940,7 +81940,7 @@
         <v>45497</v>
       </c>
       <c r="E1052" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1052" t="inlineStr">
         <is>
@@ -82013,7 +82013,7 @@
         <v>45497</v>
       </c>
       <c r="E1053" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1053" t="inlineStr">
         <is>
@@ -82086,7 +82086,7 @@
         <v>45106</v>
       </c>
       <c r="E1054" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1054" t="inlineStr">
         <is>
@@ -82159,7 +82159,7 @@
         <v>45646</v>
       </c>
       <c r="E1055" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1055" t="inlineStr">
         <is>
@@ -82232,7 +82232,7 @@
         <v>45646</v>
       </c>
       <c r="E1056" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1056" t="inlineStr">
         <is>
@@ -82305,7 +82305,7 @@
         <v>45580</v>
       </c>
       <c r="E1057" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1057" t="inlineStr">
         <is>
@@ -82378,7 +82378,7 @@
         <v>45646</v>
       </c>
       <c r="E1058" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1058" t="inlineStr">
         <is>
@@ -82451,7 +82451,7 @@
         <v>45646</v>
       </c>
       <c r="E1059" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1059" t="inlineStr">
         <is>
@@ -82524,7 +82524,7 @@
         <v>45408</v>
       </c>
       <c r="E1060" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1060" t="inlineStr">
         <is>
@@ -82597,7 +82597,7 @@
         <v>45414</v>
       </c>
       <c r="E1061" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1061" t="inlineStr">
         <is>
@@ -82670,7 +82670,7 @@
         <v>45173</v>
       </c>
       <c r="E1062" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1062" t="inlineStr">
         <is>
@@ -82743,7 +82743,7 @@
         <v>45646</v>
       </c>
       <c r="E1063" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1063" t="inlineStr">
         <is>
@@ -82816,7 +82816,7 @@
         <v>45715</v>
       </c>
       <c r="E1064" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1064" t="inlineStr">
         <is>
@@ -82889,7 +82889,7 @@
         <v>45720</v>
       </c>
       <c r="E1065" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1065" t="inlineStr">
         <is>
@@ -82962,7 +82962,7 @@
         <v>45800</v>
       </c>
       <c r="E1066" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1066" t="inlineStr">
         <is>
@@ -83040,7 +83040,7 @@
         <v>45831</v>
       </c>
       <c r="E1067" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1067" t="inlineStr">
         <is>
@@ -83113,7 +83113,7 @@
         <v>45785</v>
       </c>
       <c r="E1068" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1068" t="inlineStr">
         <is>
@@ -83186,7 +83186,7 @@
         <v>46073</v>
       </c>
       <c r="E1069" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1069" t="inlineStr">
         <is>
@@ -83259,7 +83259,7 @@
         <v>46163</v>
       </c>
       <c r="E1070" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1070" t="inlineStr">
         <is>
@@ -83332,7 +83332,7 @@
         <v>46274</v>
       </c>
       <c r="E1071" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1071" t="inlineStr">
         <is>
@@ -83405,7 +83405,7 @@
         <v>46296</v>
       </c>
       <c r="E1072" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1072" t="inlineStr">
         <is>

--- a/Översikt VETLANDA.xlsx
+++ b/Översikt VETLANDA.xlsx
@@ -601,7 +601,7 @@
         <v>45097</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>46178</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         <v>45371</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>44890</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>44817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>45183</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>45558</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>45168</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>46107</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>45520</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>45957</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>45930</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>45170</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>44612</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>44840</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>45203</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>46100</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>44908</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>46002</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>45819</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>46163</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>46188</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>44564</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>44545</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>44819</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>45763</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>45477</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>45599</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3796,7 +3796,7 @@
         <v>45048</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>45583</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>46045</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>45814</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4224,7 +4224,7 @@
         <v>46255</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>45646</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>45131</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>44515</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>44752</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4767,7 +4767,7 @@
         <v>44643</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>45673</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>45400</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>45148</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5209,7 +5209,7 @@
         <v>45310</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5315,7 +5315,7 @@
         <v>45616</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5421,7 +5421,7 @@
         <v>45035</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>45303</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>45357</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>44572</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         <v>45589</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>45792</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         <v>45835</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         <v>45840</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
         <v>45965</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6379,7 +6379,7 @@
         <v>45713</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6489,7 +6489,7 @@
         <v>45860</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>45713</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>45891</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         <v>45211</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6913,7 +6913,7 @@
         <v>46166</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>46279</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>46293</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         <v>45106</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         <v>45509</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7448,7 +7448,7 @@
         <v>45497</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>45201</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>45539</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         <v>46051</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7876,7 +7876,7 @@
         <v>44490</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         <v>44834</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         <v>44592</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8191,7 +8191,7 @@
         <v>44747</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
         <v>44721</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8401,7 +8401,7 @@
         <v>45378</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8506,7 +8506,7 @@
         <v>44740</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8616,7 +8616,7 @@
         <v>45342</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         <v>45104</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8830,7 +8830,7 @@
         <v>44824</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
         <v>45119</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9040,7 +9040,7 @@
         <v>44833</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9145,7 +9145,7 @@
         <v>44728</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>45240</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9359,7 +9359,7 @@
         <v>44819</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
         <v>45337</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9569,7 +9569,7 @@
         <v>45835</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         <v>45672</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9783,7 +9783,7 @@
         <v>45532</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9888,7 +9888,7 @@
         <v>44998</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9993,7 +9993,7 @@
         <v>45419</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>44880</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
         <v>45645</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10308,7 +10308,7 @@
         <v>45643</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         <v>45352</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10518,7 +10518,7 @@
         <v>45021</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10623,7 +10623,7 @@
         <v>45791</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
         <v>45565</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>45586</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10938,7 +10938,7 @@
         <v>45596</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11043,7 +11043,7 @@
         <v>45597</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11148,7 +11148,7 @@
         <v>45586</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11253,7 +11253,7 @@
         <v>45555</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11358,7 +11358,7 @@
         <v>45736</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11467,7 +11467,7 @@
         <v>45408</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11572,7 +11572,7 @@
         <v>45085</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>44781</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11782,7 +11782,7 @@
         <v>45820</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
         <v>45261</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11997,7 +11997,7 @@
         <v>45839</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12102,7 +12102,7 @@
         <v>44816</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12207,7 +12207,7 @@
         <v>44748</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12312,7 +12312,7 @@
         <v>44830</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12417,7 +12417,7 @@
         <v>45009</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12522,7 +12522,7 @@
         <v>44916</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12627,7 +12627,7 @@
         <v>45880</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12732,7 +12732,7 @@
         <v>45239</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12842,7 +12842,7 @@
         <v>45775</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12947,7 +12947,7 @@
         <v>46071</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13052,7 +13052,7 @@
         <v>46188</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13157,7 +13157,7 @@
         <v>45930</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13271,7 +13271,7 @@
         <v>46248</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>46297</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13481,7 +13481,7 @@
         <v>46069</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>45904</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>45604</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13796,7 +13796,7 @@
         <v>45497</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13901,7 +13901,7 @@
         <v>45614</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14006,7 +14006,7 @@
         <v>45742</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14115,7 +14115,7 @@
         <v>44858</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14188,7 +14188,7 @@
         <v>44781</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14261,7 +14261,7 @@
         <v>44838</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>44781</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         <v>44732</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14480,7 +14480,7 @@
         <v>44515</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14553,7 +14553,7 @@
         <v>44508</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>44504</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14699,7 +14699,7 @@
         <v>44496</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14772,7 +14772,7 @@
         <v>44579</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14845,7 +14845,7 @@
         <v>44889</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14918,7 +14918,7 @@
         <v>44601</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>44544</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15064,7 +15064,7 @@
         <v>44510</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15137,7 +15137,7 @@
         <v>44517</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15210,7 +15210,7 @@
         <v>44764</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15283,7 +15283,7 @@
         <v>44510</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15356,7 +15356,7 @@
         <v>44503</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15429,7 +15429,7 @@
         <v>44819</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15502,7 +15502,7 @@
         <v>44592</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15575,7 +15575,7 @@
         <v>44750</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15648,7 +15648,7 @@
         <v>44825</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15721,7 +15721,7 @@
         <v>44488</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15794,7 +15794,7 @@
         <v>44602</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15867,7 +15867,7 @@
         <v>44638</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15940,7 +15940,7 @@
         <v>44510</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16013,7 +16013,7 @@
         <v>44721</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16086,7 +16086,7 @@
         <v>44785</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16159,7 +16159,7 @@
         <v>44592</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>44587</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16305,7 +16305,7 @@
         <v>44782</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16378,7 +16378,7 @@
         <v>44815</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16451,7 +16451,7 @@
         <v>44504</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16524,7 +16524,7 @@
         <v>44580</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16597,7 +16597,7 @@
         <v>44691</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16670,7 +16670,7 @@
         <v>44880</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16743,7 +16743,7 @@
         <v>44545</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16816,7 +16816,7 @@
         <v>44750</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16889,7 +16889,7 @@
         <v>44624</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16962,7 +16962,7 @@
         <v>44834</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17035,7 +17035,7 @@
         <v>44655</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17108,7 +17108,7 @@
         <v>44595</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17181,7 +17181,7 @@
         <v>44750</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17254,7 +17254,7 @@
         <v>44740</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17332,7 +17332,7 @@
         <v>44587</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17405,7 +17405,7 @@
         <v>44502</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17478,7 +17478,7 @@
         <v>44515</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17556,7 +17556,7 @@
         <v>44834</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17629,7 +17629,7 @@
         <v>44592</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17702,7 +17702,7 @@
         <v>44482</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17775,7 +17775,7 @@
         <v>44509</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17848,7 +17848,7 @@
         <v>44743</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17921,7 +17921,7 @@
         <v>44564</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17994,7 +17994,7 @@
         <v>44781</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18067,7 +18067,7 @@
         <v>44592</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18140,7 +18140,7 @@
         <v>44608</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18213,7 +18213,7 @@
         <v>44517</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>44600</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18359,7 +18359,7 @@
         <v>44820</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18432,7 +18432,7 @@
         <v>44816</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18505,7 +18505,7 @@
         <v>44572</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18578,7 +18578,7 @@
         <v>44721</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18651,7 +18651,7 @@
         <v>44859</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18724,7 +18724,7 @@
         <v>44841</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18797,7 +18797,7 @@
         <v>44531</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18870,7 +18870,7 @@
         <v>44645</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>44888</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>44819</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19089,7 +19089,7 @@
         <v>44656</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19162,7 +19162,7 @@
         <v>44636</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19235,7 +19235,7 @@
         <v>44784</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19308,7 +19308,7 @@
         <v>44593</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19381,7 +19381,7 @@
         <v>44834</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19454,7 +19454,7 @@
         <v>44743</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19527,7 +19527,7 @@
         <v>44587</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19600,7 +19600,7 @@
         <v>44585</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19678,7 +19678,7 @@
         <v>44585</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19756,7 +19756,7 @@
         <v>44585</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19834,7 +19834,7 @@
         <v>44733</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19907,7 +19907,7 @@
         <v>44683</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19980,7 +19980,7 @@
         <v>45232</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20053,7 +20053,7 @@
         <v>44778</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20126,7 +20126,7 @@
         <v>44602</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20199,7 +20199,7 @@
         <v>44792</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20272,7 +20272,7 @@
         <v>44504</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20345,7 +20345,7 @@
         <v>44747</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20418,7 +20418,7 @@
         <v>44818</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20491,7 +20491,7 @@
         <v>45082</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20564,7 +20564,7 @@
         <v>44815</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20637,7 +20637,7 @@
         <v>45364</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>45091</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20783,7 +20783,7 @@
         <v>45568</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20861,7 +20861,7 @@
         <v>45329</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20939,7 +20939,7 @@
         <v>44511</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21012,7 +21012,7 @@
         <v>44657</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21085,7 +21085,7 @@
         <v>45538</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21158,7 +21158,7 @@
         <v>45406</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21231,7 +21231,7 @@
         <v>45414</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21309,7 +21309,7 @@
         <v>44827</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21382,7 +21382,7 @@
         <v>45134</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21455,7 +21455,7 @@
         <v>45211</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21528,7 +21528,7 @@
         <v>44753</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21601,7 +21601,7 @@
         <v>45097</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21674,7 +21674,7 @@
         <v>45365</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21747,7 +21747,7 @@
         <v>45748</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21825,7 +21825,7 @@
         <v>45748</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21903,7 +21903,7 @@
         <v>44869</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         <v>45099</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22049,7 +22049,7 @@
         <v>45462</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22122,7 +22122,7 @@
         <v>44965</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22195,7 +22195,7 @@
         <v>45484</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22268,7 +22268,7 @@
         <v>45526</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
         <v>45384</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22414,7 +22414,7 @@
         <v>45323</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22487,7 +22487,7 @@
         <v>45438</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22560,7 +22560,7 @@
         <v>45526</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22633,7 +22633,7 @@
         <v>45406</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22706,7 +22706,7 @@
         <v>45303</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22779,7 +22779,7 @@
         <v>45335</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22852,7 +22852,7 @@
         <v>44834</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22925,7 +22925,7 @@
         <v>45104</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22998,7 +22998,7 @@
         <v>44487</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23071,7 +23071,7 @@
         <v>45329</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23144,7 +23144,7 @@
         <v>45297</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23217,7 +23217,7 @@
         <v>45226</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23290,7 +23290,7 @@
         <v>45042</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23363,7 +23363,7 @@
         <v>45114</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23436,7 +23436,7 @@
         <v>45278</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23509,7 +23509,7 @@
         <v>45771</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23587,7 +23587,7 @@
         <v>45771</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23665,7 +23665,7 @@
         <v>45351</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23738,7 +23738,7 @@
         <v>45250</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23811,7 +23811,7 @@
         <v>45267</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23884,7 +23884,7 @@
         <v>45376</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23957,7 +23957,7 @@
         <v>45327</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24030,7 +24030,7 @@
         <v>45099</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24103,7 +24103,7 @@
         <v>45035</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24176,7 +24176,7 @@
         <v>45329</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24249,7 +24249,7 @@
         <v>45202</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24322,7 +24322,7 @@
         <v>45097</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24395,7 +24395,7 @@
         <v>45298</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
         <v>44929</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24541,7 +24541,7 @@
         <v>45769</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24619,7 +24619,7 @@
         <v>45104</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>45107</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24765,7 +24765,7 @@
         <v>45296</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24838,7 +24838,7 @@
         <v>45684</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24916,7 +24916,7 @@
         <v>45240</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24989,7 +24989,7 @@
         <v>45314</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25062,7 +25062,7 @@
         <v>44902</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25135,7 +25135,7 @@
         <v>45384</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25208,7 +25208,7 @@
         <v>45660</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25281,7 +25281,7 @@
         <v>44530</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25354,7 +25354,7 @@
         <v>45182</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25432,7 +25432,7 @@
         <v>45182</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25510,7 +25510,7 @@
         <v>45182</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25583,7 +25583,7 @@
         <v>45188</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25656,7 +25656,7 @@
         <v>45370</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25729,7 +25729,7 @@
         <v>44825</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25802,7 +25802,7 @@
         <v>45272</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25875,7 +25875,7 @@
         <v>44813</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25948,7 +25948,7 @@
         <v>44946</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26021,7 +26021,7 @@
         <v>45401</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26094,7 +26094,7 @@
         <v>45089</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26167,7 +26167,7 @@
         <v>45394</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26240,7 +26240,7 @@
         <v>45300</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26313,7 +26313,7 @@
         <v>45222</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26386,7 +26386,7 @@
         <v>45119</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26459,7 +26459,7 @@
         <v>45089</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26532,7 +26532,7 @@
         <v>44837</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26605,7 +26605,7 @@
         <v>45532</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26678,7 +26678,7 @@
         <v>45336</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26751,7 +26751,7 @@
         <v>45461</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26824,7 +26824,7 @@
         <v>45440</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26897,7 +26897,7 @@
         <v>45439</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26970,7 +26970,7 @@
         <v>45345</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27043,7 +27043,7 @@
         <v>44880</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27116,7 +27116,7 @@
         <v>44880</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27189,7 +27189,7 @@
         <v>45602</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27262,7 +27262,7 @@
         <v>45701</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27340,7 +27340,7 @@
         <v>45104</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27413,7 +27413,7 @@
         <v>45104</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27486,7 +27486,7 @@
         <v>45335</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27559,7 +27559,7 @@
         <v>45372</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27632,7 +27632,7 @@
         <v>45309</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27705,7 +27705,7 @@
         <v>45231</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27778,7 +27778,7 @@
         <v>45363</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27856,7 +27856,7 @@
         <v>45099</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27929,7 +27929,7 @@
         <v>45645</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28002,7 +28002,7 @@
         <v>45580</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28075,7 +28075,7 @@
         <v>45580</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28148,7 +28148,7 @@
         <v>44710</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28221,7 +28221,7 @@
         <v>44482</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28294,7 +28294,7 @@
         <v>45763</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28367,7 +28367,7 @@
         <v>45763</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28440,7 +28440,7 @@
         <v>45763</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28513,7 +28513,7 @@
         <v>45201</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28586,7 +28586,7 @@
         <v>45321</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28659,7 +28659,7 @@
         <v>45183</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28732,7 +28732,7 @@
         <v>45884</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28805,7 +28805,7 @@
         <v>45443</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28878,7 +28878,7 @@
         <v>44743</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28951,7 +28951,7 @@
         <v>45435</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29024,7 +29024,7 @@
         <v>45132</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29097,7 +29097,7 @@
         <v>45649</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29175,7 +29175,7 @@
         <v>44837</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29248,7 +29248,7 @@
         <v>45330</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29321,7 +29321,7 @@
         <v>45254</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29399,7 +29399,7 @@
         <v>45247</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29472,7 +29472,7 @@
         <v>45449</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29545,7 +29545,7 @@
         <v>45265</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29618,7 +29618,7 @@
         <v>45826</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29691,7 +29691,7 @@
         <v>44831</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29764,7 +29764,7 @@
         <v>44510</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29837,7 +29837,7 @@
         <v>45526</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29910,7 +29910,7 @@
         <v>45673</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29983,7 +29983,7 @@
         <v>45888</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30056,7 +30056,7 @@
         <v>45701</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30134,7 +30134,7 @@
         <v>45446</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30207,7 +30207,7 @@
         <v>44970</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30280,7 +30280,7 @@
         <v>45331</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30353,7 +30353,7 @@
         <v>45742</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30426,7 +30426,7 @@
         <v>45330</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30499,7 +30499,7 @@
         <v>45575</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30572,7 +30572,7 @@
         <v>45888</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30645,7 +30645,7 @@
         <v>45786</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30718,7 +30718,7 @@
         <v>45742</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30791,7 +30791,7 @@
         <v>45888</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30864,7 +30864,7 @@
         <v>45839</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30937,7 +30937,7 @@
         <v>45541</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31010,7 +31010,7 @@
         <v>45888</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31083,7 +31083,7 @@
         <v>45888</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31156,7 +31156,7 @@
         <v>45888</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31229,7 +31229,7 @@
         <v>45341</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31302,7 +31302,7 @@
         <v>45889</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31375,7 +31375,7 @@
         <v>45163</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31448,7 +31448,7 @@
         <v>45092</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31521,7 +31521,7 @@
         <v>45414</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31594,7 +31594,7 @@
         <v>45006</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31667,7 +31667,7 @@
         <v>44503</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31740,7 +31740,7 @@
         <v>45677</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31813,7 +31813,7 @@
         <v>45359</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31886,7 +31886,7 @@
         <v>45497</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31959,7 +31959,7 @@
         <v>45497</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32032,7 +32032,7 @@
         <v>45569</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32110,7 +32110,7 @@
         <v>45544</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32183,7 +32183,7 @@
         <v>45546</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32256,7 +32256,7 @@
         <v>45625</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32329,7 +32329,7 @@
         <v>45889</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32402,7 +32402,7 @@
         <v>44984</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32475,7 +32475,7 @@
         <v>44984</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32548,7 +32548,7 @@
         <v>45433</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32621,7 +32621,7 @@
         <v>44879</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32694,7 +32694,7 @@
         <v>45544</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32767,7 +32767,7 @@
         <v>45462</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32840,7 +32840,7 @@
         <v>44859</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32913,7 +32913,7 @@
         <v>45455</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32986,7 +32986,7 @@
         <v>45030</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33059,7 +33059,7 @@
         <v>45889</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33132,7 +33132,7 @@
         <v>44970</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33205,7 +33205,7 @@
         <v>45770</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33278,7 +33278,7 @@
         <v>45839</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33351,7 +33351,7 @@
         <v>45623</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33424,7 +33424,7 @@
         <v>45898</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33497,7 +33497,7 @@
         <v>45674</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33570,7 +33570,7 @@
         <v>45602</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33643,7 +33643,7 @@
         <v>45385</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33716,7 +33716,7 @@
         <v>44481</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33789,7 +33789,7 @@
         <v>44858</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33862,7 +33862,7 @@
         <v>44515</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33940,7 +33940,7 @@
         <v>45902</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34013,7 +34013,7 @@
         <v>45188</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34086,7 +34086,7 @@
         <v>45314</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34159,7 +34159,7 @@
         <v>44564</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34237,7 +34237,7 @@
         <v>45819</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34310,7 +34310,7 @@
         <v>45737</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34383,7 +34383,7 @@
         <v>45645</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34461,7 +34461,7 @@
         <v>45228</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34534,7 +34534,7 @@
         <v>45329</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34607,7 +34607,7 @@
         <v>45737</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34680,7 +34680,7 @@
         <v>45737</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34753,7 +34753,7 @@
         <v>45587</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34826,7 +34826,7 @@
         <v>45303</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34899,7 +34899,7 @@
         <v>45376</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34972,7 +34972,7 @@
         <v>44531</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35045,7 +35045,7 @@
         <v>44995</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35118,7 +35118,7 @@
         <v>45702</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35196,7 +35196,7 @@
         <v>45615</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35269,7 +35269,7 @@
         <v>45348</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35342,7 +35342,7 @@
         <v>44602</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35415,7 +35415,7 @@
         <v>45538</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35488,7 +35488,7 @@
         <v>45315</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35561,7 +35561,7 @@
         <v>45117</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35634,7 +35634,7 @@
         <v>45112</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35707,7 +35707,7 @@
         <v>44949</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35780,7 +35780,7 @@
         <v>45174</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35858,7 +35858,7 @@
         <v>45230</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35936,7 +35936,7 @@
         <v>44592</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36009,7 +36009,7 @@
         <v>45595</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36082,7 +36082,7 @@
         <v>45274</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36155,7 +36155,7 @@
         <v>45106</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36228,7 +36228,7 @@
         <v>44781</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36301,7 +36301,7 @@
         <v>45439</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36374,7 +36374,7 @@
         <v>45581</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36452,7 +36452,7 @@
         <v>45084</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36525,7 +36525,7 @@
         <v>44587</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36598,7 +36598,7 @@
         <v>45348</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36671,7 +36671,7 @@
         <v>44600</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36744,7 +36744,7 @@
         <v>45166</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36817,7 +36817,7 @@
         <v>45911</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36890,7 +36890,7 @@
         <v>45911</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36963,7 +36963,7 @@
         <v>45401</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37036,7 +37036,7 @@
         <v>45616</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37109,7 +37109,7 @@
         <v>44523</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37182,7 +37182,7 @@
         <v>45048</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37255,7 +37255,7 @@
         <v>45783</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37328,7 +37328,7 @@
         <v>45357</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37401,7 +37401,7 @@
         <v>45175</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37474,7 +37474,7 @@
         <v>45170</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37547,7 +37547,7 @@
         <v>45170</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37620,7 +37620,7 @@
         <v>45783</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37693,7 +37693,7 @@
         <v>44587</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37766,7 +37766,7 @@
         <v>44902</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37839,7 +37839,7 @@
         <v>44926</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37912,7 +37912,7 @@
         <v>44926</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37985,7 +37985,7 @@
         <v>45420</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38058,7 +38058,7 @@
         <v>45401</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38131,7 +38131,7 @@
         <v>45716</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38204,7 +38204,7 @@
         <v>45168</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38277,7 +38277,7 @@
         <v>45456</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38350,7 +38350,7 @@
         <v>44592</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38423,7 +38423,7 @@
         <v>44545</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38496,7 +38496,7 @@
         <v>45161</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38569,7 +38569,7 @@
         <v>45439</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38642,7 +38642,7 @@
         <v>45216</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38715,7 +38715,7 @@
         <v>45786</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38788,7 +38788,7 @@
         <v>45113</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38861,7 +38861,7 @@
         <v>45470</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38934,7 +38934,7 @@
         <v>45182</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39007,7 +39007,7 @@
         <v>45478</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39080,7 +39080,7 @@
         <v>45406</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39153,7 +39153,7 @@
         <v>45742</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39226,7 +39226,7 @@
         <v>45561</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39299,7 +39299,7 @@
         <v>45545</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39372,7 +39372,7 @@
         <v>45601</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39445,7 +39445,7 @@
         <v>45922</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39518,7 +39518,7 @@
         <v>45492</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39591,7 +39591,7 @@
         <v>45569</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39664,7 +39664,7 @@
         <v>45462</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39737,7 +39737,7 @@
         <v>45519</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39810,7 +39810,7 @@
         <v>45540</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39883,7 +39883,7 @@
         <v>45350</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39956,7 +39956,7 @@
         <v>45525</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40029,7 +40029,7 @@
         <v>45925</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40102,7 +40102,7 @@
         <v>45691</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40175,7 +40175,7 @@
         <v>45031</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40248,7 +40248,7 @@
         <v>44946</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40321,7 +40321,7 @@
         <v>45792</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40394,7 +40394,7 @@
         <v>45033</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40467,7 +40467,7 @@
         <v>45022</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40540,7 +40540,7 @@
         <v>45341</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40613,7 +40613,7 @@
         <v>45168</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40686,7 +40686,7 @@
         <v>45563</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40764,7 +40764,7 @@
         <v>45706</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>45545</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40910,7 +40910,7 @@
         <v>45091</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40983,7 +40983,7 @@
         <v>44600</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41056,7 +41056,7 @@
         <v>45104</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41129,7 +41129,7 @@
         <v>45663</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41202,7 +41202,7 @@
         <v>45107</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41275,7 +41275,7 @@
         <v>45170</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41348,7 +41348,7 @@
         <v>45170</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41421,7 +41421,7 @@
         <v>44592</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41494,7 +41494,7 @@
         <v>45678</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41567,7 +41567,7 @@
         <v>45602</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41640,7 +41640,7 @@
         <v>45699</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41713,7 +41713,7 @@
         <v>44715</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41786,7 +41786,7 @@
         <v>45162</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41859,7 +41859,7 @@
         <v>45222</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41932,7 +41932,7 @@
         <v>45743</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42005,7 +42005,7 @@
         <v>45733</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42078,7 +42078,7 @@
         <v>45733</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42151,7 +42151,7 @@
         <v>45737</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42224,7 +42224,7 @@
         <v>45737</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42297,7 +42297,7 @@
         <v>44641</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42370,7 +42370,7 @@
         <v>45742</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42443,7 +42443,7 @@
         <v>45728</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42516,7 +42516,7 @@
         <v>45741</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42594,7 +42594,7 @@
         <v>44965</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42667,7 +42667,7 @@
         <v>45741</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42745,7 +42745,7 @@
         <v>44602</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42818,7 +42818,7 @@
         <v>44580</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42891,7 +42891,7 @@
         <v>44607</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42964,7 +42964,7 @@
         <v>45163</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43037,7 +43037,7 @@
         <v>44945</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43110,7 +43110,7 @@
         <v>45259</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43183,7 +43183,7 @@
         <v>45610</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43256,7 +43256,7 @@
         <v>45189</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43334,7 +43334,7 @@
         <v>45177</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43412,7 +43412,7 @@
         <v>44916</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43485,7 +43485,7 @@
         <v>45708</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43558,7 +43558,7 @@
         <v>45209</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43631,7 +43631,7 @@
         <v>45174</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43704,7 +43704,7 @@
         <v>45442</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43777,7 +43777,7 @@
         <v>45448</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43850,7 +43850,7 @@
         <v>44916</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43923,7 +43923,7 @@
         <v>44916</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43996,7 +43996,7 @@
         <v>45610</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44069,7 +44069,7 @@
         <v>45743</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44142,7 +44142,7 @@
         <v>45803</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44215,7 +44215,7 @@
         <v>45936</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44288,7 +44288,7 @@
         <v>45352</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44361,7 +44361,7 @@
         <v>45366</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44434,7 +44434,7 @@
         <v>44977</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44507,7 +44507,7 @@
         <v>45645</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44580,7 +44580,7 @@
         <v>45448</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44653,7 +44653,7 @@
         <v>44930</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44726,7 +44726,7 @@
         <v>45616</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44799,7 +44799,7 @@
         <v>44600</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44872,7 +44872,7 @@
         <v>45681</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44945,7 +44945,7 @@
         <v>45359</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45018,7 +45018,7 @@
         <v>45006</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45091,7 +45091,7 @@
         <v>45805</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45164,7 +45164,7 @@
         <v>45006</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45237,7 +45237,7 @@
         <v>45505</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45310,7 +45310,7 @@
         <v>45089</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45383,7 +45383,7 @@
         <v>45589</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45456,7 +45456,7 @@
         <v>45589</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45529,7 +45529,7 @@
         <v>45062</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45602,7 +45602,7 @@
         <v>45434</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45675,7 +45675,7 @@
         <v>45183</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45748,7 +45748,7 @@
         <v>45184</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45821,7 +45821,7 @@
         <v>45251</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45894,7 +45894,7 @@
         <v>45615</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45967,7 +45967,7 @@
         <v>45625</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46040,7 +46040,7 @@
         <v>45812</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46113,7 +46113,7 @@
         <v>44693</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46186,7 +46186,7 @@
         <v>45231</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46259,7 +46259,7 @@
         <v>45944</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46332,7 +46332,7 @@
         <v>45607</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46405,7 +46405,7 @@
         <v>45811</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46478,7 +46478,7 @@
         <v>45946</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46551,7 +46551,7 @@
         <v>45281</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46624,7 +46624,7 @@
         <v>45351</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46697,7 +46697,7 @@
         <v>45118</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46770,7 +46770,7 @@
         <v>45357</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46843,7 +46843,7 @@
         <v>45816</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46916,7 +46916,7 @@
         <v>45510</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46989,7 +46989,7 @@
         <v>45134</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47062,7 +47062,7 @@
         <v>45950</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47135,7 +47135,7 @@
         <v>45195</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47208,7 +47208,7 @@
         <v>45133</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47281,7 +47281,7 @@
         <v>45819</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47354,7 +47354,7 @@
         <v>45090</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47427,7 +47427,7 @@
         <v>45819</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47500,7 +47500,7 @@
         <v>45819</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47573,7 +47573,7 @@
         <v>45819</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47646,7 +47646,7 @@
         <v>45580</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47719,7 +47719,7 @@
         <v>44984</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47792,7 +47792,7 @@
         <v>45307</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47865,7 +47865,7 @@
         <v>45097</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47938,7 +47938,7 @@
         <v>45216</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48016,7 +48016,7 @@
         <v>45209</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48089,7 +48089,7 @@
         <v>45211</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48162,7 +48162,7 @@
         <v>45230</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48240,7 +48240,7 @@
         <v>45107</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48313,7 +48313,7 @@
         <v>45561</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48386,7 +48386,7 @@
         <v>45113</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48459,7 +48459,7 @@
         <v>44655</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48532,7 +48532,7 @@
         <v>45572</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48605,7 +48605,7 @@
         <v>45398</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48678,7 +48678,7 @@
         <v>45628</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48751,7 +48751,7 @@
         <v>45446</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48824,7 +48824,7 @@
         <v>45392</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48897,7 +48897,7 @@
         <v>44888</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48970,7 +48970,7 @@
         <v>45097</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49043,7 +49043,7 @@
         <v>45097</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49116,7 +49116,7 @@
         <v>45202</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49189,7 +49189,7 @@
         <v>45525</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49262,7 +49262,7 @@
         <v>45236</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49335,7 +49335,7 @@
         <v>45672</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49408,7 +49408,7 @@
         <v>45953</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49481,7 +49481,7 @@
         <v>45229</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49554,7 +49554,7 @@
         <v>45173</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49627,7 +49627,7 @@
         <v>45173</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49700,7 +49700,7 @@
         <v>45180</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49773,7 +49773,7 @@
         <v>45188</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49846,7 +49846,7 @@
         <v>45737</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49919,7 +49919,7 @@
         <v>45631</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49992,7 +49992,7 @@
         <v>45838</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50065,7 +50065,7 @@
         <v>44762</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50138,7 +50138,7 @@
         <v>44936</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50211,7 +50211,7 @@
         <v>45400</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50284,7 +50284,7 @@
         <v>45191</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50357,7 +50357,7 @@
         <v>45188</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50430,7 +50430,7 @@
         <v>45840</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50503,7 +50503,7 @@
         <v>45840</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50576,7 +50576,7 @@
         <v>45839</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50649,7 +50649,7 @@
         <v>44802</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50727,7 +50727,7 @@
         <v>45204</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50800,7 +50800,7 @@
         <v>45015</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50873,7 +50873,7 @@
         <v>45238</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50951,7 +50951,7 @@
         <v>45163</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51024,7 +51024,7 @@
         <v>45135</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51097,7 +51097,7 @@
         <v>45135</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51170,7 +51170,7 @@
         <v>45135</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51243,7 +51243,7 @@
         <v>45259</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51316,7 +51316,7 @@
         <v>45322</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51389,7 +51389,7 @@
         <v>45625</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51462,7 +51462,7 @@
         <v>45715</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51535,7 +51535,7 @@
         <v>45747</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51608,7 +51608,7 @@
         <v>45629</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51681,7 +51681,7 @@
         <v>45164</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51754,7 +51754,7 @@
         <v>45729</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51827,7 +51827,7 @@
         <v>45845</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51900,7 +51900,7 @@
         <v>45715</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51973,7 +51973,7 @@
         <v>45748</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52046,7 +52046,7 @@
         <v>45974</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52119,7 +52119,7 @@
         <v>45319</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52192,7 +52192,7 @@
         <v>45000</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52265,7 +52265,7 @@
         <v>45245</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52338,7 +52338,7 @@
         <v>44770</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52411,7 +52411,7 @@
         <v>45754</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52489,7 +52489,7 @@
         <v>45754</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52567,7 +52567,7 @@
         <v>45847</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52640,7 +52640,7 @@
         <v>44834</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52713,7 +52713,7 @@
         <v>45307</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52786,7 +52786,7 @@
         <v>44741</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52859,7 +52859,7 @@
         <v>45852</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52932,7 +52932,7 @@
         <v>45763</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53005,7 +53005,7 @@
         <v>44595</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53078,7 +53078,7 @@
         <v>44813</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53151,7 +53151,7 @@
         <v>45076</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53224,7 +53224,7 @@
         <v>45719</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53297,7 +53297,7 @@
         <v>45671</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53370,7 +53370,7 @@
         <v>45331</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53443,7 +53443,7 @@
         <v>45170</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53516,7 +53516,7 @@
         <v>44970</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53589,7 +53589,7 @@
         <v>44783</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53662,7 +53662,7 @@
         <v>44986</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53735,7 +53735,7 @@
         <v>45357</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53808,7 +53808,7 @@
         <v>45113</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53881,7 +53881,7 @@
         <v>45114</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53954,7 +53954,7 @@
         <v>45631</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54027,7 +54027,7 @@
         <v>45309</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54100,7 +54100,7 @@
         <v>45322</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54173,7 +54173,7 @@
         <v>45352</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54246,7 +54246,7 @@
         <v>44830</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54319,7 +54319,7 @@
         <v>45005</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54392,7 +54392,7 @@
         <v>45309</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54465,7 +54465,7 @@
         <v>45309</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54538,7 +54538,7 @@
         <v>45163</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54611,7 +54611,7 @@
         <v>44549</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54684,7 +54684,7 @@
         <v>45672</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54757,7 +54757,7 @@
         <v>44564</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54830,7 +54830,7 @@
         <v>44839</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54903,7 +54903,7 @@
         <v>45733</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54976,7 +54976,7 @@
         <v>45692</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55049,7 +55049,7 @@
         <v>45113</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55122,7 +55122,7 @@
         <v>45866</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55195,7 +55195,7 @@
         <v>45250</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55268,7 +55268,7 @@
         <v>45314</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55341,7 +55341,7 @@
         <v>45309</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55414,7 +55414,7 @@
         <v>44805</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55487,7 +55487,7 @@
         <v>45288</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55560,7 +55560,7 @@
         <v>45691</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55633,7 +55633,7 @@
         <v>44582</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55706,7 +55706,7 @@
         <v>45975</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55779,7 +55779,7 @@
         <v>45076</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55852,7 +55852,7 @@
         <v>45709</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55925,7 +55925,7 @@
         <v>44839</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55998,7 +55998,7 @@
         <v>45007</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56071,7 +56071,7 @@
         <v>45644</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56144,7 +56144,7 @@
         <v>44792</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56217,7 +56217,7 @@
         <v>45303</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56290,7 +56290,7 @@
         <v>45365</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56363,7 +56363,7 @@
         <v>44481</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56436,7 +56436,7 @@
         <v>45133</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56509,7 +56509,7 @@
         <v>45302</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56582,7 +56582,7 @@
         <v>45264</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56655,7 +56655,7 @@
         <v>45264</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56728,7 +56728,7 @@
         <v>45330</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56801,7 +56801,7 @@
         <v>45763</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56874,7 +56874,7 @@
         <v>45222</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56947,7 +56947,7 @@
         <v>45719</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57020,7 +57020,7 @@
         <v>45875</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57093,7 +57093,7 @@
         <v>45875</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57166,7 +57166,7 @@
         <v>45875</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57239,7 +57239,7 @@
         <v>44815</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57312,7 +57312,7 @@
         <v>44894</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57385,7 +57385,7 @@
         <v>45981</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57458,7 +57458,7 @@
         <v>45434</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57531,7 +57531,7 @@
         <v>45981</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57609,7 +57609,7 @@
         <v>45351</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57682,7 +57682,7 @@
         <v>45272</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57755,7 +57755,7 @@
         <v>45981</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57828,7 +57828,7 @@
         <v>45882</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57901,7 +57901,7 @@
         <v>45882</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57974,7 +57974,7 @@
         <v>44810</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58047,7 +58047,7 @@
         <v>45205</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58120,7 +58120,7 @@
         <v>45071</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58193,7 +58193,7 @@
         <v>46097</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58266,7 +58266,7 @@
         <v>45981</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58339,7 +58339,7 @@
         <v>45982</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58412,7 +58412,7 @@
         <v>45274</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58485,7 +58485,7 @@
         <v>46098</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58558,7 +58558,7 @@
         <v>45071</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58631,7 +58631,7 @@
         <v>46099</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58704,7 +58704,7 @@
         <v>46100</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58777,7 +58777,7 @@
         <v>45173</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58850,7 +58850,7 @@
         <v>45645</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58923,7 +58923,7 @@
         <v>45370</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58996,7 +58996,7 @@
         <v>45259</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59069,7 +59069,7 @@
         <v>44888</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59142,7 +59142,7 @@
         <v>46104</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59215,7 +59215,7 @@
         <v>45079</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59288,7 +59288,7 @@
         <v>45595</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59361,7 +59361,7 @@
         <v>44740</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59439,7 +59439,7 @@
         <v>45674</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59512,7 +59512,7 @@
         <v>46104</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59585,7 +59585,7 @@
         <v>46107</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59658,7 +59658,7 @@
         <v>45316</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59731,7 +59731,7 @@
         <v>45001</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59809,7 +59809,7 @@
         <v>46107</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59882,7 +59882,7 @@
         <v>46107</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59955,7 +59955,7 @@
         <v>45702</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60028,7 +60028,7 @@
         <v>44971</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60101,7 +60101,7 @@
         <v>44851</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60174,7 +60174,7 @@
         <v>45475</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60247,7 +60247,7 @@
         <v>46111</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60320,7 +60320,7 @@
         <v>46111</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60393,7 +60393,7 @@
         <v>45992</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60466,7 +60466,7 @@
         <v>45572</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60539,7 +60539,7 @@
         <v>45329</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60612,7 +60612,7 @@
         <v>45329</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60685,7 +60685,7 @@
         <v>44965</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60758,7 +60758,7 @@
         <v>45069</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60831,7 +60831,7 @@
         <v>44916</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60904,7 +60904,7 @@
         <v>45105</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60977,7 +60977,7 @@
         <v>44497</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61050,7 +61050,7 @@
         <v>46121</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61123,7 +61123,7 @@
         <v>44484</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61196,7 +61196,7 @@
         <v>44916</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61269,7 +61269,7 @@
         <v>44488</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61342,7 +61342,7 @@
         <v>46121</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61415,7 +61415,7 @@
         <v>46122</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61488,7 +61488,7 @@
         <v>44502</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61561,7 +61561,7 @@
         <v>45999</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61634,7 +61634,7 @@
         <v>45999</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61707,7 +61707,7 @@
         <v>46126</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61780,7 +61780,7 @@
         <v>46001</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61853,7 +61853,7 @@
         <v>46127</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61926,7 +61926,7 @@
         <v>46128</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61999,7 +61999,7 @@
         <v>46128</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62072,7 +62072,7 @@
         <v>46128</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62145,7 +62145,7 @@
         <v>44957</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62218,7 +62218,7 @@
         <v>44967</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62291,7 +62291,7 @@
         <v>44967</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62364,7 +62364,7 @@
         <v>44903</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62437,7 +62437,7 @@
         <v>46128</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62510,7 +62510,7 @@
         <v>46128</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62583,7 +62583,7 @@
         <v>45414</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62661,7 +62661,7 @@
         <v>45414</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62734,7 +62734,7 @@
         <v>44952</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62807,7 +62807,7 @@
         <v>44607</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62880,7 +62880,7 @@
         <v>46133</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62953,7 +62953,7 @@
         <v>44831</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63026,7 +63026,7 @@
         <v>45408</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63099,7 +63099,7 @@
         <v>44880</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63172,7 +63172,7 @@
         <v>46003</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63245,7 +63245,7 @@
         <v>46133</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63318,7 +63318,7 @@
         <v>44998</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63391,7 +63391,7 @@
         <v>44592</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63464,7 +63464,7 @@
         <v>46006</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63537,7 +63537,7 @@
         <v>45153</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63610,7 +63610,7 @@
         <v>45891</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63683,7 +63683,7 @@
         <v>46037</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63756,7 +63756,7 @@
         <v>46007</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63829,7 +63829,7 @@
         <v>46007</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63902,7 +63902,7 @@
         <v>45302</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63975,7 +63975,7 @@
         <v>46112</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64053,7 +64053,7 @@
         <v>45306</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64126,7 +64126,7 @@
         <v>45883</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64199,7 +64199,7 @@
         <v>45895</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64272,7 +64272,7 @@
         <v>45912</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64345,7 +64345,7 @@
         <v>44946</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64418,7 +64418,7 @@
         <v>45944</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64491,7 +64491,7 @@
         <v>45755</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64564,7 +64564,7 @@
         <v>44683</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64637,7 +64637,7 @@
         <v>45440</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64710,7 +64710,7 @@
         <v>45699</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64783,7 +64783,7 @@
         <v>45889</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64856,7 +64856,7 @@
         <v>45902</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64929,7 +64929,7 @@
         <v>45971</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65002,7 +65002,7 @@
         <v>45999</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65075,7 +65075,7 @@
         <v>45348</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65148,7 +65148,7 @@
         <v>45608</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65221,7 +65221,7 @@
         <v>45825</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65294,7 +65294,7 @@
         <v>45971</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65367,7 +65367,7 @@
         <v>45610</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65440,7 +65440,7 @@
         <v>44538</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65513,7 +65513,7 @@
         <v>46010</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65586,7 +65586,7 @@
         <v>45112</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65659,7 +65659,7 @@
         <v>46010</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65732,7 +65732,7 @@
         <v>46009</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65805,7 +65805,7 @@
         <v>44677</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65878,7 +65878,7 @@
         <v>46009</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65951,7 +65951,7 @@
         <v>45674</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66024,7 +66024,7 @@
         <v>45903</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66097,7 +66097,7 @@
         <v>45351</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66170,7 +66170,7 @@
         <v>45363</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66248,7 +66248,7 @@
         <v>45363</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66326,7 +66326,7 @@
         <v>45839</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66399,7 +66399,7 @@
         <v>46052</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66472,7 +66472,7 @@
         <v>45799</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66545,7 +66545,7 @@
         <v>45827</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66618,7 +66618,7 @@
         <v>45670</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66691,7 +66691,7 @@
         <v>45931</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66764,7 +66764,7 @@
         <v>45965</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66837,7 +66837,7 @@
         <v>45839</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66910,7 +66910,7 @@
         <v>45866</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -66983,7 +66983,7 @@
         <v>45873</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67056,7 +67056,7 @@
         <v>45883</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67129,7 +67129,7 @@
         <v>45693</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67202,7 +67202,7 @@
         <v>45763</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67275,7 +67275,7 @@
         <v>45925</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67348,7 +67348,7 @@
         <v>44917</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67421,7 +67421,7 @@
         <v>44747</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67494,7 +67494,7 @@
         <v>45827</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67567,7 +67567,7 @@
         <v>45363</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67645,7 +67645,7 @@
         <v>45363</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -67723,7 +67723,7 @@
         <v>45190</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -67796,7 +67796,7 @@
         <v>45441</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67869,7 +67869,7 @@
         <v>44785</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -67942,7 +67942,7 @@
         <v>44972</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -68015,7 +68015,7 @@
         <v>44488</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -68088,7 +68088,7 @@
         <v>45785</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -68161,7 +68161,7 @@
         <v>46030</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -68234,7 +68234,7 @@
         <v>46030</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -68307,7 +68307,7 @@
         <v>44952</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68380,7 +68380,7 @@
         <v>45827</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68453,7 +68453,7 @@
         <v>44984</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68526,7 +68526,7 @@
         <v>46029</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -68599,7 +68599,7 @@
         <v>46031</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -68672,7 +68672,7 @@
         <v>44510</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -68745,7 +68745,7 @@
         <v>45152</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68818,7 +68818,7 @@
         <v>45840</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -68891,7 +68891,7 @@
         <v>44480</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -68964,7 +68964,7 @@
         <v>45525</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -69037,7 +69037,7 @@
         <v>44655</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -69110,7 +69110,7 @@
         <v>45055</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -69183,7 +69183,7 @@
         <v>44495</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -69256,7 +69256,7 @@
         <v>45224</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -69334,7 +69334,7 @@
         <v>45097</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -69407,7 +69407,7 @@
         <v>45069</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69480,7 +69480,7 @@
         <v>45691</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -69558,7 +69558,7 @@
         <v>45669</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -69631,7 +69631,7 @@
         <v>45107</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -69704,7 +69704,7 @@
         <v>46044</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -69777,7 +69777,7 @@
         <v>45313</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -69850,7 +69850,7 @@
         <v>45219</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -69923,7 +69923,7 @@
         <v>45841</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -69996,7 +69996,7 @@
         <v>45615</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -70069,7 +70069,7 @@
         <v>45183</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -70142,7 +70142,7 @@
         <v>45364</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -70215,7 +70215,7 @@
         <v>44963</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -70288,7 +70288,7 @@
         <v>46048</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -70361,7 +70361,7 @@
         <v>45785</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -70434,7 +70434,7 @@
         <v>45135</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70507,7 +70507,7 @@
         <v>46048</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -70580,7 +70580,7 @@
         <v>45219</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -70658,7 +70658,7 @@
         <v>44930</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -70731,7 +70731,7 @@
         <v>45282</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -70804,7 +70804,7 @@
         <v>45245</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -70877,7 +70877,7 @@
         <v>44847</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -70950,7 +70950,7 @@
         <v>45310</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -71023,7 +71023,7 @@
         <v>46045</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -71096,7 +71096,7 @@
         <v>45763</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -71169,7 +71169,7 @@
         <v>45589</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -71242,7 +71242,7 @@
         <v>45574</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -71320,7 +71320,7 @@
         <v>46122</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -71393,7 +71393,7 @@
         <v>45575</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -71466,7 +71466,7 @@
         <v>45362</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -71539,7 +71539,7 @@
         <v>45251</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -71612,7 +71612,7 @@
         <v>45057</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -71685,7 +71685,7 @@
         <v>46048</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -71758,7 +71758,7 @@
         <v>44998</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -71831,7 +71831,7 @@
         <v>44970</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -71904,7 +71904,7 @@
         <v>46049</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -71977,7 +71977,7 @@
         <v>45164</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -72050,7 +72050,7 @@
         <v>46055</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -72123,7 +72123,7 @@
         <v>45133</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -72196,7 +72196,7 @@
         <v>46062</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -72269,7 +72269,7 @@
         <v>46063</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -72342,7 +72342,7 @@
         <v>46063</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -72415,7 +72415,7 @@
         <v>46063</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -72488,7 +72488,7 @@
         <v>46063</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -72561,7 +72561,7 @@
         <v>46153</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -72634,7 +72634,7 @@
         <v>46153</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -72707,7 +72707,7 @@
         <v>46077</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -72780,7 +72780,7 @@
         <v>46077</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -72853,7 +72853,7 @@
         <v>46153</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -72926,7 +72926,7 @@
         <v>46154</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -73004,7 +73004,7 @@
         <v>45400</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -73082,7 +73082,7 @@
         <v>46084</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -73155,7 +73155,7 @@
         <v>46084</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -73228,7 +73228,7 @@
         <v>46084</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -73301,7 +73301,7 @@
         <v>45639</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -73374,7 +73374,7 @@
         <v>46126</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -73447,7 +73447,7 @@
         <v>45866</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -73520,7 +73520,7 @@
         <v>46087</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -73593,7 +73593,7 @@
         <v>46064</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -73666,7 +73666,7 @@
         <v>45761</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -73739,7 +73739,7 @@
         <v>46091</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -73812,7 +73812,7 @@
         <v>45930</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -73885,7 +73885,7 @@
         <v>46160</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -73958,7 +73958,7 @@
         <v>46160</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -74031,7 +74031,7 @@
         <v>46160</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -74104,7 +74104,7 @@
         <v>46161</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -74177,7 +74177,7 @@
         <v>46002</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -74250,7 +74250,7 @@
         <v>46092</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -74323,7 +74323,7 @@
         <v>46160</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -74396,7 +74396,7 @@
         <v>46161</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -74469,7 +74469,7 @@
         <v>45930</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -74547,7 +74547,7 @@
         <v>46163</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -74620,7 +74620,7 @@
         <v>46175</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -74693,7 +74693,7 @@
         <v>46178</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -74766,7 +74766,7 @@
         <v>46178</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -74839,7 +74839,7 @@
         <v>46182</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -74912,7 +74912,7 @@
         <v>46182</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -74985,7 +74985,7 @@
         <v>46184</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -75058,7 +75058,7 @@
         <v>46182</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -75131,7 +75131,7 @@
         <v>46184</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -75204,7 +75204,7 @@
         <v>46184</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -75277,7 +75277,7 @@
         <v>46185</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -75350,7 +75350,7 @@
         <v>46188</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -75423,7 +75423,7 @@
         <v>45925</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -75496,7 +75496,7 @@
         <v>46190</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -75569,7 +75569,7 @@
         <v>46195</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -75642,7 +75642,7 @@
         <v>46197</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -75715,7 +75715,7 @@
         <v>46196</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -75788,7 +75788,7 @@
         <v>46202</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -75861,7 +75861,7 @@
         <v>46204</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -75934,7 +75934,7 @@
         <v>46069</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -76007,7 +76007,7 @@
         <v>46213</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -76080,7 +76080,7 @@
         <v>46168</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -76153,7 +76153,7 @@
         <v>46177</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -76226,7 +76226,7 @@
         <v>46265</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -76299,7 +76299,7 @@
         <v>46268</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -76372,7 +76372,7 @@
         <v>46269</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -76445,7 +76445,7 @@
         <v>46274</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -76518,7 +76518,7 @@
         <v>46273</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -76591,7 +76591,7 @@
         <v>46273</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -76664,7 +76664,7 @@
         <v>46276</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -76737,7 +76737,7 @@
         <v>46233</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -76810,7 +76810,7 @@
         <v>46276</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -76883,7 +76883,7 @@
         <v>46276</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -76956,7 +76956,7 @@
         <v>46276</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -77029,7 +77029,7 @@
         <v>46276</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -77102,7 +77102,7 @@
         <v>46279</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -77175,7 +77175,7 @@
         <v>46234</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -77248,7 +77248,7 @@
         <v>46237</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -77321,7 +77321,7 @@
         <v>46234</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -77394,7 +77394,7 @@
         <v>46234</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -77467,7 +77467,7 @@
         <v>46283</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -77540,7 +77540,7 @@
         <v>45953</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -77613,7 +77613,7 @@
         <v>46240</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -77686,7 +77686,7 @@
         <v>46245</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -77759,7 +77759,7 @@
         <v>46244</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -77832,7 +77832,7 @@
         <v>46280</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -77905,7 +77905,7 @@
         <v>46244</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -77978,7 +77978,7 @@
         <v>46009</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -78051,7 +78051,7 @@
         <v>46289</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -78124,7 +78124,7 @@
         <v>46290</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -78197,7 +78197,7 @@
         <v>46178</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -78270,7 +78270,7 @@
         <v>46289</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -78343,7 +78343,7 @@
         <v>46246</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -78416,7 +78416,7 @@
         <v>46178</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -78489,7 +78489,7 @@
         <v>46293</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -78562,7 +78562,7 @@
         <v>46293</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -78635,7 +78635,7 @@
         <v>46293</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -78708,7 +78708,7 @@
         <v>45925</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -78781,7 +78781,7 @@
         <v>46295</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -78854,7 +78854,7 @@
         <v>46296</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -78927,7 +78927,7 @@
         <v>46296</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -79000,7 +79000,7 @@
         <v>46252</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -79073,7 +79073,7 @@
         <v>46062</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -79146,7 +79146,7 @@
         <v>46297</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -79219,7 +79219,7 @@
         <v>46031</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -79292,7 +79292,7 @@
         <v>45936</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -79365,7 +79365,7 @@
         <v>46247</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -79443,7 +79443,7 @@
         <v>46247</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -79521,7 +79521,7 @@
         <v>46297</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -79594,7 +79594,7 @@
         <v>46248</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -79672,7 +79672,7 @@
         <v>46258</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -79745,7 +79745,7 @@
         <v>46259</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -79818,7 +79818,7 @@
         <v>46259</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -79891,7 +79891,7 @@
         <v>46301</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -79964,7 +79964,7 @@
         <v>46294</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -80037,7 +80037,7 @@
         <v>46258</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -80110,7 +80110,7 @@
         <v>46294</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -80183,7 +80183,7 @@
         <v>46301</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -80256,7 +80256,7 @@
         <v>46302</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -80329,7 +80329,7 @@
         <v>46153</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -80402,7 +80402,7 @@
         <v>46302</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
@@ -80475,7 +80475,7 @@
         <v>46303</v>
       </c>
       <c r="E1032" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
@@ -80548,7 +80548,7 @@
         <v>46003</v>
       </c>
       <c r="E1033" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
@@ -80621,7 +80621,7 @@
         <v>46185</v>
       </c>
       <c r="E1034" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
@@ -80694,7 +80694,7 @@
         <v>46303</v>
       </c>
       <c r="E1035" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
@@ -80767,7 +80767,7 @@
         <v>46178</v>
       </c>
       <c r="E1036" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
@@ -80840,7 +80840,7 @@
         <v>46196</v>
       </c>
       <c r="E1037" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
@@ -80913,7 +80913,7 @@
         <v>46304</v>
       </c>
       <c r="E1038" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1038" t="inlineStr">
         <is>
@@ -80986,7 +80986,7 @@
         <v>46302</v>
       </c>
       <c r="E1039" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1039" t="inlineStr">
         <is>
@@ -81059,7 +81059,7 @@
         <v>46303</v>
       </c>
       <c r="E1040" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1040" t="inlineStr">
         <is>
@@ -81132,7 +81132,7 @@
         <v>45884</v>
       </c>
       <c r="E1041" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1041" t="inlineStr">
         <is>
@@ -81205,7 +81205,7 @@
         <v>45636</v>
       </c>
       <c r="E1042" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1042" t="inlineStr">
         <is>
@@ -81278,7 +81278,7 @@
         <v>45580</v>
       </c>
       <c r="E1043" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1043" t="inlineStr">
         <is>
@@ -81351,7 +81351,7 @@
         <v>45447</v>
       </c>
       <c r="E1044" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1044" t="inlineStr">
         <is>
@@ -81424,7 +81424,7 @@
         <v>45170</v>
       </c>
       <c r="E1045" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1045" t="inlineStr">
         <is>
@@ -81497,7 +81497,7 @@
         <v>45106</v>
       </c>
       <c r="E1046" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1046" t="inlineStr">
         <is>
@@ -81570,7 +81570,7 @@
         <v>45467</v>
       </c>
       <c r="E1047" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1047" t="inlineStr">
         <is>
@@ -81643,7 +81643,7 @@
         <v>44509</v>
       </c>
       <c r="E1048" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1048" t="inlineStr">
         <is>
@@ -81721,7 +81721,7 @@
         <v>45664</v>
       </c>
       <c r="E1049" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1049" t="inlineStr">
         <is>
@@ -81794,7 +81794,7 @@
         <v>45208</v>
       </c>
       <c r="E1050" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1050" t="inlineStr">
         <is>
@@ -81867,7 +81867,7 @@
         <v>45406</v>
       </c>
       <c r="E1051" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1051" t="inlineStr">
         <is>
@@ -81940,7 +81940,7 @@
         <v>45497</v>
       </c>
       <c r="E1052" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1052" t="inlineStr">
         <is>
@@ -82013,7 +82013,7 @@
         <v>45497</v>
       </c>
       <c r="E1053" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1053" t="inlineStr">
         <is>
@@ -82086,7 +82086,7 @@
         <v>45106</v>
       </c>
       <c r="E1054" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1054" t="inlineStr">
         <is>
@@ -82159,7 +82159,7 @@
         <v>45646</v>
       </c>
       <c r="E1055" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1055" t="inlineStr">
         <is>
@@ -82232,7 +82232,7 @@
         <v>45646</v>
       </c>
       <c r="E1056" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1056" t="inlineStr">
         <is>
@@ -82305,7 +82305,7 @@
         <v>45580</v>
       </c>
       <c r="E1057" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1057" t="inlineStr">
         <is>
@@ -82378,7 +82378,7 @@
         <v>45646</v>
       </c>
       <c r="E1058" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1058" t="inlineStr">
         <is>
@@ -82451,7 +82451,7 @@
         <v>45646</v>
       </c>
       <c r="E1059" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1059" t="inlineStr">
         <is>
@@ -82524,7 +82524,7 @@
         <v>45408</v>
       </c>
       <c r="E1060" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1060" t="inlineStr">
         <is>
@@ -82597,7 +82597,7 @@
         <v>45414</v>
       </c>
       <c r="E1061" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1061" t="inlineStr">
         <is>
@@ -82670,7 +82670,7 @@
         <v>45173</v>
       </c>
       <c r="E1062" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1062" t="inlineStr">
         <is>
@@ -82743,7 +82743,7 @@
         <v>45646</v>
       </c>
       <c r="E1063" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1063" t="inlineStr">
         <is>
@@ -82816,7 +82816,7 @@
         <v>45715</v>
       </c>
       <c r="E1064" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1064" t="inlineStr">
         <is>
@@ -82889,7 +82889,7 @@
         <v>45720</v>
       </c>
       <c r="E1065" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1065" t="inlineStr">
         <is>
@@ -82962,7 +82962,7 @@
         <v>45800</v>
       </c>
       <c r="E1066" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1066" t="inlineStr">
         <is>
@@ -83040,7 +83040,7 @@
         <v>45831</v>
       </c>
       <c r="E1067" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1067" t="inlineStr">
         <is>
@@ -83113,7 +83113,7 @@
         <v>45785</v>
       </c>
       <c r="E1068" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1068" t="inlineStr">
         <is>
@@ -83186,7 +83186,7 @@
         <v>46073</v>
       </c>
       <c r="E1069" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1069" t="inlineStr">
         <is>
@@ -83259,7 +83259,7 @@
         <v>46163</v>
       </c>
       <c r="E1070" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1070" t="inlineStr">
         <is>
@@ -83332,7 +83332,7 @@
         <v>46274</v>
       </c>
       <c r="E1071" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1071" t="inlineStr">
         <is>
@@ -83405,7 +83405,7 @@
         <v>46296</v>
       </c>
       <c r="E1072" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1072" t="inlineStr">
         <is>

--- a/Översikt VETLANDA.xlsx
+++ b/Översikt VETLANDA.xlsx
@@ -601,7 +601,7 @@
         <v>45097</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>46178</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         <v>45371</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>44817</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>44890</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>45183</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>45558</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>45168</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>46107</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>45957</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>45520</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>45930</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>45170</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>44612</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>44840</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>44908</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>46002</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>46100</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         <v>45203</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>45819</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>46163</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>46188</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>44545</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>44564</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>45583</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>44819</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>45763</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>45814</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         <v>45477</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>46045</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>45048</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>45599</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4224,7 +4224,7 @@
         <v>46255</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>45646</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>45131</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>44515</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>44752</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4767,7 +4767,7 @@
         <v>44643</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>45589</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>45713</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5094,7 +5094,7 @@
         <v>45673</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         <v>45891</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>44572</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         <v>45965</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>46166</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>45303</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
         <v>45148</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>45357</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         <v>45616</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         <v>45035</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6158,7 +6158,7 @@
         <v>45400</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6273,7 +6273,7 @@
         <v>46279</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
         <v>45211</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         <v>46293</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         <v>45310</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         <v>46306</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>45792</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>45835</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>45840</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         <v>45713</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         <v>45860</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         <v>45106</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7448,7 +7448,7 @@
         <v>45509</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>45497</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>45201</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         <v>45539</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7872,7 +7872,7 @@
         <v>46051</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7982,7 +7982,7 @@
         <v>44490</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8087,7 +8087,7 @@
         <v>44834</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>44721</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>44747</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8402,7 +8402,7 @@
         <v>44592</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         <v>44740</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         <v>45596</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8722,7 +8722,7 @@
         <v>45597</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>44830</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8932,7 +8932,7 @@
         <v>45555</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9037,7 +9037,7 @@
         <v>45021</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>44781</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9247,7 +9247,7 @@
         <v>44748</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9352,7 +9352,7 @@
         <v>44824</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9457,7 +9457,7 @@
         <v>45240</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>44728</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9671,7 +9671,7 @@
         <v>45342</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>45586</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9881,7 +9881,7 @@
         <v>45835</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         <v>45586</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10091,7 +10091,7 @@
         <v>45672</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10200,7 +10200,7 @@
         <v>45880</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10305,7 +10305,7 @@
         <v>45239</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>45645</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10520,7 +10520,7 @@
         <v>44998</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10625,7 +10625,7 @@
         <v>44880</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>45419</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10835,7 +10835,7 @@
         <v>45085</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10940,7 +10940,7 @@
         <v>45408</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11045,7 +11045,7 @@
         <v>46071</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         <v>46188</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>44819</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         <v>45119</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11465,7 +11465,7 @@
         <v>45009</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
         <v>45261</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11675,7 +11675,7 @@
         <v>45378</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11780,7 +11780,7 @@
         <v>45775</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11885,7 +11885,7 @@
         <v>45930</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11999,7 +11999,7 @@
         <v>45104</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12108,7 +12108,7 @@
         <v>44816</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12213,7 +12213,7 @@
         <v>45532</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12318,7 +12318,7 @@
         <v>44833</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12423,7 +12423,7 @@
         <v>45337</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12528,7 +12528,7 @@
         <v>46248</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12633,7 +12633,7 @@
         <v>45565</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12738,7 +12738,7 @@
         <v>44916</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12843,7 +12843,7 @@
         <v>46297</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12948,7 +12948,7 @@
         <v>45352</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13053,7 +13053,7 @@
         <v>45643</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13158,7 +13158,7 @@
         <v>45791</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13263,7 +13263,7 @@
         <v>46069</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13368,7 +13368,7 @@
         <v>45904</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13473,7 +13473,7 @@
         <v>45736</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
         <v>45820</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13692,7 +13692,7 @@
         <v>45839</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13797,7 +13797,7 @@
         <v>45604</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13902,7 +13902,7 @@
         <v>45497</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14007,7 +14007,7 @@
         <v>45614</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14112,7 +14112,7 @@
         <v>45742</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         <v>44858</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14294,7 +14294,7 @@
         <v>44781</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14367,7 +14367,7 @@
         <v>44838</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>44732</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14513,7 +14513,7 @@
         <v>44781</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14586,7 +14586,7 @@
         <v>44515</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14659,7 +14659,7 @@
         <v>44508</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14732,7 +14732,7 @@
         <v>44504</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14805,7 +14805,7 @@
         <v>44496</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14878,7 +14878,7 @@
         <v>44579</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>44601</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15024,7 +15024,7 @@
         <v>44889</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15097,7 +15097,7 @@
         <v>44544</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15170,7 +15170,7 @@
         <v>44510</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15243,7 +15243,7 @@
         <v>44517</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15316,7 +15316,7 @@
         <v>44764</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15389,7 +15389,7 @@
         <v>44503</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>44510</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15535,7 +15535,7 @@
         <v>44819</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
         <v>44592</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15681,7 +15681,7 @@
         <v>44750</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15754,7 +15754,7 @@
         <v>44825</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         <v>44488</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15900,7 +15900,7 @@
         <v>44602</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15973,7 +15973,7 @@
         <v>44638</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16046,7 +16046,7 @@
         <v>44721</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16119,7 +16119,7 @@
         <v>44510</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16192,7 +16192,7 @@
         <v>44785</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16265,7 +16265,7 @@
         <v>44592</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16338,7 +16338,7 @@
         <v>44587</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>44782</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16484,7 +16484,7 @@
         <v>44815</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16557,7 +16557,7 @@
         <v>44504</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16630,7 +16630,7 @@
         <v>44580</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16703,7 +16703,7 @@
         <v>44691</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16776,7 +16776,7 @@
         <v>44880</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16849,7 +16849,7 @@
         <v>44545</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16922,7 +16922,7 @@
         <v>44750</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16995,7 +16995,7 @@
         <v>44624</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17068,7 +17068,7 @@
         <v>44595</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17141,7 +17141,7 @@
         <v>44608</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17214,7 +17214,7 @@
         <v>44820</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17287,7 +17287,7 @@
         <v>44816</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17360,7 +17360,7 @@
         <v>44645</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17433,7 +17433,7 @@
         <v>44819</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17506,7 +17506,7 @@
         <v>44784</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17579,7 +17579,7 @@
         <v>44656</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17652,7 +17652,7 @@
         <v>44585</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17730,7 +17730,7 @@
         <v>44585</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17808,7 +17808,7 @@
         <v>44585</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17886,7 +17886,7 @@
         <v>44834</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17959,7 +17959,7 @@
         <v>44740</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18037,7 +18037,7 @@
         <v>44750</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18110,7 +18110,7 @@
         <v>44587</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>44743</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18256,7 +18256,7 @@
         <v>44600</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18329,7 +18329,7 @@
         <v>44859</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18402,7 +18402,7 @@
         <v>44593</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>44743</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18548,7 +18548,7 @@
         <v>44778</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18621,7 +18621,7 @@
         <v>44504</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18694,7 +18694,7 @@
         <v>44834</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18767,7 +18767,7 @@
         <v>44509</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>44592</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18913,7 +18913,7 @@
         <v>44517</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18986,7 +18986,7 @@
         <v>44572</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19059,7 +19059,7 @@
         <v>44721</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19132,7 +19132,7 @@
         <v>44841</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19205,7 +19205,7 @@
         <v>44888</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19278,7 +19278,7 @@
         <v>44587</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19351,7 +19351,7 @@
         <v>44655</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19424,7 +19424,7 @@
         <v>44502</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19497,7 +19497,7 @@
         <v>44592</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19570,7 +19570,7 @@
         <v>44515</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19648,7 +19648,7 @@
         <v>44564</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19721,7 +19721,7 @@
         <v>44781</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19794,7 +19794,7 @@
         <v>44531</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19867,7 +19867,7 @@
         <v>44636</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19940,7 +19940,7 @@
         <v>44834</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20013,7 +20013,7 @@
         <v>44733</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         <v>44683</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20159,7 +20159,7 @@
         <v>44602</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20232,7 +20232,7 @@
         <v>44792</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20305,7 +20305,7 @@
         <v>44657</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20378,7 +20378,7 @@
         <v>44827</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20451,7 +20451,7 @@
         <v>44902</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20524,7 +20524,7 @@
         <v>44488</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>45561</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20670,7 +20670,7 @@
         <v>45251</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20743,7 +20743,7 @@
         <v>45351</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20816,7 +20816,7 @@
         <v>45602</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20889,7 +20889,7 @@
         <v>45575</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20962,7 +20962,7 @@
         <v>44967</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21035,7 +21035,7 @@
         <v>44967</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21108,7 +21108,7 @@
         <v>45265</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21181,7 +21181,7 @@
         <v>44792</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21254,7 +21254,7 @@
         <v>45267</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21327,7 +21327,7 @@
         <v>44592</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21400,7 +21400,7 @@
         <v>44880</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21473,7 +21473,7 @@
         <v>45569</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21551,7 +21551,7 @@
         <v>44903</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21624,7 +21624,7 @@
         <v>45674</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21697,7 +21697,7 @@
         <v>45580</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21770,7 +21770,7 @@
         <v>44998</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21843,7 +21843,7 @@
         <v>45175</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21916,7 +21916,7 @@
         <v>45278</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21989,7 +21989,7 @@
         <v>45259</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22062,7 +22062,7 @@
         <v>45663</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22135,7 +22135,7 @@
         <v>44582</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22208,7 +22208,7 @@
         <v>45205</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22281,7 +22281,7 @@
         <v>45771</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22359,7 +22359,7 @@
         <v>45771</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22437,7 +22437,7 @@
         <v>44831</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22510,7 +22510,7 @@
         <v>45057</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22583,7 +22583,7 @@
         <v>44936</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>45188</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>45307</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>45264</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22875,7 +22875,7 @@
         <v>44530</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22948,7 +22948,7 @@
         <v>45350</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23021,7 +23021,7 @@
         <v>45071</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23094,7 +23094,7 @@
         <v>45135</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23167,7 +23167,7 @@
         <v>45229</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23240,7 +23240,7 @@
         <v>45055</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23313,7 +23313,7 @@
         <v>44851</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23386,7 +23386,7 @@
         <v>44600</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23459,7 +23459,7 @@
         <v>44986</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23532,7 +23532,7 @@
         <v>45406</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23605,7 +23605,7 @@
         <v>44762</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23678,7 +23678,7 @@
         <v>45097</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23751,7 +23751,7 @@
         <v>45097</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23824,7 +23824,7 @@
         <v>45335</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23897,7 +23897,7 @@
         <v>44710</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23970,7 +23970,7 @@
         <v>45384</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24043,7 +24043,7 @@
         <v>45434</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24116,7 +24116,7 @@
         <v>45104</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24189,7 +24189,7 @@
         <v>45300</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24262,7 +24262,7 @@
         <v>45439</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24335,7 +24335,7 @@
         <v>45099</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24408,7 +24408,7 @@
         <v>45709</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24481,7 +24481,7 @@
         <v>45645</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24554,7 +24554,7 @@
         <v>45645</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24627,7 +24627,7 @@
         <v>45470</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24700,7 +24700,7 @@
         <v>45309</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24773,7 +24773,7 @@
         <v>45309</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24846,7 +24846,7 @@
         <v>45097</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24919,7 +24919,7 @@
         <v>45272</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24992,7 +24992,7 @@
         <v>45113</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25065,7 +25065,7 @@
         <v>45363</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25143,7 +25143,7 @@
         <v>44949</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25216,7 +25216,7 @@
         <v>45118</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25289,7 +25289,7 @@
         <v>45309</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25362,7 +25362,7 @@
         <v>45336</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25435,7 +25435,7 @@
         <v>44487</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25508,7 +25508,7 @@
         <v>45162</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25581,7 +25581,7 @@
         <v>45414</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25659,7 +25659,7 @@
         <v>45161</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25732,7 +25732,7 @@
         <v>45226</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25805,7 +25805,7 @@
         <v>45188</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25878,7 +25878,7 @@
         <v>45191</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25951,7 +25951,7 @@
         <v>44916</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26024,7 +26024,7 @@
         <v>44916</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26097,7 +26097,7 @@
         <v>44747</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26170,7 +26170,7 @@
         <v>45580</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26243,7 +26243,7 @@
         <v>45701</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26321,7 +26321,7 @@
         <v>44952</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26394,7 +26394,7 @@
         <v>45082</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26467,7 +26467,7 @@
         <v>45209</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26540,7 +26540,7 @@
         <v>45461</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26613,7 +26613,7 @@
         <v>45163</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26686,7 +26686,7 @@
         <v>44888</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26759,7 +26759,7 @@
         <v>45188</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26832,7 +26832,7 @@
         <v>44655</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26905,7 +26905,7 @@
         <v>45754</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26983,7 +26983,7 @@
         <v>45754</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27061,7 +27061,7 @@
         <v>45351</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27134,7 +27134,7 @@
         <v>45628</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27207,7 +27207,7 @@
         <v>44972</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27280,7 +27280,7 @@
         <v>44916</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27353,7 +27353,7 @@
         <v>45097</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27426,7 +27426,7 @@
         <v>44770</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27499,7 +27499,7 @@
         <v>45572</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27572,7 +27572,7 @@
         <v>45031</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27645,7 +27645,7 @@
         <v>44592</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27718,7 +27718,7 @@
         <v>45448</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27791,7 +27791,7 @@
         <v>45190</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27864,7 +27864,7 @@
         <v>45580</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27937,7 +27937,7 @@
         <v>45166</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28010,7 +28010,7 @@
         <v>45362</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28083,7 +28083,7 @@
         <v>45625</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28156,7 +28156,7 @@
         <v>45104</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28229,7 +28229,7 @@
         <v>44977</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28302,7 +28302,7 @@
         <v>45645</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28375,7 +28375,7 @@
         <v>45135</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28448,7 +28448,7 @@
         <v>45135</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28521,7 +28521,7 @@
         <v>45135</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28594,7 +28594,7 @@
         <v>45545</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28667,7 +28667,7 @@
         <v>45117</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28740,7 +28740,7 @@
         <v>44888</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28813,7 +28813,7 @@
         <v>44984</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28886,7 +28886,7 @@
         <v>45099</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28959,7 +28959,7 @@
         <v>45610</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29032,7 +29032,7 @@
         <v>45742</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29105,7 +29105,7 @@
         <v>44641</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>45228</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29251,7 +29251,7 @@
         <v>45330</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29324,7 +29324,7 @@
         <v>44693</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29397,7 +29397,7 @@
         <v>45202</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29470,7 +29470,7 @@
         <v>45702</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29543,7 +29543,7 @@
         <v>45441</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29616,7 +29616,7 @@
         <v>45376</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29689,7 +29689,7 @@
         <v>45274</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29762,7 +29762,7 @@
         <v>45595</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29835,7 +29835,7 @@
         <v>45363</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29913,7 +29913,7 @@
         <v>44916</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29986,7 +29986,7 @@
         <v>44531</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30059,7 +30059,7 @@
         <v>45365</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30132,7 +30132,7 @@
         <v>45414</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30210,7 +30210,7 @@
         <v>45107</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30283,7 +30283,7 @@
         <v>45251</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30356,7 +30356,7 @@
         <v>45048</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30429,7 +30429,7 @@
         <v>44515</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30507,7 +30507,7 @@
         <v>44984</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30580,7 +30580,7 @@
         <v>45232</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30653,7 +30653,7 @@
         <v>45462</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30726,7 +30726,7 @@
         <v>45319</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30799,7 +30799,7 @@
         <v>44984</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30872,7 +30872,7 @@
         <v>44984</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30945,7 +30945,7 @@
         <v>45357</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31018,7 +31018,7 @@
         <v>45006</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31091,7 +31091,7 @@
         <v>45581</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31169,7 +31169,7 @@
         <v>44945</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31242,7 +31242,7 @@
         <v>45069</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31315,7 +31315,7 @@
         <v>45484</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31388,7 +31388,7 @@
         <v>45015</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31461,7 +31461,7 @@
         <v>45310</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31534,7 +31534,7 @@
         <v>45351</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31607,7 +31607,7 @@
         <v>45170</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31680,7 +31680,7 @@
         <v>45107</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31753,7 +31753,7 @@
         <v>45684</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31831,7 +31831,7 @@
         <v>45097</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31904,7 +31904,7 @@
         <v>45330</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31977,7 +31977,7 @@
         <v>45042</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32050,7 +32050,7 @@
         <v>45099</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32123,7 +32123,7 @@
         <v>44946</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32196,7 +32196,7 @@
         <v>45352</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32269,7 +32269,7 @@
         <v>44837</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32342,7 +32342,7 @@
         <v>45329</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32415,7 +32415,7 @@
         <v>45329</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32488,7 +32488,7 @@
         <v>45882</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32561,7 +32561,7 @@
         <v>45882</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32634,7 +32634,7 @@
         <v>45883</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32707,7 +32707,7 @@
         <v>45201</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32780,7 +32780,7 @@
         <v>45884</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32853,7 +32853,7 @@
         <v>45902</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32926,7 +32926,7 @@
         <v>45351</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32999,7 +32999,7 @@
         <v>46112</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33077,7 +33077,7 @@
         <v>45965</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33150,7 +33150,7 @@
         <v>45525</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33223,7 +33223,7 @@
         <v>45785</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33296,7 +33296,7 @@
         <v>45912</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33369,7 +33369,7 @@
         <v>45840</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33442,7 +33442,7 @@
         <v>45866</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33515,7 +33515,7 @@
         <v>45748</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33593,7 +33593,7 @@
         <v>45748</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33671,7 +33671,7 @@
         <v>45925</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33744,7 +33744,7 @@
         <v>45971</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33817,7 +33817,7 @@
         <v>46006</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33890,7 +33890,7 @@
         <v>45763</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33963,7 +33963,7 @@
         <v>44965</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34036,7 +34036,7 @@
         <v>45693</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34109,7 +34109,7 @@
         <v>45889</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34182,7 +34182,7 @@
         <v>45888</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34255,7 +34255,7 @@
         <v>45888</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34328,7 +34328,7 @@
         <v>45541</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34401,7 +34401,7 @@
         <v>45677</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34474,7 +34474,7 @@
         <v>45889</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34547,7 +34547,7 @@
         <v>45786</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34620,7 +34620,7 @@
         <v>45888</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34693,7 +34693,7 @@
         <v>45742</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34766,7 +34766,7 @@
         <v>44970</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34839,7 +34839,7 @@
         <v>45889</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34912,7 +34912,7 @@
         <v>45888</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34985,7 +34985,7 @@
         <v>45785</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35058,7 +35058,7 @@
         <v>45888</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35131,7 +35131,7 @@
         <v>45888</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35204,7 +35204,7 @@
         <v>45826</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35277,7 +35277,7 @@
         <v>45133</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35350,7 +35350,7 @@
         <v>45889</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35423,7 +35423,7 @@
         <v>45742</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35496,7 +35496,7 @@
         <v>45770</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35569,7 +35569,7 @@
         <v>45357</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35642,7 +35642,7 @@
         <v>45841</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35715,7 +35715,7 @@
         <v>45231</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35788,7 +35788,7 @@
         <v>45839</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35861,7 +35861,7 @@
         <v>45623</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35934,7 +35934,7 @@
         <v>45608</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36007,7 +36007,7 @@
         <v>44545</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36080,7 +36080,7 @@
         <v>45681</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36153,7 +36153,7 @@
         <v>45152</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36226,7 +36226,7 @@
         <v>44503</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36299,7 +36299,7 @@
         <v>45873</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36372,7 +36372,7 @@
         <v>45971</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36445,7 +36445,7 @@
         <v>45230</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36523,7 +36523,7 @@
         <v>45610</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36596,7 +36596,7 @@
         <v>46122</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36669,7 +36669,7 @@
         <v>45153</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36742,7 +36742,7 @@
         <v>45755</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36815,7 +36815,7 @@
         <v>45670</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36888,7 +36888,7 @@
         <v>44741</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36961,7 +36961,7 @@
         <v>45825</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37034,7 +37034,7 @@
         <v>45272</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37107,7 +37107,7 @@
         <v>45084</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37180,7 +37180,7 @@
         <v>45341</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37253,7 +37253,7 @@
         <v>45348</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37326,7 +37326,7 @@
         <v>45839</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37399,7 +37399,7 @@
         <v>44538</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37472,7 +37472,7 @@
         <v>44785</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37545,7 +37545,7 @@
         <v>46052</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37618,7 +37618,7 @@
         <v>45883</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37691,7 +37691,7 @@
         <v>45839</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37764,7 +37764,7 @@
         <v>45691</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37842,7 +37842,7 @@
         <v>44600</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37915,7 +37915,7 @@
         <v>45331</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37988,7 +37988,7 @@
         <v>45331</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38061,7 +38061,7 @@
         <v>45898</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38134,7 +38134,7 @@
         <v>45222</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38207,7 +38207,7 @@
         <v>45819</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38280,7 +38280,7 @@
         <v>44970</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38353,7 +38353,7 @@
         <v>45671</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38426,7 +38426,7 @@
         <v>45737</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38499,7 +38499,7 @@
         <v>45435</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38572,7 +38572,7 @@
         <v>45587</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38645,7 +38645,7 @@
         <v>45230</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38723,7 +38723,7 @@
         <v>45827</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38796,7 +38796,7 @@
         <v>45902</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38869,7 +38869,7 @@
         <v>45204</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38942,7 +38942,7 @@
         <v>45455</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39015,7 +39015,7 @@
         <v>45561</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39088,7 +39088,7 @@
         <v>45282</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39161,7 +39161,7 @@
         <v>45245</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39234,7 +39234,7 @@
         <v>45631</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39307,7 +39307,7 @@
         <v>45247</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39380,7 +39380,7 @@
         <v>45259</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39453,7 +39453,7 @@
         <v>45911</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39526,7 +39526,7 @@
         <v>45589</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39599,7 +39599,7 @@
         <v>45911</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39672,7 +39672,7 @@
         <v>45370</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39745,7 +39745,7 @@
         <v>45322</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39818,7 +39818,7 @@
         <v>45035</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39891,7 +39891,7 @@
         <v>45645</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39969,7 +39969,7 @@
         <v>45076</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40042,7 +40042,7 @@
         <v>45006</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40115,7 +40115,7 @@
         <v>44580</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40188,7 +40188,7 @@
         <v>45089</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40261,7 +40261,7 @@
         <v>45615</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40334,7 +40334,7 @@
         <v>45922</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40407,7 +40407,7 @@
         <v>45538</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40480,7 +40480,7 @@
         <v>45298</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40553,7 +40553,7 @@
         <v>45925</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40626,7 +40626,7 @@
         <v>45372</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40699,7 +40699,7 @@
         <v>45076</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40772,7 +40772,7 @@
         <v>45170</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40845,7 +40845,7 @@
         <v>45401</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40918,7 +40918,7 @@
         <v>44607</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40991,7 +40991,7 @@
         <v>44837</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41064,7 +41064,7 @@
         <v>46153</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41137,7 +41137,7 @@
         <v>46153</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41210,7 +41210,7 @@
         <v>45936</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41283,7 +41283,7 @@
         <v>44511</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41356,7 +41356,7 @@
         <v>45089</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41429,7 +41429,7 @@
         <v>46153</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41502,7 +41502,7 @@
         <v>45443</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41575,7 +41575,7 @@
         <v>45240</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41648,7 +41648,7 @@
         <v>45168</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41721,7 +41721,7 @@
         <v>45321</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41794,7 +41794,7 @@
         <v>45163</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41867,7 +41867,7 @@
         <v>44510</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41940,7 +41940,7 @@
         <v>45944</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42013,7 +42013,7 @@
         <v>45211</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42086,7 +42086,7 @@
         <v>46154</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42164,7 +42164,7 @@
         <v>45414</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42237,7 +42237,7 @@
         <v>44894</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42310,7 +42310,7 @@
         <v>45519</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42383,7 +42383,7 @@
         <v>45946</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42456,7 +42456,7 @@
         <v>45314</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42529,7 +42529,7 @@
         <v>45433</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42602,7 +42602,7 @@
         <v>45097</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42675,7 +42675,7 @@
         <v>45448</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42748,7 +42748,7 @@
         <v>45866</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42821,7 +42821,7 @@
         <v>45639</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42894,7 +42894,7 @@
         <v>45950</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42967,7 +42967,7 @@
         <v>45953</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43040,7 +43040,7 @@
         <v>45644</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43113,7 +43113,7 @@
         <v>45649</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43191,7 +43191,7 @@
         <v>46126</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43264,7 +43264,7 @@
         <v>45114</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43337,7 +43337,7 @@
         <v>44858</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43410,7 +43410,7 @@
         <v>45545</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43483,7 +43483,7 @@
         <v>45250</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43556,7 +43556,7 @@
         <v>45224</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43634,7 +43634,7 @@
         <v>45400</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43712,7 +43712,7 @@
         <v>46160</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43785,7 +43785,7 @@
         <v>46161</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43858,7 +43858,7 @@
         <v>46160</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43931,7 +43931,7 @@
         <v>45761</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44004,7 +44004,7 @@
         <v>45763</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44077,7 +44077,7 @@
         <v>46160</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44150,7 +44150,7 @@
         <v>45672</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44223,7 +44223,7 @@
         <v>46064</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44296,7 +44296,7 @@
         <v>45930</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44369,7 +44369,7 @@
         <v>45264</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44442,7 +44442,7 @@
         <v>45525</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44515,7 +44515,7 @@
         <v>44965</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44588,7 +44588,7 @@
         <v>46160</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44661,7 +44661,7 @@
         <v>44926</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44734,7 +44734,7 @@
         <v>44926</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44807,7 +44807,7 @@
         <v>45401</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44880,7 +44880,7 @@
         <v>45392</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44953,7 +44953,7 @@
         <v>46163</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45026,7 +45026,7 @@
         <v>45394</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45099,7 +45099,7 @@
         <v>45974</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45172,7 +45172,7 @@
         <v>45975</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45245,7 +45245,7 @@
         <v>44602</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45318,7 +45318,7 @@
         <v>46161</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45391,7 +45391,7 @@
         <v>45007</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45464,7 +45464,7 @@
         <v>45568</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45542,7 +45542,7 @@
         <v>45297</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45615,7 +45615,7 @@
         <v>45236</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45688,7 +45688,7 @@
         <v>45625</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45761,7 +45761,7 @@
         <v>45105</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45834,7 +45834,7 @@
         <v>45981</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45912,7 +45912,7 @@
         <v>44859</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45985,7 +45985,7 @@
         <v>45981</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46058,7 +46058,7 @@
         <v>45981</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46131,7 +46131,7 @@
         <v>45674</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46204,7 +46204,7 @@
         <v>45982</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46277,7 +46277,7 @@
         <v>45981</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46350,7 +46350,7 @@
         <v>45930</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46428,7 +46428,7 @@
         <v>44655</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46501,7 +46501,7 @@
         <v>44970</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46574,7 +46574,7 @@
         <v>45329</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46647,7 +46647,7 @@
         <v>44847</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46720,7 +46720,7 @@
         <v>45992</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46793,7 +46793,7 @@
         <v>45180</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46866,7 +46866,7 @@
         <v>45173</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46939,7 +46939,7 @@
         <v>45173</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47012,7 +47012,7 @@
         <v>45345</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47085,7 +47085,7 @@
         <v>45526</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47158,7 +47158,7 @@
         <v>45170</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47231,7 +47231,7 @@
         <v>45170</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47304,7 +47304,7 @@
         <v>45999</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47377,7 +47377,7 @@
         <v>45999</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47450,7 +47450,7 @@
         <v>45303</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47523,7 +47523,7 @@
         <v>45104</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47596,7 +47596,7 @@
         <v>46001</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47669,7 +47669,7 @@
         <v>45113</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47742,7 +47742,7 @@
         <v>45446</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47815,7 +47815,7 @@
         <v>46003</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47888,7 +47888,7 @@
         <v>45438</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47961,7 +47961,7 @@
         <v>46009</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48034,7 +48034,7 @@
         <v>46007</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48107,7 +48107,7 @@
         <v>46007</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48180,7 +48180,7 @@
         <v>46009</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48253,7 +48253,7 @@
         <v>45182</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48331,7 +48331,7 @@
         <v>45182</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48404,7 +48404,7 @@
         <v>45999</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48477,7 +48477,7 @@
         <v>44607</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48550,7 +48550,7 @@
         <v>46010</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48623,7 +48623,7 @@
         <v>45669</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48696,7 +48696,7 @@
         <v>46010</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48769,7 +48769,7 @@
         <v>45315</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48842,7 +48842,7 @@
         <v>45462</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48915,7 +48915,7 @@
         <v>45449</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48988,7 +48988,7 @@
         <v>45827</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49061,7 +49061,7 @@
         <v>45327</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49134,7 +49134,7 @@
         <v>45164</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49207,7 +49207,7 @@
         <v>45330</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49280,7 +49280,7 @@
         <v>44995</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49353,7 +49353,7 @@
         <v>45692</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49426,7 +49426,7 @@
         <v>45106</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49499,7 +49499,7 @@
         <v>45574</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49577,7 +49577,7 @@
         <v>46029</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49650,7 +49650,7 @@
         <v>45616</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49723,7 +49723,7 @@
         <v>45510</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49796,7 +49796,7 @@
         <v>46030</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49869,7 +49869,7 @@
         <v>46030</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49942,7 +49942,7 @@
         <v>45219</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50020,7 +50020,7 @@
         <v>45274</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50093,7 +50093,7 @@
         <v>46031</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50166,7 +50166,7 @@
         <v>46175</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50239,7 +50239,7 @@
         <v>45250</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50312,7 +50312,7 @@
         <v>44587</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50385,7 +50385,7 @@
         <v>44783</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50458,7 +50458,7 @@
         <v>46178</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50531,7 +50531,7 @@
         <v>44830</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50604,7 +50604,7 @@
         <v>45544</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50677,7 +50677,7 @@
         <v>45133</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50750,7 +50750,7 @@
         <v>45408</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50823,7 +50823,7 @@
         <v>46178</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50896,7 +50896,7 @@
         <v>44834</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50969,7 +50969,7 @@
         <v>45366</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51042,7 +51042,7 @@
         <v>44815</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51115,7 +51115,7 @@
         <v>45069</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51188,7 +51188,7 @@
         <v>45440</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51261,7 +51261,7 @@
         <v>45701</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51339,7 +51339,7 @@
         <v>45302</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51412,7 +51412,7 @@
         <v>46182</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51485,7 +51485,7 @@
         <v>45615</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51558,7 +51558,7 @@
         <v>45113</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51631,7 +51631,7 @@
         <v>46044</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51704,7 +51704,7 @@
         <v>46045</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51777,7 +51777,7 @@
         <v>46182</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51850,7 +51850,7 @@
         <v>46048</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51923,7 +51923,7 @@
         <v>46048</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51996,7 +51996,7 @@
         <v>46048</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52069,7 +52069,7 @@
         <v>44683</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52142,7 +52142,7 @@
         <v>46049</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52215,7 +52215,7 @@
         <v>45546</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52288,7 +52288,7 @@
         <v>44839</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52361,7 +52361,7 @@
         <v>44970</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52434,7 +52434,7 @@
         <v>46182</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52507,7 +52507,7 @@
         <v>45222</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52580,7 +52580,7 @@
         <v>45183</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52653,7 +52653,7 @@
         <v>44965</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52726,7 +52726,7 @@
         <v>46055</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52799,7 +52799,7 @@
         <v>45000</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52872,7 +52872,7 @@
         <v>45133</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52945,7 +52945,7 @@
         <v>45183</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53018,7 +53018,7 @@
         <v>46184</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53091,7 +53091,7 @@
         <v>45706</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53164,7 +53164,7 @@
         <v>44839</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53237,7 +53237,7 @@
         <v>46184</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53310,7 +53310,7 @@
         <v>46062</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53383,7 +53383,7 @@
         <v>46063</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53456,7 +53456,7 @@
         <v>44753</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53529,7 +53529,7 @@
         <v>46063</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53602,7 +53602,7 @@
         <v>46063</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53675,7 +53675,7 @@
         <v>46063</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53748,7 +53748,7 @@
         <v>46184</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53821,7 +53821,7 @@
         <v>46185</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53894,7 +53894,7 @@
         <v>46188</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53967,7 +53967,7 @@
         <v>44802</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54045,7 +54045,7 @@
         <v>45446</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54118,7 +54118,7 @@
         <v>46077</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54191,7 +54191,7 @@
         <v>44929</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54264,7 +54264,7 @@
         <v>44743</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54337,7 +54337,7 @@
         <v>46077</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54410,7 +54410,7 @@
         <v>45170</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54483,7 +54483,7 @@
         <v>45497</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54556,7 +54556,7 @@
         <v>45497</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54629,7 +54629,7 @@
         <v>45119</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54702,7 +54702,7 @@
         <v>45401</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54775,7 +54775,7 @@
         <v>46084</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54848,7 +54848,7 @@
         <v>46084</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54921,7 +54921,7 @@
         <v>44952</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54994,7 +54994,7 @@
         <v>45112</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55067,7 +55067,7 @@
         <v>46084</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55140,7 +55140,7 @@
         <v>45107</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55213,7 +55213,7 @@
         <v>44747</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55286,7 +55286,7 @@
         <v>45526</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55359,7 +55359,7 @@
         <v>44600</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55432,7 +55432,7 @@
         <v>46190</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55505,7 +55505,7 @@
         <v>46087</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55578,7 +55578,7 @@
         <v>46091</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55651,7 +55651,7 @@
         <v>45569</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55724,7 +55724,7 @@
         <v>46092</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55797,7 +55797,7 @@
         <v>44930</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55870,7 +55870,7 @@
         <v>45925</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55943,7 +55943,7 @@
         <v>45033</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56016,7 +56016,7 @@
         <v>46002</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56089,7 +56089,7 @@
         <v>46097</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56162,7 +56162,7 @@
         <v>45572</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56235,7 +56235,7 @@
         <v>46098</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56308,7 +56308,7 @@
         <v>45341</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56381,7 +56381,7 @@
         <v>45348</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56454,7 +56454,7 @@
         <v>46099</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56527,7 +56527,7 @@
         <v>46100</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56600,7 +56600,7 @@
         <v>46195</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56673,7 +56673,7 @@
         <v>46104</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56746,7 +56746,7 @@
         <v>46104</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56819,7 +56819,7 @@
         <v>46196</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56892,7 +56892,7 @@
         <v>44740</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56970,7 +56970,7 @@
         <v>45406</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57043,7 +57043,7 @@
         <v>44998</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57116,7 +57116,7 @@
         <v>45302</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57189,7 +57189,7 @@
         <v>44869</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57262,7 +57262,7 @@
         <v>45174</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57335,7 +57335,7 @@
         <v>46107</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57408,7 +57408,7 @@
         <v>46107</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57481,7 +57481,7 @@
         <v>46107</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57554,7 +57554,7 @@
         <v>46111</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57627,7 +57627,7 @@
         <v>46111</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57700,7 +57700,7 @@
         <v>45363</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57778,7 +57778,7 @@
         <v>45363</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57856,7 +57856,7 @@
         <v>45363</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57934,7 +57934,7 @@
         <v>45364</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58007,7 +58007,7 @@
         <v>45104</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58080,7 +58080,7 @@
         <v>45281</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58153,7 +58153,7 @@
         <v>45525</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58226,7 +58226,7 @@
         <v>46197</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58299,7 +58299,7 @@
         <v>45006</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58372,7 +58372,7 @@
         <v>45202</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58445,7 +58445,7 @@
         <v>45563</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58523,7 +58523,7 @@
         <v>45357</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58596,7 +58596,7 @@
         <v>46202</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58669,7 +58669,7 @@
         <v>45173</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58742,7 +58742,7 @@
         <v>46121</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58815,7 +58815,7 @@
         <v>46122</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58888,7 +58888,7 @@
         <v>46121</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58961,7 +58961,7 @@
         <v>45629</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59034,7 +59034,7 @@
         <v>46126</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59107,7 +59107,7 @@
         <v>46128</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59180,7 +59180,7 @@
         <v>46128</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59253,7 +59253,7 @@
         <v>46128</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59326,7 +59326,7 @@
         <v>46128</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59399,7 +59399,7 @@
         <v>45314</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59472,7 +59472,7 @@
         <v>46127</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59545,7 +59545,7 @@
         <v>46128</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59618,7 +59618,7 @@
         <v>45420</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59691,7 +59691,7 @@
         <v>45195</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59764,7 +59764,7 @@
         <v>46133</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59837,7 +59837,7 @@
         <v>46133</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59910,7 +59910,7 @@
         <v>45238</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59988,7 +59988,7 @@
         <v>46204</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60061,7 +60061,7 @@
         <v>44880</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60134,7 +60134,7 @@
         <v>44880</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60207,7 +60207,7 @@
         <v>45079</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60280,7 +60280,7 @@
         <v>45091</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60353,7 +60353,7 @@
         <v>44602</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60426,7 +60426,7 @@
         <v>45163</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60499,7 +60499,7 @@
         <v>45903</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60572,7 +60572,7 @@
         <v>44523</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60645,7 +60645,7 @@
         <v>45839</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60718,7 +60718,7 @@
         <v>45699</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60791,7 +60791,7 @@
         <v>45827</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60864,7 +60864,7 @@
         <v>44677</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60937,7 +60937,7 @@
         <v>46037</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61010,7 +61010,7 @@
         <v>45944</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61083,7 +61083,7 @@
         <v>45112</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61156,7 +61156,7 @@
         <v>45303</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61229,7 +61229,7 @@
         <v>44592</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61302,7 +61302,7 @@
         <v>45891</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61375,7 +61375,7 @@
         <v>45313</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61448,7 +61448,7 @@
         <v>45799</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61521,7 +61521,7 @@
         <v>45306</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61594,7 +61594,7 @@
         <v>45475</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61667,7 +61667,7 @@
         <v>45211</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61740,7 +61740,7 @@
         <v>45931</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61813,7 +61813,7 @@
         <v>44510</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61886,7 +61886,7 @@
         <v>45352</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61959,7 +61959,7 @@
         <v>45538</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62032,7 +62032,7 @@
         <v>45329</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62110,7 +62110,7 @@
         <v>45895</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62183,7 +62183,7 @@
         <v>45314</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62256,7 +62256,7 @@
         <v>44815</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62329,7 +62329,7 @@
         <v>44497</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62402,7 +62402,7 @@
         <v>45091</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62475,7 +62475,7 @@
         <v>45022</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62548,7 +62548,7 @@
         <v>45526</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62621,7 +62621,7 @@
         <v>45114</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62694,7 +62694,7 @@
         <v>45440</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62767,7 +62767,7 @@
         <v>44587</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62840,7 +62840,7 @@
         <v>44715</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62913,7 +62913,7 @@
         <v>44813</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62986,7 +62986,7 @@
         <v>45365</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63059,7 +63059,7 @@
         <v>45385</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63132,7 +63132,7 @@
         <v>46069</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63205,7 +63205,7 @@
         <v>44946</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63278,7 +63278,7 @@
         <v>46213</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63351,7 +63351,7 @@
         <v>46168</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63424,7 +63424,7 @@
         <v>46177</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63497,7 +63497,7 @@
         <v>44805</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63570,7 +63570,7 @@
         <v>44813</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63643,7 +63643,7 @@
         <v>45398</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63716,7 +63716,7 @@
         <v>45307</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63789,7 +63789,7 @@
         <v>44825</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63862,7 +63862,7 @@
         <v>44917</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63935,7 +63935,7 @@
         <v>45177</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64013,7 +64013,7 @@
         <v>45174</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64091,7 +64091,7 @@
         <v>45329</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64164,7 +64164,7 @@
         <v>45245</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64237,7 +64237,7 @@
         <v>45737</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64310,7 +64310,7 @@
         <v>46273</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64383,7 +64383,7 @@
         <v>45719</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64456,7 +64456,7 @@
         <v>45364</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64529,7 +64529,7 @@
         <v>46274</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64602,7 +64602,7 @@
         <v>46273</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64675,7 +64675,7 @@
         <v>45089</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64748,7 +64748,7 @@
         <v>45660</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64821,7 +64821,7 @@
         <v>45107</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64894,7 +64894,7 @@
         <v>45184</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64967,7 +64967,7 @@
         <v>45589</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65040,7 +65040,7 @@
         <v>45589</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65113,7 +65113,7 @@
         <v>45532</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65186,7 +65186,7 @@
         <v>45370</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65259,7 +65259,7 @@
         <v>45406</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65332,7 +65332,7 @@
         <v>46234</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65405,7 +65405,7 @@
         <v>46276</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65478,7 +65478,7 @@
         <v>46276</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65551,7 +65551,7 @@
         <v>46234</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65624,7 +65624,7 @@
         <v>44595</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65697,7 +65697,7 @@
         <v>46279</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65770,7 +65770,7 @@
         <v>46276</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65843,7 +65843,7 @@
         <v>46276</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65916,7 +65916,7 @@
         <v>46276</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65989,7 +65989,7 @@
         <v>46233</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66062,7 +66062,7 @@
         <v>45104</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66135,7 +66135,7 @@
         <v>45071</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66208,7 +66208,7 @@
         <v>46234</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66281,7 +66281,7 @@
         <v>45216</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66354,7 +66354,7 @@
         <v>46237</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66427,7 +66427,7 @@
         <v>45303</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66500,7 +66500,7 @@
         <v>45678</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66573,7 +66573,7 @@
         <v>45182</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66646,7 +66646,7 @@
         <v>44495</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66719,7 +66719,7 @@
         <v>45219</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66792,7 +66792,7 @@
         <v>45030</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66865,7 +66865,7 @@
         <v>45544</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66938,7 +66938,7 @@
         <v>45691</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67011,7 +67011,7 @@
         <v>46240</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67084,7 +67084,7 @@
         <v>44488</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67157,7 +67157,7 @@
         <v>45631</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67230,7 +67230,7 @@
         <v>45216</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67308,7 +67308,7 @@
         <v>46283</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67381,7 +67381,7 @@
         <v>45359</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67454,7 +67454,7 @@
         <v>46244</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67527,7 +67527,7 @@
         <v>45376</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67600,7 +67600,7 @@
         <v>44810</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67673,7 +67673,7 @@
         <v>45209</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -67746,7 +67746,7 @@
         <v>45183</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -67819,7 +67819,7 @@
         <v>45595</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67892,7 +67892,7 @@
         <v>45953</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -67965,7 +67965,7 @@
         <v>45575</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -68038,7 +68038,7 @@
         <v>46245</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -68111,7 +68111,7 @@
         <v>46244</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -68184,7 +68184,7 @@
         <v>45062</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -68257,7 +68257,7 @@
         <v>45231</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -68330,7 +68330,7 @@
         <v>45699</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68403,7 +68403,7 @@
         <v>45737</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68476,7 +68476,7 @@
         <v>44930</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68549,7 +68549,7 @@
         <v>44971</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -68622,7 +68622,7 @@
         <v>45602</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -68695,7 +68695,7 @@
         <v>45092</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -68768,7 +68768,7 @@
         <v>45674</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68841,7 +68841,7 @@
         <v>46289</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -68914,7 +68914,7 @@
         <v>45478</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -68987,7 +68987,7 @@
         <v>45769</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -69065,7 +69065,7 @@
         <v>45164</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -69138,7 +69138,7 @@
         <v>46289</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -69211,7 +69211,7 @@
         <v>46246</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -69284,7 +69284,7 @@
         <v>45309</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -69357,7 +69357,7 @@
         <v>45309</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -69430,7 +69430,7 @@
         <v>45182</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69508,7 +69508,7 @@
         <v>46280</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -69581,7 +69581,7 @@
         <v>46293</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -69654,7 +69654,7 @@
         <v>46178</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -69727,7 +69727,7 @@
         <v>46178</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -69800,7 +69800,7 @@
         <v>45329</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -69873,7 +69873,7 @@
         <v>45222</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -69946,7 +69946,7 @@
         <v>45492</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -70019,7 +70019,7 @@
         <v>45323</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -70092,7 +70092,7 @@
         <v>46293</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -70165,7 +70165,7 @@
         <v>46293</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -70238,7 +70238,7 @@
         <v>45763</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -70311,7 +70311,7 @@
         <v>45384</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -70384,7 +70384,7 @@
         <v>45296</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -70457,7 +70457,7 @@
         <v>46290</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70530,7 +70530,7 @@
         <v>45763</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -70603,7 +70603,7 @@
         <v>45763</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -70676,7 +70676,7 @@
         <v>45763</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -70749,7 +70749,7 @@
         <v>45925</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -70822,7 +70822,7 @@
         <v>44946</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -70895,7 +70895,7 @@
         <v>45462</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -70968,7 +70968,7 @@
         <v>44879</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -71041,7 +71041,7 @@
         <v>45719</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -71114,7 +71114,7 @@
         <v>45540</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -71187,7 +71187,7 @@
         <v>45134</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -71260,7 +71260,7 @@
         <v>45316</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -71333,7 +71333,7 @@
         <v>46009</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -71406,7 +71406,7 @@
         <v>45414</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -71479,7 +71479,7 @@
         <v>45607</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -71552,7 +71552,7 @@
         <v>44818</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -71625,7 +71625,7 @@
         <v>45673</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -71698,7 +71698,7 @@
         <v>46252</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -71771,7 +71771,7 @@
         <v>44831</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -71844,7 +71844,7 @@
         <v>45001</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -71922,7 +71922,7 @@
         <v>45254</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -72000,7 +72000,7 @@
         <v>45090</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -72073,7 +72073,7 @@
         <v>45132</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -72146,7 +72146,7 @@
         <v>45335</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -72219,7 +72219,7 @@
         <v>45602</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -72292,7 +72292,7 @@
         <v>44963</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -72365,7 +72365,7 @@
         <v>45168</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -72438,7 +72438,7 @@
         <v>45400</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -72511,7 +72511,7 @@
         <v>45188</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -72584,7 +72584,7 @@
         <v>44902</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -72657,7 +72657,7 @@
         <v>44564</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -72735,7 +72735,7 @@
         <v>45189</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -72813,7 +72813,7 @@
         <v>45691</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -72886,7 +72886,7 @@
         <v>46248</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -72964,7 +72964,7 @@
         <v>44916</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -73037,7 +73037,7 @@
         <v>46296</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -73110,7 +73110,7 @@
         <v>44957</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -73183,7 +73183,7 @@
         <v>46247</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -73261,7 +73261,7 @@
         <v>46247</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -73339,7 +73339,7 @@
         <v>46297</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -73412,7 +73412,7 @@
         <v>46296</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -73485,7 +73485,7 @@
         <v>46297</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -73558,7 +73558,7 @@
         <v>45936</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -73631,7 +73631,7 @@
         <v>46062</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -73704,7 +73704,7 @@
         <v>46295</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -73777,7 +73777,7 @@
         <v>46031</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -73850,7 +73850,7 @@
         <v>44502</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -73923,7 +73923,7 @@
         <v>46258</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -73996,7 +73996,7 @@
         <v>45702</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -74074,7 +74074,7 @@
         <v>45134</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -74147,7 +74147,7 @@
         <v>45348</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -74220,7 +74220,7 @@
         <v>45439</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -74293,7 +74293,7 @@
         <v>44781</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -74366,7 +74366,7 @@
         <v>46258</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -74439,7 +74439,7 @@
         <v>45783</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -74512,7 +74512,7 @@
         <v>45783</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -74585,7 +74585,7 @@
         <v>46301</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -74658,7 +74658,7 @@
         <v>46301</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -74731,7 +74731,7 @@
         <v>46259</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -74804,7 +74804,7 @@
         <v>45439</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -74877,7 +74877,7 @@
         <v>46153</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -74950,7 +74950,7 @@
         <v>46185</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -75023,7 +75023,7 @@
         <v>46294</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -75096,7 +75096,7 @@
         <v>46196</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -75169,7 +75169,7 @@
         <v>44592</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -75242,7 +75242,7 @@
         <v>46303</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -75315,7 +75315,7 @@
         <v>45884</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -75388,7 +75388,7 @@
         <v>46303</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -75461,7 +75461,7 @@
         <v>45786</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -75534,7 +75534,7 @@
         <v>46178</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -75607,7 +75607,7 @@
         <v>45601</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -75680,7 +75680,7 @@
         <v>45456</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -75753,7 +75753,7 @@
         <v>45716</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -75826,7 +75826,7 @@
         <v>46302</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -75899,7 +75899,7 @@
         <v>46302</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -75972,7 +75972,7 @@
         <v>46003</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -76045,7 +76045,7 @@
         <v>46259</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -76118,7 +76118,7 @@
         <v>46303</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -76191,7 +76191,7 @@
         <v>46294</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -76264,7 +76264,7 @@
         <v>45792</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -76337,7 +76337,7 @@
         <v>46302</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -76410,7 +76410,7 @@
         <v>46306</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -76483,7 +76483,7 @@
         <v>45741</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -76561,7 +76561,7 @@
         <v>45741</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -76639,7 +76639,7 @@
         <v>45728</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -76712,7 +76712,7 @@
         <v>45259</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -76785,7 +76785,7 @@
         <v>45610</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -76858,7 +76858,7 @@
         <v>45743</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -76931,7 +76931,7 @@
         <v>45737</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -77004,7 +77004,7 @@
         <v>45737</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -77077,7 +77077,7 @@
         <v>46304</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -77150,7 +77150,7 @@
         <v>45742</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -77223,7 +77223,7 @@
         <v>45733</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -77296,7 +77296,7 @@
         <v>45733</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -77369,7 +77369,7 @@
         <v>45803</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -77442,7 +77442,7 @@
         <v>45743</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -77515,7 +77515,7 @@
         <v>45442</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -77588,7 +77588,7 @@
         <v>45708</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -77661,7 +77661,7 @@
         <v>46308</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -77734,7 +77734,7 @@
         <v>45616</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -77807,7 +77807,7 @@
         <v>46265</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -77880,7 +77880,7 @@
         <v>45359</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -77953,7 +77953,7 @@
         <v>45805</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -78026,7 +78026,7 @@
         <v>45434</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -78099,7 +78099,7 @@
         <v>45811</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -78172,7 +78172,7 @@
         <v>46308</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -78245,7 +78245,7 @@
         <v>45615</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -78318,7 +78318,7 @@
         <v>45505</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -78391,7 +78391,7 @@
         <v>46268</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -78464,7 +78464,7 @@
         <v>45812</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -78537,7 +78537,7 @@
         <v>45816</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -78610,7 +78610,7 @@
         <v>46269</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -78683,7 +78683,7 @@
         <v>45819</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -78756,7 +78756,7 @@
         <v>45819</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -78829,7 +78829,7 @@
         <v>45819</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -78902,7 +78902,7 @@
         <v>45819</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -78975,7 +78975,7 @@
         <v>45737</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -79048,7 +79048,7 @@
         <v>45838</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -79121,7 +79121,7 @@
         <v>45839</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -79194,7 +79194,7 @@
         <v>45840</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -79267,7 +79267,7 @@
         <v>45840</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -79340,7 +79340,7 @@
         <v>45845</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -79413,7 +79413,7 @@
         <v>45729</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -79486,7 +79486,7 @@
         <v>45748</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -79559,7 +79559,7 @@
         <v>45747</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -79632,7 +79632,7 @@
         <v>45625</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -79705,7 +79705,7 @@
         <v>45715</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -79778,7 +79778,7 @@
         <v>45715</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -79851,7 +79851,7 @@
         <v>44834</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -79924,7 +79924,7 @@
         <v>45847</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -79997,7 +79997,7 @@
         <v>45763</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -80070,7 +80070,7 @@
         <v>45852</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -80143,7 +80143,7 @@
         <v>45672</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -80216,7 +80216,7 @@
         <v>45163</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -80289,7 +80289,7 @@
         <v>44549</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -80362,7 +80362,7 @@
         <v>45322</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -80435,7 +80435,7 @@
         <v>45005</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
@@ -80508,7 +80508,7 @@
         <v>44564</v>
       </c>
       <c r="E1032" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
@@ -80581,7 +80581,7 @@
         <v>45866</v>
       </c>
       <c r="E1033" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
@@ -80654,7 +80654,7 @@
         <v>45288</v>
       </c>
       <c r="E1034" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
@@ -80727,7 +80727,7 @@
         <v>45733</v>
       </c>
       <c r="E1035" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
@@ -80800,7 +80800,7 @@
         <v>45113</v>
       </c>
       <c r="E1036" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
@@ -80873,7 +80873,7 @@
         <v>45875</v>
       </c>
       <c r="E1037" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
@@ -80946,7 +80946,7 @@
         <v>45875</v>
       </c>
       <c r="E1038" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1038" t="inlineStr">
         <is>
@@ -81019,7 +81019,7 @@
         <v>45875</v>
       </c>
       <c r="E1039" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1039" t="inlineStr">
         <is>
@@ -81092,7 +81092,7 @@
         <v>45636</v>
       </c>
       <c r="E1040" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1040" t="inlineStr">
         <is>
@@ -81165,7 +81165,7 @@
         <v>45580</v>
       </c>
       <c r="E1041" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1041" t="inlineStr">
         <is>
@@ -81238,7 +81238,7 @@
         <v>45447</v>
       </c>
       <c r="E1042" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1042" t="inlineStr">
         <is>
@@ -81311,7 +81311,7 @@
         <v>45170</v>
       </c>
       <c r="E1043" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1043" t="inlineStr">
         <is>
@@ -81384,7 +81384,7 @@
         <v>45106</v>
       </c>
       <c r="E1044" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1044" t="inlineStr">
         <is>
@@ -81457,7 +81457,7 @@
         <v>45467</v>
       </c>
       <c r="E1045" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1045" t="inlineStr">
         <is>
@@ -81530,7 +81530,7 @@
         <v>44509</v>
       </c>
       <c r="E1046" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1046" t="inlineStr">
         <is>
@@ -81608,7 +81608,7 @@
         <v>45664</v>
       </c>
       <c r="E1047" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1047" t="inlineStr">
         <is>
@@ -81681,7 +81681,7 @@
         <v>45208</v>
       </c>
       <c r="E1048" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1048" t="inlineStr">
         <is>
@@ -81754,7 +81754,7 @@
         <v>45406</v>
       </c>
       <c r="E1049" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1049" t="inlineStr">
         <is>
@@ -81827,7 +81827,7 @@
         <v>45497</v>
       </c>
       <c r="E1050" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1050" t="inlineStr">
         <is>
@@ -81900,7 +81900,7 @@
         <v>45497</v>
       </c>
       <c r="E1051" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1051" t="inlineStr">
         <is>
@@ -81973,7 +81973,7 @@
         <v>45106</v>
       </c>
       <c r="E1052" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1052" t="inlineStr">
         <is>
@@ -82046,7 +82046,7 @@
         <v>45646</v>
       </c>
       <c r="E1053" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1053" t="inlineStr">
         <is>
@@ -82119,7 +82119,7 @@
         <v>45646</v>
       </c>
       <c r="E1054" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1054" t="inlineStr">
         <is>
@@ -82192,7 +82192,7 @@
         <v>45580</v>
       </c>
       <c r="E1055" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1055" t="inlineStr">
         <is>
@@ -82265,7 +82265,7 @@
         <v>45646</v>
       </c>
       <c r="E1056" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1056" t="inlineStr">
         <is>
@@ -82338,7 +82338,7 @@
         <v>45646</v>
       </c>
       <c r="E1057" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1057" t="inlineStr">
         <is>
@@ -82411,7 +82411,7 @@
         <v>45408</v>
       </c>
       <c r="E1058" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1058" t="inlineStr">
         <is>
@@ -82484,7 +82484,7 @@
         <v>45414</v>
       </c>
       <c r="E1059" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1059" t="inlineStr">
         <is>
@@ -82557,7 +82557,7 @@
         <v>45173</v>
       </c>
       <c r="E1060" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1060" t="inlineStr">
         <is>
@@ -82630,7 +82630,7 @@
         <v>45646</v>
       </c>
       <c r="E1061" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1061" t="inlineStr">
         <is>
@@ -82703,7 +82703,7 @@
         <v>45715</v>
       </c>
       <c r="E1062" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1062" t="inlineStr">
         <is>
@@ -82776,7 +82776,7 @@
         <v>45720</v>
       </c>
       <c r="E1063" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1063" t="inlineStr">
         <is>
@@ -82849,7 +82849,7 @@
         <v>45800</v>
       </c>
       <c r="E1064" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1064" t="inlineStr">
         <is>
@@ -82927,7 +82927,7 @@
         <v>45831</v>
       </c>
       <c r="E1065" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1065" t="inlineStr">
         <is>
@@ -83000,7 +83000,7 @@
         <v>45785</v>
       </c>
       <c r="E1066" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1066" t="inlineStr">
         <is>
@@ -83073,7 +83073,7 @@
         <v>46073</v>
       </c>
       <c r="E1067" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1067" t="inlineStr">
         <is>
@@ -83146,7 +83146,7 @@
         <v>46163</v>
       </c>
       <c r="E1068" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1068" t="inlineStr">
         <is>
@@ -83219,7 +83219,7 @@
         <v>46274</v>
       </c>
       <c r="E1069" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1069" t="inlineStr">
         <is>
@@ -83292,7 +83292,7 @@
         <v>46296</v>
       </c>
       <c r="E1070" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1070" t="inlineStr">
         <is>

--- a/Översikt VETLANDA.xlsx
+++ b/Översikt VETLANDA.xlsx
@@ -601,7 +601,7 @@
         <v>45097</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>46178</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         <v>45371</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>44817</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>44890</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>45183</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>45558</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>45168</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>46107</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>45957</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>45520</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>45930</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>45170</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>44612</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>44840</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>44908</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>46002</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>46100</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         <v>45203</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>45819</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>46163</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>46188</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>44545</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>44564</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>45583</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>44819</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>45763</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>45814</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         <v>45477</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>46045</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>45048</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>45599</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4224,7 +4224,7 @@
         <v>46255</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>45646</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>45131</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>44515</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>44752</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4767,7 +4767,7 @@
         <v>44643</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>45589</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>45713</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5094,7 +5094,7 @@
         <v>45673</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         <v>45891</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>44572</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         <v>45965</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>46166</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>45303</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
         <v>45148</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>45357</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         <v>45616</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         <v>45035</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6158,7 +6158,7 @@
         <v>45400</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6273,7 +6273,7 @@
         <v>46279</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
         <v>45211</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         <v>46293</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         <v>45310</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         <v>46306</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>45792</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>45835</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>45840</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         <v>45713</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         <v>45860</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         <v>45106</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7448,7 +7448,7 @@
         <v>45509</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>45497</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>45201</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         <v>45539</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7872,7 +7872,7 @@
         <v>46051</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7982,7 +7982,7 @@
         <v>44490</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8087,7 +8087,7 @@
         <v>44834</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>44721</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>44747</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8402,7 +8402,7 @@
         <v>44592</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         <v>44740</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         <v>45596</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8722,7 +8722,7 @@
         <v>45597</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>44830</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8932,7 +8932,7 @@
         <v>45555</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9037,7 +9037,7 @@
         <v>45021</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>44781</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9247,7 +9247,7 @@
         <v>44748</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9352,7 +9352,7 @@
         <v>44824</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9457,7 +9457,7 @@
         <v>45240</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>44728</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9671,7 +9671,7 @@
         <v>45342</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>45586</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9881,7 +9881,7 @@
         <v>45835</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         <v>45586</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10091,7 +10091,7 @@
         <v>45672</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10200,7 +10200,7 @@
         <v>45880</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10305,7 +10305,7 @@
         <v>45239</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>45645</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10520,7 +10520,7 @@
         <v>44998</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10625,7 +10625,7 @@
         <v>44880</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>45419</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10835,7 +10835,7 @@
         <v>45085</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10940,7 +10940,7 @@
         <v>45408</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11045,7 +11045,7 @@
         <v>46071</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         <v>46188</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>44819</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         <v>45119</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11465,7 +11465,7 @@
         <v>45009</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
         <v>45261</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11675,7 +11675,7 @@
         <v>45378</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11780,7 +11780,7 @@
         <v>45775</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11885,7 +11885,7 @@
         <v>45930</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11999,7 +11999,7 @@
         <v>45104</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12108,7 +12108,7 @@
         <v>44816</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12213,7 +12213,7 @@
         <v>45532</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12318,7 +12318,7 @@
         <v>44833</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12423,7 +12423,7 @@
         <v>45337</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12528,7 +12528,7 @@
         <v>46248</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12633,7 +12633,7 @@
         <v>45565</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12738,7 +12738,7 @@
         <v>44916</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12843,7 +12843,7 @@
         <v>46297</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12948,7 +12948,7 @@
         <v>45352</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13053,7 +13053,7 @@
         <v>45643</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13158,7 +13158,7 @@
         <v>45791</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13263,7 +13263,7 @@
         <v>46069</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13368,7 +13368,7 @@
         <v>45904</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13473,7 +13473,7 @@
         <v>45736</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
         <v>45820</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13692,7 +13692,7 @@
         <v>45839</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13797,7 +13797,7 @@
         <v>45604</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13902,7 +13902,7 @@
         <v>45497</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14007,7 +14007,7 @@
         <v>45614</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14112,7 +14112,7 @@
         <v>45742</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         <v>44858</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14294,7 +14294,7 @@
         <v>44781</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14367,7 +14367,7 @@
         <v>44838</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>44732</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14513,7 +14513,7 @@
         <v>44781</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14586,7 +14586,7 @@
         <v>44515</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14659,7 +14659,7 @@
         <v>44508</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14732,7 +14732,7 @@
         <v>44504</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14805,7 +14805,7 @@
         <v>44496</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14878,7 +14878,7 @@
         <v>44579</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>44601</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15024,7 +15024,7 @@
         <v>44889</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15097,7 +15097,7 @@
         <v>44544</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15170,7 +15170,7 @@
         <v>44510</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15243,7 +15243,7 @@
         <v>44517</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15316,7 +15316,7 @@
         <v>44764</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15389,7 +15389,7 @@
         <v>44503</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>44510</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15535,7 +15535,7 @@
         <v>44819</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
         <v>44592</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15681,7 +15681,7 @@
         <v>44750</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15754,7 +15754,7 @@
         <v>44825</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         <v>44488</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15900,7 +15900,7 @@
         <v>44602</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15973,7 +15973,7 @@
         <v>44638</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16046,7 +16046,7 @@
         <v>44721</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16119,7 +16119,7 @@
         <v>44510</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16192,7 +16192,7 @@
         <v>44785</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16265,7 +16265,7 @@
         <v>44592</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16338,7 +16338,7 @@
         <v>44587</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>44782</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16484,7 +16484,7 @@
         <v>44815</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16557,7 +16557,7 @@
         <v>44504</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16630,7 +16630,7 @@
         <v>44580</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16703,7 +16703,7 @@
         <v>44691</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16776,7 +16776,7 @@
         <v>44880</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16849,7 +16849,7 @@
         <v>44545</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16922,7 +16922,7 @@
         <v>44750</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16995,7 +16995,7 @@
         <v>44624</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17068,7 +17068,7 @@
         <v>44595</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17141,7 +17141,7 @@
         <v>44608</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17214,7 +17214,7 @@
         <v>44820</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17287,7 +17287,7 @@
         <v>44816</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17360,7 +17360,7 @@
         <v>44645</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17433,7 +17433,7 @@
         <v>44819</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17506,7 +17506,7 @@
         <v>44784</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17579,7 +17579,7 @@
         <v>44656</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17652,7 +17652,7 @@
         <v>44585</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17730,7 +17730,7 @@
         <v>44585</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17808,7 +17808,7 @@
         <v>44585</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17886,7 +17886,7 @@
         <v>44834</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17959,7 +17959,7 @@
         <v>44740</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18037,7 +18037,7 @@
         <v>44750</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18110,7 +18110,7 @@
         <v>44587</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>44743</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18256,7 +18256,7 @@
         <v>44600</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18329,7 +18329,7 @@
         <v>44859</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18402,7 +18402,7 @@
         <v>44593</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>44743</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18548,7 +18548,7 @@
         <v>44778</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18621,7 +18621,7 @@
         <v>44504</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18694,7 +18694,7 @@
         <v>44834</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18767,7 +18767,7 @@
         <v>44509</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>44592</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18913,7 +18913,7 @@
         <v>44517</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18986,7 +18986,7 @@
         <v>44572</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19059,7 +19059,7 @@
         <v>44721</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19132,7 +19132,7 @@
         <v>44841</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19205,7 +19205,7 @@
         <v>44888</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19278,7 +19278,7 @@
         <v>44587</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19351,7 +19351,7 @@
         <v>44655</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19424,7 +19424,7 @@
         <v>44502</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19497,7 +19497,7 @@
         <v>44592</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19570,7 +19570,7 @@
         <v>44515</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19648,7 +19648,7 @@
         <v>44564</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19721,7 +19721,7 @@
         <v>44781</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19794,7 +19794,7 @@
         <v>44531</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19867,7 +19867,7 @@
         <v>44636</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19940,7 +19940,7 @@
         <v>44834</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20013,7 +20013,7 @@
         <v>44733</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         <v>44683</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20159,7 +20159,7 @@
         <v>44602</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20232,7 +20232,7 @@
         <v>44792</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20305,7 +20305,7 @@
         <v>44657</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20378,7 +20378,7 @@
         <v>44827</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20451,7 +20451,7 @@
         <v>44902</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20524,7 +20524,7 @@
         <v>44488</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>45561</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20670,7 +20670,7 @@
         <v>45251</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20743,7 +20743,7 @@
         <v>45351</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20816,7 +20816,7 @@
         <v>45602</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20889,7 +20889,7 @@
         <v>45575</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20962,7 +20962,7 @@
         <v>44967</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21035,7 +21035,7 @@
         <v>44967</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21108,7 +21108,7 @@
         <v>45265</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21181,7 +21181,7 @@
         <v>44792</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21254,7 +21254,7 @@
         <v>45267</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21327,7 +21327,7 @@
         <v>44592</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21400,7 +21400,7 @@
         <v>44880</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21473,7 +21473,7 @@
         <v>45569</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21551,7 +21551,7 @@
         <v>44903</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21624,7 +21624,7 @@
         <v>45674</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21697,7 +21697,7 @@
         <v>45580</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21770,7 +21770,7 @@
         <v>44998</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21843,7 +21843,7 @@
         <v>45175</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21916,7 +21916,7 @@
         <v>45278</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21989,7 +21989,7 @@
         <v>45259</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22062,7 +22062,7 @@
         <v>45663</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22135,7 +22135,7 @@
         <v>44582</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22208,7 +22208,7 @@
         <v>45205</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22281,7 +22281,7 @@
         <v>45771</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22359,7 +22359,7 @@
         <v>45771</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22437,7 +22437,7 @@
         <v>44831</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22510,7 +22510,7 @@
         <v>45057</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22583,7 +22583,7 @@
         <v>44936</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>45188</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>45307</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>45264</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22875,7 +22875,7 @@
         <v>44530</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22948,7 +22948,7 @@
         <v>45350</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23021,7 +23021,7 @@
         <v>45071</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23094,7 +23094,7 @@
         <v>45135</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23167,7 +23167,7 @@
         <v>45229</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23240,7 +23240,7 @@
         <v>45055</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23313,7 +23313,7 @@
         <v>44851</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23386,7 +23386,7 @@
         <v>44600</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23459,7 +23459,7 @@
         <v>44986</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23532,7 +23532,7 @@
         <v>45406</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23605,7 +23605,7 @@
         <v>44762</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23678,7 +23678,7 @@
         <v>45097</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23751,7 +23751,7 @@
         <v>45097</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23824,7 +23824,7 @@
         <v>45335</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23897,7 +23897,7 @@
         <v>44710</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23970,7 +23970,7 @@
         <v>45384</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24043,7 +24043,7 @@
         <v>45434</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24116,7 +24116,7 @@
         <v>45104</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24189,7 +24189,7 @@
         <v>45300</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24262,7 +24262,7 @@
         <v>45439</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24335,7 +24335,7 @@
         <v>45099</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24408,7 +24408,7 @@
         <v>45709</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24481,7 +24481,7 @@
         <v>45645</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24554,7 +24554,7 @@
         <v>45645</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24627,7 +24627,7 @@
         <v>45470</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24700,7 +24700,7 @@
         <v>45309</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24773,7 +24773,7 @@
         <v>45309</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24846,7 +24846,7 @@
         <v>45097</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24919,7 +24919,7 @@
         <v>45272</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24992,7 +24992,7 @@
         <v>45113</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25065,7 +25065,7 @@
         <v>45363</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25143,7 +25143,7 @@
         <v>44949</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25216,7 +25216,7 @@
         <v>45118</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25289,7 +25289,7 @@
         <v>45309</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25362,7 +25362,7 @@
         <v>45336</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25435,7 +25435,7 @@
         <v>44487</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25508,7 +25508,7 @@
         <v>45162</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25581,7 +25581,7 @@
         <v>45414</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25659,7 +25659,7 @@
         <v>45161</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25732,7 +25732,7 @@
         <v>45226</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25805,7 +25805,7 @@
         <v>45188</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25878,7 +25878,7 @@
         <v>45191</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25951,7 +25951,7 @@
         <v>44916</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26024,7 +26024,7 @@
         <v>44916</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26097,7 +26097,7 @@
         <v>44747</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26170,7 +26170,7 @@
         <v>45580</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26243,7 +26243,7 @@
         <v>45701</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26321,7 +26321,7 @@
         <v>44952</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26394,7 +26394,7 @@
         <v>45082</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26467,7 +26467,7 @@
         <v>45209</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26540,7 +26540,7 @@
         <v>45461</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26613,7 +26613,7 @@
         <v>45163</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26686,7 +26686,7 @@
         <v>44888</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26759,7 +26759,7 @@
         <v>45188</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26832,7 +26832,7 @@
         <v>44655</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26905,7 +26905,7 @@
         <v>45754</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26983,7 +26983,7 @@
         <v>45754</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27061,7 +27061,7 @@
         <v>45351</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27134,7 +27134,7 @@
         <v>45628</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27207,7 +27207,7 @@
         <v>44972</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27280,7 +27280,7 @@
         <v>44916</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27353,7 +27353,7 @@
         <v>45097</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27426,7 +27426,7 @@
         <v>44770</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27499,7 +27499,7 @@
         <v>45572</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27572,7 +27572,7 @@
         <v>45031</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27645,7 +27645,7 @@
         <v>44592</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27718,7 +27718,7 @@
         <v>45448</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27791,7 +27791,7 @@
         <v>45190</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27864,7 +27864,7 @@
         <v>45580</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27937,7 +27937,7 @@
         <v>45166</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28010,7 +28010,7 @@
         <v>45362</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28083,7 +28083,7 @@
         <v>45625</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28156,7 +28156,7 @@
         <v>45104</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28229,7 +28229,7 @@
         <v>44977</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28302,7 +28302,7 @@
         <v>45645</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28375,7 +28375,7 @@
         <v>45135</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28448,7 +28448,7 @@
         <v>45135</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28521,7 +28521,7 @@
         <v>45135</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28594,7 +28594,7 @@
         <v>45545</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28667,7 +28667,7 @@
         <v>45117</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28740,7 +28740,7 @@
         <v>44888</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28813,7 +28813,7 @@
         <v>44984</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28886,7 +28886,7 @@
         <v>45099</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28959,7 +28959,7 @@
         <v>45610</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29032,7 +29032,7 @@
         <v>45742</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29105,7 +29105,7 @@
         <v>44641</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>45228</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29251,7 +29251,7 @@
         <v>45330</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29324,7 +29324,7 @@
         <v>44693</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29397,7 +29397,7 @@
         <v>45202</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29470,7 +29470,7 @@
         <v>45702</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29543,7 +29543,7 @@
         <v>45441</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29616,7 +29616,7 @@
         <v>45376</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29689,7 +29689,7 @@
         <v>45274</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29762,7 +29762,7 @@
         <v>45595</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29835,7 +29835,7 @@
         <v>45363</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29913,7 +29913,7 @@
         <v>44916</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29986,7 +29986,7 @@
         <v>44531</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30059,7 +30059,7 @@
         <v>45365</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30132,7 +30132,7 @@
         <v>45414</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30210,7 +30210,7 @@
         <v>45107</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30283,7 +30283,7 @@
         <v>45251</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30356,7 +30356,7 @@
         <v>45048</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30429,7 +30429,7 @@
         <v>44515</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30507,7 +30507,7 @@
         <v>44984</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30580,7 +30580,7 @@
         <v>45232</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30653,7 +30653,7 @@
         <v>45462</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30726,7 +30726,7 @@
         <v>45319</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30799,7 +30799,7 @@
         <v>44984</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30872,7 +30872,7 @@
         <v>44984</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30945,7 +30945,7 @@
         <v>45357</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31018,7 +31018,7 @@
         <v>45006</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31091,7 +31091,7 @@
         <v>45581</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31169,7 +31169,7 @@
         <v>44945</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31242,7 +31242,7 @@
         <v>45069</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31315,7 +31315,7 @@
         <v>45484</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31388,7 +31388,7 @@
         <v>45015</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31461,7 +31461,7 @@
         <v>45310</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31534,7 +31534,7 @@
         <v>45351</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31607,7 +31607,7 @@
         <v>45170</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31680,7 +31680,7 @@
         <v>45107</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31753,7 +31753,7 @@
         <v>45684</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31831,7 +31831,7 @@
         <v>45097</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31904,7 +31904,7 @@
         <v>45330</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31977,7 +31977,7 @@
         <v>45042</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32050,7 +32050,7 @@
         <v>45099</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32123,7 +32123,7 @@
         <v>44946</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32196,7 +32196,7 @@
         <v>45352</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32269,7 +32269,7 @@
         <v>44837</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32342,7 +32342,7 @@
         <v>45329</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32415,7 +32415,7 @@
         <v>45329</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32488,7 +32488,7 @@
         <v>45882</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32561,7 +32561,7 @@
         <v>45882</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32634,7 +32634,7 @@
         <v>45883</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32707,7 +32707,7 @@
         <v>45201</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32780,7 +32780,7 @@
         <v>45884</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32853,7 +32853,7 @@
         <v>45902</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32926,7 +32926,7 @@
         <v>45351</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32999,7 +32999,7 @@
         <v>46112</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33077,7 +33077,7 @@
         <v>45965</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33150,7 +33150,7 @@
         <v>45525</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33223,7 +33223,7 @@
         <v>45785</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33296,7 +33296,7 @@
         <v>45912</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33369,7 +33369,7 @@
         <v>45840</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33442,7 +33442,7 @@
         <v>45866</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33515,7 +33515,7 @@
         <v>45748</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33593,7 +33593,7 @@
         <v>45748</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33671,7 +33671,7 @@
         <v>45925</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33744,7 +33744,7 @@
         <v>45971</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33817,7 +33817,7 @@
         <v>46006</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33890,7 +33890,7 @@
         <v>45763</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33963,7 +33963,7 @@
         <v>44965</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34036,7 +34036,7 @@
         <v>45693</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34109,7 +34109,7 @@
         <v>45889</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34182,7 +34182,7 @@
         <v>45888</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34255,7 +34255,7 @@
         <v>45888</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34328,7 +34328,7 @@
         <v>45541</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34401,7 +34401,7 @@
         <v>45677</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34474,7 +34474,7 @@
         <v>45889</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34547,7 +34547,7 @@
         <v>45786</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34620,7 +34620,7 @@
         <v>45888</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34693,7 +34693,7 @@
         <v>45742</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34766,7 +34766,7 @@
         <v>44970</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34839,7 +34839,7 @@
         <v>45889</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34912,7 +34912,7 @@
         <v>45888</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34985,7 +34985,7 @@
         <v>45785</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35058,7 +35058,7 @@
         <v>45888</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35131,7 +35131,7 @@
         <v>45888</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35204,7 +35204,7 @@
         <v>45826</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35277,7 +35277,7 @@
         <v>45133</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35350,7 +35350,7 @@
         <v>45889</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35423,7 +35423,7 @@
         <v>45742</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35496,7 +35496,7 @@
         <v>45770</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35569,7 +35569,7 @@
         <v>45357</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35642,7 +35642,7 @@
         <v>45841</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35715,7 +35715,7 @@
         <v>45231</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35788,7 +35788,7 @@
         <v>45839</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35861,7 +35861,7 @@
         <v>45623</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35934,7 +35934,7 @@
         <v>45608</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36007,7 +36007,7 @@
         <v>44545</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36080,7 +36080,7 @@
         <v>45681</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36153,7 +36153,7 @@
         <v>45152</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36226,7 +36226,7 @@
         <v>44503</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36299,7 +36299,7 @@
         <v>45873</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36372,7 +36372,7 @@
         <v>45971</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36445,7 +36445,7 @@
         <v>45230</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36523,7 +36523,7 @@
         <v>45610</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36596,7 +36596,7 @@
         <v>46122</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36669,7 +36669,7 @@
         <v>45153</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36742,7 +36742,7 @@
         <v>45755</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36815,7 +36815,7 @@
         <v>45670</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36888,7 +36888,7 @@
         <v>44741</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36961,7 +36961,7 @@
         <v>45825</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37034,7 +37034,7 @@
         <v>45272</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37107,7 +37107,7 @@
         <v>45084</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37180,7 +37180,7 @@
         <v>45341</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37253,7 +37253,7 @@
         <v>45348</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37326,7 +37326,7 @@
         <v>45839</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37399,7 +37399,7 @@
         <v>44538</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37472,7 +37472,7 @@
         <v>44785</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37545,7 +37545,7 @@
         <v>46052</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37618,7 +37618,7 @@
         <v>45883</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37691,7 +37691,7 @@
         <v>45839</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37764,7 +37764,7 @@
         <v>45691</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37842,7 +37842,7 @@
         <v>44600</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37915,7 +37915,7 @@
         <v>45331</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37988,7 +37988,7 @@
         <v>45331</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38061,7 +38061,7 @@
         <v>45898</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38134,7 +38134,7 @@
         <v>45222</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38207,7 +38207,7 @@
         <v>45819</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38280,7 +38280,7 @@
         <v>44970</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38353,7 +38353,7 @@
         <v>45671</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38426,7 +38426,7 @@
         <v>45737</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38499,7 +38499,7 @@
         <v>45435</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38572,7 +38572,7 @@
         <v>45587</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38645,7 +38645,7 @@
         <v>45230</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38723,7 +38723,7 @@
         <v>45827</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38796,7 +38796,7 @@
         <v>45902</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38869,7 +38869,7 @@
         <v>45204</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38942,7 +38942,7 @@
         <v>45455</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39015,7 +39015,7 @@
         <v>45561</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39088,7 +39088,7 @@
         <v>45282</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39161,7 +39161,7 @@
         <v>45245</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39234,7 +39234,7 @@
         <v>45631</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39307,7 +39307,7 @@
         <v>45247</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39380,7 +39380,7 @@
         <v>45259</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39453,7 +39453,7 @@
         <v>45911</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39526,7 +39526,7 @@
         <v>45589</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39599,7 +39599,7 @@
         <v>45911</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39672,7 +39672,7 @@
         <v>45370</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39745,7 +39745,7 @@
         <v>45322</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39818,7 +39818,7 @@
         <v>45035</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39891,7 +39891,7 @@
         <v>45645</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39969,7 +39969,7 @@
         <v>45076</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40042,7 +40042,7 @@
         <v>45006</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40115,7 +40115,7 @@
         <v>44580</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40188,7 +40188,7 @@
         <v>45089</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40261,7 +40261,7 @@
         <v>45615</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40334,7 +40334,7 @@
         <v>45922</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40407,7 +40407,7 @@
         <v>45538</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40480,7 +40480,7 @@
         <v>45298</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40553,7 +40553,7 @@
         <v>45925</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40626,7 +40626,7 @@
         <v>45372</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40699,7 +40699,7 @@
         <v>45076</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40772,7 +40772,7 @@
         <v>45170</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40845,7 +40845,7 @@
         <v>45401</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40918,7 +40918,7 @@
         <v>44607</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40991,7 +40991,7 @@
         <v>44837</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41064,7 +41064,7 @@
         <v>46153</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41137,7 +41137,7 @@
         <v>46153</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41210,7 +41210,7 @@
         <v>45936</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41283,7 +41283,7 @@
         <v>44511</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41356,7 +41356,7 @@
         <v>45089</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41429,7 +41429,7 @@
         <v>46153</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41502,7 +41502,7 @@
         <v>45443</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41575,7 +41575,7 @@
         <v>45240</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41648,7 +41648,7 @@
         <v>45168</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41721,7 +41721,7 @@
         <v>45321</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41794,7 +41794,7 @@
         <v>45163</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41867,7 +41867,7 @@
         <v>44510</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41940,7 +41940,7 @@
         <v>45944</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42013,7 +42013,7 @@
         <v>45211</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42086,7 +42086,7 @@
         <v>46154</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42164,7 +42164,7 @@
         <v>45414</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42237,7 +42237,7 @@
         <v>44894</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42310,7 +42310,7 @@
         <v>45519</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42383,7 +42383,7 @@
         <v>45946</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42456,7 +42456,7 @@
         <v>45314</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42529,7 +42529,7 @@
         <v>45433</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42602,7 +42602,7 @@
         <v>45097</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42675,7 +42675,7 @@
         <v>45448</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42748,7 +42748,7 @@
         <v>45866</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42821,7 +42821,7 @@
         <v>45639</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42894,7 +42894,7 @@
         <v>45950</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42967,7 +42967,7 @@
         <v>45953</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43040,7 +43040,7 @@
         <v>45644</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43113,7 +43113,7 @@
         <v>45649</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43191,7 +43191,7 @@
         <v>46126</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43264,7 +43264,7 @@
         <v>45114</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43337,7 +43337,7 @@
         <v>44858</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43410,7 +43410,7 @@
         <v>45545</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43483,7 +43483,7 @@
         <v>45250</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43556,7 +43556,7 @@
         <v>45224</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43634,7 +43634,7 @@
         <v>45400</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43712,7 +43712,7 @@
         <v>46160</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43785,7 +43785,7 @@
         <v>46161</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43858,7 +43858,7 @@
         <v>46160</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43931,7 +43931,7 @@
         <v>45761</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44004,7 +44004,7 @@
         <v>45763</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44077,7 +44077,7 @@
         <v>46160</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44150,7 +44150,7 @@
         <v>45672</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44223,7 +44223,7 @@
         <v>46064</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44296,7 +44296,7 @@
         <v>45930</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44369,7 +44369,7 @@
         <v>45264</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44442,7 +44442,7 @@
         <v>45525</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44515,7 +44515,7 @@
         <v>44965</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44588,7 +44588,7 @@
         <v>46160</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44661,7 +44661,7 @@
         <v>44926</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44734,7 +44734,7 @@
         <v>44926</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44807,7 +44807,7 @@
         <v>45401</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44880,7 +44880,7 @@
         <v>45392</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44953,7 +44953,7 @@
         <v>46163</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45026,7 +45026,7 @@
         <v>45394</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45099,7 +45099,7 @@
         <v>45974</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45172,7 +45172,7 @@
         <v>45975</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45245,7 +45245,7 @@
         <v>44602</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45318,7 +45318,7 @@
         <v>46161</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45391,7 +45391,7 @@
         <v>45007</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45464,7 +45464,7 @@
         <v>45568</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45542,7 +45542,7 @@
         <v>45297</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45615,7 +45615,7 @@
         <v>45236</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45688,7 +45688,7 @@
         <v>45625</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45761,7 +45761,7 @@
         <v>45105</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45834,7 +45834,7 @@
         <v>45981</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45912,7 +45912,7 @@
         <v>44859</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45985,7 +45985,7 @@
         <v>45981</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46058,7 +46058,7 @@
         <v>45981</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46131,7 +46131,7 @@
         <v>45674</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46204,7 +46204,7 @@
         <v>45982</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46277,7 +46277,7 @@
         <v>45981</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46350,7 +46350,7 @@
         <v>45930</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46428,7 +46428,7 @@
         <v>44655</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46501,7 +46501,7 @@
         <v>44970</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46574,7 +46574,7 @@
         <v>45329</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46647,7 +46647,7 @@
         <v>44847</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46720,7 +46720,7 @@
         <v>45992</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46793,7 +46793,7 @@
         <v>45180</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46866,7 +46866,7 @@
         <v>45173</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46939,7 +46939,7 @@
         <v>45173</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47012,7 +47012,7 @@
         <v>45345</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47085,7 +47085,7 @@
         <v>45526</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47158,7 +47158,7 @@
         <v>45170</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47231,7 +47231,7 @@
         <v>45170</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47304,7 +47304,7 @@
         <v>45999</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47377,7 +47377,7 @@
         <v>45999</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47450,7 +47450,7 @@
         <v>45303</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47523,7 +47523,7 @@
         <v>45104</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47596,7 +47596,7 @@
         <v>46001</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47669,7 +47669,7 @@
         <v>45113</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47742,7 +47742,7 @@
         <v>45446</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47815,7 +47815,7 @@
         <v>46003</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47888,7 +47888,7 @@
         <v>45438</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47961,7 +47961,7 @@
         <v>46009</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48034,7 +48034,7 @@
         <v>46007</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48107,7 +48107,7 @@
         <v>46007</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48180,7 +48180,7 @@
         <v>46009</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48253,7 +48253,7 @@
         <v>45182</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48331,7 +48331,7 @@
         <v>45182</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48404,7 +48404,7 @@
         <v>45999</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48477,7 +48477,7 @@
         <v>44607</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48550,7 +48550,7 @@
         <v>46010</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48623,7 +48623,7 @@
         <v>45669</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48696,7 +48696,7 @@
         <v>46010</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48769,7 +48769,7 @@
         <v>45315</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48842,7 +48842,7 @@
         <v>45462</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48915,7 +48915,7 @@
         <v>45449</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48988,7 +48988,7 @@
         <v>45827</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49061,7 +49061,7 @@
         <v>45327</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49134,7 +49134,7 @@
         <v>45164</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49207,7 +49207,7 @@
         <v>45330</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49280,7 +49280,7 @@
         <v>44995</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49353,7 +49353,7 @@
         <v>45692</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49426,7 +49426,7 @@
         <v>45106</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49499,7 +49499,7 @@
         <v>45574</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49577,7 +49577,7 @@
         <v>46029</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49650,7 +49650,7 @@
         <v>45616</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49723,7 +49723,7 @@
         <v>45510</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49796,7 +49796,7 @@
         <v>46030</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49869,7 +49869,7 @@
         <v>46030</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49942,7 +49942,7 @@
         <v>45219</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50020,7 +50020,7 @@
         <v>45274</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50093,7 +50093,7 @@
         <v>46031</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50166,7 +50166,7 @@
         <v>46175</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50239,7 +50239,7 @@
         <v>45250</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50312,7 +50312,7 @@
         <v>44587</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50385,7 +50385,7 @@
         <v>44783</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50458,7 +50458,7 @@
         <v>46178</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50531,7 +50531,7 @@
         <v>44830</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50604,7 +50604,7 @@
         <v>45544</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50677,7 +50677,7 @@
         <v>45133</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50750,7 +50750,7 @@
         <v>45408</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50823,7 +50823,7 @@
         <v>46178</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50896,7 +50896,7 @@
         <v>44834</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50969,7 +50969,7 @@
         <v>45366</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51042,7 +51042,7 @@
         <v>44815</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51115,7 +51115,7 @@
         <v>45069</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51188,7 +51188,7 @@
         <v>45440</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51261,7 +51261,7 @@
         <v>45701</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51339,7 +51339,7 @@
         <v>45302</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51412,7 +51412,7 @@
         <v>46182</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51485,7 +51485,7 @@
         <v>45615</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51558,7 +51558,7 @@
         <v>45113</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51631,7 +51631,7 @@
         <v>46044</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51704,7 +51704,7 @@
         <v>46045</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51777,7 +51777,7 @@
         <v>46182</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51850,7 +51850,7 @@
         <v>46048</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51923,7 +51923,7 @@
         <v>46048</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51996,7 +51996,7 @@
         <v>46048</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52069,7 +52069,7 @@
         <v>44683</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52142,7 +52142,7 @@
         <v>46049</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52215,7 +52215,7 @@
         <v>45546</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52288,7 +52288,7 @@
         <v>44839</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52361,7 +52361,7 @@
         <v>44970</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52434,7 +52434,7 @@
         <v>46182</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52507,7 +52507,7 @@
         <v>45222</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52580,7 +52580,7 @@
         <v>45183</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52653,7 +52653,7 @@
         <v>44965</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52726,7 +52726,7 @@
         <v>46055</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52799,7 +52799,7 @@
         <v>45000</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52872,7 +52872,7 @@
         <v>45133</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52945,7 +52945,7 @@
         <v>45183</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53018,7 +53018,7 @@
         <v>46184</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53091,7 +53091,7 @@
         <v>45706</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53164,7 +53164,7 @@
         <v>44839</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53237,7 +53237,7 @@
         <v>46184</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53310,7 +53310,7 @@
         <v>46062</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53383,7 +53383,7 @@
         <v>46063</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53456,7 +53456,7 @@
         <v>44753</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53529,7 +53529,7 @@
         <v>46063</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53602,7 +53602,7 @@
         <v>46063</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53675,7 +53675,7 @@
         <v>46063</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53748,7 +53748,7 @@
         <v>46184</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53821,7 +53821,7 @@
         <v>46185</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53894,7 +53894,7 @@
         <v>46188</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53967,7 +53967,7 @@
         <v>44802</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54045,7 +54045,7 @@
         <v>45446</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54118,7 +54118,7 @@
         <v>46077</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54191,7 +54191,7 @@
         <v>44929</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54264,7 +54264,7 @@
         <v>44743</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54337,7 +54337,7 @@
         <v>46077</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54410,7 +54410,7 @@
         <v>45170</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54483,7 +54483,7 @@
         <v>45497</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54556,7 +54556,7 @@
         <v>45497</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54629,7 +54629,7 @@
         <v>45119</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54702,7 +54702,7 @@
         <v>45401</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54775,7 +54775,7 @@
         <v>46084</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54848,7 +54848,7 @@
         <v>46084</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54921,7 +54921,7 @@
         <v>44952</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54994,7 +54994,7 @@
         <v>45112</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55067,7 +55067,7 @@
         <v>46084</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55140,7 +55140,7 @@
         <v>45107</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55213,7 +55213,7 @@
         <v>44747</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55286,7 +55286,7 @@
         <v>45526</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55359,7 +55359,7 @@
         <v>44600</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55432,7 +55432,7 @@
         <v>46190</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55505,7 +55505,7 @@
         <v>46087</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55578,7 +55578,7 @@
         <v>46091</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55651,7 +55651,7 @@
         <v>45569</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55724,7 +55724,7 @@
         <v>46092</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55797,7 +55797,7 @@
         <v>44930</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55870,7 +55870,7 @@
         <v>45925</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55943,7 +55943,7 @@
         <v>45033</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56016,7 +56016,7 @@
         <v>46002</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56089,7 +56089,7 @@
         <v>46097</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56162,7 +56162,7 @@
         <v>45572</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56235,7 +56235,7 @@
         <v>46098</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56308,7 +56308,7 @@
         <v>45341</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56381,7 +56381,7 @@
         <v>45348</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56454,7 +56454,7 @@
         <v>46099</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56527,7 +56527,7 @@
         <v>46100</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56600,7 +56600,7 @@
         <v>46195</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56673,7 +56673,7 @@
         <v>46104</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56746,7 +56746,7 @@
         <v>46104</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56819,7 +56819,7 @@
         <v>46196</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56892,7 +56892,7 @@
         <v>44740</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56970,7 +56970,7 @@
         <v>45406</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57043,7 +57043,7 @@
         <v>44998</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57116,7 +57116,7 @@
         <v>45302</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57189,7 +57189,7 @@
         <v>44869</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57262,7 +57262,7 @@
         <v>45174</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57335,7 +57335,7 @@
         <v>46107</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57408,7 +57408,7 @@
         <v>46107</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57481,7 +57481,7 @@
         <v>46107</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57554,7 +57554,7 @@
         <v>46111</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57627,7 +57627,7 @@
         <v>46111</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57700,7 +57700,7 @@
         <v>45363</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57778,7 +57778,7 @@
         <v>45363</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57856,7 +57856,7 @@
         <v>45363</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57934,7 +57934,7 @@
         <v>45364</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58007,7 +58007,7 @@
         <v>45104</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58080,7 +58080,7 @@
         <v>45281</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58153,7 +58153,7 @@
         <v>45525</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58226,7 +58226,7 @@
         <v>46197</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58299,7 +58299,7 @@
         <v>45006</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58372,7 +58372,7 @@
         <v>45202</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58445,7 +58445,7 @@
         <v>45563</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58523,7 +58523,7 @@
         <v>45357</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58596,7 +58596,7 @@
         <v>46202</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58669,7 +58669,7 @@
         <v>45173</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58742,7 +58742,7 @@
         <v>46121</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58815,7 +58815,7 @@
         <v>46122</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58888,7 +58888,7 @@
         <v>46121</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58961,7 +58961,7 @@
         <v>45629</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59034,7 +59034,7 @@
         <v>46126</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59107,7 +59107,7 @@
         <v>46128</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59180,7 +59180,7 @@
         <v>46128</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59253,7 +59253,7 @@
         <v>46128</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59326,7 +59326,7 @@
         <v>46128</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59399,7 +59399,7 @@
         <v>45314</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59472,7 +59472,7 @@
         <v>46127</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59545,7 +59545,7 @@
         <v>46128</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59618,7 +59618,7 @@
         <v>45420</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59691,7 +59691,7 @@
         <v>45195</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59764,7 +59764,7 @@
         <v>46133</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59837,7 +59837,7 @@
         <v>46133</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59910,7 +59910,7 @@
         <v>45238</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59988,7 +59988,7 @@
         <v>46204</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60061,7 +60061,7 @@
         <v>44880</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60134,7 +60134,7 @@
         <v>44880</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60207,7 +60207,7 @@
         <v>45079</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60280,7 +60280,7 @@
         <v>45091</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60353,7 +60353,7 @@
         <v>44602</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60426,7 +60426,7 @@
         <v>45163</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60499,7 +60499,7 @@
         <v>45903</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60572,7 +60572,7 @@
         <v>44523</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60645,7 +60645,7 @@
         <v>45839</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60718,7 +60718,7 @@
         <v>45699</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60791,7 +60791,7 @@
         <v>45827</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60864,7 +60864,7 @@
         <v>44677</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60937,7 +60937,7 @@
         <v>46037</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61010,7 +61010,7 @@
         <v>45944</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61083,7 +61083,7 @@
         <v>45112</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61156,7 +61156,7 @@
         <v>45303</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61229,7 +61229,7 @@
         <v>44592</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61302,7 +61302,7 @@
         <v>45891</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61375,7 +61375,7 @@
         <v>45313</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61448,7 +61448,7 @@
         <v>45799</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61521,7 +61521,7 @@
         <v>45306</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61594,7 +61594,7 @@
         <v>45475</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61667,7 +61667,7 @@
         <v>45211</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61740,7 +61740,7 @@
         <v>45931</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61813,7 +61813,7 @@
         <v>44510</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61886,7 +61886,7 @@
         <v>45352</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61959,7 +61959,7 @@
         <v>45538</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62032,7 +62032,7 @@
         <v>45329</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62110,7 +62110,7 @@
         <v>45895</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62183,7 +62183,7 @@
         <v>45314</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62256,7 +62256,7 @@
         <v>44815</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62329,7 +62329,7 @@
         <v>44497</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62402,7 +62402,7 @@
         <v>45091</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62475,7 +62475,7 @@
         <v>45022</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62548,7 +62548,7 @@
         <v>45526</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62621,7 +62621,7 @@
         <v>45114</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62694,7 +62694,7 @@
         <v>45440</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62767,7 +62767,7 @@
         <v>44587</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62840,7 +62840,7 @@
         <v>44715</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62913,7 +62913,7 @@
         <v>44813</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62986,7 +62986,7 @@
         <v>45365</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63059,7 +63059,7 @@
         <v>45385</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63132,7 +63132,7 @@
         <v>46069</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63205,7 +63205,7 @@
         <v>44946</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63278,7 +63278,7 @@
         <v>46213</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63351,7 +63351,7 @@
         <v>46168</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63424,7 +63424,7 @@
         <v>46177</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63497,7 +63497,7 @@
         <v>44805</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63570,7 +63570,7 @@
         <v>44813</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63643,7 +63643,7 @@
         <v>45398</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63716,7 +63716,7 @@
         <v>45307</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63789,7 +63789,7 @@
         <v>44825</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63862,7 +63862,7 @@
         <v>44917</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63935,7 +63935,7 @@
         <v>45177</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64013,7 +64013,7 @@
         <v>45174</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64091,7 +64091,7 @@
         <v>45329</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64164,7 +64164,7 @@
         <v>45245</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64237,7 +64237,7 @@
         <v>45737</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64310,7 +64310,7 @@
         <v>46273</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64383,7 +64383,7 @@
         <v>45719</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64456,7 +64456,7 @@
         <v>45364</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64529,7 +64529,7 @@
         <v>46274</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64602,7 +64602,7 @@
         <v>46273</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64675,7 +64675,7 @@
         <v>45089</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64748,7 +64748,7 @@
         <v>45660</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64821,7 +64821,7 @@
         <v>45107</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64894,7 +64894,7 @@
         <v>45184</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64967,7 +64967,7 @@
         <v>45589</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65040,7 +65040,7 @@
         <v>45589</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65113,7 +65113,7 @@
         <v>45532</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65186,7 +65186,7 @@
         <v>45370</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65259,7 +65259,7 @@
         <v>45406</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65332,7 +65332,7 @@
         <v>46234</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65405,7 +65405,7 @@
         <v>46276</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65478,7 +65478,7 @@
         <v>46276</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65551,7 +65551,7 @@
         <v>46234</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65624,7 +65624,7 @@
         <v>44595</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65697,7 +65697,7 @@
         <v>46279</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65770,7 +65770,7 @@
         <v>46276</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65843,7 +65843,7 @@
         <v>46276</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65916,7 +65916,7 @@
         <v>46276</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65989,7 +65989,7 @@
         <v>46233</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66062,7 +66062,7 @@
         <v>45104</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66135,7 +66135,7 @@
         <v>45071</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66208,7 +66208,7 @@
         <v>46234</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66281,7 +66281,7 @@
         <v>45216</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66354,7 +66354,7 @@
         <v>46237</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66427,7 +66427,7 @@
         <v>45303</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66500,7 +66500,7 @@
         <v>45678</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66573,7 +66573,7 @@
         <v>45182</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66646,7 +66646,7 @@
         <v>44495</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66719,7 +66719,7 @@
         <v>45219</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66792,7 +66792,7 @@
         <v>45030</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66865,7 +66865,7 @@
         <v>45544</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66938,7 +66938,7 @@
         <v>45691</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67011,7 +67011,7 @@
         <v>46240</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67084,7 +67084,7 @@
         <v>44488</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67157,7 +67157,7 @@
         <v>45631</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67230,7 +67230,7 @@
         <v>45216</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67308,7 +67308,7 @@
         <v>46283</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67381,7 +67381,7 @@
         <v>45359</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67454,7 +67454,7 @@
         <v>46244</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67527,7 +67527,7 @@
         <v>45376</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67600,7 +67600,7 @@
         <v>44810</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67673,7 +67673,7 @@
         <v>45209</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -67746,7 +67746,7 @@
         <v>45183</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -67819,7 +67819,7 @@
         <v>45595</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67892,7 +67892,7 @@
         <v>45953</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -67965,7 +67965,7 @@
         <v>45575</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -68038,7 +68038,7 @@
         <v>46245</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -68111,7 +68111,7 @@
         <v>46244</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -68184,7 +68184,7 @@
         <v>45062</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -68257,7 +68257,7 @@
         <v>45231</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -68330,7 +68330,7 @@
         <v>45699</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68403,7 +68403,7 @@
         <v>45737</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68476,7 +68476,7 @@
         <v>44930</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68549,7 +68549,7 @@
         <v>44971</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -68622,7 +68622,7 @@
         <v>45602</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -68695,7 +68695,7 @@
         <v>45092</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -68768,7 +68768,7 @@
         <v>45674</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68841,7 +68841,7 @@
         <v>46289</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -68914,7 +68914,7 @@
         <v>45478</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -68987,7 +68987,7 @@
         <v>45769</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -69065,7 +69065,7 @@
         <v>45164</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -69138,7 +69138,7 @@
         <v>46289</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -69211,7 +69211,7 @@
         <v>46246</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -69284,7 +69284,7 @@
         <v>45309</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -69357,7 +69357,7 @@
         <v>45309</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -69430,7 +69430,7 @@
         <v>45182</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69508,7 +69508,7 @@
         <v>46280</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -69581,7 +69581,7 @@
         <v>46293</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -69654,7 +69654,7 @@
         <v>46178</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -69727,7 +69727,7 @@
         <v>46178</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -69800,7 +69800,7 @@
         <v>45329</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -69873,7 +69873,7 @@
         <v>45222</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -69946,7 +69946,7 @@
         <v>45492</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -70019,7 +70019,7 @@
         <v>45323</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -70092,7 +70092,7 @@
         <v>46293</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -70165,7 +70165,7 @@
         <v>46293</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -70238,7 +70238,7 @@
         <v>45763</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -70311,7 +70311,7 @@
         <v>45384</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -70384,7 +70384,7 @@
         <v>45296</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -70457,7 +70457,7 @@
         <v>46290</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70530,7 +70530,7 @@
         <v>45763</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -70603,7 +70603,7 @@
         <v>45763</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -70676,7 +70676,7 @@
         <v>45763</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -70749,7 +70749,7 @@
         <v>45925</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -70822,7 +70822,7 @@
         <v>44946</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -70895,7 +70895,7 @@
         <v>45462</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -70968,7 +70968,7 @@
         <v>44879</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -71041,7 +71041,7 @@
         <v>45719</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -71114,7 +71114,7 @@
         <v>45540</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -71187,7 +71187,7 @@
         <v>45134</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -71260,7 +71260,7 @@
         <v>45316</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -71333,7 +71333,7 @@
         <v>46009</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -71406,7 +71406,7 @@
         <v>45414</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -71479,7 +71479,7 @@
         <v>45607</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -71552,7 +71552,7 @@
         <v>44818</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -71625,7 +71625,7 @@
         <v>45673</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -71698,7 +71698,7 @@
         <v>46252</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -71771,7 +71771,7 @@
         <v>44831</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -71844,7 +71844,7 @@
         <v>45001</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -71922,7 +71922,7 @@
         <v>45254</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -72000,7 +72000,7 @@
         <v>45090</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -72073,7 +72073,7 @@
         <v>45132</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -72146,7 +72146,7 @@
         <v>45335</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -72219,7 +72219,7 @@
         <v>45602</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -72292,7 +72292,7 @@
         <v>44963</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -72365,7 +72365,7 @@
         <v>45168</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -72438,7 +72438,7 @@
         <v>45400</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -72511,7 +72511,7 @@
         <v>45188</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -72584,7 +72584,7 @@
         <v>44902</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -72657,7 +72657,7 @@
         <v>44564</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -72735,7 +72735,7 @@
         <v>45189</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -72813,7 +72813,7 @@
         <v>45691</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -72886,7 +72886,7 @@
         <v>46248</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -72964,7 +72964,7 @@
         <v>44916</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -73037,7 +73037,7 @@
         <v>46296</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -73110,7 +73110,7 @@
         <v>44957</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -73183,7 +73183,7 @@
         <v>46247</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -73261,7 +73261,7 @@
         <v>46247</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -73339,7 +73339,7 @@
         <v>46297</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -73412,7 +73412,7 @@
         <v>46296</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -73485,7 +73485,7 @@
         <v>46297</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -73558,7 +73558,7 @@
         <v>45936</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -73631,7 +73631,7 @@
         <v>46062</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -73704,7 +73704,7 @@
         <v>46295</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -73777,7 +73777,7 @@
         <v>46031</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -73850,7 +73850,7 @@
         <v>44502</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -73923,7 +73923,7 @@
         <v>46258</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -73996,7 +73996,7 @@
         <v>45702</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -74074,7 +74074,7 @@
         <v>45134</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -74147,7 +74147,7 @@
         <v>45348</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -74220,7 +74220,7 @@
         <v>45439</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -74293,7 +74293,7 @@
         <v>44781</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -74366,7 +74366,7 @@
         <v>46258</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -74439,7 +74439,7 @@
         <v>45783</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -74512,7 +74512,7 @@
         <v>45783</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -74585,7 +74585,7 @@
         <v>46301</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -74658,7 +74658,7 @@
         <v>46301</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -74731,7 +74731,7 @@
         <v>46259</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -74804,7 +74804,7 @@
         <v>45439</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -74877,7 +74877,7 @@
         <v>46153</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -74950,7 +74950,7 @@
         <v>46185</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -75023,7 +75023,7 @@
         <v>46294</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -75096,7 +75096,7 @@
         <v>46196</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -75169,7 +75169,7 @@
         <v>44592</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -75242,7 +75242,7 @@
         <v>46303</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -75315,7 +75315,7 @@
         <v>45884</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -75388,7 +75388,7 @@
         <v>46303</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -75461,7 +75461,7 @@
         <v>45786</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -75534,7 +75534,7 @@
         <v>46178</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -75607,7 +75607,7 @@
         <v>45601</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -75680,7 +75680,7 @@
         <v>45456</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -75753,7 +75753,7 @@
         <v>45716</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -75826,7 +75826,7 @@
         <v>46302</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -75899,7 +75899,7 @@
         <v>46302</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -75972,7 +75972,7 @@
         <v>46003</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -76045,7 +76045,7 @@
         <v>46259</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -76118,7 +76118,7 @@
         <v>46303</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -76191,7 +76191,7 @@
         <v>46294</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -76264,7 +76264,7 @@
         <v>45792</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -76337,7 +76337,7 @@
         <v>46302</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -76410,7 +76410,7 @@
         <v>46306</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -76483,7 +76483,7 @@
         <v>45741</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -76561,7 +76561,7 @@
         <v>45741</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -76639,7 +76639,7 @@
         <v>45728</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -76712,7 +76712,7 @@
         <v>45259</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -76785,7 +76785,7 @@
         <v>45610</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -76858,7 +76858,7 @@
         <v>45743</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -76931,7 +76931,7 @@
         <v>45737</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -77004,7 +77004,7 @@
         <v>45737</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -77077,7 +77077,7 @@
         <v>46304</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -77150,7 +77150,7 @@
         <v>45742</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -77223,7 +77223,7 @@
         <v>45733</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -77296,7 +77296,7 @@
         <v>45733</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -77369,7 +77369,7 @@
         <v>45803</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -77442,7 +77442,7 @@
         <v>45743</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -77515,7 +77515,7 @@
         <v>45442</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -77588,7 +77588,7 @@
         <v>45708</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -77661,7 +77661,7 @@
         <v>46308</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -77734,7 +77734,7 @@
         <v>45616</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -77807,7 +77807,7 @@
         <v>46265</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -77880,7 +77880,7 @@
         <v>45359</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -77953,7 +77953,7 @@
         <v>45805</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -78026,7 +78026,7 @@
         <v>45434</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -78099,7 +78099,7 @@
         <v>45811</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -78172,7 +78172,7 @@
         <v>46308</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -78245,7 +78245,7 @@
         <v>45615</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -78318,7 +78318,7 @@
         <v>45505</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -78391,7 +78391,7 @@
         <v>46268</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -78464,7 +78464,7 @@
         <v>45812</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -78537,7 +78537,7 @@
         <v>45816</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -78610,7 +78610,7 @@
         <v>46269</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -78683,7 +78683,7 @@
         <v>45819</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -78756,7 +78756,7 @@
         <v>45819</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -78829,7 +78829,7 @@
         <v>45819</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -78902,7 +78902,7 @@
         <v>45819</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -78975,7 +78975,7 @@
         <v>45737</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -79048,7 +79048,7 @@
         <v>45838</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -79121,7 +79121,7 @@
         <v>45839</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -79194,7 +79194,7 @@
         <v>45840</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -79267,7 +79267,7 @@
         <v>45840</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -79340,7 +79340,7 @@
         <v>45845</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -79413,7 +79413,7 @@
         <v>45729</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -79486,7 +79486,7 @@
         <v>45748</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -79559,7 +79559,7 @@
         <v>45747</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -79632,7 +79632,7 @@
         <v>45625</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -79705,7 +79705,7 @@
         <v>45715</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -79778,7 +79778,7 @@
         <v>45715</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -79851,7 +79851,7 @@
         <v>44834</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -79924,7 +79924,7 @@
         <v>45847</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -79997,7 +79997,7 @@
         <v>45763</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -80070,7 +80070,7 @@
         <v>45852</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -80143,7 +80143,7 @@
         <v>45672</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -80216,7 +80216,7 @@
         <v>45163</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -80289,7 +80289,7 @@
         <v>44549</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -80362,7 +80362,7 @@
         <v>45322</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -80435,7 +80435,7 @@
         <v>45005</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
@@ -80508,7 +80508,7 @@
         <v>44564</v>
       </c>
       <c r="E1032" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
@@ -80581,7 +80581,7 @@
         <v>45866</v>
       </c>
       <c r="E1033" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
@@ -80654,7 +80654,7 @@
         <v>45288</v>
       </c>
       <c r="E1034" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
@@ -80727,7 +80727,7 @@
         <v>45733</v>
       </c>
       <c r="E1035" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
@@ -80800,7 +80800,7 @@
         <v>45113</v>
       </c>
       <c r="E1036" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
@@ -80873,7 +80873,7 @@
         <v>45875</v>
       </c>
       <c r="E1037" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
@@ -80946,7 +80946,7 @@
         <v>45875</v>
       </c>
       <c r="E1038" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1038" t="inlineStr">
         <is>
@@ -81019,7 +81019,7 @@
         <v>45875</v>
       </c>
       <c r="E1039" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1039" t="inlineStr">
         <is>
@@ -81092,7 +81092,7 @@
         <v>45636</v>
       </c>
       <c r="E1040" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1040" t="inlineStr">
         <is>
@@ -81165,7 +81165,7 @@
         <v>45580</v>
       </c>
       <c r="E1041" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1041" t="inlineStr">
         <is>
@@ -81238,7 +81238,7 @@
         <v>45447</v>
       </c>
       <c r="E1042" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1042" t="inlineStr">
         <is>
@@ -81311,7 +81311,7 @@
         <v>45170</v>
       </c>
       <c r="E1043" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1043" t="inlineStr">
         <is>
@@ -81384,7 +81384,7 @@
         <v>45106</v>
       </c>
       <c r="E1044" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1044" t="inlineStr">
         <is>
@@ -81457,7 +81457,7 @@
         <v>45467</v>
       </c>
       <c r="E1045" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1045" t="inlineStr">
         <is>
@@ -81530,7 +81530,7 @@
         <v>44509</v>
       </c>
       <c r="E1046" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1046" t="inlineStr">
         <is>
@@ -81608,7 +81608,7 @@
         <v>45664</v>
       </c>
       <c r="E1047" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1047" t="inlineStr">
         <is>
@@ -81681,7 +81681,7 @@
         <v>45208</v>
       </c>
       <c r="E1048" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1048" t="inlineStr">
         <is>
@@ -81754,7 +81754,7 @@
         <v>45406</v>
       </c>
       <c r="E1049" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1049" t="inlineStr">
         <is>
@@ -81827,7 +81827,7 @@
         <v>45497</v>
       </c>
       <c r="E1050" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1050" t="inlineStr">
         <is>
@@ -81900,7 +81900,7 @@
         <v>45497</v>
       </c>
       <c r="E1051" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1051" t="inlineStr">
         <is>
@@ -81973,7 +81973,7 @@
         <v>45106</v>
       </c>
       <c r="E1052" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1052" t="inlineStr">
         <is>
@@ -82046,7 +82046,7 @@
         <v>45646</v>
       </c>
       <c r="E1053" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1053" t="inlineStr">
         <is>
@@ -82119,7 +82119,7 @@
         <v>45646</v>
       </c>
       <c r="E1054" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1054" t="inlineStr">
         <is>
@@ -82192,7 +82192,7 @@
         <v>45580</v>
       </c>
       <c r="E1055" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1055" t="inlineStr">
         <is>
@@ -82265,7 +82265,7 @@
         <v>45646</v>
       </c>
       <c r="E1056" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1056" t="inlineStr">
         <is>
@@ -82338,7 +82338,7 @@
         <v>45646</v>
       </c>
       <c r="E1057" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1057" t="inlineStr">
         <is>
@@ -82411,7 +82411,7 @@
         <v>45408</v>
       </c>
       <c r="E1058" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1058" t="inlineStr">
         <is>
@@ -82484,7 +82484,7 @@
         <v>45414</v>
       </c>
       <c r="E1059" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1059" t="inlineStr">
         <is>
@@ -82557,7 +82557,7 @@
         <v>45173</v>
       </c>
       <c r="E1060" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1060" t="inlineStr">
         <is>
@@ -82630,7 +82630,7 @@
         <v>45646</v>
       </c>
       <c r="E1061" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1061" t="inlineStr">
         <is>
@@ -82703,7 +82703,7 @@
         <v>45715</v>
       </c>
       <c r="E1062" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1062" t="inlineStr">
         <is>
@@ -82776,7 +82776,7 @@
         <v>45720</v>
       </c>
       <c r="E1063" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1063" t="inlineStr">
         <is>
@@ -82849,7 +82849,7 @@
         <v>45800</v>
       </c>
       <c r="E1064" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1064" t="inlineStr">
         <is>
@@ -82927,7 +82927,7 @@
         <v>45831</v>
       </c>
       <c r="E1065" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1065" t="inlineStr">
         <is>
@@ -83000,7 +83000,7 @@
         <v>45785</v>
       </c>
       <c r="E1066" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1066" t="inlineStr">
         <is>
@@ -83073,7 +83073,7 @@
         <v>46073</v>
       </c>
       <c r="E1067" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1067" t="inlineStr">
         <is>
@@ -83146,7 +83146,7 @@
         <v>46163</v>
       </c>
       <c r="E1068" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1068" t="inlineStr">
         <is>
@@ -83219,7 +83219,7 @@
         <v>46274</v>
       </c>
       <c r="E1069" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1069" t="inlineStr">
         <is>
@@ -83292,7 +83292,7 @@
         <v>46296</v>
       </c>
       <c r="E1070" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1070" t="inlineStr">
         <is>

--- a/Översikt VETLANDA.xlsx
+++ b/Översikt VETLANDA.xlsx
@@ -601,7 +601,7 @@
         <v>45097</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>46178</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         <v>45371</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>44890</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>44817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>45183</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>45558</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>45168</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>46107</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>45520</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>45930</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>45957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>45170</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>44612</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>44840</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>45203</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>46002</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>46100</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>44908</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>45819</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>46163</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>46188</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>44545</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>44564</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>45583</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>45814</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>45763</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>46045</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>45599</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>45477</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4005,7 +4005,7 @@
         <v>46255</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>45048</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         <v>44819</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>45646</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>45131</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>44515</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>44752</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4767,7 +4767,7 @@
         <v>44643</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>46166</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>45211</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5094,7 +5094,7 @@
         <v>45673</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         <v>45400</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5315,7 +5315,7 @@
         <v>45965</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         <v>45616</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5531,7 +5531,7 @@
         <v>45310</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
         <v>46279</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
         <v>46293</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>45792</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>45835</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>45840</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6172,7 +6172,7 @@
         <v>45713</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         <v>45860</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6388,7 +6388,7 @@
         <v>45035</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6494,7 +6494,7 @@
         <v>46306</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>45357</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         <v>45891</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>46317</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         <v>44572</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
         <v>45589</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         <v>45148</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7241,7 +7241,7 @@
         <v>45303</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7347,7 +7347,7 @@
         <v>45713</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7453,7 +7453,7 @@
         <v>45106</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>45509</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>45497</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         <v>45201</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         <v>45539</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7983,7 +7983,7 @@
         <v>46051</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         <v>44834</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8198,7 +8198,7 @@
         <v>44721</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
         <v>44747</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8408,7 +8408,7 @@
         <v>44592</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
         <v>44740</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         <v>45835</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         <v>45672</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>44824</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8942,7 +8942,7 @@
         <v>45378</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9047,7 +9047,7 @@
         <v>45342</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9152,7 +9152,7 @@
         <v>45645</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9257,7 +9257,7 @@
         <v>45239</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>45119</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9472,7 +9472,7 @@
         <v>44833</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9577,7 +9577,7 @@
         <v>45104</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9686,7 +9686,7 @@
         <v>46188</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>44728</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9900,7 +9900,7 @@
         <v>44819</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
         <v>45337</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10110,7 +10110,7 @@
         <v>45532</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10215,7 +10215,7 @@
         <v>44998</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>45930</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10434,7 +10434,7 @@
         <v>45643</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10539,7 +10539,7 @@
         <v>45352</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10644,7 +10644,7 @@
         <v>45791</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
         <v>45736</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>46248</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10963,7 +10963,7 @@
         <v>46071</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11068,7 +11068,7 @@
         <v>45820</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11178,7 +11178,7 @@
         <v>45839</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
         <v>46297</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11388,7 +11388,7 @@
         <v>46069</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11493,7 +11493,7 @@
         <v>45904</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11598,7 +11598,7 @@
         <v>45880</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11703,7 +11703,7 @@
         <v>45021</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11808,7 +11808,7 @@
         <v>45775</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
         <v>46316</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12018,7 +12018,7 @@
         <v>45586</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12123,7 +12123,7 @@
         <v>46317</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12233,7 +12233,7 @@
         <v>45085</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12338,7 +12338,7 @@
         <v>44781</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
         <v>44816</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12548,7 +12548,7 @@
         <v>45009</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12653,7 +12653,7 @@
         <v>45240</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>45419</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12863,7 +12863,7 @@
         <v>44880</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12968,7 +12968,7 @@
         <v>45565</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13073,7 +13073,7 @@
         <v>45586</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13178,7 +13178,7 @@
         <v>45596</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
         <v>45597</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13388,7 +13388,7 @@
         <v>45555</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13493,7 +13493,7 @@
         <v>45408</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13598,7 +13598,7 @@
         <v>45261</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13703,7 +13703,7 @@
         <v>44748</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13808,7 +13808,7 @@
         <v>44830</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13913,7 +13913,7 @@
         <v>44916</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14018,7 +14018,7 @@
         <v>45604</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14123,7 +14123,7 @@
         <v>45497</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14228,7 +14228,7 @@
         <v>45614</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14333,7 +14333,7 @@
         <v>45742</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14442,7 +14442,7 @@
         <v>44858</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>44781</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14588,7 +14588,7 @@
         <v>44838</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14661,7 +14661,7 @@
         <v>44732</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14734,7 +14734,7 @@
         <v>44781</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14807,7 +14807,7 @@
         <v>44515</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14880,7 +14880,7 @@
         <v>44508</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14953,7 +14953,7 @@
         <v>44504</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>44496</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15099,7 +15099,7 @@
         <v>44889</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15172,7 +15172,7 @@
         <v>44579</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15245,7 +15245,7 @@
         <v>44601</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15318,7 +15318,7 @@
         <v>44544</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15391,7 +15391,7 @@
         <v>44510</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15464,7 +15464,7 @@
         <v>44517</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15537,7 +15537,7 @@
         <v>44764</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15610,7 +15610,7 @@
         <v>44503</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15683,7 +15683,7 @@
         <v>44510</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15756,7 +15756,7 @@
         <v>44819</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15829,7 +15829,7 @@
         <v>44592</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15902,7 +15902,7 @@
         <v>44750</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15975,7 +15975,7 @@
         <v>44825</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16048,7 +16048,7 @@
         <v>44638</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16121,7 +16121,7 @@
         <v>44602</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16194,7 +16194,7 @@
         <v>44721</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16267,7 +16267,7 @@
         <v>44510</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16340,7 +16340,7 @@
         <v>44785</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16413,7 +16413,7 @@
         <v>44592</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16486,7 +16486,7 @@
         <v>44587</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16559,7 +16559,7 @@
         <v>44782</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16632,7 +16632,7 @@
         <v>44815</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16705,7 +16705,7 @@
         <v>44504</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16778,7 +16778,7 @@
         <v>44580</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16851,7 +16851,7 @@
         <v>44691</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         <v>44880</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16997,7 +16997,7 @@
         <v>44545</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17070,7 +17070,7 @@
         <v>44750</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17143,7 +17143,7 @@
         <v>44624</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17216,7 +17216,7 @@
         <v>44595</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
         <v>44608</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         <v>44820</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17435,7 +17435,7 @@
         <v>44816</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17508,7 +17508,7 @@
         <v>44645</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17581,7 +17581,7 @@
         <v>44819</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17654,7 +17654,7 @@
         <v>44656</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17727,7 +17727,7 @@
         <v>44784</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17800,7 +17800,7 @@
         <v>44585</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>44585</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17956,7 +17956,7 @@
         <v>44585</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18034,7 +18034,7 @@
         <v>44834</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18107,7 +18107,7 @@
         <v>44740</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18185,7 +18185,7 @@
         <v>44750</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18258,7 +18258,7 @@
         <v>44587</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18331,7 +18331,7 @@
         <v>44743</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18404,7 +18404,7 @@
         <v>44600</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18477,7 +18477,7 @@
         <v>44859</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>44743</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18623,7 +18623,7 @@
         <v>44593</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18696,7 +18696,7 @@
         <v>44778</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18769,7 +18769,7 @@
         <v>44504</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18842,7 +18842,7 @@
         <v>44834</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18915,7 +18915,7 @@
         <v>44509</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18988,7 +18988,7 @@
         <v>44517</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19061,7 +19061,7 @@
         <v>44592</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19134,7 +19134,7 @@
         <v>44721</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19207,7 +19207,7 @@
         <v>44572</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19280,7 +19280,7 @@
         <v>44841</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19353,7 +19353,7 @@
         <v>44888</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19426,7 +19426,7 @@
         <v>44587</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19499,7 +19499,7 @@
         <v>44655</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19572,7 +19572,7 @@
         <v>44515</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19650,7 +19650,7 @@
         <v>44502</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19723,7 +19723,7 @@
         <v>44592</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19796,7 +19796,7 @@
         <v>44564</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19869,7 +19869,7 @@
         <v>44781</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19942,7 +19942,7 @@
         <v>44531</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20015,7 +20015,7 @@
         <v>44636</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20088,7 +20088,7 @@
         <v>44834</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20161,7 +20161,7 @@
         <v>44733</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20234,7 +20234,7 @@
         <v>44683</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20307,7 +20307,7 @@
         <v>44602</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20380,7 +20380,7 @@
         <v>44998</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20453,7 +20453,7 @@
         <v>44592</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20526,7 +20526,7 @@
         <v>44792</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20599,7 +20599,7 @@
         <v>45826</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20672,7 +20672,7 @@
         <v>45888</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20745,7 +20745,7 @@
         <v>45742</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20818,7 +20818,7 @@
         <v>45888</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20891,7 +20891,7 @@
         <v>45786</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20964,7 +20964,7 @@
         <v>44657</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21037,7 +21037,7 @@
         <v>45742</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>45888</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21183,7 +21183,7 @@
         <v>45839</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21256,7 +21256,7 @@
         <v>45541</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21329,7 +21329,7 @@
         <v>45888</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21402,7 +21402,7 @@
         <v>44827</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21475,7 +21475,7 @@
         <v>45302</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21548,7 +21548,7 @@
         <v>44946</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21621,7 +21621,7 @@
         <v>44683</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>45888</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21767,7 +21767,7 @@
         <v>45888</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21840,7 +21840,7 @@
         <v>45323</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21913,7 +21913,7 @@
         <v>45341</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21986,7 +21986,7 @@
         <v>45335</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22059,7 +22059,7 @@
         <v>45889</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22132,7 +22132,7 @@
         <v>44834</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22205,7 +22205,7 @@
         <v>45677</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>45329</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22351,7 +22351,7 @@
         <v>45440</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22424,7 +22424,7 @@
         <v>45267</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22497,7 +22497,7 @@
         <v>45889</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22570,7 +22570,7 @@
         <v>45889</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22643,7 +22643,7 @@
         <v>45770</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22716,7 +22716,7 @@
         <v>45839</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22789,7 +22789,7 @@
         <v>45329</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22862,7 +22862,7 @@
         <v>45202</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22935,7 +22935,7 @@
         <v>45623</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23008,7 +23008,7 @@
         <v>45201</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23081,7 +23081,7 @@
         <v>45898</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23154,7 +23154,7 @@
         <v>44677</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23227,7 +23227,7 @@
         <v>44825</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23300,7 +23300,7 @@
         <v>45272</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23373,7 +23373,7 @@
         <v>45401</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23446,7 +23446,7 @@
         <v>45674</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23519,7 +23519,7 @@
         <v>45300</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23592,7 +23592,7 @@
         <v>45351</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23665,7 +23665,7 @@
         <v>45363</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23743,7 +23743,7 @@
         <v>45363</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23821,7 +23821,7 @@
         <v>45345</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23894,7 +23894,7 @@
         <v>44917</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23967,7 +23967,7 @@
         <v>45902</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24040,7 +24040,7 @@
         <v>44747</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24113,7 +24113,7 @@
         <v>45884</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24186,7 +24186,7 @@
         <v>45819</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
         <v>45737</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24332,7 +24332,7 @@
         <v>45363</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24410,7 +24410,7 @@
         <v>45363</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24488,7 +24488,7 @@
         <v>45190</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24561,7 +24561,7 @@
         <v>45587</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24634,7 +24634,7 @@
         <v>45441</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24707,7 +24707,7 @@
         <v>44972</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24780,7 +24780,7 @@
         <v>46160</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24853,7 +24853,7 @@
         <v>46161</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24926,7 +24926,7 @@
         <v>44815</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24999,7 +24999,7 @@
         <v>46160</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25072,7 +25072,7 @@
         <v>44952</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25145,7 +25145,7 @@
         <v>44984</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25218,7 +25218,7 @@
         <v>46161</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25291,7 +25291,7 @@
         <v>45911</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25364,7 +25364,7 @@
         <v>45911</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25437,7 +25437,7 @@
         <v>45152</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25510,7 +25510,7 @@
         <v>44655</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25583,7 +25583,7 @@
         <v>45055</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25656,7 +25656,7 @@
         <v>45930</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25734,7 +25734,7 @@
         <v>44495</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25807,7 +25807,7 @@
         <v>46163</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25880,7 +25880,7 @@
         <v>45224</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25958,7 +25958,7 @@
         <v>45097</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26031,7 +26031,7 @@
         <v>45069</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26104,7 +26104,7 @@
         <v>45922</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26177,7 +26177,7 @@
         <v>45364</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26250,7 +26250,7 @@
         <v>45669</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26323,7 +26323,7 @@
         <v>45107</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26396,7 +26396,7 @@
         <v>45925</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26469,7 +26469,7 @@
         <v>45414</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26547,7 +26547,7 @@
         <v>45219</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26620,7 +26620,7 @@
         <v>45211</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26693,7 +26693,7 @@
         <v>45097</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26766,7 +26766,7 @@
         <v>45615</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26839,7 +26839,7 @@
         <v>45183</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26912,7 +26912,7 @@
         <v>45364</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26985,7 +26985,7 @@
         <v>44963</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27058,7 +27058,7 @@
         <v>45135</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27131,7 +27131,7 @@
         <v>45219</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27209,7 +27209,7 @@
         <v>44930</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27282,7 +27282,7 @@
         <v>45282</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27355,7 +27355,7 @@
         <v>46175</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27428,7 +27428,7 @@
         <v>45245</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27501,7 +27501,7 @@
         <v>44847</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27574,7 +27574,7 @@
         <v>45310</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27647,7 +27647,7 @@
         <v>45763</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27720,7 +27720,7 @@
         <v>45574</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27798,7 +27798,7 @@
         <v>45936</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27871,7 +27871,7 @@
         <v>45575</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27944,7 +27944,7 @@
         <v>45362</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28017,7 +28017,7 @@
         <v>45251</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28090,7 +28090,7 @@
         <v>45057</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28163,7 +28163,7 @@
         <v>44998</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28236,7 +28236,7 @@
         <v>44970</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28309,7 +28309,7 @@
         <v>45164</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28382,7 +28382,7 @@
         <v>44747</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28455,7 +28455,7 @@
         <v>45384</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28528,7 +28528,7 @@
         <v>45944</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28601,7 +28601,7 @@
         <v>45091</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28674,7 +28674,7 @@
         <v>45329</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28752,7 +28752,7 @@
         <v>45406</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28825,7 +28825,7 @@
         <v>45134</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28898,7 +28898,7 @@
         <v>44929</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28971,7 +28971,7 @@
         <v>45107</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29044,7 +29044,7 @@
         <v>45296</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29117,7 +29117,7 @@
         <v>45240</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29190,7 +29190,7 @@
         <v>45365</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29263,7 +29263,7 @@
         <v>44902</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29336,7 +29336,7 @@
         <v>45099</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29409,7 +29409,7 @@
         <v>44530</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29482,7 +29482,7 @@
         <v>45946</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29555,7 +29555,7 @@
         <v>45462</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29628,7 +29628,7 @@
         <v>44965</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29701,7 +29701,7 @@
         <v>45370</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29774,7 +29774,7 @@
         <v>44813</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29847,7 +29847,7 @@
         <v>45394</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29920,7 +29920,7 @@
         <v>45119</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29993,7 +29993,7 @@
         <v>44837</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30066,7 +30066,7 @@
         <v>45532</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30139,7 +30139,7 @@
         <v>46178</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30212,7 +30212,7 @@
         <v>45484</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30285,7 +30285,7 @@
         <v>45950</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30358,7 +30358,7 @@
         <v>45526</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30431,7 +30431,7 @@
         <v>45303</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30504,7 +30504,7 @@
         <v>46178</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30577,7 +30577,7 @@
         <v>46182</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30650,7 +30650,7 @@
         <v>45461</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30723,7 +30723,7 @@
         <v>45440</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30796,7 +30796,7 @@
         <v>45226</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30869,7 +30869,7 @@
         <v>45042</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30942,7 +30942,7 @@
         <v>45114</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31015,7 +31015,7 @@
         <v>46182</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31088,7 +31088,7 @@
         <v>45439</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31161,7 +31161,7 @@
         <v>46184</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31234,7 +31234,7 @@
         <v>45327</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31307,7 +31307,7 @@
         <v>45953</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31380,7 +31380,7 @@
         <v>46182</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31453,7 +31453,7 @@
         <v>45035</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31526,7 +31526,7 @@
         <v>46184</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31599,7 +31599,7 @@
         <v>46184</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31672,7 +31672,7 @@
         <v>45298</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31745,7 +31745,7 @@
         <v>45684</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31823,7 +31823,7 @@
         <v>44880</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31896,7 +31896,7 @@
         <v>44880</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31969,7 +31969,7 @@
         <v>46185</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32042,7 +32042,7 @@
         <v>45660</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32115,7 +32115,7 @@
         <v>45182</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32193,7 +32193,7 @@
         <v>45182</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32271,7 +32271,7 @@
         <v>45182</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32344,7 +32344,7 @@
         <v>45188</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32417,7 +32417,7 @@
         <v>45089</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32490,7 +32490,7 @@
         <v>45222</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>46188</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32636,7 +32636,7 @@
         <v>45602</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32709,7 +32709,7 @@
         <v>45925</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32782,7 +32782,7 @@
         <v>46190</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32855,7 +32855,7 @@
         <v>45335</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32928,7 +32928,7 @@
         <v>45309</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33001,7 +33001,7 @@
         <v>46195</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33074,7 +33074,7 @@
         <v>46197</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33147,7 +33147,7 @@
         <v>45645</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33220,7 +33220,7 @@
         <v>45974</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>45580</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33366,7 +33366,7 @@
         <v>46196</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33439,7 +33439,7 @@
         <v>44710</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33512,7 +33512,7 @@
         <v>45321</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33585,7 +33585,7 @@
         <v>45183</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33658,7 +33658,7 @@
         <v>44743</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33731,7 +33731,7 @@
         <v>45132</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33804,7 +33804,7 @@
         <v>45975</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33877,7 +33877,7 @@
         <v>45363</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33955,7 +33955,7 @@
         <v>45649</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34033,7 +34033,7 @@
         <v>45526</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34106,7 +34106,7 @@
         <v>45673</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34179,7 +34179,7 @@
         <v>45701</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34257,7 +34257,7 @@
         <v>44970</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34330,7 +34330,7 @@
         <v>45981</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34403,7 +34403,7 @@
         <v>45981</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34481,7 +34481,7 @@
         <v>45981</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34554,7 +34554,7 @@
         <v>45981</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34627,7 +34627,7 @@
         <v>45359</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34700,7 +34700,7 @@
         <v>45982</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34773,7 +34773,7 @@
         <v>46204</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34846,7 +34846,7 @@
         <v>45625</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34919,7 +34919,7 @@
         <v>45544</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34992,7 +34992,7 @@
         <v>44970</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35065,7 +35065,7 @@
         <v>45674</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35138,7 +35138,7 @@
         <v>45385</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35211,7 +35211,7 @@
         <v>45188</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35284,7 +35284,7 @@
         <v>45314</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35357,7 +35357,7 @@
         <v>45645</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35435,7 +35435,7 @@
         <v>45228</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35508,7 +35508,7 @@
         <v>45992</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35581,7 +35581,7 @@
         <v>45329</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35654,7 +35654,7 @@
         <v>45737</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35727,7 +35727,7 @@
         <v>45737</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35800,7 +35800,7 @@
         <v>46069</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35873,7 +35873,7 @@
         <v>45763</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35946,7 +35946,7 @@
         <v>45763</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36019,7 +36019,7 @@
         <v>45763</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36092,7 +36092,7 @@
         <v>45376</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36165,7 +36165,7 @@
         <v>46213</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36238,7 +36238,7 @@
         <v>46168</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36311,7 +36311,7 @@
         <v>45702</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36389,7 +36389,7 @@
         <v>45315</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36462,7 +36462,7 @@
         <v>46177</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36535,7 +36535,7 @@
         <v>44949</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36608,7 +36608,7 @@
         <v>45230</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36686,7 +36686,7 @@
         <v>45999</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36759,7 +36759,7 @@
         <v>45999</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36832,7 +36832,7 @@
         <v>45595</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36905,7 +36905,7 @@
         <v>45274</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36978,7 +36978,7 @@
         <v>44781</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37051,7 +37051,7 @@
         <v>45439</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37124,7 +37124,7 @@
         <v>46001</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37197,7 +37197,7 @@
         <v>45443</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37270,7 +37270,7 @@
         <v>45435</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37343,7 +37343,7 @@
         <v>45348</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37416,7 +37416,7 @@
         <v>46003</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37489,7 +37489,7 @@
         <v>46007</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37562,7 +37562,7 @@
         <v>46007</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37635,7 +37635,7 @@
         <v>45783</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37708,7 +37708,7 @@
         <v>45783</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37781,7 +37781,7 @@
         <v>45999</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37854,7 +37854,7 @@
         <v>46233</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37927,7 +37927,7 @@
         <v>45716</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38000,7 +38000,7 @@
         <v>44837</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38073,7 +38073,7 @@
         <v>46010</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38146,7 +38146,7 @@
         <v>45456</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38219,7 +38219,7 @@
         <v>46010</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38292,7 +38292,7 @@
         <v>46279</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38365,7 +38365,7 @@
         <v>46009</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38438,7 +38438,7 @@
         <v>46009</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38511,7 +38511,7 @@
         <v>46234</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38584,7 +38584,7 @@
         <v>44592</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38657,7 +38657,7 @@
         <v>45439</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38730,7 +38730,7 @@
         <v>46237</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38803,7 +38803,7 @@
         <v>45786</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38876,7 +38876,7 @@
         <v>46234</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38949,7 +38949,7 @@
         <v>45601</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39022,7 +39022,7 @@
         <v>46234</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39095,7 +39095,7 @@
         <v>45827</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39168,7 +39168,7 @@
         <v>46030</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39241,7 +39241,7 @@
         <v>46030</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39314,7 +39314,7 @@
         <v>45792</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39387,7 +39387,7 @@
         <v>46283</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39460,7 +39460,7 @@
         <v>46029</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39533,7 +39533,7 @@
         <v>45449</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39606,7 +39606,7 @@
         <v>46031</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39679,7 +39679,7 @@
         <v>45953</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39752,7 +39752,7 @@
         <v>46240</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39825,7 +39825,7 @@
         <v>45743</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39898,7 +39898,7 @@
         <v>45733</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39971,7 +39971,7 @@
         <v>45733</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40044,7 +40044,7 @@
         <v>45737</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40117,7 +40117,7 @@
         <v>45737</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40190,7 +40190,7 @@
         <v>45742</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40263,7 +40263,7 @@
         <v>45728</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40336,7 +40336,7 @@
         <v>45741</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40414,7 +40414,7 @@
         <v>46044</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40487,7 +40487,7 @@
         <v>45741</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40565,7 +40565,7 @@
         <v>46245</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40638,7 +40638,7 @@
         <v>46244</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40711,7 +40711,7 @@
         <v>46280</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40784,7 +40784,7 @@
         <v>46048</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40857,7 +40857,7 @@
         <v>46048</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40930,7 +40930,7 @@
         <v>46244</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41003,7 +41003,7 @@
         <v>45259</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41076,7 +41076,7 @@
         <v>46045</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41149,7 +41149,7 @@
         <v>45610</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41222,7 +41222,7 @@
         <v>46048</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41295,7 +41295,7 @@
         <v>45708</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41368,7 +41368,7 @@
         <v>46009</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41441,7 +41441,7 @@
         <v>46049</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41514,7 +41514,7 @@
         <v>45442</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41587,7 +41587,7 @@
         <v>45743</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41660,7 +41660,7 @@
         <v>45803</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41733,7 +41733,7 @@
         <v>46289</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41806,7 +41806,7 @@
         <v>46290</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41879,7 +41879,7 @@
         <v>45446</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41952,7 +41952,7 @@
         <v>45616</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42025,7 +42025,7 @@
         <v>45359</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42098,7 +42098,7 @@
         <v>45330</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42171,7 +42171,7 @@
         <v>46178</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42244,7 +42244,7 @@
         <v>46289</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42317,7 +42317,7 @@
         <v>45805</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42390,7 +42390,7 @@
         <v>46055</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42463,7 +42463,7 @@
         <v>45505</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42536,7 +42536,7 @@
         <v>45434</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42609,7 +42609,7 @@
         <v>46246</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42682,7 +42682,7 @@
         <v>45133</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42755,7 +42755,7 @@
         <v>45615</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42828,7 +42828,7 @@
         <v>46178</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42901,7 +42901,7 @@
         <v>45812</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42974,7 +42974,7 @@
         <v>46062</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43047,7 +43047,7 @@
         <v>45811</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43120,7 +43120,7 @@
         <v>46063</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43193,7 +43193,7 @@
         <v>46063</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43266,7 +43266,7 @@
         <v>46063</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43339,7 +43339,7 @@
         <v>46063</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43412,7 +43412,7 @@
         <v>46293</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43485,7 +43485,7 @@
         <v>45816</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43558,7 +43558,7 @@
         <v>46293</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43631,7 +43631,7 @@
         <v>45819</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43704,7 +43704,7 @@
         <v>45819</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43777,7 +43777,7 @@
         <v>45925</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43850,7 +43850,7 @@
         <v>45819</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43923,7 +43923,7 @@
         <v>45819</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43996,7 +43996,7 @@
         <v>46077</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44069,7 +44069,7 @@
         <v>46077</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44142,7 +44142,7 @@
         <v>46295</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44215,7 +44215,7 @@
         <v>46296</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44288,7 +44288,7 @@
         <v>46084</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44361,7 +44361,7 @@
         <v>46296</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44434,7 +44434,7 @@
         <v>46252</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44507,7 +44507,7 @@
         <v>46084</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44580,7 +44580,7 @@
         <v>46084</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44653,7 +44653,7 @@
         <v>46062</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44726,7 +44726,7 @@
         <v>46087</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44799,7 +44799,7 @@
         <v>46297</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44872,7 +44872,7 @@
         <v>45497</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44945,7 +44945,7 @@
         <v>45497</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45018,7 +45018,7 @@
         <v>45737</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45091,7 +45091,7 @@
         <v>46091</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45164,7 +45164,7 @@
         <v>45838</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45237,7 +45237,7 @@
         <v>46002</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45310,7 +45310,7 @@
         <v>46092</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45383,7 +45383,7 @@
         <v>45544</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45456,7 +45456,7 @@
         <v>45840</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45529,7 +45529,7 @@
         <v>45840</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45602,7 +45602,7 @@
         <v>45839</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45675,7 +45675,7 @@
         <v>45546</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45748,7 +45748,7 @@
         <v>45936</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45821,7 +45821,7 @@
         <v>46097</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45894,7 +45894,7 @@
         <v>46247</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45972,7 +45972,7 @@
         <v>46247</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46050,7 +46050,7 @@
         <v>46098</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46123,7 +46123,7 @@
         <v>46099</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46196,7 +46196,7 @@
         <v>45625</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46269,7 +46269,7 @@
         <v>46248</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46347,7 +46347,7 @@
         <v>46100</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46420,7 +46420,7 @@
         <v>45715</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46493,7 +46493,7 @@
         <v>45747</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46566,7 +46566,7 @@
         <v>45729</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46639,7 +46639,7 @@
         <v>45845</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46712,7 +46712,7 @@
         <v>46258</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46785,7 +46785,7 @@
         <v>45715</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46858,7 +46858,7 @@
         <v>45748</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46931,7 +46931,7 @@
         <v>46259</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47004,7 +47004,7 @@
         <v>46104</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47077,7 +47077,7 @@
         <v>46259</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47150,7 +47150,7 @@
         <v>44858</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47223,7 +47223,7 @@
         <v>45847</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47296,7 +47296,7 @@
         <v>44834</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47369,7 +47369,7 @@
         <v>46301</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47442,7 +47442,7 @@
         <v>46104</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47515,7 +47515,7 @@
         <v>44515</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47593,7 +47593,7 @@
         <v>46107</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47666,7 +47666,7 @@
         <v>46294</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47739,7 +47739,7 @@
         <v>46258</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47812,7 +47812,7 @@
         <v>46107</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47885,7 +47885,7 @@
         <v>45852</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47958,7 +47958,7 @@
         <v>45763</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48031,7 +48031,7 @@
         <v>46294</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48104,7 +48104,7 @@
         <v>46107</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48177,7 +48177,7 @@
         <v>46301</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48250,7 +48250,7 @@
         <v>44564</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48328,7 +48328,7 @@
         <v>46302</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48401,7 +48401,7 @@
         <v>46111</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48474,7 +48474,7 @@
         <v>46111</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48547,7 +48547,7 @@
         <v>45322</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48620,7 +48620,7 @@
         <v>45005</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48693,7 +48693,7 @@
         <v>45163</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48766,7 +48766,7 @@
         <v>44549</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48839,7 +48839,7 @@
         <v>45672</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineS